--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="308">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -454,6 +454,12 @@
   </si>
   <si>
     <t>EMI FROM JULY 1740</t>
+  </si>
+  <si>
+    <t>Thandal</t>
+  </si>
+  <si>
+    <t>From Raghuls 6250                           2 June</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -946,17 +952,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0;\(&quot;₹&quot;#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="₹#,##0"/>
     <numFmt numFmtId="167" formatCode="mmm yyyy"/>
     <numFmt numFmtId="168" formatCode="₹#,##0.00"/>
     <numFmt numFmtId="169" formatCode="d mmmm"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="172" formatCode="d mmm yyyy"/>
-    <numFmt numFmtId="173" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="170" formatCode="mmmm yyyy"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="173" formatCode="d mmm yyyy"/>
+    <numFmt numFmtId="174" formatCode="d mmmm yyyy"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1331,7 +1338,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1639,6 +1646,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="168" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1656,13 +1666,13 @@
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1750,7 +1760,7 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1759,10 +1769,10 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="174" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -3991,11 +4001,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>47293</v>
+        <v>49293</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-30629</v>
+        <v>-32629</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -7984,537 +7994,545 @@
       <c r="D11" s="108"/>
     </row>
     <row r="12">
-      <c r="A12" s="108"/>
-      <c r="B12" s="108"/>
-      <c r="C12" s="109"/>
-      <c r="D12" s="108"/>
+      <c r="A12" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B12" s="101" t="s">
+        <v>144</v>
+      </c>
+      <c r="C12" s="102">
+        <v>2000.0</v>
+      </c>
+      <c r="D12" s="101" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="108"/>
       <c r="B13" s="108"/>
-      <c r="C13" s="109"/>
+      <c r="C13" s="110"/>
       <c r="D13" s="108"/>
     </row>
     <row r="14">
       <c r="A14" s="108"/>
       <c r="B14" s="108"/>
-      <c r="C14" s="109"/>
+      <c r="C14" s="110"/>
       <c r="D14" s="108"/>
     </row>
     <row r="15">
       <c r="A15" s="108"/>
       <c r="B15" s="108"/>
-      <c r="C15" s="109"/>
+      <c r="C15" s="110"/>
       <c r="D15" s="108"/>
     </row>
     <row r="16">
       <c r="A16" s="108"/>
       <c r="B16" s="108"/>
-      <c r="C16" s="109"/>
+      <c r="C16" s="110"/>
       <c r="D16" s="108"/>
     </row>
     <row r="17">
       <c r="A17" s="108"/>
       <c r="B17" s="108"/>
-      <c r="C17" s="109"/>
+      <c r="C17" s="110"/>
       <c r="D17" s="108"/>
     </row>
     <row r="18">
       <c r="A18" s="108"/>
       <c r="B18" s="108"/>
-      <c r="C18" s="109"/>
+      <c r="C18" s="110"/>
       <c r="D18" s="108"/>
     </row>
     <row r="19">
       <c r="A19" s="108"/>
       <c r="B19" s="108"/>
-      <c r="C19" s="109"/>
+      <c r="C19" s="110"/>
       <c r="D19" s="108"/>
     </row>
     <row r="20">
       <c r="A20" s="108"/>
       <c r="B20" s="108"/>
-      <c r="C20" s="109"/>
+      <c r="C20" s="110"/>
       <c r="D20" s="108"/>
     </row>
     <row r="21">
       <c r="A21" s="108"/>
       <c r="B21" s="108"/>
-      <c r="C21" s="109"/>
+      <c r="C21" s="110"/>
       <c r="D21" s="108"/>
     </row>
     <row r="22">
       <c r="A22" s="108"/>
       <c r="B22" s="108"/>
-      <c r="C22" s="109"/>
+      <c r="C22" s="110"/>
       <c r="D22" s="108"/>
     </row>
     <row r="23">
       <c r="A23" s="108"/>
       <c r="B23" s="108"/>
-      <c r="C23" s="109"/>
+      <c r="C23" s="110"/>
       <c r="D23" s="108"/>
     </row>
     <row r="24">
       <c r="A24" s="108"/>
       <c r="B24" s="108"/>
-      <c r="C24" s="109"/>
+      <c r="C24" s="110"/>
       <c r="D24" s="108"/>
     </row>
     <row r="25">
       <c r="A25" s="108"/>
       <c r="B25" s="108"/>
-      <c r="C25" s="109"/>
+      <c r="C25" s="110"/>
       <c r="D25" s="108"/>
     </row>
     <row r="26">
       <c r="A26" s="108"/>
       <c r="B26" s="108"/>
-      <c r="C26" s="109"/>
+      <c r="C26" s="110"/>
       <c r="D26" s="108"/>
     </row>
     <row r="27">
       <c r="A27" s="108"/>
       <c r="B27" s="108"/>
-      <c r="C27" s="109"/>
+      <c r="C27" s="110"/>
       <c r="D27" s="108"/>
     </row>
     <row r="28">
       <c r="A28" s="108"/>
       <c r="B28" s="108"/>
-      <c r="C28" s="109"/>
+      <c r="C28" s="110"/>
       <c r="D28" s="108"/>
     </row>
     <row r="29">
       <c r="A29" s="108"/>
       <c r="B29" s="108"/>
-      <c r="C29" s="109"/>
+      <c r="C29" s="110"/>
       <c r="D29" s="108"/>
     </row>
     <row r="30">
       <c r="A30" s="108"/>
       <c r="B30" s="108"/>
-      <c r="C30" s="109"/>
+      <c r="C30" s="110"/>
       <c r="D30" s="108"/>
     </row>
     <row r="31">
       <c r="A31" s="108"/>
       <c r="B31" s="108"/>
-      <c r="C31" s="109"/>
+      <c r="C31" s="110"/>
       <c r="D31" s="108"/>
     </row>
     <row r="32">
       <c r="A32" s="108"/>
       <c r="B32" s="108"/>
-      <c r="C32" s="109"/>
+      <c r="C32" s="110"/>
       <c r="D32" s="108"/>
     </row>
     <row r="33">
       <c r="A33" s="108"/>
       <c r="B33" s="108"/>
-      <c r="C33" s="109"/>
+      <c r="C33" s="110"/>
       <c r="D33" s="108"/>
     </row>
     <row r="34">
       <c r="A34" s="108"/>
       <c r="B34" s="108"/>
-      <c r="C34" s="109"/>
+      <c r="C34" s="110"/>
       <c r="D34" s="108"/>
     </row>
     <row r="35">
       <c r="A35" s="108"/>
       <c r="B35" s="108"/>
-      <c r="C35" s="109"/>
+      <c r="C35" s="110"/>
       <c r="D35" s="108"/>
     </row>
     <row r="36">
       <c r="A36" s="108"/>
       <c r="B36" s="108"/>
-      <c r="C36" s="109"/>
+      <c r="C36" s="110"/>
       <c r="D36" s="108"/>
     </row>
     <row r="37">
       <c r="A37" s="108"/>
       <c r="B37" s="108"/>
-      <c r="C37" s="109"/>
+      <c r="C37" s="110"/>
       <c r="D37" s="108"/>
     </row>
     <row r="38">
       <c r="A38" s="108"/>
       <c r="B38" s="108"/>
-      <c r="C38" s="109"/>
+      <c r="C38" s="110"/>
       <c r="D38" s="108"/>
     </row>
     <row r="39">
       <c r="A39" s="108"/>
       <c r="B39" s="108"/>
-      <c r="C39" s="109"/>
+      <c r="C39" s="110"/>
       <c r="D39" s="108"/>
     </row>
     <row r="40">
       <c r="A40" s="108"/>
       <c r="B40" s="108"/>
-      <c r="C40" s="109"/>
+      <c r="C40" s="110"/>
       <c r="D40" s="108"/>
     </row>
     <row r="41">
       <c r="A41" s="108"/>
       <c r="B41" s="108"/>
-      <c r="C41" s="109"/>
+      <c r="C41" s="110"/>
       <c r="D41" s="108"/>
     </row>
     <row r="42">
       <c r="A42" s="108"/>
       <c r="B42" s="108"/>
-      <c r="C42" s="109"/>
+      <c r="C42" s="110"/>
       <c r="D42" s="108"/>
     </row>
     <row r="43">
       <c r="A43" s="108"/>
       <c r="B43" s="108"/>
-      <c r="C43" s="109"/>
+      <c r="C43" s="110"/>
       <c r="D43" s="108"/>
     </row>
     <row r="44">
       <c r="A44" s="108"/>
       <c r="B44" s="108"/>
-      <c r="C44" s="109"/>
+      <c r="C44" s="110"/>
       <c r="D44" s="108"/>
     </row>
     <row r="45">
       <c r="A45" s="108"/>
       <c r="B45" s="108"/>
-      <c r="C45" s="109"/>
+      <c r="C45" s="110"/>
       <c r="D45" s="108"/>
     </row>
     <row r="46">
       <c r="A46" s="108"/>
       <c r="B46" s="108"/>
-      <c r="C46" s="109"/>
+      <c r="C46" s="110"/>
       <c r="D46" s="108"/>
     </row>
     <row r="47">
       <c r="A47" s="108"/>
       <c r="B47" s="108"/>
-      <c r="C47" s="109"/>
+      <c r="C47" s="110"/>
       <c r="D47" s="108"/>
     </row>
     <row r="48">
       <c r="A48" s="108"/>
       <c r="B48" s="108"/>
-      <c r="C48" s="109"/>
+      <c r="C48" s="110"/>
       <c r="D48" s="108"/>
     </row>
     <row r="49">
       <c r="A49" s="108"/>
       <c r="B49" s="108"/>
-      <c r="C49" s="109"/>
+      <c r="C49" s="110"/>
       <c r="D49" s="108"/>
     </row>
     <row r="50">
       <c r="A50" s="108"/>
       <c r="B50" s="108"/>
-      <c r="C50" s="109"/>
+      <c r="C50" s="110"/>
       <c r="D50" s="108"/>
     </row>
     <row r="51">
       <c r="A51" s="108"/>
       <c r="B51" s="108"/>
-      <c r="C51" s="109"/>
+      <c r="C51" s="110"/>
       <c r="D51" s="108"/>
     </row>
     <row r="52">
       <c r="A52" s="108"/>
       <c r="B52" s="108"/>
-      <c r="C52" s="109"/>
+      <c r="C52" s="110"/>
       <c r="D52" s="108"/>
     </row>
     <row r="53">
       <c r="A53" s="108"/>
       <c r="B53" s="108"/>
-      <c r="C53" s="109"/>
+      <c r="C53" s="110"/>
       <c r="D53" s="108"/>
     </row>
     <row r="54">
       <c r="A54" s="108"/>
       <c r="B54" s="108"/>
-      <c r="C54" s="109"/>
+      <c r="C54" s="110"/>
       <c r="D54" s="108"/>
     </row>
     <row r="55">
       <c r="A55" s="108"/>
       <c r="B55" s="108"/>
-      <c r="C55" s="109"/>
+      <c r="C55" s="110"/>
       <c r="D55" s="108"/>
     </row>
     <row r="56">
       <c r="A56" s="108"/>
       <c r="B56" s="108"/>
-      <c r="C56" s="109"/>
+      <c r="C56" s="110"/>
       <c r="D56" s="108"/>
     </row>
     <row r="57">
       <c r="A57" s="108"/>
       <c r="B57" s="108"/>
-      <c r="C57" s="109"/>
+      <c r="C57" s="110"/>
       <c r="D57" s="108"/>
     </row>
     <row r="58">
       <c r="A58" s="108"/>
       <c r="B58" s="108"/>
-      <c r="C58" s="109"/>
+      <c r="C58" s="110"/>
       <c r="D58" s="108"/>
     </row>
     <row r="59">
       <c r="A59" s="108"/>
       <c r="B59" s="108"/>
-      <c r="C59" s="109"/>
+      <c r="C59" s="110"/>
       <c r="D59" s="108"/>
     </row>
     <row r="60">
       <c r="A60" s="108"/>
       <c r="B60" s="108"/>
-      <c r="C60" s="109"/>
+      <c r="C60" s="110"/>
       <c r="D60" s="108"/>
     </row>
     <row r="61">
       <c r="A61" s="108"/>
       <c r="B61" s="108"/>
-      <c r="C61" s="109"/>
+      <c r="C61" s="110"/>
       <c r="D61" s="108"/>
     </row>
     <row r="62">
       <c r="A62" s="108"/>
       <c r="B62" s="108"/>
-      <c r="C62" s="109"/>
+      <c r="C62" s="110"/>
       <c r="D62" s="108"/>
     </row>
     <row r="63">
       <c r="A63" s="108"/>
       <c r="B63" s="108"/>
-      <c r="C63" s="109"/>
+      <c r="C63" s="110"/>
       <c r="D63" s="108"/>
     </row>
     <row r="64">
       <c r="A64" s="108"/>
       <c r="B64" s="108"/>
-      <c r="C64" s="109"/>
+      <c r="C64" s="110"/>
       <c r="D64" s="108"/>
     </row>
     <row r="65">
       <c r="A65" s="108"/>
       <c r="B65" s="108"/>
-      <c r="C65" s="109"/>
+      <c r="C65" s="110"/>
       <c r="D65" s="108"/>
     </row>
     <row r="66">
       <c r="A66" s="108"/>
       <c r="B66" s="108"/>
-      <c r="C66" s="109"/>
+      <c r="C66" s="110"/>
       <c r="D66" s="108"/>
     </row>
     <row r="67">
       <c r="A67" s="108"/>
       <c r="B67" s="108"/>
-      <c r="C67" s="109"/>
+      <c r="C67" s="110"/>
       <c r="D67" s="108"/>
     </row>
     <row r="68">
       <c r="A68" s="108"/>
       <c r="B68" s="108"/>
-      <c r="C68" s="109"/>
+      <c r="C68" s="110"/>
       <c r="D68" s="108"/>
     </row>
     <row r="69">
       <c r="A69" s="108"/>
       <c r="B69" s="108"/>
-      <c r="C69" s="109"/>
+      <c r="C69" s="110"/>
       <c r="D69" s="108"/>
     </row>
     <row r="70">
       <c r="A70" s="108"/>
       <c r="B70" s="108"/>
-      <c r="C70" s="109"/>
+      <c r="C70" s="110"/>
       <c r="D70" s="108"/>
     </row>
     <row r="71">
       <c r="A71" s="108"/>
       <c r="B71" s="108"/>
-      <c r="C71" s="109"/>
+      <c r="C71" s="110"/>
       <c r="D71" s="108"/>
     </row>
     <row r="72">
       <c r="A72" s="108"/>
       <c r="B72" s="108"/>
-      <c r="C72" s="109"/>
+      <c r="C72" s="110"/>
       <c r="D72" s="108"/>
     </row>
     <row r="73">
       <c r="A73" s="108"/>
       <c r="B73" s="108"/>
-      <c r="C73" s="109"/>
+      <c r="C73" s="110"/>
       <c r="D73" s="108"/>
     </row>
     <row r="74">
       <c r="A74" s="108"/>
       <c r="B74" s="108"/>
-      <c r="C74" s="109"/>
+      <c r="C74" s="110"/>
       <c r="D74" s="108"/>
     </row>
     <row r="75">
       <c r="A75" s="108"/>
       <c r="B75" s="108"/>
-      <c r="C75" s="109"/>
+      <c r="C75" s="110"/>
       <c r="D75" s="108"/>
     </row>
     <row r="76">
       <c r="A76" s="108"/>
       <c r="B76" s="108"/>
-      <c r="C76" s="109"/>
+      <c r="C76" s="110"/>
       <c r="D76" s="108"/>
     </row>
     <row r="77">
       <c r="A77" s="108"/>
       <c r="B77" s="108"/>
-      <c r="C77" s="109"/>
+      <c r="C77" s="110"/>
       <c r="D77" s="108"/>
     </row>
     <row r="78">
       <c r="A78" s="108"/>
       <c r="B78" s="108"/>
-      <c r="C78" s="109"/>
+      <c r="C78" s="110"/>
       <c r="D78" s="108"/>
     </row>
     <row r="79">
       <c r="A79" s="108"/>
       <c r="B79" s="108"/>
-      <c r="C79" s="109"/>
+      <c r="C79" s="110"/>
       <c r="D79" s="108"/>
     </row>
     <row r="80">
       <c r="A80" s="108"/>
       <c r="B80" s="108"/>
-      <c r="C80" s="109"/>
+      <c r="C80" s="110"/>
       <c r="D80" s="108"/>
     </row>
     <row r="81">
       <c r="A81" s="108"/>
       <c r="B81" s="108"/>
-      <c r="C81" s="109"/>
+      <c r="C81" s="110"/>
       <c r="D81" s="108"/>
     </row>
     <row r="82">
       <c r="A82" s="108"/>
       <c r="B82" s="108"/>
-      <c r="C82" s="109"/>
+      <c r="C82" s="110"/>
       <c r="D82" s="108"/>
     </row>
     <row r="83">
       <c r="A83" s="108"/>
       <c r="B83" s="108"/>
-      <c r="C83" s="109"/>
+      <c r="C83" s="110"/>
       <c r="D83" s="108"/>
     </row>
     <row r="84">
       <c r="A84" s="108"/>
       <c r="B84" s="108"/>
-      <c r="C84" s="109"/>
+      <c r="C84" s="110"/>
       <c r="D84" s="108"/>
     </row>
     <row r="85">
       <c r="A85" s="108"/>
       <c r="B85" s="108"/>
-      <c r="C85" s="109"/>
+      <c r="C85" s="110"/>
       <c r="D85" s="108"/>
     </row>
     <row r="86">
       <c r="A86" s="108"/>
       <c r="B86" s="108"/>
-      <c r="C86" s="109"/>
+      <c r="C86" s="110"/>
       <c r="D86" s="108"/>
     </row>
     <row r="87">
       <c r="A87" s="108"/>
       <c r="B87" s="108"/>
-      <c r="C87" s="109"/>
+      <c r="C87" s="110"/>
       <c r="D87" s="108"/>
     </row>
     <row r="88">
       <c r="A88" s="108"/>
       <c r="B88" s="108"/>
-      <c r="C88" s="109"/>
+      <c r="C88" s="110"/>
       <c r="D88" s="108"/>
     </row>
     <row r="89">
       <c r="A89" s="108"/>
       <c r="B89" s="108"/>
-      <c r="C89" s="109"/>
+      <c r="C89" s="110"/>
       <c r="D89" s="108"/>
     </row>
     <row r="90">
       <c r="A90" s="108"/>
       <c r="B90" s="108"/>
-      <c r="C90" s="109"/>
+      <c r="C90" s="110"/>
       <c r="D90" s="108"/>
     </row>
     <row r="91">
       <c r="A91" s="108"/>
       <c r="B91" s="108"/>
-      <c r="C91" s="109"/>
+      <c r="C91" s="110"/>
       <c r="D91" s="108"/>
     </row>
     <row r="92">
       <c r="A92" s="108"/>
       <c r="B92" s="108"/>
-      <c r="C92" s="109"/>
+      <c r="C92" s="110"/>
       <c r="D92" s="108"/>
     </row>
     <row r="93">
       <c r="A93" s="108"/>
       <c r="B93" s="108"/>
-      <c r="C93" s="109"/>
+      <c r="C93" s="110"/>
       <c r="D93" s="108"/>
     </row>
     <row r="94">
       <c r="A94" s="108"/>
       <c r="B94" s="108"/>
-      <c r="C94" s="109"/>
+      <c r="C94" s="110"/>
       <c r="D94" s="108"/>
     </row>
     <row r="95">
       <c r="A95" s="108"/>
       <c r="B95" s="108"/>
-      <c r="C95" s="109"/>
+      <c r="C95" s="110"/>
       <c r="D95" s="108"/>
     </row>
     <row r="96">
       <c r="A96" s="108"/>
       <c r="B96" s="108"/>
-      <c r="C96" s="109"/>
+      <c r="C96" s="110"/>
       <c r="D96" s="108"/>
     </row>
     <row r="97">
       <c r="A97" s="108"/>
       <c r="B97" s="108"/>
-      <c r="C97" s="109"/>
+      <c r="C97" s="110"/>
       <c r="D97" s="108"/>
     </row>
     <row r="98">
       <c r="A98" s="108"/>
       <c r="B98" s="108"/>
-      <c r="C98" s="109"/>
+      <c r="C98" s="110"/>
       <c r="D98" s="108"/>
     </row>
     <row r="99">
       <c r="A99" s="108"/>
       <c r="B99" s="108"/>
-      <c r="C99" s="109"/>
+      <c r="C99" s="110"/>
       <c r="D99" s="108"/>
     </row>
     <row r="100">
       <c r="A100" s="108"/>
       <c r="B100" s="108"/>
-      <c r="C100" s="109"/>
+      <c r="C100" s="110"/>
       <c r="D100" s="108"/>
     </row>
   </sheetData>
@@ -8541,50 +8559,50 @@
   <sheetData>
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
-      <c r="B2" s="110" t="s">
-        <v>144</v>
+      <c r="B2" s="111" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="111" t="s">
-        <v>145</v>
-      </c>
-      <c r="C4" s="111" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="111" t="s">
+      <c r="B4" s="112" t="s">
         <v>147</v>
       </c>
-      <c r="E4" s="111" t="s">
+      <c r="C4" s="112" t="s">
         <v>148</v>
       </c>
-      <c r="F4" s="111" t="s">
+      <c r="D4" s="112" t="s">
         <v>149</v>
       </c>
-      <c r="G4" s="111" t="s">
+      <c r="E4" s="112" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="112" t="s">
+      <c r="F4" s="112" t="s">
         <v>151</v>
       </c>
+      <c r="G4" s="112" t="s">
+        <v>152</v>
+      </c>
+      <c r="H4" s="113" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="113">
+      <c r="B5" s="114">
         <v>55.8</v>
       </c>
-      <c r="C5" s="114">
+      <c r="C5" s="115">
         <v>0.11</v>
       </c>
-      <c r="D5" s="113" t="s">
-        <v>152</v>
-      </c>
-      <c r="E5" s="113" t="s">
-        <v>153</v>
-      </c>
-      <c r="F5" s="115">
+      <c r="D5" s="114" t="s">
+        <v>154</v>
+      </c>
+      <c r="E5" s="114" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="116">
         <v>391560.0</v>
       </c>
-      <c r="G5" s="116">
+      <c r="G5" s="117">
         <v>46010.0</v>
       </c>
       <c r="H5" s="10">
@@ -8593,22 +8611,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="113">
+      <c r="B6" s="114">
         <v>30.0</v>
       </c>
-      <c r="C6" s="114">
+      <c r="C6" s="115">
         <v>0.1</v>
       </c>
-      <c r="D6" s="113" t="s">
-        <v>152</v>
-      </c>
-      <c r="E6" s="113" t="s">
+      <c r="D6" s="114" t="s">
         <v>154</v>
       </c>
-      <c r="F6" s="115">
+      <c r="E6" s="114" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="116">
         <v>229500.0</v>
       </c>
-      <c r="G6" s="116">
+      <c r="G6" s="117">
         <v>45966.0</v>
       </c>
       <c r="H6" s="10">
@@ -8617,22 +8635,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="113">
+      <c r="B7" s="114">
         <v>36.9</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="115">
         <v>0.105</v>
       </c>
-      <c r="D7" s="113" t="s">
-        <v>152</v>
-      </c>
-      <c r="E7" s="113" t="s">
-        <v>155</v>
-      </c>
-      <c r="F7" s="115">
+      <c r="D7" s="114" t="s">
+        <v>154</v>
+      </c>
+      <c r="E7" s="114" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="116">
         <v>300000.0</v>
       </c>
-      <c r="G7" s="116">
+      <c r="G7" s="117">
         <v>46169.0</v>
       </c>
       <c r="H7" s="10">
@@ -8641,20 +8659,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="113">
+      <c r="B8" s="114">
         <v>15.0</v>
       </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="113" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" s="113" t="s">
-        <v>155</v>
-      </c>
-      <c r="F8" s="115">
+      <c r="C8" s="118"/>
+      <c r="D8" s="114" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8" s="114" t="s">
+        <v>157</v>
+      </c>
+      <c r="F8" s="116">
         <v>135000.0</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="117">
         <v>46178.0</v>
       </c>
       <c r="H8" s="10">
@@ -8663,18 +8681,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="118"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="113" t="s">
-        <v>152</v>
-      </c>
-      <c r="E9" s="113" t="s">
-        <v>156</v>
-      </c>
-      <c r="F9" s="115">
+      <c r="B9" s="119"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="114" t="s">
+        <v>154</v>
+      </c>
+      <c r="E9" s="114" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="116">
         <v>297698.0</v>
       </c>
-      <c r="G9" s="116">
+      <c r="G9" s="117">
         <v>46035.0</v>
       </c>
       <c r="H9" s="10">
@@ -8683,1044 +8701,1044 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="118"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="121"/>
       <c r="H10" s="10" t="str">
         <f t="shared" ref="H10:H96" si="2">IF(OR(ISBLANK(F10), ISBLANK(G10)), "", F10 * (C10/100) * (TODAY() - G10) / 365)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="118"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="120"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="121"/>
       <c r="H11" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="118"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="120"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="121"/>
       <c r="H12" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="118"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="120"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="121"/>
       <c r="H13" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="118"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="120"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="121"/>
       <c r="H14" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="118"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="120"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="121"/>
       <c r="H15" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="118"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="120"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="121"/>
       <c r="H16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="118"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="120"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="121"/>
       <c r="H17" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="118"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="120"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="121"/>
       <c r="H18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="118"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="120"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="121"/>
       <c r="H19" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="118"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="120"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="121"/>
       <c r="H20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="118"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="120"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="121"/>
       <c r="H21" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="118"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="120"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="121"/>
       <c r="H22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="118"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="120"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="121"/>
       <c r="H23" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="118"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="120"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="121"/>
       <c r="H24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="118"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="120"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="121"/>
       <c r="H25" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="118"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="120"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="121"/>
       <c r="H26" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="118"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="120"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="121"/>
       <c r="H27" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="118"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="120"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="121"/>
       <c r="H28" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="118"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="120"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="121"/>
       <c r="H29" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="118"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="120"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="121"/>
       <c r="H30" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="118"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="120"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="121"/>
       <c r="H31" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="118"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="120"/>
+      <c r="B32" s="119"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="121"/>
       <c r="H32" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="118"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="120"/>
+      <c r="B33" s="119"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="121"/>
       <c r="H33" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="118"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="120"/>
+      <c r="B34" s="119"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="121"/>
       <c r="H34" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="118"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="120"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="121"/>
       <c r="H35" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="118"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="120"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="121"/>
       <c r="H36" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="118"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="120"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="121"/>
       <c r="H37" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="118"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="120"/>
+      <c r="B38" s="119"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="121"/>
       <c r="H38" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="118"/>
-      <c r="C39" s="117"/>
-      <c r="D39" s="118"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="120"/>
+      <c r="B39" s="119"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="121"/>
       <c r="H39" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="118"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="118"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="119"/>
-      <c r="G40" s="120"/>
+      <c r="B40" s="119"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="121"/>
       <c r="H40" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="118"/>
-      <c r="C41" s="117"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="120"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="121"/>
       <c r="H41" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="118"/>
-      <c r="C42" s="117"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="119"/>
-      <c r="G42" s="120"/>
+      <c r="B42" s="119"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="121"/>
       <c r="H42" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="118"/>
-      <c r="C43" s="117"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="120"/>
+      <c r="B43" s="119"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="121"/>
       <c r="H43" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="118"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="118"/>
-      <c r="E44" s="118"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="120"/>
+      <c r="B44" s="119"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="121"/>
       <c r="H44" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="118"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="119"/>
-      <c r="G45" s="120"/>
+      <c r="B45" s="119"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="121"/>
       <c r="H45" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="118"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="120"/>
+      <c r="B46" s="119"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="120"/>
+      <c r="G46" s="121"/>
       <c r="H46" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="118"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="120"/>
+      <c r="B47" s="119"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="121"/>
       <c r="H47" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="118"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="120"/>
+      <c r="B48" s="119"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="121"/>
       <c r="H48" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="118"/>
-      <c r="C49" s="117"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="120"/>
+      <c r="B49" s="119"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="119"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="121"/>
       <c r="H49" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="118"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="118"/>
-      <c r="E50" s="118"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="120"/>
+      <c r="B50" s="119"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="119"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="121"/>
       <c r="H50" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="118"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="120"/>
+      <c r="B51" s="119"/>
+      <c r="C51" s="118"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="120"/>
+      <c r="G51" s="121"/>
       <c r="H51" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="118"/>
-      <c r="C52" s="117"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="120"/>
+      <c r="B52" s="119"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="120"/>
+      <c r="G52" s="121"/>
       <c r="H52" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="118"/>
-      <c r="C53" s="117"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="120"/>
+      <c r="B53" s="119"/>
+      <c r="C53" s="118"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="119"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="121"/>
       <c r="H53" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="118"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="120"/>
+      <c r="B54" s="119"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="119"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="121"/>
       <c r="H54" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="118"/>
-      <c r="C55" s="117"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="118"/>
-      <c r="F55" s="119"/>
-      <c r="G55" s="120"/>
+      <c r="B55" s="119"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="119"/>
+      <c r="E55" s="119"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="121"/>
       <c r="H55" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="118"/>
-      <c r="C56" s="117"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="118"/>
-      <c r="F56" s="119"/>
-      <c r="G56" s="120"/>
+      <c r="B56" s="119"/>
+      <c r="C56" s="118"/>
+      <c r="D56" s="119"/>
+      <c r="E56" s="119"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="121"/>
       <c r="H56" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="118"/>
-      <c r="C57" s="117"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="119"/>
-      <c r="G57" s="120"/>
+      <c r="B57" s="119"/>
+      <c r="C57" s="118"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="119"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="121"/>
       <c r="H57" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="118"/>
-      <c r="C58" s="117"/>
-      <c r="D58" s="118"/>
-      <c r="E58" s="118"/>
-      <c r="F58" s="119"/>
-      <c r="G58" s="120"/>
+      <c r="B58" s="119"/>
+      <c r="C58" s="118"/>
+      <c r="D58" s="119"/>
+      <c r="E58" s="119"/>
+      <c r="F58" s="120"/>
+      <c r="G58" s="121"/>
       <c r="H58" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="118"/>
-      <c r="C59" s="117"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="118"/>
-      <c r="F59" s="119"/>
-      <c r="G59" s="120"/>
+      <c r="B59" s="119"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="119"/>
+      <c r="E59" s="119"/>
+      <c r="F59" s="120"/>
+      <c r="G59" s="121"/>
       <c r="H59" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="118"/>
-      <c r="C60" s="117"/>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="119"/>
-      <c r="G60" s="120"/>
+      <c r="B60" s="119"/>
+      <c r="C60" s="118"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="120"/>
+      <c r="G60" s="121"/>
       <c r="H60" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="118"/>
-      <c r="C61" s="117"/>
-      <c r="D61" s="118"/>
-      <c r="E61" s="118"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="120"/>
+      <c r="B61" s="119"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="119"/>
+      <c r="E61" s="119"/>
+      <c r="F61" s="120"/>
+      <c r="G61" s="121"/>
       <c r="H61" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="118"/>
-      <c r="C62" s="117"/>
-      <c r="D62" s="118"/>
-      <c r="E62" s="118"/>
-      <c r="F62" s="119"/>
-      <c r="G62" s="120"/>
+      <c r="B62" s="119"/>
+      <c r="C62" s="118"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="119"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="121"/>
       <c r="H62" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="118"/>
-      <c r="C63" s="117"/>
-      <c r="D63" s="118"/>
-      <c r="E63" s="118"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="120"/>
+      <c r="B63" s="119"/>
+      <c r="C63" s="118"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="119"/>
+      <c r="F63" s="120"/>
+      <c r="G63" s="121"/>
       <c r="H63" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="118"/>
-      <c r="C64" s="117"/>
-      <c r="D64" s="118"/>
-      <c r="E64" s="118"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="120"/>
+      <c r="B64" s="119"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="119"/>
+      <c r="F64" s="120"/>
+      <c r="G64" s="121"/>
       <c r="H64" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="118"/>
-      <c r="C65" s="117"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="118"/>
-      <c r="F65" s="119"/>
-      <c r="G65" s="120"/>
+      <c r="B65" s="119"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="121"/>
       <c r="H65" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="118"/>
-      <c r="C66" s="117"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="119"/>
-      <c r="G66" s="120"/>
+      <c r="B66" s="119"/>
+      <c r="C66" s="118"/>
+      <c r="D66" s="119"/>
+      <c r="E66" s="119"/>
+      <c r="F66" s="120"/>
+      <c r="G66" s="121"/>
       <c r="H66" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="118"/>
-      <c r="C67" s="117"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="118"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="120"/>
+      <c r="B67" s="119"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="119"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="121"/>
       <c r="H67" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="118"/>
-      <c r="C68" s="117"/>
-      <c r="D68" s="118"/>
-      <c r="E68" s="118"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="120"/>
+      <c r="B68" s="119"/>
+      <c r="C68" s="118"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="119"/>
+      <c r="F68" s="120"/>
+      <c r="G68" s="121"/>
       <c r="H68" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="118"/>
-      <c r="C69" s="117"/>
-      <c r="D69" s="118"/>
-      <c r="E69" s="118"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="120"/>
+      <c r="B69" s="119"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="119"/>
+      <c r="F69" s="120"/>
+      <c r="G69" s="121"/>
       <c r="H69" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="118"/>
-      <c r="C70" s="117"/>
-      <c r="D70" s="118"/>
-      <c r="E70" s="118"/>
-      <c r="F70" s="119"/>
-      <c r="G70" s="120"/>
+      <c r="B70" s="119"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="119"/>
+      <c r="E70" s="119"/>
+      <c r="F70" s="120"/>
+      <c r="G70" s="121"/>
       <c r="H70" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="118"/>
-      <c r="C71" s="117"/>
-      <c r="D71" s="118"/>
-      <c r="E71" s="118"/>
-      <c r="F71" s="119"/>
-      <c r="G71" s="120"/>
+      <c r="B71" s="119"/>
+      <c r="C71" s="118"/>
+      <c r="D71" s="119"/>
+      <c r="E71" s="119"/>
+      <c r="F71" s="120"/>
+      <c r="G71" s="121"/>
       <c r="H71" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="118"/>
-      <c r="C72" s="117"/>
-      <c r="D72" s="118"/>
-      <c r="E72" s="118"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="120"/>
+      <c r="B72" s="119"/>
+      <c r="C72" s="118"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="120"/>
+      <c r="G72" s="121"/>
       <c r="H72" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="118"/>
-      <c r="C73" s="117"/>
-      <c r="D73" s="118"/>
-      <c r="E73" s="118"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="120"/>
+      <c r="B73" s="119"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="119"/>
+      <c r="E73" s="119"/>
+      <c r="F73" s="120"/>
+      <c r="G73" s="121"/>
       <c r="H73" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="118"/>
-      <c r="C74" s="117"/>
-      <c r="D74" s="118"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="120"/>
+      <c r="B74" s="119"/>
+      <c r="C74" s="118"/>
+      <c r="D74" s="119"/>
+      <c r="E74" s="119"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="121"/>
       <c r="H74" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="118"/>
-      <c r="C75" s="117"/>
-      <c r="D75" s="118"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="119"/>
-      <c r="G75" s="120"/>
+      <c r="B75" s="119"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="119"/>
+      <c r="E75" s="119"/>
+      <c r="F75" s="120"/>
+      <c r="G75" s="121"/>
       <c r="H75" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="118"/>
-      <c r="C76" s="117"/>
-      <c r="D76" s="118"/>
-      <c r="E76" s="118"/>
-      <c r="F76" s="119"/>
-      <c r="G76" s="120"/>
+      <c r="B76" s="119"/>
+      <c r="C76" s="118"/>
+      <c r="D76" s="119"/>
+      <c r="E76" s="119"/>
+      <c r="F76" s="120"/>
+      <c r="G76" s="121"/>
       <c r="H76" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="118"/>
-      <c r="C77" s="117"/>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="120"/>
+      <c r="B77" s="119"/>
+      <c r="C77" s="118"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="119"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="121"/>
       <c r="H77" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="118"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="118"/>
-      <c r="E78" s="118"/>
-      <c r="F78" s="119"/>
-      <c r="G78" s="120"/>
+      <c r="B78" s="119"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="119"/>
+      <c r="E78" s="119"/>
+      <c r="F78" s="120"/>
+      <c r="G78" s="121"/>
       <c r="H78" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="118"/>
-      <c r="C79" s="117"/>
-      <c r="D79" s="118"/>
-      <c r="E79" s="118"/>
-      <c r="F79" s="119"/>
-      <c r="G79" s="120"/>
+      <c r="B79" s="119"/>
+      <c r="C79" s="118"/>
+      <c r="D79" s="119"/>
+      <c r="E79" s="119"/>
+      <c r="F79" s="120"/>
+      <c r="G79" s="121"/>
       <c r="H79" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="118"/>
-      <c r="C80" s="117"/>
-      <c r="D80" s="118"/>
-      <c r="E80" s="118"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="120"/>
+      <c r="B80" s="119"/>
+      <c r="C80" s="118"/>
+      <c r="D80" s="119"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="120"/>
+      <c r="G80" s="121"/>
       <c r="H80" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="118"/>
-      <c r="C81" s="117"/>
-      <c r="D81" s="118"/>
-      <c r="E81" s="118"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="120"/>
+      <c r="B81" s="119"/>
+      <c r="C81" s="118"/>
+      <c r="D81" s="119"/>
+      <c r="E81" s="119"/>
+      <c r="F81" s="120"/>
+      <c r="G81" s="121"/>
       <c r="H81" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="118"/>
-      <c r="C82" s="117"/>
-      <c r="D82" s="118"/>
-      <c r="E82" s="118"/>
-      <c r="F82" s="119"/>
-      <c r="G82" s="120"/>
+      <c r="B82" s="119"/>
+      <c r="C82" s="118"/>
+      <c r="D82" s="119"/>
+      <c r="E82" s="119"/>
+      <c r="F82" s="120"/>
+      <c r="G82" s="121"/>
       <c r="H82" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="118"/>
-      <c r="C83" s="117"/>
-      <c r="D83" s="118"/>
-      <c r="E83" s="118"/>
-      <c r="F83" s="119"/>
-      <c r="G83" s="120"/>
+      <c r="B83" s="119"/>
+      <c r="C83" s="118"/>
+      <c r="D83" s="119"/>
+      <c r="E83" s="119"/>
+      <c r="F83" s="120"/>
+      <c r="G83" s="121"/>
       <c r="H83" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="118"/>
-      <c r="C84" s="117"/>
-      <c r="D84" s="118"/>
-      <c r="E84" s="118"/>
-      <c r="F84" s="119"/>
-      <c r="G84" s="120"/>
+      <c r="B84" s="119"/>
+      <c r="C84" s="118"/>
+      <c r="D84" s="119"/>
+      <c r="E84" s="119"/>
+      <c r="F84" s="120"/>
+      <c r="G84" s="121"/>
       <c r="H84" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="118"/>
-      <c r="C85" s="117"/>
-      <c r="D85" s="118"/>
-      <c r="E85" s="118"/>
-      <c r="F85" s="119"/>
-      <c r="G85" s="120"/>
+      <c r="B85" s="119"/>
+      <c r="C85" s="118"/>
+      <c r="D85" s="119"/>
+      <c r="E85" s="119"/>
+      <c r="F85" s="120"/>
+      <c r="G85" s="121"/>
       <c r="H85" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="118"/>
-      <c r="C86" s="117"/>
-      <c r="D86" s="118"/>
-      <c r="E86" s="118"/>
-      <c r="F86" s="119"/>
-      <c r="G86" s="120"/>
+      <c r="B86" s="119"/>
+      <c r="C86" s="118"/>
+      <c r="D86" s="119"/>
+      <c r="E86" s="119"/>
+      <c r="F86" s="120"/>
+      <c r="G86" s="121"/>
       <c r="H86" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="118"/>
-      <c r="C87" s="117"/>
-      <c r="D87" s="118"/>
-      <c r="E87" s="118"/>
-      <c r="F87" s="119"/>
-      <c r="G87" s="120"/>
+      <c r="B87" s="119"/>
+      <c r="C87" s="118"/>
+      <c r="D87" s="119"/>
+      <c r="E87" s="119"/>
+      <c r="F87" s="120"/>
+      <c r="G87" s="121"/>
       <c r="H87" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="118"/>
-      <c r="C88" s="117"/>
-      <c r="D88" s="118"/>
-      <c r="E88" s="118"/>
-      <c r="F88" s="119"/>
-      <c r="G88" s="120"/>
+      <c r="B88" s="119"/>
+      <c r="C88" s="118"/>
+      <c r="D88" s="119"/>
+      <c r="E88" s="119"/>
+      <c r="F88" s="120"/>
+      <c r="G88" s="121"/>
       <c r="H88" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="118"/>
-      <c r="C89" s="117"/>
-      <c r="D89" s="118"/>
-      <c r="E89" s="118"/>
-      <c r="F89" s="119"/>
-      <c r="G89" s="120"/>
+      <c r="B89" s="119"/>
+      <c r="C89" s="118"/>
+      <c r="D89" s="119"/>
+      <c r="E89" s="119"/>
+      <c r="F89" s="120"/>
+      <c r="G89" s="121"/>
       <c r="H89" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="118"/>
-      <c r="C90" s="117"/>
-      <c r="D90" s="118"/>
-      <c r="E90" s="118"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="120"/>
+      <c r="B90" s="119"/>
+      <c r="C90" s="118"/>
+      <c r="D90" s="119"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="120"/>
+      <c r="G90" s="121"/>
       <c r="H90" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="118"/>
-      <c r="C91" s="117"/>
-      <c r="D91" s="118"/>
-      <c r="E91" s="118"/>
-      <c r="F91" s="119"/>
-      <c r="G91" s="120"/>
+      <c r="B91" s="119"/>
+      <c r="C91" s="118"/>
+      <c r="D91" s="119"/>
+      <c r="E91" s="119"/>
+      <c r="F91" s="120"/>
+      <c r="G91" s="121"/>
       <c r="H91" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="118"/>
-      <c r="C92" s="117"/>
-      <c r="D92" s="118"/>
-      <c r="E92" s="118"/>
-      <c r="F92" s="119"/>
-      <c r="G92" s="120"/>
+      <c r="B92" s="119"/>
+      <c r="C92" s="118"/>
+      <c r="D92" s="119"/>
+      <c r="E92" s="119"/>
+      <c r="F92" s="120"/>
+      <c r="G92" s="121"/>
       <c r="H92" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="118"/>
-      <c r="C93" s="117"/>
-      <c r="D93" s="118"/>
-      <c r="E93" s="118"/>
-      <c r="F93" s="119"/>
-      <c r="G93" s="120"/>
+      <c r="B93" s="119"/>
+      <c r="C93" s="118"/>
+      <c r="D93" s="119"/>
+      <c r="E93" s="119"/>
+      <c r="F93" s="120"/>
+      <c r="G93" s="121"/>
       <c r="H93" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="118"/>
-      <c r="C94" s="117"/>
-      <c r="D94" s="118"/>
-      <c r="E94" s="118"/>
-      <c r="F94" s="119"/>
-      <c r="G94" s="120"/>
+      <c r="B94" s="119"/>
+      <c r="C94" s="118"/>
+      <c r="D94" s="119"/>
+      <c r="E94" s="119"/>
+      <c r="F94" s="120"/>
+      <c r="G94" s="121"/>
       <c r="H94" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="118"/>
-      <c r="C95" s="117"/>
-      <c r="D95" s="118"/>
-      <c r="E95" s="118"/>
-      <c r="F95" s="119"/>
-      <c r="G95" s="120"/>
+      <c r="B95" s="119"/>
+      <c r="C95" s="118"/>
+      <c r="D95" s="119"/>
+      <c r="E95" s="119"/>
+      <c r="F95" s="120"/>
+      <c r="G95" s="121"/>
       <c r="H95" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="118"/>
-      <c r="C96" s="117"/>
-      <c r="D96" s="118"/>
-      <c r="E96" s="118"/>
-      <c r="F96" s="119"/>
-      <c r="G96" s="120"/>
+      <c r="B96" s="119"/>
+      <c r="C96" s="118"/>
+      <c r="D96" s="119"/>
+      <c r="E96" s="119"/>
+      <c r="F96" s="120"/>
+      <c r="G96" s="121"/>
       <c r="H96" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -9749,333 +9767,333 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="B1" s="121" t="s">
-        <v>157</v>
+      <c r="B1" s="122" t="s">
+        <v>159</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="122" t="s">
-        <v>158</v>
+      <c r="B2" s="123" t="s">
+        <v>160</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
     </row>
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
-      <c r="B4" s="123" t="s">
-        <v>159</v>
-      </c>
-      <c r="C4" s="124" t="s">
-        <v>160</v>
-      </c>
-      <c r="D4" s="125" t="s">
+      <c r="B4" s="124" t="s">
         <v>161</v>
       </c>
+      <c r="C4" s="125" t="s">
+        <v>162</v>
+      </c>
+      <c r="D4" s="126" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
-      <c r="B5" s="123" t="s">
-        <v>162</v>
-      </c>
-      <c r="C5" s="124" t="s">
-        <v>163</v>
-      </c>
-      <c r="D5" s="125" t="s">
+      <c r="B5" s="124" t="s">
         <v>164</v>
       </c>
+      <c r="C5" s="125" t="s">
+        <v>165</v>
+      </c>
+      <c r="D5" s="126" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
-      <c r="B6" s="123" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="124" t="s">
-        <v>166</v>
-      </c>
-      <c r="D6" s="125" t="s">
+      <c r="B6" s="124" t="s">
         <v>167</v>
       </c>
+      <c r="C6" s="125" t="s">
+        <v>168</v>
+      </c>
+      <c r="D6" s="126" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
-      <c r="B7" s="123" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="124" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" s="125" t="s">
+      <c r="B7" s="124" t="s">
         <v>170</v>
       </c>
+      <c r="C7" s="125" t="s">
+        <v>171</v>
+      </c>
+      <c r="D7" s="126" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
-      <c r="B8" s="126" t="s">
-        <v>171</v>
-      </c>
-      <c r="C8" s="127" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" s="125" t="s">
+      <c r="B8" s="127" t="s">
         <v>173</v>
       </c>
+      <c r="C8" s="128" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="126" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="B9" s="126" t="s">
-        <v>174</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="125" t="s">
+      <c r="B9" s="127" t="s">
         <v>176</v>
       </c>
+      <c r="C9" s="128" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="126" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
-      <c r="B10" s="128" t="s">
-        <v>177</v>
-      </c>
-      <c r="C10" s="129" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="125" t="s">
+      <c r="B10" s="129" t="s">
         <v>179</v>
       </c>
+      <c r="C10" s="130" t="s">
+        <v>180</v>
+      </c>
+      <c r="D10" s="126" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
-      <c r="B11" s="128" t="s">
-        <v>180</v>
-      </c>
-      <c r="C11" s="129" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="125" t="s">
+      <c r="B11" s="129" t="s">
         <v>182</v>
       </c>
+      <c r="C11" s="130" t="s">
+        <v>183</v>
+      </c>
+      <c r="D11" s="126" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
-      <c r="B12" s="130" t="s">
-        <v>183</v>
-      </c>
-      <c r="C12" s="131" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="125" t="s">
+      <c r="B12" s="131" t="s">
         <v>185</v>
       </c>
+      <c r="C12" s="132" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="126" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
-      <c r="B13" s="130" t="s">
-        <v>186</v>
-      </c>
-      <c r="C13" s="131" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="125" t="s">
+      <c r="B13" s="131" t="s">
         <v>188</v>
       </c>
+      <c r="C13" s="132" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13" s="126" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
-      <c r="B14" s="132" t="s">
-        <v>189</v>
-      </c>
-      <c r="C14" s="133" t="s">
-        <v>190</v>
-      </c>
-      <c r="D14" s="125" t="s">
+      <c r="B14" s="133" t="s">
         <v>191</v>
       </c>
+      <c r="C14" s="134" t="s">
+        <v>192</v>
+      </c>
+      <c r="D14" s="126" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
-      <c r="B15" s="134" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="135" t="s">
-        <v>193</v>
-      </c>
-      <c r="D15" s="125" t="s">
+      <c r="B15" s="135" t="s">
         <v>194</v>
       </c>
+      <c r="C15" s="136" t="s">
+        <v>195</v>
+      </c>
+      <c r="D15" s="126" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
-      <c r="B16" s="128" t="s">
-        <v>195</v>
-      </c>
-      <c r="C16" s="129" t="s">
-        <v>196</v>
-      </c>
-      <c r="D16" s="125" t="s">
+      <c r="B16" s="129" t="s">
         <v>197</v>
       </c>
+      <c r="C16" s="130" t="s">
+        <v>198</v>
+      </c>
+      <c r="D16" s="126" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
-      <c r="B17" s="134" t="s">
-        <v>198</v>
-      </c>
-      <c r="C17" s="135" t="s">
-        <v>199</v>
-      </c>
-      <c r="D17" s="125" t="s">
+      <c r="B17" s="135" t="s">
         <v>200</v>
       </c>
+      <c r="C17" s="136" t="s">
+        <v>201</v>
+      </c>
+      <c r="D17" s="126" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
-      <c r="B18" s="130" t="s">
-        <v>201</v>
-      </c>
-      <c r="C18" s="131" t="s">
-        <v>202</v>
-      </c>
-      <c r="D18" s="125" t="s">
+      <c r="B18" s="131" t="s">
         <v>203</v>
       </c>
+      <c r="C18" s="132" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="126" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="B20" s="136" t="s">
-        <v>204</v>
+      <c r="B20" s="137" t="s">
+        <v>206</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="B21" s="137" t="s">
+      <c r="B21" s="138" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="137" t="s">
-        <v>205</v>
-      </c>
-      <c r="D21" s="137" t="s">
-        <v>206</v>
+      <c r="C21" s="138" t="s">
+        <v>207</v>
+      </c>
+      <c r="D21" s="138" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="139" t="s">
-        <v>207</v>
-      </c>
-      <c r="D22" s="140" t="s">
-        <v>208</v>
+      <c r="C22" s="140" t="s">
+        <v>209</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="139" t="s">
-        <v>209</v>
-      </c>
-      <c r="D23" s="140" t="s">
-        <v>210</v>
+      <c r="C23" s="140" t="s">
+        <v>211</v>
+      </c>
+      <c r="D23" s="141" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
-      <c r="B24" s="141" t="s">
+      <c r="B24" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="142" t="s">
-        <v>211</v>
-      </c>
-      <c r="D24" s="140" t="s">
-        <v>212</v>
+      <c r="C24" s="143" t="s">
+        <v>213</v>
+      </c>
+      <c r="D24" s="141" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
-      <c r="B25" s="138" t="s">
+      <c r="B25" s="139" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="139" t="s">
-        <v>213</v>
-      </c>
-      <c r="D25" s="140" t="s">
-        <v>214</v>
+      <c r="C25" s="140" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="141" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="B26" s="143" t="s">
+      <c r="B26" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="144" t="s">
-        <v>215</v>
-      </c>
-      <c r="D26" s="140" t="s">
-        <v>216</v>
+      <c r="C26" s="145" t="s">
+        <v>217</v>
+      </c>
+      <c r="D26" s="141" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="146" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="146" t="s">
-        <v>217</v>
-      </c>
-      <c r="D27" s="140" t="s">
-        <v>218</v>
+      <c r="C27" s="147" t="s">
+        <v>219</v>
+      </c>
+      <c r="D27" s="141" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
-      <c r="B28" s="138" t="s">
+      <c r="B28" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="139" t="s">
-        <v>219</v>
-      </c>
-      <c r="D28" s="140" t="s">
-        <v>220</v>
+      <c r="C28" s="140" t="s">
+        <v>221</v>
+      </c>
+      <c r="D28" s="141" t="s">
+        <v>222</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
-      <c r="B29" s="138" t="s">
+      <c r="B29" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="139" t="s">
-        <v>221</v>
-      </c>
-      <c r="D29" s="140" t="s">
-        <v>222</v>
+      <c r="C29" s="140" t="s">
+        <v>223</v>
+      </c>
+      <c r="D29" s="141" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
-      <c r="B30" s="143" t="s">
+      <c r="B30" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="144" t="s">
-        <v>223</v>
-      </c>
-      <c r="D30" s="140" t="s">
-        <v>224</v>
+      <c r="C30" s="145" t="s">
+        <v>225</v>
+      </c>
+      <c r="D30" s="141" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="B31" s="143" t="s">
+      <c r="B31" s="144" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="144" t="s">
-        <v>225</v>
-      </c>
-      <c r="D31" s="140" t="s">
-        <v>226</v>
+      <c r="C31" s="145" t="s">
+        <v>227</v>
+      </c>
+      <c r="D31" s="141" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
-      <c r="B32" s="147" t="s">
+      <c r="B32" s="148" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="148" t="s">
-        <v>227</v>
-      </c>
-      <c r="D32" s="140" t="s">
-        <v>228</v>
+      <c r="C32" s="149" t="s">
+        <v>229</v>
+      </c>
+      <c r="D32" s="141" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="B33" s="138" t="s">
+      <c r="B33" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="139" t="s">
-        <v>229</v>
-      </c>
-      <c r="D33" s="140" t="s">
-        <v>230</v>
+      <c r="C33" s="140" t="s">
+        <v>231</v>
+      </c>
+      <c r="D33" s="141" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11066,967 +11084,967 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="149" t="s">
-        <v>231</v>
-      </c>
-      <c r="B1" s="149" t="s">
-        <v>232</v>
-      </c>
-      <c r="C1" s="149" t="s">
+      <c r="A1" s="150" t="s">
+        <v>233</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" s="150" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
     </row>
     <row r="2">
-      <c r="A2" s="150">
+      <c r="A2" s="151">
         <v>46165.0</v>
       </c>
-      <c r="B2" s="149" t="s">
+      <c r="B2" s="150" t="s">
+        <v>235</v>
+      </c>
+      <c r="C2" s="152">
+        <v>10000.0</v>
+      </c>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="151">
+        <v>46166.0</v>
+      </c>
+      <c r="B3" s="150" t="s">
+        <v>236</v>
+      </c>
+      <c r="C3" s="152">
+        <v>19000.0</v>
+      </c>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="151">
+        <v>46168.0</v>
+      </c>
+      <c r="B4" s="150" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" s="153">
+        <v>2500.0</v>
+      </c>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B5" s="150" t="s">
+        <v>238</v>
+      </c>
+      <c r="C5" s="152">
+        <v>29050.0</v>
+      </c>
+      <c r="D5" s="150"/>
+      <c r="E5" s="150"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B6" s="150" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="153">
+        <v>100.0</v>
+      </c>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B7" s="150" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="153">
+        <v>300.0</v>
+      </c>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B8" s="150" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="153">
+        <v>370.0</v>
+      </c>
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B9" s="150" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="153">
+        <v>2494.0</v>
+      </c>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B10" s="150" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="153">
+        <v>5000.0</v>
+      </c>
+      <c r="D10" s="150"/>
+      <c r="E10" s="150"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B11" s="150" t="s">
+        <v>244</v>
+      </c>
+      <c r="C11" s="152">
+        <v>29000.0</v>
+      </c>
+      <c r="D11" s="150" t="s">
+        <v>245</v>
+      </c>
+      <c r="E11" s="153">
+        <v>24000.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B12" s="150" t="s">
+        <v>246</v>
+      </c>
+      <c r="C12" s="153">
+        <v>400.0</v>
+      </c>
+      <c r="D12" s="150" t="s">
+        <v>247</v>
+      </c>
+      <c r="E12" s="152">
+        <v>53000.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="151">
+        <v>46169.0</v>
+      </c>
+      <c r="B13" s="150" t="s">
+        <v>248</v>
+      </c>
+      <c r="C13" s="153">
+        <v>600.0</v>
+      </c>
+      <c r="D13" s="150"/>
+      <c r="E13" s="150"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="151">
+        <v>46170.0</v>
+      </c>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="150" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="150" t="s">
         <v>233</v>
       </c>
-      <c r="C2" s="151">
-        <v>10000.0</v>
-      </c>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="150">
-        <v>46166.0</v>
-      </c>
-      <c r="B3" s="149" t="s">
-        <v>234</v>
-      </c>
-      <c r="C3" s="151">
-        <v>19000.0</v>
-      </c>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="150">
-        <v>46168.0</v>
-      </c>
-      <c r="B4" s="149" t="s">
-        <v>235</v>
-      </c>
-      <c r="C4" s="152">
-        <v>2500.0</v>
-      </c>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B5" s="149" t="s">
-        <v>236</v>
-      </c>
-      <c r="C5" s="151">
-        <v>29050.0</v>
-      </c>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B6" s="149" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="152">
-        <v>100.0</v>
-      </c>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B7" s="149" t="s">
-        <v>238</v>
-      </c>
-      <c r="C7" s="152">
-        <v>300.0</v>
-      </c>
-      <c r="D7" s="149"/>
-      <c r="E7" s="149"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B8" s="149" t="s">
-        <v>239</v>
-      </c>
-      <c r="C8" s="152">
-        <v>370.0</v>
-      </c>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B9" s="149" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="152">
-        <v>2494.0</v>
-      </c>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B10" s="149" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="152">
+      <c r="C22" s="150" t="s">
+        <v>250</v>
+      </c>
+      <c r="D22" s="150" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="150" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B23" s="150" t="s">
+        <v>253</v>
+      </c>
+      <c r="C23" s="150" t="s">
+        <v>254</v>
+      </c>
+      <c r="D23" s="153">
+        <v>3150.0</v>
+      </c>
+      <c r="E23" s="154">
+        <v>46464.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B24" s="150" t="s">
+        <v>253</v>
+      </c>
+      <c r="C24" s="150" t="s">
+        <v>255</v>
+      </c>
+      <c r="D24" s="153">
+        <v>2650.0</v>
+      </c>
+      <c r="E24" s="154">
+        <v>46219.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B25" s="150" t="s">
+        <v>253</v>
+      </c>
+      <c r="C25" s="150" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="153">
+        <v>2600.0</v>
+      </c>
+      <c r="E25" s="154">
+        <v>46828.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B26" s="150" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26" s="150" t="s">
+        <v>257</v>
+      </c>
+      <c r="D26" s="153">
+        <v>2680.0</v>
+      </c>
+      <c r="E26" s="155">
+        <v>46863.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="150" t="s">
+        <v>258</v>
+      </c>
+      <c r="B27" s="150" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" s="150" t="s">
+        <v>260</v>
+      </c>
+      <c r="D27" s="153">
+        <v>5390.0</v>
+      </c>
+      <c r="E27" s="154">
+        <v>46764.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="150" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" s="150" t="s">
+        <v>259</v>
+      </c>
+      <c r="C28" s="150" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="153">
+        <v>3235.0</v>
+      </c>
+      <c r="E28" s="154">
+        <v>46673.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="150" t="s">
+        <v>258</v>
+      </c>
+      <c r="B29" s="150" t="s">
+        <v>259</v>
+      </c>
+      <c r="C29" s="150" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" s="153">
+        <v>1230.0</v>
+      </c>
+      <c r="E29" s="150" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="150" t="s">
+        <v>264</v>
+      </c>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150" t="s">
+        <v>254</v>
+      </c>
+      <c r="D30" s="153">
+        <v>2960.0</v>
+      </c>
+      <c r="E30" s="150"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="150" t="s">
+        <v>264</v>
+      </c>
+      <c r="B31" s="150"/>
+      <c r="C31" s="150" t="s">
+        <v>260</v>
+      </c>
+      <c r="D31" s="153">
+        <v>2960.0</v>
+      </c>
+      <c r="E31" s="150"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="150" t="s">
+        <v>265</v>
+      </c>
+      <c r="B32" s="150" t="s">
+        <v>266</v>
+      </c>
+      <c r="C32" s="150"/>
+      <c r="D32" s="153">
         <v>5000.0</v>
       </c>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B11" s="149" t="s">
-        <v>242</v>
-      </c>
-      <c r="C11" s="151">
-        <v>29000.0</v>
-      </c>
-      <c r="D11" s="149" t="s">
-        <v>243</v>
-      </c>
-      <c r="E11" s="152">
-        <v>24000.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B12" s="149" t="s">
-        <v>244</v>
-      </c>
-      <c r="C12" s="152">
-        <v>400.0</v>
-      </c>
-      <c r="D12" s="149" t="s">
-        <v>245</v>
-      </c>
-      <c r="E12" s="151">
-        <v>53000.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="150">
-        <v>46169.0</v>
-      </c>
-      <c r="B13" s="149" t="s">
-        <v>246</v>
-      </c>
-      <c r="C13" s="152">
-        <v>600.0</v>
-      </c>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="150">
-        <v>46170.0</v>
-      </c>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="149" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="149" t="s">
-        <v>231</v>
-      </c>
-      <c r="C22" s="149" t="s">
-        <v>248</v>
-      </c>
-      <c r="D22" s="149" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="149" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="149" t="s">
-        <v>250</v>
-      </c>
-      <c r="B23" s="149" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>252</v>
-      </c>
-      <c r="D23" s="152">
-        <v>3150.0</v>
-      </c>
-      <c r="E23" s="153">
-        <v>46464.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="149" t="s">
-        <v>250</v>
-      </c>
-      <c r="B24" s="149" t="s">
-        <v>251</v>
-      </c>
-      <c r="C24" s="149" t="s">
-        <v>253</v>
-      </c>
-      <c r="D24" s="152">
-        <v>2650.0</v>
-      </c>
-      <c r="E24" s="153">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="149" t="s">
-        <v>250</v>
-      </c>
-      <c r="B25" s="149" t="s">
-        <v>251</v>
-      </c>
-      <c r="C25" s="149" t="s">
-        <v>254</v>
-      </c>
-      <c r="D25" s="152">
-        <v>2600.0</v>
-      </c>
-      <c r="E25" s="153">
-        <v>46828.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="149" t="s">
-        <v>250</v>
-      </c>
-      <c r="B26" s="149" t="s">
-        <v>251</v>
-      </c>
-      <c r="C26" s="149" t="s">
-        <v>255</v>
-      </c>
-      <c r="D26" s="152">
-        <v>2680.0</v>
-      </c>
-      <c r="E26" s="154">
-        <v>46863.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="B27" s="149" t="s">
-        <v>257</v>
-      </c>
-      <c r="C27" s="149" t="s">
-        <v>258</v>
-      </c>
-      <c r="D27" s="152">
-        <v>5390.0</v>
-      </c>
-      <c r="E27" s="153">
-        <v>46764.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="B28" s="149" t="s">
-        <v>257</v>
-      </c>
-      <c r="C28" s="149" t="s">
-        <v>259</v>
-      </c>
-      <c r="D28" s="152">
-        <v>3235.0</v>
-      </c>
-      <c r="E28" s="153">
-        <v>46673.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="B29" s="149" t="s">
-        <v>257</v>
-      </c>
-      <c r="C29" s="149" t="s">
-        <v>260</v>
-      </c>
-      <c r="D29" s="152">
-        <v>1230.0</v>
-      </c>
-      <c r="E29" s="149" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="149" t="s">
-        <v>262</v>
-      </c>
-      <c r="B30" s="149"/>
-      <c r="C30" s="149" t="s">
-        <v>252</v>
-      </c>
-      <c r="D30" s="152">
-        <v>2960.0</v>
-      </c>
-      <c r="E30" s="149"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="149" t="s">
-        <v>262</v>
-      </c>
-      <c r="B31" s="149"/>
-      <c r="C31" s="149" t="s">
-        <v>258</v>
-      </c>
-      <c r="D31" s="152">
-        <v>2960.0</v>
-      </c>
-      <c r="E31" s="149"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="149" t="s">
-        <v>263</v>
-      </c>
-      <c r="B32" s="149" t="s">
-        <v>264</v>
-      </c>
-      <c r="C32" s="149"/>
-      <c r="D32" s="152">
-        <v>5000.0</v>
-      </c>
-      <c r="E32" s="149" t="s">
-        <v>265</v>
+      <c r="E32" s="150" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="155" t="s">
-        <v>266</v>
-      </c>
-      <c r="B42" s="149"/>
-      <c r="C42" s="149"/>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
+      <c r="A42" s="156" t="s">
+        <v>268</v>
+      </c>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+      <c r="I42" s="150"/>
+      <c r="J42" s="150"/>
     </row>
     <row r="43">
-      <c r="A43" s="149"/>
-      <c r="B43" s="149"/>
-      <c r="C43" s="149"/>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="149"/>
-      <c r="H43" s="149"/>
-      <c r="I43" s="149"/>
-      <c r="J43" s="149"/>
+      <c r="A43" s="150"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="150"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="150"/>
     </row>
     <row r="44">
-      <c r="A44" s="149"/>
-      <c r="B44" s="149"/>
-      <c r="C44" s="149"/>
-      <c r="D44" s="149"/>
-      <c r="E44" s="149"/>
-      <c r="F44" s="149"/>
-      <c r="G44" s="149"/>
-      <c r="H44" s="149"/>
-      <c r="I44" s="149"/>
-      <c r="J44" s="149"/>
+      <c r="A44" s="150"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
+      <c r="D44" s="150"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="150"/>
+      <c r="H44" s="150"/>
+      <c r="I44" s="150"/>
+      <c r="J44" s="150"/>
     </row>
     <row r="45">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="156" t="s">
-        <v>267</v>
-      </c>
-      <c r="C45" s="156" t="s">
-        <v>268</v>
-      </c>
-      <c r="D45" s="156" t="s">
+      <c r="B45" s="157" t="s">
+        <v>269</v>
+      </c>
+      <c r="C45" s="157" t="s">
+        <v>270</v>
+      </c>
+      <c r="D45" s="157" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="156" t="s">
-        <v>269</v>
-      </c>
-      <c r="F45" s="156" t="s">
-        <v>270</v>
-      </c>
-      <c r="G45" s="156" t="s">
+      <c r="E45" s="157" t="s">
         <v>271</v>
       </c>
-      <c r="H45" s="156" t="s">
+      <c r="F45" s="157" t="s">
         <v>272</v>
       </c>
-      <c r="I45" s="156" t="s">
+      <c r="G45" s="157" t="s">
         <v>273</v>
       </c>
-      <c r="J45" s="156" t="s">
+      <c r="H45" s="157" t="s">
         <v>274</v>
       </c>
+      <c r="I45" s="157" t="s">
+        <v>275</v>
+      </c>
+      <c r="J45" s="157" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="157" t="s">
-        <v>275</v>
-      </c>
-      <c r="B46" s="158">
+      <c r="A46" s="158" t="s">
+        <v>277</v>
+      </c>
+      <c r="B46" s="159">
         <v>1000000.0</v>
       </c>
-      <c r="C46" s="159">
+      <c r="C46" s="160">
         <v>0.2</v>
       </c>
-      <c r="D46" s="158">
+      <c r="D46" s="159">
         <f>IF(AND(B46&lt;&gt;"", C46&lt;&gt;"", E46&lt;&gt;""), PMT(C46/12, E46, -B46), "")</f>
         <v>26493.88371</v>
       </c>
-      <c r="E46" s="160">
+      <c r="E46" s="161">
         <v>60.0</v>
       </c>
-      <c r="F46" s="160">
+      <c r="F46" s="161">
         <v>0.0</v>
       </c>
-      <c r="G46" s="160">
+      <c r="G46" s="161">
         <f t="shared" ref="G46:G52" si="1">IF(E46="", "", E46 - F46)</f>
         <v>60</v>
       </c>
-      <c r="H46" s="158">
+      <c r="H46" s="159">
         <f t="shared" ref="H46:H52" si="2">IF(D46="", "", D46 * F46)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="158">
+      <c r="I46" s="159">
         <f t="shared" ref="I46:I52" si="3">IF(G46="", "", IFERROR(PV(C46/12, G46, -D46), ""))</f>
         <v>1000000</v>
       </c>
-      <c r="J46" s="161">
+      <c r="J46" s="162">
         <f t="shared" ref="J46:J52" si="4">IF(AND(D46&lt;&gt;"", E46&lt;&gt;""), (D46 * E46) - B46, "")</f>
         <v>589633.0229</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="162" t="s">
-        <v>276</v>
-      </c>
-      <c r="B47" s="163">
+      <c r="A47" s="163" t="s">
+        <v>278</v>
+      </c>
+      <c r="B47" s="164">
         <v>596000.0</v>
       </c>
-      <c r="C47" s="164">
+      <c r="C47" s="165">
         <v>0.126</v>
       </c>
-      <c r="D47" s="163">
+      <c r="D47" s="164">
         <f>IF(AND(B47&lt;&gt;"", C47&lt;&gt;"", E47&lt;&gt;""), PMT(C47/12, E47, -B47), 11839)</f>
         <v>11838.71102</v>
       </c>
-      <c r="E47" s="165">
+      <c r="E47" s="166">
         <v>72.0</v>
       </c>
-      <c r="F47" s="165">
+      <c r="F47" s="166">
         <v>52.0</v>
       </c>
-      <c r="G47" s="165">
+      <c r="G47" s="166">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="H47" s="163">
+      <c r="H47" s="164">
         <f t="shared" si="2"/>
         <v>615612.9729</v>
       </c>
-      <c r="I47" s="163">
+      <c r="I47" s="164">
         <f t="shared" si="3"/>
         <v>212564.401</v>
       </c>
-      <c r="J47" s="166">
+      <c r="J47" s="167">
         <f t="shared" si="4"/>
         <v>256387.1932</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="157" t="s">
-        <v>277</v>
-      </c>
-      <c r="B48" s="167"/>
-      <c r="C48" s="168"/>
-      <c r="D48" s="158">
+      <c r="A48" s="158" t="s">
+        <v>279</v>
+      </c>
+      <c r="B48" s="168"/>
+      <c r="C48" s="169"/>
+      <c r="D48" s="159">
         <f>IF(AND(B48&lt;&gt;"", C48&lt;&gt;"", E48&lt;&gt;""), PMT(C48/12, E48, -B48), 15250)</f>
         <v>15250</v>
       </c>
-      <c r="E48" s="169"/>
-      <c r="F48" s="160">
+      <c r="E48" s="170"/>
+      <c r="F48" s="161">
         <v>0.0</v>
       </c>
-      <c r="G48" s="169" t="str">
+      <c r="G48" s="170" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="158">
+      <c r="H48" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="167" t="str">
+      <c r="I48" s="168" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J48" s="170" t="str">
+      <c r="J48" s="171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="162" t="s">
+      <c r="A49" s="163" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="163">
+      <c r="B49" s="164">
         <v>97110.0</v>
       </c>
-      <c r="C49" s="171"/>
-      <c r="D49" s="163">
+      <c r="C49" s="172"/>
+      <c r="D49" s="164">
         <f>IF(AND(B49&lt;&gt;"", C49&lt;&gt;"", E49&lt;&gt;""), PMT(C49/12, E49, -B49), 18972)</f>
         <v>18972</v>
       </c>
-      <c r="E49" s="172"/>
-      <c r="F49" s="165">
+      <c r="E49" s="173"/>
+      <c r="F49" s="166">
         <v>0.0</v>
       </c>
-      <c r="G49" s="172" t="str">
+      <c r="G49" s="173" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="163">
+      <c r="H49" s="164">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="173" t="str">
+      <c r="I49" s="174" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J49" s="174" t="str">
+      <c r="J49" s="175" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="157" t="s">
-        <v>278</v>
-      </c>
-      <c r="B50" s="158">
+      <c r="A50" s="158" t="s">
+        <v>280</v>
+      </c>
+      <c r="B50" s="159">
         <v>83419.0</v>
       </c>
-      <c r="C50" s="159">
+      <c r="C50" s="160">
         <v>0.12</v>
       </c>
-      <c r="D50" s="158">
+      <c r="D50" s="159">
         <f t="shared" ref="D50:D51" si="5">IF(AND(B50&lt;&gt;"", C50&lt;&gt;"", E50&lt;&gt;""), PMT(C50/12, E50, -B50), 4627)</f>
         <v>5087.061453</v>
       </c>
-      <c r="E50" s="160">
+      <c r="E50" s="161">
         <v>18.0</v>
       </c>
-      <c r="F50" s="160">
+      <c r="F50" s="161">
         <v>3.0</v>
       </c>
-      <c r="G50" s="160">
+      <c r="G50" s="161">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H50" s="158">
+      <c r="H50" s="159">
         <f t="shared" si="2"/>
         <v>15261.18436</v>
       </c>
-      <c r="I50" s="158">
+      <c r="I50" s="159">
         <f t="shared" si="3"/>
         <v>70532.37421</v>
       </c>
-      <c r="J50" s="161">
+      <c r="J50" s="162">
         <f t="shared" si="4"/>
         <v>8148.106161</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="175" t="s">
-        <v>279</v>
-      </c>
-      <c r="B51" s="176">
+      <c r="A51" s="176" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" s="177">
         <v>149100.0</v>
       </c>
-      <c r="C51" s="177">
+      <c r="C51" s="178">
         <v>0.1</v>
       </c>
-      <c r="D51" s="176">
+      <c r="D51" s="177">
         <f t="shared" si="5"/>
         <v>5637.681256</v>
       </c>
-      <c r="E51" s="178">
+      <c r="E51" s="179">
         <v>30.0</v>
       </c>
-      <c r="F51" s="178">
+      <c r="F51" s="179">
         <v>15.0</v>
       </c>
-      <c r="G51" s="178">
+      <c r="G51" s="179">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H51" s="176">
+      <c r="H51" s="177">
         <f t="shared" si="2"/>
         <v>84565.21884</v>
       </c>
-      <c r="I51" s="176">
+      <c r="I51" s="177">
         <f t="shared" si="3"/>
         <v>79184.0856</v>
       </c>
-      <c r="J51" s="179">
+      <c r="J51" s="180">
         <f t="shared" si="4"/>
         <v>20030.43769</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="157" t="s">
-        <v>280</v>
-      </c>
-      <c r="B52" s="167"/>
-      <c r="C52" s="168"/>
-      <c r="D52" s="158">
+      <c r="A52" s="158" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="168"/>
+      <c r="C52" s="169"/>
+      <c r="D52" s="159">
         <f>IF(AND(B52&lt;&gt;"", C52&lt;&gt;"", E52&lt;&gt;""), PMT(C52/12, E52, -B52), 3850)</f>
         <v>3850</v>
       </c>
-      <c r="E52" s="169"/>
-      <c r="F52" s="160">
+      <c r="E52" s="170"/>
+      <c r="F52" s="161">
         <v>0.0</v>
       </c>
-      <c r="G52" s="169" t="str">
+      <c r="G52" s="170" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H52" s="158">
+      <c r="H52" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="167" t="str">
+      <c r="I52" s="168" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J52" s="170" t="str">
+      <c r="J52" s="171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="180" t="s">
-        <v>231</v>
-      </c>
-      <c r="B61" s="180" t="s">
-        <v>281</v>
-      </c>
-      <c r="C61" s="180" t="s">
+      <c r="A61" s="181" t="s">
+        <v>233</v>
+      </c>
+      <c r="B61" s="181" t="s">
+        <v>283</v>
+      </c>
+      <c r="C61" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="D61" s="180" t="s">
-        <v>282</v>
-      </c>
-      <c r="E61" s="180" t="s">
-        <v>283</v>
-      </c>
-      <c r="F61" s="180" t="s">
+      <c r="D61" s="181" t="s">
         <v>284</v>
       </c>
-      <c r="G61" s="180" t="s">
+      <c r="E61" s="181" t="s">
+        <v>285</v>
+      </c>
+      <c r="F61" s="181" t="s">
+        <v>286</v>
+      </c>
+      <c r="G61" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="H61" s="149"/>
-      <c r="I61" s="180" t="s">
-        <v>285</v>
-      </c>
-      <c r="J61" s="149" t="s">
-        <v>286</v>
+      <c r="H61" s="150"/>
+      <c r="I61" s="181" t="s">
+        <v>287</v>
+      </c>
+      <c r="J61" s="150" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="150">
+      <c r="A62" s="151">
         <v>46143.0</v>
       </c>
-      <c r="B62" s="149" t="s">
-        <v>287</v>
-      </c>
-      <c r="C62" s="181">
+      <c r="B62" s="150" t="s">
+        <v>289</v>
+      </c>
+      <c r="C62" s="182">
         <v>11839.0</v>
       </c>
-      <c r="D62" s="182" t="b">
+      <c r="D62" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="149" t="s">
-        <v>288</v>
-      </c>
-      <c r="F62" s="149" t="s">
-        <v>289</v>
-      </c>
-      <c r="G62" s="181">
+      <c r="E62" s="150" t="s">
+        <v>290</v>
+      </c>
+      <c r="F62" s="150" t="s">
+        <v>291</v>
+      </c>
+      <c r="G62" s="182">
         <v>71000.0</v>
       </c>
-      <c r="H62" s="149"/>
-      <c r="I62" s="180" t="s">
-        <v>290</v>
-      </c>
-      <c r="J62" s="181">
+      <c r="H62" s="150"/>
+      <c r="I62" s="181" t="s">
+        <v>292</v>
+      </c>
+      <c r="J62" s="182">
         <f>SUM(C62:C1000)</f>
         <v>84657</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="150">
+      <c r="A63" s="151">
         <v>46144.0</v>
       </c>
-      <c r="B63" s="149" t="s">
-        <v>291</v>
-      </c>
-      <c r="C63" s="181">
+      <c r="B63" s="150" t="s">
+        <v>293</v>
+      </c>
+      <c r="C63" s="182">
         <v>3850.0</v>
       </c>
-      <c r="D63" s="182" t="b">
+      <c r="D63" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="149" t="s">
-        <v>292</v>
-      </c>
-      <c r="F63" s="149"/>
-      <c r="G63" s="183"/>
-      <c r="H63" s="149"/>
-      <c r="I63" s="180" t="s">
-        <v>272</v>
-      </c>
-      <c r="J63" s="181">
+      <c r="E63" s="150" t="s">
+        <v>294</v>
+      </c>
+      <c r="F63" s="150"/>
+      <c r="G63" s="184"/>
+      <c r="H63" s="150"/>
+      <c r="I63" s="181" t="s">
+        <v>274</v>
+      </c>
+      <c r="J63" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
         <v>50435</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="150">
+      <c r="A64" s="151">
         <v>46145.0</v>
       </c>
-      <c r="B64" s="149" t="s">
-        <v>293</v>
-      </c>
-      <c r="C64" s="181">
+      <c r="B64" s="150" t="s">
+        <v>295</v>
+      </c>
+      <c r="C64" s="182">
         <v>4627.0</v>
       </c>
-      <c r="D64" s="182" t="b">
+      <c r="D64" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="149"/>
-      <c r="F64" s="149"/>
-      <c r="G64" s="183"/>
-      <c r="H64" s="149"/>
-      <c r="I64" s="180" t="s">
-        <v>294</v>
-      </c>
-      <c r="J64" s="181">
+      <c r="E64" s="150"/>
+      <c r="F64" s="150"/>
+      <c r="G64" s="184"/>
+      <c r="H64" s="150"/>
+      <c r="I64" s="181" t="s">
+        <v>296</v>
+      </c>
+      <c r="J64" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
         <v>34222</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="150">
+      <c r="A65" s="151">
         <v>46147.0</v>
       </c>
-      <c r="B65" s="149" t="s">
-        <v>295</v>
-      </c>
-      <c r="C65" s="181">
+      <c r="B65" s="150" t="s">
+        <v>297</v>
+      </c>
+      <c r="C65" s="182">
         <v>5000.0</v>
       </c>
-      <c r="D65" s="182" t="b">
+      <c r="D65" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="149"/>
-      <c r="F65" s="149"/>
-      <c r="G65" s="183"/>
-      <c r="H65" s="149"/>
-      <c r="I65" s="180" t="s">
-        <v>296</v>
-      </c>
-      <c r="J65" s="181">
+      <c r="E65" s="150"/>
+      <c r="F65" s="150"/>
+      <c r="G65" s="184"/>
+      <c r="H65" s="150"/>
+      <c r="I65" s="181" t="s">
+        <v>298</v>
+      </c>
+      <c r="J65" s="182">
         <f>SUM(G62:G1000)</f>
         <v>71000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="150">
+      <c r="A66" s="151">
         <v>46167.0</v>
       </c>
-      <c r="B66" s="149" t="s">
-        <v>297</v>
-      </c>
-      <c r="C66" s="181">
+      <c r="B66" s="150" t="s">
+        <v>299</v>
+      </c>
+      <c r="C66" s="182">
         <v>18972.0</v>
       </c>
-      <c r="D66" s="182" t="b">
+      <c r="D66" s="183" t="b">
         <v>0</v>
       </c>
-      <c r="E66" s="184">
+      <c r="E66" s="185">
         <v>97110.0</v>
       </c>
-      <c r="F66" s="149"/>
-      <c r="G66" s="183"/>
-      <c r="H66" s="149"/>
-      <c r="I66" s="180" t="s">
-        <v>298</v>
-      </c>
-      <c r="J66" s="181">
+      <c r="F66" s="150"/>
+      <c r="G66" s="184"/>
+      <c r="H66" s="150"/>
+      <c r="I66" s="181" t="s">
+        <v>300</v>
+      </c>
+      <c r="J66" s="182">
         <f>J65-J62</f>
         <v>-13657</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="150">
+      <c r="A67" s="151">
         <v>46146.0</v>
       </c>
-      <c r="B67" s="149" t="s">
-        <v>299</v>
-      </c>
-      <c r="C67" s="181">
+      <c r="B67" s="150" t="s">
+        <v>301</v>
+      </c>
+      <c r="C67" s="182">
         <v>13625.0</v>
       </c>
-      <c r="D67" s="182" t="b">
+      <c r="D67" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="149" t="s">
-        <v>300</v>
-      </c>
-      <c r="F67" s="149"/>
-      <c r="G67" s="183"/>
-      <c r="H67" s="149"/>
-      <c r="I67" s="149"/>
-      <c r="J67" s="149"/>
+      <c r="E67" s="150" t="s">
+        <v>302</v>
+      </c>
+      <c r="F67" s="150"/>
+      <c r="G67" s="184"/>
+      <c r="H67" s="150"/>
+      <c r="I67" s="150"/>
+      <c r="J67" s="150"/>
     </row>
     <row r="68">
-      <c r="A68" s="150">
+      <c r="A68" s="151">
         <v>46145.0</v>
       </c>
-      <c r="B68" s="149" t="s">
-        <v>301</v>
-      </c>
-      <c r="C68" s="181">
+      <c r="B68" s="150" t="s">
+        <v>303</v>
+      </c>
+      <c r="C68" s="182">
         <v>2494.0</v>
       </c>
-      <c r="D68" s="182" t="b">
+      <c r="D68" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="149"/>
-      <c r="F68" s="149"/>
-      <c r="G68" s="183"/>
-      <c r="H68" s="149"/>
-      <c r="I68" s="149"/>
-      <c r="J68" s="149"/>
+      <c r="E68" s="150"/>
+      <c r="F68" s="150"/>
+      <c r="G68" s="184"/>
+      <c r="H68" s="150"/>
+      <c r="I68" s="150"/>
+      <c r="J68" s="150"/>
     </row>
     <row r="69">
-      <c r="A69" s="150">
+      <c r="A69" s="151">
         <v>46144.0</v>
       </c>
-      <c r="B69" s="149" t="s">
-        <v>302</v>
-      </c>
-      <c r="C69" s="181">
+      <c r="B69" s="150" t="s">
+        <v>304</v>
+      </c>
+      <c r="C69" s="182">
         <v>4500.0</v>
       </c>
-      <c r="D69" s="182" t="b">
+      <c r="D69" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E69" s="149"/>
-      <c r="F69" s="149"/>
-      <c r="G69" s="183"/>
-      <c r="H69" s="149"/>
-      <c r="I69" s="149"/>
-      <c r="J69" s="149"/>
+      <c r="E69" s="150"/>
+      <c r="F69" s="150"/>
+      <c r="G69" s="184"/>
+      <c r="H69" s="150"/>
+      <c r="I69" s="150"/>
+      <c r="J69" s="150"/>
     </row>
     <row r="70">
-      <c r="A70" s="150">
+      <c r="A70" s="151">
         <v>46152.0</v>
       </c>
-      <c r="B70" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C70" s="181">
+      <c r="B70" s="150" t="s">
+        <v>305</v>
+      </c>
+      <c r="C70" s="182">
         <v>1500.0</v>
       </c>
-      <c r="D70" s="182" t="b">
+      <c r="D70" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="149"/>
-      <c r="F70" s="149"/>
-      <c r="G70" s="183"/>
-      <c r="H70" s="149"/>
-      <c r="I70" s="149"/>
-      <c r="J70" s="149"/>
+      <c r="E70" s="150"/>
+      <c r="F70" s="150"/>
+      <c r="G70" s="184"/>
+      <c r="H70" s="150"/>
+      <c r="I70" s="150"/>
+      <c r="J70" s="150"/>
     </row>
     <row r="71">
-      <c r="A71" s="150">
+      <c r="A71" s="151">
         <v>46152.0</v>
       </c>
-      <c r="B71" s="149" t="s">
-        <v>304</v>
-      </c>
-      <c r="C71" s="181">
+      <c r="B71" s="150" t="s">
+        <v>306</v>
+      </c>
+      <c r="C71" s="182">
         <v>3000.0</v>
       </c>
-      <c r="D71" s="182" t="b">
+      <c r="D71" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E71" s="149"/>
-      <c r="F71" s="149"/>
-      <c r="G71" s="183"/>
-      <c r="H71" s="149"/>
-      <c r="I71" s="149"/>
-      <c r="J71" s="149"/>
+      <c r="E71" s="150"/>
+      <c r="F71" s="150"/>
+      <c r="G71" s="184"/>
+      <c r="H71" s="150"/>
+      <c r="I71" s="150"/>
+      <c r="J71" s="150"/>
     </row>
     <row r="72">
-      <c r="A72" s="150">
+      <c r="A72" s="151">
         <v>46157.0</v>
       </c>
-      <c r="B72" s="149" t="s">
-        <v>305</v>
-      </c>
-      <c r="C72" s="181">
+      <c r="B72" s="150" t="s">
+        <v>307</v>
+      </c>
+      <c r="C72" s="182">
         <v>15250.0</v>
       </c>
-      <c r="D72" s="182" t="b">
+      <c r="D72" s="183" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="149"/>
-      <c r="F72" s="149"/>
-      <c r="G72" s="183"/>
-      <c r="H72" s="149"/>
-      <c r="I72" s="149"/>
-      <c r="J72" s="149"/>
+      <c r="E72" s="150"/>
+      <c r="F72" s="150"/>
+      <c r="G72" s="184"/>
+      <c r="H72" s="150"/>
+      <c r="I72" s="150"/>
+      <c r="J72" s="150"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="311">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -460,6 +460,15 @@
   </si>
   <si>
     <t>From Raghuls 6250                           2 June</t>
+  </si>
+  <si>
+    <t>Naresh shoe &amp; cable - June 7</t>
+  </si>
+  <si>
+    <t>Internet</t>
+  </si>
+  <si>
+    <t>WIFI BILL - June 8</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -952,18 +961,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0;\(&quot;₹&quot;#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="₹#,##0"/>
     <numFmt numFmtId="167" formatCode="mmm yyyy"/>
     <numFmt numFmtId="168" formatCode="₹#,##0.00"/>
     <numFmt numFmtId="169" formatCode="d mmmm"/>
-    <numFmt numFmtId="170" formatCode="mmmm yyyy"/>
-    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="173" formatCode="d mmm yyyy"/>
-    <numFmt numFmtId="174" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="172" formatCode="d mmm yyyy"/>
+    <numFmt numFmtId="173" formatCode="d mmmm yyyy"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1338,7 +1346,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="185">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1646,9 +1654,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="168" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1666,13 +1671,13 @@
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1760,19 +1765,19 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="174" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -4001,11 +4006,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>49293</v>
+        <v>29893</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-32629</v>
+        <v>-13229</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -7989,13 +7994,13 @@
         <v>139</v>
       </c>
       <c r="C11" s="102">
-        <v>24000.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D11" s="108"/>
     </row>
     <row r="12">
-      <c r="A12" s="109">
-        <v>46174.0</v>
+      <c r="A12" s="100">
+        <v>46182.0</v>
       </c>
       <c r="B12" s="101" t="s">
         <v>144</v>
@@ -8008,531 +8013,547 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="108"/>
-      <c r="B13" s="108"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="108"/>
+      <c r="A13" s="100">
+        <v>46183.0</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>3</v>
+      </c>
+      <c r="C13" s="102">
+        <v>2000.0</v>
+      </c>
+      <c r="D13" s="101" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="108"/>
-      <c r="B14" s="108"/>
-      <c r="C14" s="110"/>
-      <c r="D14" s="108"/>
+      <c r="A14" s="100">
+        <v>46184.0</v>
+      </c>
+      <c r="B14" s="101" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" s="102">
+        <v>600.0</v>
+      </c>
+      <c r="D14" s="101" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="108"/>
       <c r="B15" s="108"/>
-      <c r="C15" s="110"/>
+      <c r="C15" s="109"/>
       <c r="D15" s="108"/>
     </row>
     <row r="16">
       <c r="A16" s="108"/>
       <c r="B16" s="108"/>
-      <c r="C16" s="110"/>
+      <c r="C16" s="109"/>
       <c r="D16" s="108"/>
     </row>
     <row r="17">
       <c r="A17" s="108"/>
       <c r="B17" s="108"/>
-      <c r="C17" s="110"/>
+      <c r="C17" s="109"/>
       <c r="D17" s="108"/>
     </row>
     <row r="18">
       <c r="A18" s="108"/>
       <c r="B18" s="108"/>
-      <c r="C18" s="110"/>
+      <c r="C18" s="109"/>
       <c r="D18" s="108"/>
     </row>
     <row r="19">
       <c r="A19" s="108"/>
       <c r="B19" s="108"/>
-      <c r="C19" s="110"/>
+      <c r="C19" s="109"/>
       <c r="D19" s="108"/>
     </row>
     <row r="20">
       <c r="A20" s="108"/>
       <c r="B20" s="108"/>
-      <c r="C20" s="110"/>
+      <c r="C20" s="109"/>
       <c r="D20" s="108"/>
     </row>
     <row r="21">
       <c r="A21" s="108"/>
       <c r="B21" s="108"/>
-      <c r="C21" s="110"/>
+      <c r="C21" s="109"/>
       <c r="D21" s="108"/>
     </row>
     <row r="22">
       <c r="A22" s="108"/>
       <c r="B22" s="108"/>
-      <c r="C22" s="110"/>
+      <c r="C22" s="109"/>
       <c r="D22" s="108"/>
     </row>
     <row r="23">
       <c r="A23" s="108"/>
       <c r="B23" s="108"/>
-      <c r="C23" s="110"/>
+      <c r="C23" s="109"/>
       <c r="D23" s="108"/>
     </row>
     <row r="24">
       <c r="A24" s="108"/>
       <c r="B24" s="108"/>
-      <c r="C24" s="110"/>
+      <c r="C24" s="109"/>
       <c r="D24" s="108"/>
     </row>
     <row r="25">
       <c r="A25" s="108"/>
       <c r="B25" s="108"/>
-      <c r="C25" s="110"/>
+      <c r="C25" s="109"/>
       <c r="D25" s="108"/>
     </row>
     <row r="26">
       <c r="A26" s="108"/>
       <c r="B26" s="108"/>
-      <c r="C26" s="110"/>
+      <c r="C26" s="109"/>
       <c r="D26" s="108"/>
     </row>
     <row r="27">
       <c r="A27" s="108"/>
       <c r="B27" s="108"/>
-      <c r="C27" s="110"/>
+      <c r="C27" s="109"/>
       <c r="D27" s="108"/>
     </row>
     <row r="28">
       <c r="A28" s="108"/>
       <c r="B28" s="108"/>
-      <c r="C28" s="110"/>
+      <c r="C28" s="109"/>
       <c r="D28" s="108"/>
     </row>
     <row r="29">
       <c r="A29" s="108"/>
       <c r="B29" s="108"/>
-      <c r="C29" s="110"/>
+      <c r="C29" s="109"/>
       <c r="D29" s="108"/>
     </row>
     <row r="30">
       <c r="A30" s="108"/>
       <c r="B30" s="108"/>
-      <c r="C30" s="110"/>
+      <c r="C30" s="109"/>
       <c r="D30" s="108"/>
     </row>
     <row r="31">
       <c r="A31" s="108"/>
       <c r="B31" s="108"/>
-      <c r="C31" s="110"/>
+      <c r="C31" s="109"/>
       <c r="D31" s="108"/>
     </row>
     <row r="32">
       <c r="A32" s="108"/>
       <c r="B32" s="108"/>
-      <c r="C32" s="110"/>
+      <c r="C32" s="109"/>
       <c r="D32" s="108"/>
     </row>
     <row r="33">
       <c r="A33" s="108"/>
       <c r="B33" s="108"/>
-      <c r="C33" s="110"/>
+      <c r="C33" s="109"/>
       <c r="D33" s="108"/>
     </row>
     <row r="34">
       <c r="A34" s="108"/>
       <c r="B34" s="108"/>
-      <c r="C34" s="110"/>
+      <c r="C34" s="109"/>
       <c r="D34" s="108"/>
     </row>
     <row r="35">
       <c r="A35" s="108"/>
       <c r="B35" s="108"/>
-      <c r="C35" s="110"/>
+      <c r="C35" s="109"/>
       <c r="D35" s="108"/>
     </row>
     <row r="36">
       <c r="A36" s="108"/>
       <c r="B36" s="108"/>
-      <c r="C36" s="110"/>
+      <c r="C36" s="109"/>
       <c r="D36" s="108"/>
     </row>
     <row r="37">
       <c r="A37" s="108"/>
       <c r="B37" s="108"/>
-      <c r="C37" s="110"/>
+      <c r="C37" s="109"/>
       <c r="D37" s="108"/>
     </row>
     <row r="38">
       <c r="A38" s="108"/>
       <c r="B38" s="108"/>
-      <c r="C38" s="110"/>
+      <c r="C38" s="109"/>
       <c r="D38" s="108"/>
     </row>
     <row r="39">
       <c r="A39" s="108"/>
       <c r="B39" s="108"/>
-      <c r="C39" s="110"/>
+      <c r="C39" s="109"/>
       <c r="D39" s="108"/>
     </row>
     <row r="40">
       <c r="A40" s="108"/>
       <c r="B40" s="108"/>
-      <c r="C40" s="110"/>
+      <c r="C40" s="109"/>
       <c r="D40" s="108"/>
     </row>
     <row r="41">
       <c r="A41" s="108"/>
       <c r="B41" s="108"/>
-      <c r="C41" s="110"/>
+      <c r="C41" s="109"/>
       <c r="D41" s="108"/>
     </row>
     <row r="42">
       <c r="A42" s="108"/>
       <c r="B42" s="108"/>
-      <c r="C42" s="110"/>
+      <c r="C42" s="109"/>
       <c r="D42" s="108"/>
     </row>
     <row r="43">
       <c r="A43" s="108"/>
       <c r="B43" s="108"/>
-      <c r="C43" s="110"/>
+      <c r="C43" s="109"/>
       <c r="D43" s="108"/>
     </row>
     <row r="44">
       <c r="A44" s="108"/>
       <c r="B44" s="108"/>
-      <c r="C44" s="110"/>
+      <c r="C44" s="109"/>
       <c r="D44" s="108"/>
     </row>
     <row r="45">
       <c r="A45" s="108"/>
       <c r="B45" s="108"/>
-      <c r="C45" s="110"/>
+      <c r="C45" s="109"/>
       <c r="D45" s="108"/>
     </row>
     <row r="46">
       <c r="A46" s="108"/>
       <c r="B46" s="108"/>
-      <c r="C46" s="110"/>
+      <c r="C46" s="109"/>
       <c r="D46" s="108"/>
     </row>
     <row r="47">
       <c r="A47" s="108"/>
       <c r="B47" s="108"/>
-      <c r="C47" s="110"/>
+      <c r="C47" s="109"/>
       <c r="D47" s="108"/>
     </row>
     <row r="48">
       <c r="A48" s="108"/>
       <c r="B48" s="108"/>
-      <c r="C48" s="110"/>
+      <c r="C48" s="109"/>
       <c r="D48" s="108"/>
     </row>
     <row r="49">
       <c r="A49" s="108"/>
       <c r="B49" s="108"/>
-      <c r="C49" s="110"/>
+      <c r="C49" s="109"/>
       <c r="D49" s="108"/>
     </row>
     <row r="50">
       <c r="A50" s="108"/>
       <c r="B50" s="108"/>
-      <c r="C50" s="110"/>
+      <c r="C50" s="109"/>
       <c r="D50" s="108"/>
     </row>
     <row r="51">
       <c r="A51" s="108"/>
       <c r="B51" s="108"/>
-      <c r="C51" s="110"/>
+      <c r="C51" s="109"/>
       <c r="D51" s="108"/>
     </row>
     <row r="52">
       <c r="A52" s="108"/>
       <c r="B52" s="108"/>
-      <c r="C52" s="110"/>
+      <c r="C52" s="109"/>
       <c r="D52" s="108"/>
     </row>
     <row r="53">
       <c r="A53" s="108"/>
       <c r="B53" s="108"/>
-      <c r="C53" s="110"/>
+      <c r="C53" s="109"/>
       <c r="D53" s="108"/>
     </row>
     <row r="54">
       <c r="A54" s="108"/>
       <c r="B54" s="108"/>
-      <c r="C54" s="110"/>
+      <c r="C54" s="109"/>
       <c r="D54" s="108"/>
     </row>
     <row r="55">
       <c r="A55" s="108"/>
       <c r="B55" s="108"/>
-      <c r="C55" s="110"/>
+      <c r="C55" s="109"/>
       <c r="D55" s="108"/>
     </row>
     <row r="56">
       <c r="A56" s="108"/>
       <c r="B56" s="108"/>
-      <c r="C56" s="110"/>
+      <c r="C56" s="109"/>
       <c r="D56" s="108"/>
     </row>
     <row r="57">
       <c r="A57" s="108"/>
       <c r="B57" s="108"/>
-      <c r="C57" s="110"/>
+      <c r="C57" s="109"/>
       <c r="D57" s="108"/>
     </row>
     <row r="58">
       <c r="A58" s="108"/>
       <c r="B58" s="108"/>
-      <c r="C58" s="110"/>
+      <c r="C58" s="109"/>
       <c r="D58" s="108"/>
     </row>
     <row r="59">
       <c r="A59" s="108"/>
       <c r="B59" s="108"/>
-      <c r="C59" s="110"/>
+      <c r="C59" s="109"/>
       <c r="D59" s="108"/>
     </row>
     <row r="60">
       <c r="A60" s="108"/>
       <c r="B60" s="108"/>
-      <c r="C60" s="110"/>
+      <c r="C60" s="109"/>
       <c r="D60" s="108"/>
     </row>
     <row r="61">
       <c r="A61" s="108"/>
       <c r="B61" s="108"/>
-      <c r="C61" s="110"/>
+      <c r="C61" s="109"/>
       <c r="D61" s="108"/>
     </row>
     <row r="62">
       <c r="A62" s="108"/>
       <c r="B62" s="108"/>
-      <c r="C62" s="110"/>
+      <c r="C62" s="109"/>
       <c r="D62" s="108"/>
     </row>
     <row r="63">
       <c r="A63" s="108"/>
       <c r="B63" s="108"/>
-      <c r="C63" s="110"/>
+      <c r="C63" s="109"/>
       <c r="D63" s="108"/>
     </row>
     <row r="64">
       <c r="A64" s="108"/>
       <c r="B64" s="108"/>
-      <c r="C64" s="110"/>
+      <c r="C64" s="109"/>
       <c r="D64" s="108"/>
     </row>
     <row r="65">
       <c r="A65" s="108"/>
       <c r="B65" s="108"/>
-      <c r="C65" s="110"/>
+      <c r="C65" s="109"/>
       <c r="D65" s="108"/>
     </row>
     <row r="66">
       <c r="A66" s="108"/>
       <c r="B66" s="108"/>
-      <c r="C66" s="110"/>
+      <c r="C66" s="109"/>
       <c r="D66" s="108"/>
     </row>
     <row r="67">
       <c r="A67" s="108"/>
       <c r="B67" s="108"/>
-      <c r="C67" s="110"/>
+      <c r="C67" s="109"/>
       <c r="D67" s="108"/>
     </row>
     <row r="68">
       <c r="A68" s="108"/>
       <c r="B68" s="108"/>
-      <c r="C68" s="110"/>
+      <c r="C68" s="109"/>
       <c r="D68" s="108"/>
     </row>
     <row r="69">
       <c r="A69" s="108"/>
       <c r="B69" s="108"/>
-      <c r="C69" s="110"/>
+      <c r="C69" s="109"/>
       <c r="D69" s="108"/>
     </row>
     <row r="70">
       <c r="A70" s="108"/>
       <c r="B70" s="108"/>
-      <c r="C70" s="110"/>
+      <c r="C70" s="109"/>
       <c r="D70" s="108"/>
     </row>
     <row r="71">
       <c r="A71" s="108"/>
       <c r="B71" s="108"/>
-      <c r="C71" s="110"/>
+      <c r="C71" s="109"/>
       <c r="D71" s="108"/>
     </row>
     <row r="72">
       <c r="A72" s="108"/>
       <c r="B72" s="108"/>
-      <c r="C72" s="110"/>
+      <c r="C72" s="109"/>
       <c r="D72" s="108"/>
     </row>
     <row r="73">
       <c r="A73" s="108"/>
       <c r="B73" s="108"/>
-      <c r="C73" s="110"/>
+      <c r="C73" s="109"/>
       <c r="D73" s="108"/>
     </row>
     <row r="74">
       <c r="A74" s="108"/>
       <c r="B74" s="108"/>
-      <c r="C74" s="110"/>
+      <c r="C74" s="109"/>
       <c r="D74" s="108"/>
     </row>
     <row r="75">
       <c r="A75" s="108"/>
       <c r="B75" s="108"/>
-      <c r="C75" s="110"/>
+      <c r="C75" s="109"/>
       <c r="D75" s="108"/>
     </row>
     <row r="76">
       <c r="A76" s="108"/>
       <c r="B76" s="108"/>
-      <c r="C76" s="110"/>
+      <c r="C76" s="109"/>
       <c r="D76" s="108"/>
     </row>
     <row r="77">
       <c r="A77" s="108"/>
       <c r="B77" s="108"/>
-      <c r="C77" s="110"/>
+      <c r="C77" s="109"/>
       <c r="D77" s="108"/>
     </row>
     <row r="78">
       <c r="A78" s="108"/>
       <c r="B78" s="108"/>
-      <c r="C78" s="110"/>
+      <c r="C78" s="109"/>
       <c r="D78" s="108"/>
     </row>
     <row r="79">
       <c r="A79" s="108"/>
       <c r="B79" s="108"/>
-      <c r="C79" s="110"/>
+      <c r="C79" s="109"/>
       <c r="D79" s="108"/>
     </row>
     <row r="80">
       <c r="A80" s="108"/>
       <c r="B80" s="108"/>
-      <c r="C80" s="110"/>
+      <c r="C80" s="109"/>
       <c r="D80" s="108"/>
     </row>
     <row r="81">
       <c r="A81" s="108"/>
       <c r="B81" s="108"/>
-      <c r="C81" s="110"/>
+      <c r="C81" s="109"/>
       <c r="D81" s="108"/>
     </row>
     <row r="82">
       <c r="A82" s="108"/>
       <c r="B82" s="108"/>
-      <c r="C82" s="110"/>
+      <c r="C82" s="109"/>
       <c r="D82" s="108"/>
     </row>
     <row r="83">
       <c r="A83" s="108"/>
       <c r="B83" s="108"/>
-      <c r="C83" s="110"/>
+      <c r="C83" s="109"/>
       <c r="D83" s="108"/>
     </row>
     <row r="84">
       <c r="A84" s="108"/>
       <c r="B84" s="108"/>
-      <c r="C84" s="110"/>
+      <c r="C84" s="109"/>
       <c r="D84" s="108"/>
     </row>
     <row r="85">
       <c r="A85" s="108"/>
       <c r="B85" s="108"/>
-      <c r="C85" s="110"/>
+      <c r="C85" s="109"/>
       <c r="D85" s="108"/>
     </row>
     <row r="86">
       <c r="A86" s="108"/>
       <c r="B86" s="108"/>
-      <c r="C86" s="110"/>
+      <c r="C86" s="109"/>
       <c r="D86" s="108"/>
     </row>
     <row r="87">
       <c r="A87" s="108"/>
       <c r="B87" s="108"/>
-      <c r="C87" s="110"/>
+      <c r="C87" s="109"/>
       <c r="D87" s="108"/>
     </row>
     <row r="88">
       <c r="A88" s="108"/>
       <c r="B88" s="108"/>
-      <c r="C88" s="110"/>
+      <c r="C88" s="109"/>
       <c r="D88" s="108"/>
     </row>
     <row r="89">
       <c r="A89" s="108"/>
       <c r="B89" s="108"/>
-      <c r="C89" s="110"/>
+      <c r="C89" s="109"/>
       <c r="D89" s="108"/>
     </row>
     <row r="90">
       <c r="A90" s="108"/>
       <c r="B90" s="108"/>
-      <c r="C90" s="110"/>
+      <c r="C90" s="109"/>
       <c r="D90" s="108"/>
     </row>
     <row r="91">
       <c r="A91" s="108"/>
       <c r="B91" s="108"/>
-      <c r="C91" s="110"/>
+      <c r="C91" s="109"/>
       <c r="D91" s="108"/>
     </row>
     <row r="92">
       <c r="A92" s="108"/>
       <c r="B92" s="108"/>
-      <c r="C92" s="110"/>
+      <c r="C92" s="109"/>
       <c r="D92" s="108"/>
     </row>
     <row r="93">
       <c r="A93" s="108"/>
       <c r="B93" s="108"/>
-      <c r="C93" s="110"/>
+      <c r="C93" s="109"/>
       <c r="D93" s="108"/>
     </row>
     <row r="94">
       <c r="A94" s="108"/>
       <c r="B94" s="108"/>
-      <c r="C94" s="110"/>
+      <c r="C94" s="109"/>
       <c r="D94" s="108"/>
     </row>
     <row r="95">
       <c r="A95" s="108"/>
       <c r="B95" s="108"/>
-      <c r="C95" s="110"/>
+      <c r="C95" s="109"/>
       <c r="D95" s="108"/>
     </row>
     <row r="96">
       <c r="A96" s="108"/>
       <c r="B96" s="108"/>
-      <c r="C96" s="110"/>
+      <c r="C96" s="109"/>
       <c r="D96" s="108"/>
     </row>
     <row r="97">
       <c r="A97" s="108"/>
       <c r="B97" s="108"/>
-      <c r="C97" s="110"/>
+      <c r="C97" s="109"/>
       <c r="D97" s="108"/>
     </row>
     <row r="98">
       <c r="A98" s="108"/>
       <c r="B98" s="108"/>
-      <c r="C98" s="110"/>
+      <c r="C98" s="109"/>
       <c r="D98" s="108"/>
     </row>
     <row r="99">
       <c r="A99" s="108"/>
       <c r="B99" s="108"/>
-      <c r="C99" s="110"/>
+      <c r="C99" s="109"/>
       <c r="D99" s="108"/>
     </row>
     <row r="100">
       <c r="A100" s="108"/>
       <c r="B100" s="108"/>
-      <c r="C100" s="110"/>
+      <c r="C100" s="109"/>
       <c r="D100" s="108"/>
     </row>
   </sheetData>
@@ -8559,50 +8580,50 @@
   <sheetData>
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
-      <c r="B2" s="111" t="s">
-        <v>146</v>
+      <c r="B2" s="110" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="112" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="112" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="112" t="s">
-        <v>149</v>
-      </c>
-      <c r="E4" s="112" t="s">
+      <c r="B4" s="111" t="s">
         <v>150</v>
       </c>
-      <c r="F4" s="112" t="s">
+      <c r="C4" s="111" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="112" t="s">
+      <c r="D4" s="111" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="113" t="s">
+      <c r="E4" s="111" t="s">
         <v>153</v>
       </c>
+      <c r="F4" s="111" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="111" t="s">
+        <v>155</v>
+      </c>
+      <c r="H4" s="112" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="114">
+      <c r="B5" s="113">
         <v>55.8</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5" s="114">
         <v>0.11</v>
       </c>
-      <c r="D5" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5" s="114" t="s">
-        <v>155</v>
-      </c>
-      <c r="F5" s="116">
+      <c r="D5" s="113" t="s">
+        <v>157</v>
+      </c>
+      <c r="E5" s="113" t="s">
+        <v>158</v>
+      </c>
+      <c r="F5" s="115">
         <v>391560.0</v>
       </c>
-      <c r="G5" s="117">
+      <c r="G5" s="116">
         <v>46010.0</v>
       </c>
       <c r="H5" s="10">
@@ -8611,22 +8632,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="114">
+      <c r="B6" s="113">
         <v>30.0</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6" s="114">
         <v>0.1</v>
       </c>
-      <c r="D6" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="E6" s="114" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" s="116">
+      <c r="D6" s="113" t="s">
+        <v>157</v>
+      </c>
+      <c r="E6" s="113" t="s">
+        <v>159</v>
+      </c>
+      <c r="F6" s="115">
         <v>229500.0</v>
       </c>
-      <c r="G6" s="117">
+      <c r="G6" s="116">
         <v>45966.0</v>
       </c>
       <c r="H6" s="10">
@@ -8635,22 +8656,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="114">
+      <c r="B7" s="113">
         <v>36.9</v>
       </c>
-      <c r="C7" s="115">
+      <c r="C7" s="114">
         <v>0.105</v>
       </c>
-      <c r="D7" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="E7" s="114" t="s">
+      <c r="D7" s="113" t="s">
         <v>157</v>
       </c>
-      <c r="F7" s="116">
+      <c r="E7" s="113" t="s">
+        <v>160</v>
+      </c>
+      <c r="F7" s="115">
         <v>300000.0</v>
       </c>
-      <c r="G7" s="117">
+      <c r="G7" s="116">
         <v>46169.0</v>
       </c>
       <c r="H7" s="10">
@@ -8659,20 +8680,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="114">
+      <c r="B8" s="113">
         <v>15.0</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="E8" s="114" t="s">
+      <c r="C8" s="117"/>
+      <c r="D8" s="113" t="s">
         <v>157</v>
       </c>
-      <c r="F8" s="116">
+      <c r="E8" s="113" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="115">
         <v>135000.0</v>
       </c>
-      <c r="G8" s="117">
+      <c r="G8" s="116">
         <v>46178.0</v>
       </c>
       <c r="H8" s="10">
@@ -8681,18 +8702,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="119"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="114" t="s">
-        <v>154</v>
-      </c>
-      <c r="E9" s="114" t="s">
-        <v>158</v>
-      </c>
-      <c r="F9" s="116">
+      <c r="B9" s="118"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="113" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="113" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="115">
         <v>297698.0</v>
       </c>
-      <c r="G9" s="117">
+      <c r="G9" s="116">
         <v>46035.0</v>
       </c>
       <c r="H9" s="10">
@@ -8701,1044 +8722,1044 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="119"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
       <c r="H10" s="10" t="str">
         <f t="shared" ref="H10:H96" si="2">IF(OR(ISBLANK(F10), ISBLANK(G10)), "", F10 * (C10/100) * (TODAY() - G10) / 365)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="119"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="121"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="120"/>
       <c r="H11" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="119"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="121"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="120"/>
       <c r="H12" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="119"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="121"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="120"/>
       <c r="H13" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="119"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="121"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="120"/>
       <c r="H14" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="119"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="121"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="120"/>
       <c r="H15" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="119"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="121"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="120"/>
       <c r="H16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="119"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="121"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="120"/>
       <c r="H17" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="119"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="120"/>
       <c r="H18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="119"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="121"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="120"/>
       <c r="H19" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="119"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="121"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="120"/>
       <c r="H20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="119"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="121"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="120"/>
       <c r="H21" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="119"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="121"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="120"/>
       <c r="H22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="119"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="121"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="120"/>
       <c r="H23" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="119"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="121"/>
+      <c r="B24" s="118"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="120"/>
       <c r="H24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="119"/>
-      <c r="C25" s="118"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="121"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="120"/>
       <c r="H25" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="119"/>
-      <c r="C26" s="118"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="121"/>
+      <c r="B26" s="118"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="120"/>
       <c r="H26" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="119"/>
-      <c r="C27" s="118"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="121"/>
+      <c r="B27" s="118"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="120"/>
       <c r="H27" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="119"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="121"/>
+      <c r="B28" s="118"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="120"/>
       <c r="H28" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="119"/>
-      <c r="C29" s="118"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="121"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="120"/>
       <c r="H29" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="119"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="121"/>
+      <c r="B30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="120"/>
       <c r="H30" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="119"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="121"/>
+      <c r="B31" s="118"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="120"/>
       <c r="H31" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="119"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="121"/>
+      <c r="B32" s="118"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="120"/>
       <c r="H32" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="119"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="121"/>
+      <c r="B33" s="118"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="120"/>
       <c r="H33" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="119"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="121"/>
+      <c r="B34" s="118"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="119"/>
+      <c r="G34" s="120"/>
       <c r="H34" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="119"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="121"/>
+      <c r="B35" s="118"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="120"/>
       <c r="H35" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="119"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="121"/>
+      <c r="B36" s="118"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="120"/>
       <c r="H36" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="119"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="121"/>
+      <c r="B37" s="118"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="120"/>
       <c r="H37" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="119"/>
-      <c r="C38" s="118"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="121"/>
+      <c r="B38" s="118"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="120"/>
       <c r="H38" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="119"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="121"/>
+      <c r="B39" s="118"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="120"/>
       <c r="H39" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="119"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="121"/>
+      <c r="B40" s="118"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="120"/>
       <c r="H40" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="119"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="121"/>
+      <c r="B41" s="118"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="120"/>
       <c r="H41" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="119"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="119"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="121"/>
+      <c r="B42" s="118"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="120"/>
       <c r="H42" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="119"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="121"/>
+      <c r="B43" s="118"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="119"/>
+      <c r="G43" s="120"/>
       <c r="H43" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="119"/>
-      <c r="C44" s="118"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="120"/>
-      <c r="G44" s="121"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="120"/>
       <c r="H44" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="119"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="120"/>
-      <c r="G45" s="121"/>
+      <c r="B45" s="118"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="120"/>
       <c r="H45" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="119"/>
-      <c r="C46" s="118"/>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="120"/>
-      <c r="G46" s="121"/>
+      <c r="B46" s="118"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="120"/>
       <c r="H46" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="119"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="120"/>
-      <c r="G47" s="121"/>
+      <c r="B47" s="118"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="119"/>
+      <c r="G47" s="120"/>
       <c r="H47" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="119"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="119"/>
-      <c r="F48" s="120"/>
-      <c r="G48" s="121"/>
+      <c r="B48" s="118"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="120"/>
       <c r="H48" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="119"/>
-      <c r="C49" s="118"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="121"/>
+      <c r="B49" s="118"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="120"/>
       <c r="H49" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="119"/>
-      <c r="C50" s="118"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="119"/>
-      <c r="F50" s="120"/>
-      <c r="G50" s="121"/>
+      <c r="B50" s="118"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="120"/>
       <c r="H50" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="119"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="121"/>
+      <c r="B51" s="118"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="118"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="120"/>
       <c r="H51" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="119"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="120"/>
-      <c r="G52" s="121"/>
+      <c r="B52" s="118"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="120"/>
       <c r="H52" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="119"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="121"/>
+      <c r="B53" s="118"/>
+      <c r="C53" s="117"/>
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="120"/>
       <c r="H53" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="119"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="121"/>
+      <c r="B54" s="118"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="120"/>
       <c r="H54" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="119"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="119"/>
-      <c r="E55" s="119"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="121"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="117"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="119"/>
+      <c r="G55" s="120"/>
       <c r="H55" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="119"/>
-      <c r="C56" s="118"/>
-      <c r="D56" s="119"/>
-      <c r="E56" s="119"/>
-      <c r="F56" s="120"/>
-      <c r="G56" s="121"/>
+      <c r="B56" s="118"/>
+      <c r="C56" s="117"/>
+      <c r="D56" s="118"/>
+      <c r="E56" s="118"/>
+      <c r="F56" s="119"/>
+      <c r="G56" s="120"/>
       <c r="H56" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="119"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="119"/>
-      <c r="E57" s="119"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="121"/>
+      <c r="B57" s="118"/>
+      <c r="C57" s="117"/>
+      <c r="D57" s="118"/>
+      <c r="E57" s="118"/>
+      <c r="F57" s="119"/>
+      <c r="G57" s="120"/>
       <c r="H57" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="119"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="119"/>
-      <c r="E58" s="119"/>
-      <c r="F58" s="120"/>
-      <c r="G58" s="121"/>
+      <c r="B58" s="118"/>
+      <c r="C58" s="117"/>
+      <c r="D58" s="118"/>
+      <c r="E58" s="118"/>
+      <c r="F58" s="119"/>
+      <c r="G58" s="120"/>
       <c r="H58" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="119"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="119"/>
-      <c r="E59" s="119"/>
-      <c r="F59" s="120"/>
-      <c r="G59" s="121"/>
+      <c r="B59" s="118"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="118"/>
+      <c r="E59" s="118"/>
+      <c r="F59" s="119"/>
+      <c r="G59" s="120"/>
       <c r="H59" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="119"/>
-      <c r="C60" s="118"/>
-      <c r="D60" s="119"/>
-      <c r="E60" s="119"/>
-      <c r="F60" s="120"/>
-      <c r="G60" s="121"/>
+      <c r="B60" s="118"/>
+      <c r="C60" s="117"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="120"/>
       <c r="H60" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="119"/>
-      <c r="C61" s="118"/>
-      <c r="D61" s="119"/>
-      <c r="E61" s="119"/>
-      <c r="F61" s="120"/>
-      <c r="G61" s="121"/>
+      <c r="B61" s="118"/>
+      <c r="C61" s="117"/>
+      <c r="D61" s="118"/>
+      <c r="E61" s="118"/>
+      <c r="F61" s="119"/>
+      <c r="G61" s="120"/>
       <c r="H61" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="119"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="119"/>
-      <c r="E62" s="119"/>
-      <c r="F62" s="120"/>
-      <c r="G62" s="121"/>
+      <c r="B62" s="118"/>
+      <c r="C62" s="117"/>
+      <c r="D62" s="118"/>
+      <c r="E62" s="118"/>
+      <c r="F62" s="119"/>
+      <c r="G62" s="120"/>
       <c r="H62" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="119"/>
-      <c r="C63" s="118"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="119"/>
-      <c r="F63" s="120"/>
-      <c r="G63" s="121"/>
+      <c r="B63" s="118"/>
+      <c r="C63" s="117"/>
+      <c r="D63" s="118"/>
+      <c r="E63" s="118"/>
+      <c r="F63" s="119"/>
+      <c r="G63" s="120"/>
       <c r="H63" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="119"/>
-      <c r="C64" s="118"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="119"/>
-      <c r="F64" s="120"/>
-      <c r="G64" s="121"/>
+      <c r="B64" s="118"/>
+      <c r="C64" s="117"/>
+      <c r="D64" s="118"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="120"/>
       <c r="H64" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="119"/>
-      <c r="C65" s="118"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
-      <c r="F65" s="120"/>
-      <c r="G65" s="121"/>
+      <c r="B65" s="118"/>
+      <c r="C65" s="117"/>
+      <c r="D65" s="118"/>
+      <c r="E65" s="118"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="120"/>
       <c r="H65" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="119"/>
-      <c r="C66" s="118"/>
-      <c r="D66" s="119"/>
-      <c r="E66" s="119"/>
-      <c r="F66" s="120"/>
-      <c r="G66" s="121"/>
+      <c r="B66" s="118"/>
+      <c r="C66" s="117"/>
+      <c r="D66" s="118"/>
+      <c r="E66" s="118"/>
+      <c r="F66" s="119"/>
+      <c r="G66" s="120"/>
       <c r="H66" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="119"/>
-      <c r="C67" s="118"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="119"/>
-      <c r="F67" s="120"/>
-      <c r="G67" s="121"/>
+      <c r="B67" s="118"/>
+      <c r="C67" s="117"/>
+      <c r="D67" s="118"/>
+      <c r="E67" s="118"/>
+      <c r="F67" s="119"/>
+      <c r="G67" s="120"/>
       <c r="H67" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="119"/>
-      <c r="C68" s="118"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="119"/>
-      <c r="F68" s="120"/>
-      <c r="G68" s="121"/>
+      <c r="B68" s="118"/>
+      <c r="C68" s="117"/>
+      <c r="D68" s="118"/>
+      <c r="E68" s="118"/>
+      <c r="F68" s="119"/>
+      <c r="G68" s="120"/>
       <c r="H68" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="119"/>
-      <c r="C69" s="118"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="119"/>
-      <c r="F69" s="120"/>
-      <c r="G69" s="121"/>
+      <c r="B69" s="118"/>
+      <c r="C69" s="117"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="118"/>
+      <c r="F69" s="119"/>
+      <c r="G69" s="120"/>
       <c r="H69" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="119"/>
-      <c r="C70" s="118"/>
-      <c r="D70" s="119"/>
-      <c r="E70" s="119"/>
-      <c r="F70" s="120"/>
-      <c r="G70" s="121"/>
+      <c r="B70" s="118"/>
+      <c r="C70" s="117"/>
+      <c r="D70" s="118"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="119"/>
+      <c r="G70" s="120"/>
       <c r="H70" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="119"/>
-      <c r="C71" s="118"/>
-      <c r="D71" s="119"/>
-      <c r="E71" s="119"/>
-      <c r="F71" s="120"/>
-      <c r="G71" s="121"/>
+      <c r="B71" s="118"/>
+      <c r="C71" s="117"/>
+      <c r="D71" s="118"/>
+      <c r="E71" s="118"/>
+      <c r="F71" s="119"/>
+      <c r="G71" s="120"/>
       <c r="H71" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="119"/>
-      <c r="C72" s="118"/>
-      <c r="D72" s="119"/>
-      <c r="E72" s="119"/>
-      <c r="F72" s="120"/>
-      <c r="G72" s="121"/>
+      <c r="B72" s="118"/>
+      <c r="C72" s="117"/>
+      <c r="D72" s="118"/>
+      <c r="E72" s="118"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="120"/>
       <c r="H72" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="119"/>
-      <c r="C73" s="118"/>
-      <c r="D73" s="119"/>
-      <c r="E73" s="119"/>
-      <c r="F73" s="120"/>
-      <c r="G73" s="121"/>
+      <c r="B73" s="118"/>
+      <c r="C73" s="117"/>
+      <c r="D73" s="118"/>
+      <c r="E73" s="118"/>
+      <c r="F73" s="119"/>
+      <c r="G73" s="120"/>
       <c r="H73" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="119"/>
-      <c r="C74" s="118"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="119"/>
-      <c r="F74" s="120"/>
-      <c r="G74" s="121"/>
+      <c r="B74" s="118"/>
+      <c r="C74" s="117"/>
+      <c r="D74" s="118"/>
+      <c r="E74" s="118"/>
+      <c r="F74" s="119"/>
+      <c r="G74" s="120"/>
       <c r="H74" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="119"/>
-      <c r="C75" s="118"/>
-      <c r="D75" s="119"/>
-      <c r="E75" s="119"/>
-      <c r="F75" s="120"/>
-      <c r="G75" s="121"/>
+      <c r="B75" s="118"/>
+      <c r="C75" s="117"/>
+      <c r="D75" s="118"/>
+      <c r="E75" s="118"/>
+      <c r="F75" s="119"/>
+      <c r="G75" s="120"/>
       <c r="H75" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="119"/>
-      <c r="C76" s="118"/>
-      <c r="D76" s="119"/>
-      <c r="E76" s="119"/>
-      <c r="F76" s="120"/>
-      <c r="G76" s="121"/>
+      <c r="B76" s="118"/>
+      <c r="C76" s="117"/>
+      <c r="D76" s="118"/>
+      <c r="E76" s="118"/>
+      <c r="F76" s="119"/>
+      <c r="G76" s="120"/>
       <c r="H76" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="119"/>
-      <c r="C77" s="118"/>
-      <c r="D77" s="119"/>
-      <c r="E77" s="119"/>
-      <c r="F77" s="120"/>
-      <c r="G77" s="121"/>
+      <c r="B77" s="118"/>
+      <c r="C77" s="117"/>
+      <c r="D77" s="118"/>
+      <c r="E77" s="118"/>
+      <c r="F77" s="119"/>
+      <c r="G77" s="120"/>
       <c r="H77" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="119"/>
-      <c r="C78" s="118"/>
-      <c r="D78" s="119"/>
-      <c r="E78" s="119"/>
-      <c r="F78" s="120"/>
-      <c r="G78" s="121"/>
+      <c r="B78" s="118"/>
+      <c r="C78" s="117"/>
+      <c r="D78" s="118"/>
+      <c r="E78" s="118"/>
+      <c r="F78" s="119"/>
+      <c r="G78" s="120"/>
       <c r="H78" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="119"/>
-      <c r="C79" s="118"/>
-      <c r="D79" s="119"/>
-      <c r="E79" s="119"/>
-      <c r="F79" s="120"/>
-      <c r="G79" s="121"/>
+      <c r="B79" s="118"/>
+      <c r="C79" s="117"/>
+      <c r="D79" s="118"/>
+      <c r="E79" s="118"/>
+      <c r="F79" s="119"/>
+      <c r="G79" s="120"/>
       <c r="H79" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="119"/>
-      <c r="C80" s="118"/>
-      <c r="D80" s="119"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="120"/>
-      <c r="G80" s="121"/>
+      <c r="B80" s="118"/>
+      <c r="C80" s="117"/>
+      <c r="D80" s="118"/>
+      <c r="E80" s="118"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="119"/>
-      <c r="C81" s="118"/>
-      <c r="D81" s="119"/>
-      <c r="E81" s="119"/>
-      <c r="F81" s="120"/>
-      <c r="G81" s="121"/>
+      <c r="B81" s="118"/>
+      <c r="C81" s="117"/>
+      <c r="D81" s="118"/>
+      <c r="E81" s="118"/>
+      <c r="F81" s="119"/>
+      <c r="G81" s="120"/>
       <c r="H81" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="119"/>
-      <c r="C82" s="118"/>
-      <c r="D82" s="119"/>
-      <c r="E82" s="119"/>
-      <c r="F82" s="120"/>
-      <c r="G82" s="121"/>
+      <c r="B82" s="118"/>
+      <c r="C82" s="117"/>
+      <c r="D82" s="118"/>
+      <c r="E82" s="118"/>
+      <c r="F82" s="119"/>
+      <c r="G82" s="120"/>
       <c r="H82" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="119"/>
-      <c r="C83" s="118"/>
-      <c r="D83" s="119"/>
-      <c r="E83" s="119"/>
-      <c r="F83" s="120"/>
-      <c r="G83" s="121"/>
+      <c r="B83" s="118"/>
+      <c r="C83" s="117"/>
+      <c r="D83" s="118"/>
+      <c r="E83" s="118"/>
+      <c r="F83" s="119"/>
+      <c r="G83" s="120"/>
       <c r="H83" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="119"/>
-      <c r="C84" s="118"/>
-      <c r="D84" s="119"/>
-      <c r="E84" s="119"/>
-      <c r="F84" s="120"/>
-      <c r="G84" s="121"/>
+      <c r="B84" s="118"/>
+      <c r="C84" s="117"/>
+      <c r="D84" s="118"/>
+      <c r="E84" s="118"/>
+      <c r="F84" s="119"/>
+      <c r="G84" s="120"/>
       <c r="H84" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="119"/>
-      <c r="C85" s="118"/>
-      <c r="D85" s="119"/>
-      <c r="E85" s="119"/>
-      <c r="F85" s="120"/>
-      <c r="G85" s="121"/>
+      <c r="B85" s="118"/>
+      <c r="C85" s="117"/>
+      <c r="D85" s="118"/>
+      <c r="E85" s="118"/>
+      <c r="F85" s="119"/>
+      <c r="G85" s="120"/>
       <c r="H85" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="119"/>
-      <c r="C86" s="118"/>
-      <c r="D86" s="119"/>
-      <c r="E86" s="119"/>
-      <c r="F86" s="120"/>
-      <c r="G86" s="121"/>
+      <c r="B86" s="118"/>
+      <c r="C86" s="117"/>
+      <c r="D86" s="118"/>
+      <c r="E86" s="118"/>
+      <c r="F86" s="119"/>
+      <c r="G86" s="120"/>
       <c r="H86" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="119"/>
-      <c r="C87" s="118"/>
-      <c r="D87" s="119"/>
-      <c r="E87" s="119"/>
-      <c r="F87" s="120"/>
-      <c r="G87" s="121"/>
+      <c r="B87" s="118"/>
+      <c r="C87" s="117"/>
+      <c r="D87" s="118"/>
+      <c r="E87" s="118"/>
+      <c r="F87" s="119"/>
+      <c r="G87" s="120"/>
       <c r="H87" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="119"/>
-      <c r="C88" s="118"/>
-      <c r="D88" s="119"/>
-      <c r="E88" s="119"/>
-      <c r="F88" s="120"/>
-      <c r="G88" s="121"/>
+      <c r="B88" s="118"/>
+      <c r="C88" s="117"/>
+      <c r="D88" s="118"/>
+      <c r="E88" s="118"/>
+      <c r="F88" s="119"/>
+      <c r="G88" s="120"/>
       <c r="H88" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="119"/>
-      <c r="C89" s="118"/>
-      <c r="D89" s="119"/>
-      <c r="E89" s="119"/>
-      <c r="F89" s="120"/>
-      <c r="G89" s="121"/>
+      <c r="B89" s="118"/>
+      <c r="C89" s="117"/>
+      <c r="D89" s="118"/>
+      <c r="E89" s="118"/>
+      <c r="F89" s="119"/>
+      <c r="G89" s="120"/>
       <c r="H89" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="119"/>
-      <c r="C90" s="118"/>
-      <c r="D90" s="119"/>
-      <c r="E90" s="119"/>
-      <c r="F90" s="120"/>
-      <c r="G90" s="121"/>
+      <c r="B90" s="118"/>
+      <c r="C90" s="117"/>
+      <c r="D90" s="118"/>
+      <c r="E90" s="118"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
       <c r="H90" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="119"/>
-      <c r="C91" s="118"/>
-      <c r="D91" s="119"/>
-      <c r="E91" s="119"/>
-      <c r="F91" s="120"/>
-      <c r="G91" s="121"/>
+      <c r="B91" s="118"/>
+      <c r="C91" s="117"/>
+      <c r="D91" s="118"/>
+      <c r="E91" s="118"/>
+      <c r="F91" s="119"/>
+      <c r="G91" s="120"/>
       <c r="H91" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="119"/>
-      <c r="C92" s="118"/>
-      <c r="D92" s="119"/>
-      <c r="E92" s="119"/>
-      <c r="F92" s="120"/>
-      <c r="G92" s="121"/>
+      <c r="B92" s="118"/>
+      <c r="C92" s="117"/>
+      <c r="D92" s="118"/>
+      <c r="E92" s="118"/>
+      <c r="F92" s="119"/>
+      <c r="G92" s="120"/>
       <c r="H92" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="119"/>
-      <c r="C93" s="118"/>
-      <c r="D93" s="119"/>
-      <c r="E93" s="119"/>
-      <c r="F93" s="120"/>
-      <c r="G93" s="121"/>
+      <c r="B93" s="118"/>
+      <c r="C93" s="117"/>
+      <c r="D93" s="118"/>
+      <c r="E93" s="118"/>
+      <c r="F93" s="119"/>
+      <c r="G93" s="120"/>
       <c r="H93" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="119"/>
-      <c r="C94" s="118"/>
-      <c r="D94" s="119"/>
-      <c r="E94" s="119"/>
-      <c r="F94" s="120"/>
-      <c r="G94" s="121"/>
+      <c r="B94" s="118"/>
+      <c r="C94" s="117"/>
+      <c r="D94" s="118"/>
+      <c r="E94" s="118"/>
+      <c r="F94" s="119"/>
+      <c r="G94" s="120"/>
       <c r="H94" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="119"/>
-      <c r="C95" s="118"/>
-      <c r="D95" s="119"/>
-      <c r="E95" s="119"/>
-      <c r="F95" s="120"/>
-      <c r="G95" s="121"/>
+      <c r="B95" s="118"/>
+      <c r="C95" s="117"/>
+      <c r="D95" s="118"/>
+      <c r="E95" s="118"/>
+      <c r="F95" s="119"/>
+      <c r="G95" s="120"/>
       <c r="H95" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="119"/>
-      <c r="C96" s="118"/>
-      <c r="D96" s="119"/>
-      <c r="E96" s="119"/>
-      <c r="F96" s="120"/>
-      <c r="G96" s="121"/>
+      <c r="B96" s="118"/>
+      <c r="C96" s="117"/>
+      <c r="D96" s="118"/>
+      <c r="E96" s="118"/>
+      <c r="F96" s="119"/>
+      <c r="G96" s="120"/>
       <c r="H96" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -9767,333 +9788,333 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="B1" s="122" t="s">
-        <v>159</v>
+      <c r="B1" s="121" t="s">
+        <v>162</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="123" t="s">
-        <v>160</v>
+      <c r="B2" s="122" t="s">
+        <v>163</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
     </row>
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
-      <c r="B4" s="124" t="s">
-        <v>161</v>
-      </c>
-      <c r="C4" s="125" t="s">
-        <v>162</v>
-      </c>
-      <c r="D4" s="126" t="s">
-        <v>163</v>
+      <c r="B4" s="123" t="s">
+        <v>164</v>
+      </c>
+      <c r="C4" s="124" t="s">
+        <v>165</v>
+      </c>
+      <c r="D4" s="125" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
-      <c r="B5" s="124" t="s">
-        <v>164</v>
-      </c>
-      <c r="C5" s="125" t="s">
-        <v>165</v>
-      </c>
-      <c r="D5" s="126" t="s">
-        <v>166</v>
+      <c r="B5" s="123" t="s">
+        <v>167</v>
+      </c>
+      <c r="C5" s="124" t="s">
+        <v>168</v>
+      </c>
+      <c r="D5" s="125" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
-      <c r="B6" s="124" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" s="125" t="s">
-        <v>168</v>
-      </c>
-      <c r="D6" s="126" t="s">
-        <v>169</v>
+      <c r="B6" s="123" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="124" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" s="125" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
-      <c r="B7" s="124" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>171</v>
-      </c>
-      <c r="D7" s="126" t="s">
-        <v>172</v>
+      <c r="B7" s="123" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" s="124" t="s">
+        <v>174</v>
+      </c>
+      <c r="D7" s="125" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
-      <c r="B8" s="127" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" s="128" t="s">
-        <v>174</v>
-      </c>
-      <c r="D8" s="126" t="s">
-        <v>175</v>
+      <c r="B8" s="126" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="125" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="B9" s="127" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>177</v>
-      </c>
-      <c r="D9" s="126" t="s">
-        <v>178</v>
+      <c r="B9" s="126" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="D9" s="125" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
-      <c r="B10" s="129" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="130" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="126" t="s">
-        <v>181</v>
+      <c r="B10" s="128" t="s">
+        <v>182</v>
+      </c>
+      <c r="C10" s="129" t="s">
+        <v>183</v>
+      </c>
+      <c r="D10" s="125" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
-      <c r="B11" s="129" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="130" t="s">
-        <v>183</v>
-      </c>
-      <c r="D11" s="126" t="s">
-        <v>184</v>
+      <c r="B11" s="128" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="129" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="125" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
-      <c r="B12" s="131" t="s">
-        <v>185</v>
-      </c>
-      <c r="C12" s="132" t="s">
-        <v>186</v>
-      </c>
-      <c r="D12" s="126" t="s">
-        <v>187</v>
+      <c r="B12" s="130" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="131" t="s">
+        <v>189</v>
+      </c>
+      <c r="D12" s="125" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
-      <c r="B13" s="131" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="132" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="126" t="s">
-        <v>190</v>
+      <c r="B13" s="130" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="131" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="125" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
-      <c r="B14" s="133" t="s">
-        <v>191</v>
-      </c>
-      <c r="C14" s="134" t="s">
-        <v>192</v>
-      </c>
-      <c r="D14" s="126" t="s">
-        <v>193</v>
+      <c r="B14" s="132" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="133" t="s">
+        <v>195</v>
+      </c>
+      <c r="D14" s="125" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
-      <c r="B15" s="135" t="s">
-        <v>194</v>
-      </c>
-      <c r="C15" s="136" t="s">
-        <v>195</v>
-      </c>
-      <c r="D15" s="126" t="s">
-        <v>196</v>
+      <c r="B15" s="134" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="135" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="125" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
-      <c r="B16" s="129" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="130" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="126" t="s">
-        <v>199</v>
+      <c r="B16" s="128" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="129" t="s">
+        <v>201</v>
+      </c>
+      <c r="D16" s="125" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
-      <c r="B17" s="135" t="s">
-        <v>200</v>
-      </c>
-      <c r="C17" s="136" t="s">
-        <v>201</v>
-      </c>
-      <c r="D17" s="126" t="s">
-        <v>202</v>
+      <c r="B17" s="134" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="135" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="125" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
-      <c r="B18" s="131" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="132" t="s">
-        <v>204</v>
-      </c>
-      <c r="D18" s="126" t="s">
-        <v>205</v>
+      <c r="B18" s="130" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="131" t="s">
+        <v>207</v>
+      </c>
+      <c r="D18" s="125" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="B20" s="137" t="s">
-        <v>206</v>
+      <c r="B20" s="136" t="s">
+        <v>209</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="B21" s="138" t="s">
+      <c r="B21" s="137" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="138" t="s">
-        <v>207</v>
-      </c>
-      <c r="D21" s="138" t="s">
-        <v>208</v>
+      <c r="C21" s="137" t="s">
+        <v>210</v>
+      </c>
+      <c r="D21" s="137" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="B22" s="139" t="s">
+      <c r="B22" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="140" t="s">
-        <v>209</v>
-      </c>
-      <c r="D22" s="141" t="s">
-        <v>210</v>
+      <c r="C22" s="139" t="s">
+        <v>212</v>
+      </c>
+      <c r="D22" s="140" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
-      <c r="B23" s="139" t="s">
+      <c r="B23" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="140" t="s">
-        <v>211</v>
-      </c>
-      <c r="D23" s="141" t="s">
-        <v>212</v>
+      <c r="C23" s="139" t="s">
+        <v>214</v>
+      </c>
+      <c r="D23" s="140" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
-      <c r="B24" s="142" t="s">
+      <c r="B24" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="143" t="s">
-        <v>213</v>
-      </c>
-      <c r="D24" s="141" t="s">
-        <v>214</v>
+      <c r="C24" s="142" t="s">
+        <v>216</v>
+      </c>
+      <c r="D24" s="140" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="138" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="140" t="s">
-        <v>215</v>
-      </c>
-      <c r="D25" s="141" t="s">
-        <v>216</v>
+      <c r="C25" s="139" t="s">
+        <v>218</v>
+      </c>
+      <c r="D25" s="140" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="145" t="s">
-        <v>217</v>
-      </c>
-      <c r="D26" s="141" t="s">
-        <v>218</v>
+      <c r="C26" s="144" t="s">
+        <v>220</v>
+      </c>
+      <c r="D26" s="140" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
-      <c r="B27" s="146" t="s">
+      <c r="B27" s="145" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="147" t="s">
-        <v>219</v>
-      </c>
-      <c r="D27" s="141" t="s">
-        <v>220</v>
+      <c r="C27" s="146" t="s">
+        <v>222</v>
+      </c>
+      <c r="D27" s="140" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
-      <c r="B28" s="139" t="s">
+      <c r="B28" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="140" t="s">
-        <v>221</v>
-      </c>
-      <c r="D28" s="141" t="s">
-        <v>222</v>
+      <c r="C28" s="139" t="s">
+        <v>224</v>
+      </c>
+      <c r="D28" s="140" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
-      <c r="B29" s="139" t="s">
+      <c r="B29" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="140" t="s">
-        <v>223</v>
-      </c>
-      <c r="D29" s="141" t="s">
-        <v>224</v>
+      <c r="C29" s="139" t="s">
+        <v>226</v>
+      </c>
+      <c r="D29" s="140" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
-      <c r="B30" s="144" t="s">
+      <c r="B30" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="145" t="s">
-        <v>225</v>
-      </c>
-      <c r="D30" s="141" t="s">
-        <v>226</v>
+      <c r="C30" s="144" t="s">
+        <v>228</v>
+      </c>
+      <c r="D30" s="140" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="B31" s="144" t="s">
+      <c r="B31" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="145" t="s">
-        <v>227</v>
-      </c>
-      <c r="D31" s="141" t="s">
-        <v>228</v>
+      <c r="C31" s="144" t="s">
+        <v>230</v>
+      </c>
+      <c r="D31" s="140" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
-      <c r="B32" s="148" t="s">
+      <c r="B32" s="147" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="149" t="s">
-        <v>229</v>
-      </c>
-      <c r="D32" s="141" t="s">
-        <v>230</v>
+      <c r="C32" s="148" t="s">
+        <v>232</v>
+      </c>
+      <c r="D32" s="140" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="B33" s="139" t="s">
+      <c r="B33" s="138" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="140" t="s">
-        <v>231</v>
-      </c>
-      <c r="D33" s="141" t="s">
-        <v>232</v>
+      <c r="C33" s="139" t="s">
+        <v>234</v>
+      </c>
+      <c r="D33" s="140" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11084,967 +11105,967 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="150" t="s">
-        <v>233</v>
-      </c>
-      <c r="B1" s="150" t="s">
-        <v>234</v>
-      </c>
-      <c r="C1" s="150" t="s">
+      <c r="A1" s="149" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="149" t="s">
+        <v>237</v>
+      </c>
+      <c r="C1" s="149" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
     </row>
     <row r="2">
-      <c r="A2" s="151">
+      <c r="A2" s="150">
         <v>46165.0</v>
       </c>
-      <c r="B2" s="150" t="s">
-        <v>235</v>
-      </c>
-      <c r="C2" s="152">
+      <c r="B2" s="149" t="s">
+        <v>238</v>
+      </c>
+      <c r="C2" s="151">
         <v>10000.0</v>
       </c>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
     </row>
     <row r="3">
-      <c r="A3" s="151">
+      <c r="A3" s="150">
         <v>46166.0</v>
       </c>
-      <c r="B3" s="150" t="s">
+      <c r="B3" s="149" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="151">
+        <v>19000.0</v>
+      </c>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="150">
+        <v>46168.0</v>
+      </c>
+      <c r="B4" s="149" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="152">
+        <v>2500.0</v>
+      </c>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B5" s="149" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="151">
+        <v>29050.0</v>
+      </c>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B6" s="149" t="s">
+        <v>242</v>
+      </c>
+      <c r="C6" s="152">
+        <v>100.0</v>
+      </c>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B7" s="149" t="s">
+        <v>243</v>
+      </c>
+      <c r="C7" s="152">
+        <v>300.0</v>
+      </c>
+      <c r="D7" s="149"/>
+      <c r="E7" s="149"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B8" s="149" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="152">
+        <v>370.0</v>
+      </c>
+      <c r="D8" s="149"/>
+      <c r="E8" s="149"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B9" s="149" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="152">
+        <v>2494.0</v>
+      </c>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B10" s="149" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="152">
+        <v>5000.0</v>
+      </c>
+      <c r="D10" s="149"/>
+      <c r="E10" s="149"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="151">
+        <v>29000.0</v>
+      </c>
+      <c r="D11" s="149" t="s">
+        <v>248</v>
+      </c>
+      <c r="E11" s="152">
+        <v>24000.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" s="152">
+        <v>400.0</v>
+      </c>
+      <c r="D12" s="149" t="s">
+        <v>250</v>
+      </c>
+      <c r="E12" s="151">
+        <v>53000.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>251</v>
+      </c>
+      <c r="C13" s="152">
+        <v>600.0</v>
+      </c>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="150">
+        <v>46170.0</v>
+      </c>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="149" t="s">
+        <v>252</v>
+      </c>
+      <c r="B22" s="149" t="s">
         <v>236</v>
       </c>
-      <c r="C3" s="152">
-        <v>19000.0</v>
-      </c>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="151">
-        <v>46168.0</v>
-      </c>
-      <c r="B4" s="150" t="s">
-        <v>237</v>
-      </c>
-      <c r="C4" s="153">
-        <v>2500.0</v>
-      </c>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B5" s="150" t="s">
-        <v>238</v>
-      </c>
-      <c r="C5" s="152">
-        <v>29050.0</v>
-      </c>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B6" s="150" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="153">
-        <v>100.0</v>
-      </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B7" s="150" t="s">
-        <v>240</v>
-      </c>
-      <c r="C7" s="153">
-        <v>300.0</v>
-      </c>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B8" s="150" t="s">
-        <v>241</v>
-      </c>
-      <c r="C8" s="153">
-        <v>370.0</v>
-      </c>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B9" s="150" t="s">
-        <v>242</v>
-      </c>
-      <c r="C9" s="153">
-        <v>2494.0</v>
-      </c>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B10" s="150" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="153">
+      <c r="C22" s="149" t="s">
+        <v>253</v>
+      </c>
+      <c r="D22" s="149" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="149" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="149" t="s">
+        <v>255</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>256</v>
+      </c>
+      <c r="C23" s="149" t="s">
+        <v>257</v>
+      </c>
+      <c r="D23" s="152">
+        <v>3150.0</v>
+      </c>
+      <c r="E23" s="153">
+        <v>46464.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="149" t="s">
+        <v>255</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>256</v>
+      </c>
+      <c r="C24" s="149" t="s">
+        <v>258</v>
+      </c>
+      <c r="D24" s="152">
+        <v>2650.0</v>
+      </c>
+      <c r="E24" s="153">
+        <v>46219.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="149" t="s">
+        <v>255</v>
+      </c>
+      <c r="B25" s="149" t="s">
+        <v>256</v>
+      </c>
+      <c r="C25" s="149" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="152">
+        <v>2600.0</v>
+      </c>
+      <c r="E25" s="153">
+        <v>46828.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="149" t="s">
+        <v>255</v>
+      </c>
+      <c r="B26" s="149" t="s">
+        <v>256</v>
+      </c>
+      <c r="C26" s="149" t="s">
+        <v>260</v>
+      </c>
+      <c r="D26" s="152">
+        <v>2680.0</v>
+      </c>
+      <c r="E26" s="154">
+        <v>46863.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="149" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="149" t="s">
+        <v>262</v>
+      </c>
+      <c r="C27" s="149" t="s">
+        <v>263</v>
+      </c>
+      <c r="D27" s="152">
+        <v>5390.0</v>
+      </c>
+      <c r="E27" s="153">
+        <v>46764.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="149" t="s">
+        <v>261</v>
+      </c>
+      <c r="B28" s="149" t="s">
+        <v>262</v>
+      </c>
+      <c r="C28" s="149" t="s">
+        <v>264</v>
+      </c>
+      <c r="D28" s="152">
+        <v>3235.0</v>
+      </c>
+      <c r="E28" s="153">
+        <v>46673.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="149" t="s">
+        <v>261</v>
+      </c>
+      <c r="B29" s="149" t="s">
+        <v>262</v>
+      </c>
+      <c r="C29" s="149" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="152">
+        <v>1230.0</v>
+      </c>
+      <c r="E29" s="149" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="149" t="s">
+        <v>267</v>
+      </c>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149" t="s">
+        <v>257</v>
+      </c>
+      <c r="D30" s="152">
+        <v>2960.0</v>
+      </c>
+      <c r="E30" s="149"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="149" t="s">
+        <v>267</v>
+      </c>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149" t="s">
+        <v>263</v>
+      </c>
+      <c r="D31" s="152">
+        <v>2960.0</v>
+      </c>
+      <c r="E31" s="149"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="149" t="s">
+        <v>268</v>
+      </c>
+      <c r="B32" s="149" t="s">
+        <v>269</v>
+      </c>
+      <c r="C32" s="149"/>
+      <c r="D32" s="152">
         <v>5000.0</v>
       </c>
-      <c r="D10" s="150"/>
-      <c r="E10" s="150"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B11" s="150" t="s">
-        <v>244</v>
-      </c>
-      <c r="C11" s="152">
-        <v>29000.0</v>
-      </c>
-      <c r="D11" s="150" t="s">
-        <v>245</v>
-      </c>
-      <c r="E11" s="153">
-        <v>24000.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B12" s="150" t="s">
-        <v>246</v>
-      </c>
-      <c r="C12" s="153">
-        <v>400.0</v>
-      </c>
-      <c r="D12" s="150" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="152">
-        <v>53000.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B13" s="150" t="s">
-        <v>248</v>
-      </c>
-      <c r="C13" s="153">
-        <v>600.0</v>
-      </c>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="151">
-        <v>46170.0</v>
-      </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="150" t="s">
-        <v>249</v>
-      </c>
-      <c r="B22" s="150" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="150" t="s">
-        <v>250</v>
-      </c>
-      <c r="D22" s="150" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="150" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="150" t="s">
-        <v>252</v>
-      </c>
-      <c r="B23" s="150" t="s">
-        <v>253</v>
-      </c>
-      <c r="C23" s="150" t="s">
-        <v>254</v>
-      </c>
-      <c r="D23" s="153">
-        <v>3150.0</v>
-      </c>
-      <c r="E23" s="154">
-        <v>46464.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="150" t="s">
-        <v>252</v>
-      </c>
-      <c r="B24" s="150" t="s">
-        <v>253</v>
-      </c>
-      <c r="C24" s="150" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="153">
-        <v>2650.0</v>
-      </c>
-      <c r="E24" s="154">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="150" t="s">
-        <v>252</v>
-      </c>
-      <c r="B25" s="150" t="s">
-        <v>253</v>
-      </c>
-      <c r="C25" s="150" t="s">
-        <v>256</v>
-      </c>
-      <c r="D25" s="153">
-        <v>2600.0</v>
-      </c>
-      <c r="E25" s="154">
-        <v>46828.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="150" t="s">
-        <v>252</v>
-      </c>
-      <c r="B26" s="150" t="s">
-        <v>253</v>
-      </c>
-      <c r="C26" s="150" t="s">
-        <v>257</v>
-      </c>
-      <c r="D26" s="153">
-        <v>2680.0</v>
-      </c>
-      <c r="E26" s="155">
-        <v>46863.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="150" t="s">
-        <v>258</v>
-      </c>
-      <c r="B27" s="150" t="s">
-        <v>259</v>
-      </c>
-      <c r="C27" s="150" t="s">
-        <v>260</v>
-      </c>
-      <c r="D27" s="153">
-        <v>5390.0</v>
-      </c>
-      <c r="E27" s="154">
-        <v>46764.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="150" t="s">
-        <v>258</v>
-      </c>
-      <c r="B28" s="150" t="s">
-        <v>259</v>
-      </c>
-      <c r="C28" s="150" t="s">
-        <v>261</v>
-      </c>
-      <c r="D28" s="153">
-        <v>3235.0</v>
-      </c>
-      <c r="E28" s="154">
-        <v>46673.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="150" t="s">
-        <v>258</v>
-      </c>
-      <c r="B29" s="150" t="s">
-        <v>259</v>
-      </c>
-      <c r="C29" s="150" t="s">
-        <v>262</v>
-      </c>
-      <c r="D29" s="153">
-        <v>1230.0</v>
-      </c>
-      <c r="E29" s="150" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="150" t="s">
-        <v>264</v>
-      </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="150" t="s">
-        <v>254</v>
-      </c>
-      <c r="D30" s="153">
-        <v>2960.0</v>
-      </c>
-      <c r="E30" s="150"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="150" t="s">
-        <v>264</v>
-      </c>
-      <c r="B31" s="150"/>
-      <c r="C31" s="150" t="s">
-        <v>260</v>
-      </c>
-      <c r="D31" s="153">
-        <v>2960.0</v>
-      </c>
-      <c r="E31" s="150"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="150" t="s">
-        <v>265</v>
-      </c>
-      <c r="B32" s="150" t="s">
-        <v>266</v>
-      </c>
-      <c r="C32" s="150"/>
-      <c r="D32" s="153">
-        <v>5000.0</v>
-      </c>
-      <c r="E32" s="150" t="s">
-        <v>267</v>
+      <c r="E32" s="149" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="156" t="s">
-        <v>268</v>
-      </c>
-      <c r="B42" s="150"/>
-      <c r="C42" s="150"/>
-      <c r="D42" s="150"/>
-      <c r="E42" s="150"/>
-      <c r="F42" s="150"/>
-      <c r="G42" s="150"/>
-      <c r="H42" s="150"/>
-      <c r="I42" s="150"/>
-      <c r="J42" s="150"/>
+      <c r="A42" s="155" t="s">
+        <v>271</v>
+      </c>
+      <c r="B42" s="149"/>
+      <c r="C42" s="149"/>
+      <c r="D42" s="149"/>
+      <c r="E42" s="149"/>
+      <c r="F42" s="149"/>
+      <c r="G42" s="149"/>
+      <c r="H42" s="149"/>
+      <c r="I42" s="149"/>
+      <c r="J42" s="149"/>
     </row>
     <row r="43">
-      <c r="A43" s="150"/>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
-      <c r="D43" s="150"/>
-      <c r="E43" s="150"/>
-      <c r="F43" s="150"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="150"/>
-      <c r="I43" s="150"/>
-      <c r="J43" s="150"/>
+      <c r="A43" s="149"/>
+      <c r="B43" s="149"/>
+      <c r="C43" s="149"/>
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="149"/>
+      <c r="H43" s="149"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="149"/>
     </row>
     <row r="44">
-      <c r="A44" s="150"/>
-      <c r="B44" s="150"/>
-      <c r="C44" s="150"/>
-      <c r="D44" s="150"/>
-      <c r="E44" s="150"/>
-      <c r="F44" s="150"/>
-      <c r="G44" s="150"/>
-      <c r="H44" s="150"/>
-      <c r="I44" s="150"/>
-      <c r="J44" s="150"/>
+      <c r="A44" s="149"/>
+      <c r="B44" s="149"/>
+      <c r="C44" s="149"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="149"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="149"/>
+      <c r="I44" s="149"/>
+      <c r="J44" s="149"/>
     </row>
     <row r="45">
-      <c r="A45" s="157" t="s">
+      <c r="A45" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="157" t="s">
-        <v>269</v>
-      </c>
-      <c r="C45" s="157" t="s">
-        <v>270</v>
-      </c>
-      <c r="D45" s="157" t="s">
+      <c r="B45" s="156" t="s">
+        <v>272</v>
+      </c>
+      <c r="C45" s="156" t="s">
+        <v>273</v>
+      </c>
+      <c r="D45" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="157" t="s">
-        <v>271</v>
-      </c>
-      <c r="F45" s="157" t="s">
-        <v>272</v>
-      </c>
-      <c r="G45" s="157" t="s">
-        <v>273</v>
-      </c>
-      <c r="H45" s="157" t="s">
+      <c r="E45" s="156" t="s">
         <v>274</v>
       </c>
-      <c r="I45" s="157" t="s">
+      <c r="F45" s="156" t="s">
         <v>275</v>
       </c>
-      <c r="J45" s="157" t="s">
+      <c r="G45" s="156" t="s">
         <v>276</v>
       </c>
+      <c r="H45" s="156" t="s">
+        <v>277</v>
+      </c>
+      <c r="I45" s="156" t="s">
+        <v>278</v>
+      </c>
+      <c r="J45" s="156" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="158" t="s">
-        <v>277</v>
-      </c>
-      <c r="B46" s="159">
+      <c r="A46" s="157" t="s">
+        <v>280</v>
+      </c>
+      <c r="B46" s="158">
         <v>1000000.0</v>
       </c>
-      <c r="C46" s="160">
+      <c r="C46" s="159">
         <v>0.2</v>
       </c>
-      <c r="D46" s="159">
+      <c r="D46" s="158">
         <f>IF(AND(B46&lt;&gt;"", C46&lt;&gt;"", E46&lt;&gt;""), PMT(C46/12, E46, -B46), "")</f>
         <v>26493.88371</v>
       </c>
-      <c r="E46" s="161">
+      <c r="E46" s="160">
         <v>60.0</v>
       </c>
-      <c r="F46" s="161">
+      <c r="F46" s="160">
         <v>0.0</v>
       </c>
-      <c r="G46" s="161">
+      <c r="G46" s="160">
         <f t="shared" ref="G46:G52" si="1">IF(E46="", "", E46 - F46)</f>
         <v>60</v>
       </c>
-      <c r="H46" s="159">
+      <c r="H46" s="158">
         <f t="shared" ref="H46:H52" si="2">IF(D46="", "", D46 * F46)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="159">
+      <c r="I46" s="158">
         <f t="shared" ref="I46:I52" si="3">IF(G46="", "", IFERROR(PV(C46/12, G46, -D46), ""))</f>
         <v>1000000</v>
       </c>
-      <c r="J46" s="162">
+      <c r="J46" s="161">
         <f t="shared" ref="J46:J52" si="4">IF(AND(D46&lt;&gt;"", E46&lt;&gt;""), (D46 * E46) - B46, "")</f>
         <v>589633.0229</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="163" t="s">
-        <v>278</v>
-      </c>
-      <c r="B47" s="164">
+      <c r="A47" s="162" t="s">
+        <v>281</v>
+      </c>
+      <c r="B47" s="163">
         <v>596000.0</v>
       </c>
-      <c r="C47" s="165">
+      <c r="C47" s="164">
         <v>0.126</v>
       </c>
-      <c r="D47" s="164">
+      <c r="D47" s="163">
         <f>IF(AND(B47&lt;&gt;"", C47&lt;&gt;"", E47&lt;&gt;""), PMT(C47/12, E47, -B47), 11839)</f>
         <v>11838.71102</v>
       </c>
-      <c r="E47" s="166">
+      <c r="E47" s="165">
         <v>72.0</v>
       </c>
-      <c r="F47" s="166">
+      <c r="F47" s="165">
         <v>52.0</v>
       </c>
-      <c r="G47" s="166">
+      <c r="G47" s="165">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="H47" s="164">
+      <c r="H47" s="163">
         <f t="shared" si="2"/>
         <v>615612.9729</v>
       </c>
-      <c r="I47" s="164">
+      <c r="I47" s="163">
         <f t="shared" si="3"/>
         <v>212564.401</v>
       </c>
-      <c r="J47" s="167">
+      <c r="J47" s="166">
         <f t="shared" si="4"/>
         <v>256387.1932</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="158" t="s">
-        <v>279</v>
-      </c>
-      <c r="B48" s="168"/>
-      <c r="C48" s="169"/>
-      <c r="D48" s="159">
+      <c r="A48" s="157" t="s">
+        <v>282</v>
+      </c>
+      <c r="B48" s="167"/>
+      <c r="C48" s="168"/>
+      <c r="D48" s="158">
         <f>IF(AND(B48&lt;&gt;"", C48&lt;&gt;"", E48&lt;&gt;""), PMT(C48/12, E48, -B48), 15250)</f>
         <v>15250</v>
       </c>
-      <c r="E48" s="170"/>
-      <c r="F48" s="161">
+      <c r="E48" s="169"/>
+      <c r="F48" s="160">
         <v>0.0</v>
       </c>
-      <c r="G48" s="170" t="str">
+      <c r="G48" s="169" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="159">
+      <c r="H48" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="168" t="str">
+      <c r="I48" s="167" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J48" s="171" t="str">
+      <c r="J48" s="170" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="163" t="s">
+      <c r="A49" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="164">
+      <c r="B49" s="163">
         <v>97110.0</v>
       </c>
-      <c r="C49" s="172"/>
-      <c r="D49" s="164">
+      <c r="C49" s="171"/>
+      <c r="D49" s="163">
         <f>IF(AND(B49&lt;&gt;"", C49&lt;&gt;"", E49&lt;&gt;""), PMT(C49/12, E49, -B49), 18972)</f>
         <v>18972</v>
       </c>
-      <c r="E49" s="173"/>
-      <c r="F49" s="166">
+      <c r="E49" s="172"/>
+      <c r="F49" s="165">
         <v>0.0</v>
       </c>
-      <c r="G49" s="173" t="str">
+      <c r="G49" s="172" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="164">
+      <c r="H49" s="163">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="174" t="str">
+      <c r="I49" s="173" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J49" s="175" t="str">
+      <c r="J49" s="174" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="158" t="s">
-        <v>280</v>
-      </c>
-      <c r="B50" s="159">
+      <c r="A50" s="157" t="s">
+        <v>283</v>
+      </c>
+      <c r="B50" s="158">
         <v>83419.0</v>
       </c>
-      <c r="C50" s="160">
+      <c r="C50" s="159">
         <v>0.12</v>
       </c>
-      <c r="D50" s="159">
+      <c r="D50" s="158">
         <f t="shared" ref="D50:D51" si="5">IF(AND(B50&lt;&gt;"", C50&lt;&gt;"", E50&lt;&gt;""), PMT(C50/12, E50, -B50), 4627)</f>
         <v>5087.061453</v>
       </c>
-      <c r="E50" s="161">
+      <c r="E50" s="160">
         <v>18.0</v>
       </c>
-      <c r="F50" s="161">
+      <c r="F50" s="160">
         <v>3.0</v>
       </c>
-      <c r="G50" s="161">
+      <c r="G50" s="160">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H50" s="159">
+      <c r="H50" s="158">
         <f t="shared" si="2"/>
         <v>15261.18436</v>
       </c>
-      <c r="I50" s="159">
+      <c r="I50" s="158">
         <f t="shared" si="3"/>
         <v>70532.37421</v>
       </c>
-      <c r="J50" s="162">
+      <c r="J50" s="161">
         <f t="shared" si="4"/>
         <v>8148.106161</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="176" t="s">
-        <v>281</v>
-      </c>
-      <c r="B51" s="177">
+      <c r="A51" s="175" t="s">
+        <v>284</v>
+      </c>
+      <c r="B51" s="176">
         <v>149100.0</v>
       </c>
-      <c r="C51" s="178">
+      <c r="C51" s="177">
         <v>0.1</v>
       </c>
-      <c r="D51" s="177">
+      <c r="D51" s="176">
         <f t="shared" si="5"/>
         <v>5637.681256</v>
       </c>
-      <c r="E51" s="179">
+      <c r="E51" s="178">
         <v>30.0</v>
       </c>
-      <c r="F51" s="179">
+      <c r="F51" s="178">
         <v>15.0</v>
       </c>
-      <c r="G51" s="179">
+      <c r="G51" s="178">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H51" s="177">
+      <c r="H51" s="176">
         <f t="shared" si="2"/>
         <v>84565.21884</v>
       </c>
-      <c r="I51" s="177">
+      <c r="I51" s="176">
         <f t="shared" si="3"/>
         <v>79184.0856</v>
       </c>
-      <c r="J51" s="180">
+      <c r="J51" s="179">
         <f t="shared" si="4"/>
         <v>20030.43769</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="158" t="s">
-        <v>282</v>
-      </c>
-      <c r="B52" s="168"/>
-      <c r="C52" s="169"/>
-      <c r="D52" s="159">
+      <c r="A52" s="157" t="s">
+        <v>285</v>
+      </c>
+      <c r="B52" s="167"/>
+      <c r="C52" s="168"/>
+      <c r="D52" s="158">
         <f>IF(AND(B52&lt;&gt;"", C52&lt;&gt;"", E52&lt;&gt;""), PMT(C52/12, E52, -B52), 3850)</f>
         <v>3850</v>
       </c>
-      <c r="E52" s="170"/>
-      <c r="F52" s="161">
+      <c r="E52" s="169"/>
+      <c r="F52" s="160">
         <v>0.0</v>
       </c>
-      <c r="G52" s="170" t="str">
+      <c r="G52" s="169" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H52" s="159">
+      <c r="H52" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="168" t="str">
+      <c r="I52" s="167" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J52" s="171" t="str">
+      <c r="J52" s="170" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="181" t="s">
-        <v>233</v>
-      </c>
-      <c r="B61" s="181" t="s">
-        <v>283</v>
-      </c>
-      <c r="C61" s="181" t="s">
+      <c r="A61" s="180" t="s">
+        <v>236</v>
+      </c>
+      <c r="B61" s="180" t="s">
+        <v>286</v>
+      </c>
+      <c r="C61" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="D61" s="181" t="s">
-        <v>284</v>
-      </c>
-      <c r="E61" s="181" t="s">
-        <v>285</v>
-      </c>
-      <c r="F61" s="181" t="s">
-        <v>286</v>
-      </c>
-      <c r="G61" s="181" t="s">
+      <c r="D61" s="180" t="s">
+        <v>287</v>
+      </c>
+      <c r="E61" s="180" t="s">
+        <v>288</v>
+      </c>
+      <c r="F61" s="180" t="s">
+        <v>289</v>
+      </c>
+      <c r="G61" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="H61" s="150"/>
-      <c r="I61" s="181" t="s">
-        <v>287</v>
-      </c>
-      <c r="J61" s="150" t="s">
-        <v>288</v>
+      <c r="H61" s="149"/>
+      <c r="I61" s="180" t="s">
+        <v>290</v>
+      </c>
+      <c r="J61" s="149" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="151">
+      <c r="A62" s="150">
         <v>46143.0</v>
       </c>
-      <c r="B62" s="150" t="s">
-        <v>289</v>
-      </c>
-      <c r="C62" s="182">
+      <c r="B62" s="149" t="s">
+        <v>292</v>
+      </c>
+      <c r="C62" s="181">
         <v>11839.0</v>
       </c>
-      <c r="D62" s="183" t="b">
+      <c r="D62" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="150" t="s">
-        <v>290</v>
-      </c>
-      <c r="F62" s="150" t="s">
-        <v>291</v>
-      </c>
-      <c r="G62" s="182">
+      <c r="E62" s="149" t="s">
+        <v>293</v>
+      </c>
+      <c r="F62" s="149" t="s">
+        <v>294</v>
+      </c>
+      <c r="G62" s="181">
         <v>71000.0</v>
       </c>
-      <c r="H62" s="150"/>
-      <c r="I62" s="181" t="s">
-        <v>292</v>
-      </c>
-      <c r="J62" s="182">
+      <c r="H62" s="149"/>
+      <c r="I62" s="180" t="s">
+        <v>295</v>
+      </c>
+      <c r="J62" s="181">
         <f>SUM(C62:C1000)</f>
         <v>84657</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="151">
+      <c r="A63" s="150">
         <v>46144.0</v>
       </c>
-      <c r="B63" s="150" t="s">
-        <v>293</v>
-      </c>
-      <c r="C63" s="182">
+      <c r="B63" s="149" t="s">
+        <v>296</v>
+      </c>
+      <c r="C63" s="181">
         <v>3850.0</v>
       </c>
-      <c r="D63" s="183" t="b">
+      <c r="D63" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="150" t="s">
-        <v>294</v>
-      </c>
-      <c r="F63" s="150"/>
-      <c r="G63" s="184"/>
-      <c r="H63" s="150"/>
-      <c r="I63" s="181" t="s">
-        <v>274</v>
-      </c>
-      <c r="J63" s="182">
+      <c r="E63" s="149" t="s">
+        <v>297</v>
+      </c>
+      <c r="F63" s="149"/>
+      <c r="G63" s="183"/>
+      <c r="H63" s="149"/>
+      <c r="I63" s="180" t="s">
+        <v>277</v>
+      </c>
+      <c r="J63" s="181">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
         <v>50435</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="151">
+      <c r="A64" s="150">
         <v>46145.0</v>
       </c>
-      <c r="B64" s="150" t="s">
-        <v>295</v>
-      </c>
-      <c r="C64" s="182">
+      <c r="B64" s="149" t="s">
+        <v>298</v>
+      </c>
+      <c r="C64" s="181">
         <v>4627.0</v>
       </c>
-      <c r="D64" s="183" t="b">
+      <c r="D64" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="150"/>
-      <c r="F64" s="150"/>
-      <c r="G64" s="184"/>
-      <c r="H64" s="150"/>
-      <c r="I64" s="181" t="s">
-        <v>296</v>
-      </c>
-      <c r="J64" s="182">
+      <c r="E64" s="149"/>
+      <c r="F64" s="149"/>
+      <c r="G64" s="183"/>
+      <c r="H64" s="149"/>
+      <c r="I64" s="180" t="s">
+        <v>299</v>
+      </c>
+      <c r="J64" s="181">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
         <v>34222</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="151">
+      <c r="A65" s="150">
         <v>46147.0</v>
       </c>
-      <c r="B65" s="150" t="s">
-        <v>297</v>
-      </c>
-      <c r="C65" s="182">
+      <c r="B65" s="149" t="s">
+        <v>300</v>
+      </c>
+      <c r="C65" s="181">
         <v>5000.0</v>
       </c>
-      <c r="D65" s="183" t="b">
+      <c r="D65" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="150"/>
-      <c r="F65" s="150"/>
-      <c r="G65" s="184"/>
-      <c r="H65" s="150"/>
-      <c r="I65" s="181" t="s">
-        <v>298</v>
-      </c>
-      <c r="J65" s="182">
+      <c r="E65" s="149"/>
+      <c r="F65" s="149"/>
+      <c r="G65" s="183"/>
+      <c r="H65" s="149"/>
+      <c r="I65" s="180" t="s">
+        <v>301</v>
+      </c>
+      <c r="J65" s="181">
         <f>SUM(G62:G1000)</f>
         <v>71000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="151">
+      <c r="A66" s="150">
         <v>46167.0</v>
       </c>
-      <c r="B66" s="150" t="s">
-        <v>299</v>
-      </c>
-      <c r="C66" s="182">
+      <c r="B66" s="149" t="s">
+        <v>302</v>
+      </c>
+      <c r="C66" s="181">
         <v>18972.0</v>
       </c>
-      <c r="D66" s="183" t="b">
+      <c r="D66" s="182" t="b">
         <v>0</v>
       </c>
-      <c r="E66" s="185">
+      <c r="E66" s="184">
         <v>97110.0</v>
       </c>
-      <c r="F66" s="150"/>
-      <c r="G66" s="184"/>
-      <c r="H66" s="150"/>
-      <c r="I66" s="181" t="s">
-        <v>300</v>
-      </c>
-      <c r="J66" s="182">
+      <c r="F66" s="149"/>
+      <c r="G66" s="183"/>
+      <c r="H66" s="149"/>
+      <c r="I66" s="180" t="s">
+        <v>303</v>
+      </c>
+      <c r="J66" s="181">
         <f>J65-J62</f>
         <v>-13657</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="151">
+      <c r="A67" s="150">
         <v>46146.0</v>
       </c>
-      <c r="B67" s="150" t="s">
-        <v>301</v>
-      </c>
-      <c r="C67" s="182">
+      <c r="B67" s="149" t="s">
+        <v>304</v>
+      </c>
+      <c r="C67" s="181">
         <v>13625.0</v>
       </c>
-      <c r="D67" s="183" t="b">
+      <c r="D67" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="150" t="s">
-        <v>302</v>
-      </c>
-      <c r="F67" s="150"/>
-      <c r="G67" s="184"/>
-      <c r="H67" s="150"/>
-      <c r="I67" s="150"/>
-      <c r="J67" s="150"/>
+      <c r="E67" s="149" t="s">
+        <v>305</v>
+      </c>
+      <c r="F67" s="149"/>
+      <c r="G67" s="183"/>
+      <c r="H67" s="149"/>
+      <c r="I67" s="149"/>
+      <c r="J67" s="149"/>
     </row>
     <row r="68">
-      <c r="A68" s="151">
+      <c r="A68" s="150">
         <v>46145.0</v>
       </c>
-      <c r="B68" s="150" t="s">
-        <v>303</v>
-      </c>
-      <c r="C68" s="182">
+      <c r="B68" s="149" t="s">
+        <v>306</v>
+      </c>
+      <c r="C68" s="181">
         <v>2494.0</v>
       </c>
-      <c r="D68" s="183" t="b">
+      <c r="D68" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="150"/>
-      <c r="F68" s="150"/>
-      <c r="G68" s="184"/>
-      <c r="H68" s="150"/>
-      <c r="I68" s="150"/>
-      <c r="J68" s="150"/>
+      <c r="E68" s="149"/>
+      <c r="F68" s="149"/>
+      <c r="G68" s="183"/>
+      <c r="H68" s="149"/>
+      <c r="I68" s="149"/>
+      <c r="J68" s="149"/>
     </row>
     <row r="69">
-      <c r="A69" s="151">
+      <c r="A69" s="150">
         <v>46144.0</v>
       </c>
-      <c r="B69" s="150" t="s">
-        <v>304</v>
-      </c>
-      <c r="C69" s="182">
+      <c r="B69" s="149" t="s">
+        <v>307</v>
+      </c>
+      <c r="C69" s="181">
         <v>4500.0</v>
       </c>
-      <c r="D69" s="183" t="b">
+      <c r="D69" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E69" s="150"/>
-      <c r="F69" s="150"/>
-      <c r="G69" s="184"/>
-      <c r="H69" s="150"/>
-      <c r="I69" s="150"/>
-      <c r="J69" s="150"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="183"/>
+      <c r="H69" s="149"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="149"/>
     </row>
     <row r="70">
-      <c r="A70" s="151">
+      <c r="A70" s="150">
         <v>46152.0</v>
       </c>
-      <c r="B70" s="150" t="s">
-        <v>305</v>
-      </c>
-      <c r="C70" s="182">
+      <c r="B70" s="149" t="s">
+        <v>308</v>
+      </c>
+      <c r="C70" s="181">
         <v>1500.0</v>
       </c>
-      <c r="D70" s="183" t="b">
+      <c r="D70" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="150"/>
-      <c r="F70" s="150"/>
-      <c r="G70" s="184"/>
-      <c r="H70" s="150"/>
-      <c r="I70" s="150"/>
-      <c r="J70" s="150"/>
+      <c r="E70" s="149"/>
+      <c r="F70" s="149"/>
+      <c r="G70" s="183"/>
+      <c r="H70" s="149"/>
+      <c r="I70" s="149"/>
+      <c r="J70" s="149"/>
     </row>
     <row r="71">
-      <c r="A71" s="151">
+      <c r="A71" s="150">
         <v>46152.0</v>
       </c>
-      <c r="B71" s="150" t="s">
-        <v>306</v>
-      </c>
-      <c r="C71" s="182">
+      <c r="B71" s="149" t="s">
+        <v>309</v>
+      </c>
+      <c r="C71" s="181">
         <v>3000.0</v>
       </c>
-      <c r="D71" s="183" t="b">
+      <c r="D71" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E71" s="150"/>
-      <c r="F71" s="150"/>
-      <c r="G71" s="184"/>
-      <c r="H71" s="150"/>
-      <c r="I71" s="150"/>
-      <c r="J71" s="150"/>
+      <c r="E71" s="149"/>
+      <c r="F71" s="149"/>
+      <c r="G71" s="183"/>
+      <c r="H71" s="149"/>
+      <c r="I71" s="149"/>
+      <c r="J71" s="149"/>
     </row>
     <row r="72">
-      <c r="A72" s="151">
+      <c r="A72" s="150">
         <v>46157.0</v>
       </c>
-      <c r="B72" s="150" t="s">
-        <v>307</v>
-      </c>
-      <c r="C72" s="182">
+      <c r="B72" s="149" t="s">
+        <v>310</v>
+      </c>
+      <c r="C72" s="181">
         <v>15250.0</v>
       </c>
-      <c r="D72" s="183" t="b">
+      <c r="D72" s="182" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="150"/>
-      <c r="F72" s="150"/>
-      <c r="G72" s="184"/>
-      <c r="H72" s="150"/>
-      <c r="I72" s="150"/>
-      <c r="J72" s="150"/>
+      <c r="E72" s="149"/>
+      <c r="F72" s="149"/>
+      <c r="G72" s="183"/>
+      <c r="H72" s="149"/>
+      <c r="I72" s="149"/>
+      <c r="J72" s="149"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8628,7 +8628,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20060.74521</v>
+        <v>20178.74959</v>
       </c>
     </row>
     <row r="6">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13455.61644</v>
+        <v>13518.49315</v>
       </c>
     </row>
     <row r="7">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>949.3150685</v>
+        <v>1035.616438</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8628,7 +8628,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20178.74959</v>
+        <v>20296.75397</v>
       </c>
     </row>
     <row r="6">
@@ -8652,7 +8652,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13518.49315</v>
+        <v>13581.36986</v>
       </c>
     </row>
     <row r="7">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1035.616438</v>
+        <v>1121.917808</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="327">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -438,7 +438,7 @@
     <t>TO Amma</t>
   </si>
   <si>
-    <t>Siva Priya</t>
+    <t>Siva Priya Loan</t>
   </si>
   <si>
     <t>APPA</t>
@@ -462,13 +462,61 @@
     <t>From Raghuls 6250                           2 June</t>
   </si>
   <si>
-    <t>Naresh shoe &amp; cable - June 7</t>
-  </si>
-  <si>
-    <t>Internet</t>
-  </si>
-  <si>
-    <t>WIFI BILL - June 8</t>
+    <t>D Mart</t>
+  </si>
+  <si>
+    <t>Naresh gave 11,000.                     6/2/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">snacks </t>
+  </si>
+  <si>
+    <t>Veera kattu potathu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TVS </t>
+  </si>
+  <si>
+    <t>(4K from Raghuls&amp; 1k Naresh).  6/4/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Home expense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Gold Loan.                                 5 June </t>
+  </si>
+  <si>
+    <t>Veera Scooty EMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">எண்ணெய் செட்டியார் </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plumper </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sivapriya Tablet </t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Gold Loan.                                 6 June </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Veera Hospital Expenses </t>
+  </si>
+  <si>
+    <t>Equitas Home loan</t>
+  </si>
+  <si>
+    <t>Appa Amma Dress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groceries </t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Gold Loan.                                 7 June </t>
+  </si>
+  <si>
+    <t>Muthu Chithapa</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -961,17 +1009,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0;\(&quot;₹&quot;#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="₹#,##0"/>
     <numFmt numFmtId="167" formatCode="mmm yyyy"/>
     <numFmt numFmtId="168" formatCode="₹#,##0.00"/>
     <numFmt numFmtId="169" formatCode="d mmmm"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="172" formatCode="d mmm yyyy"/>
-    <numFmt numFmtId="173" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="170" formatCode="mmmm yyyy"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="173" formatCode="d mmm yyyy"/>
+    <numFmt numFmtId="174" formatCode="d mmmm yyyy"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1346,7 +1395,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="186">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1654,6 +1703,9 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="168" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1671,13 +1723,13 @@
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1765,7 +1817,7 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1774,10 +1826,10 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="174" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -4006,11 +4058,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>29893</v>
+        <v>74178</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-13229</v>
+        <v>-57514</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -7888,7 +7940,7 @@
         <v>138</v>
       </c>
       <c r="C5" s="102">
-        <v>11000.0</v>
+        <v>12000.0</v>
       </c>
       <c r="D5" s="103">
         <v>46174.0</v>
@@ -8013,547 +8065,649 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="100">
+      <c r="A13" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B13" s="101" t="s">
+        <v>146</v>
+      </c>
+      <c r="C13" s="102">
+        <v>9975.0</v>
+      </c>
+      <c r="D13" s="101" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B14" s="101" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="102">
+        <v>185.0</v>
+      </c>
+      <c r="D14" s="101" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B15" s="101" t="s">
+        <v>149</v>
+      </c>
+      <c r="C15" s="102">
+        <v>650.0</v>
+      </c>
+      <c r="D15" s="101" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B16" s="101" t="s">
+        <v>150</v>
+      </c>
+      <c r="C16" s="102">
+        <v>5077.0</v>
+      </c>
+      <c r="D16" s="101" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B17" s="101" t="s">
+        <v>152</v>
+      </c>
+      <c r="C17" s="102">
+        <v>716.0</v>
+      </c>
+      <c r="D17" s="101" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="109">
+        <v>46175.0</v>
+      </c>
+      <c r="B18" s="101" t="s">
+        <v>154</v>
+      </c>
+      <c r="C18" s="102">
+        <v>5000.0</v>
+      </c>
+      <c r="D18" s="101" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="109">
+        <v>46176.0</v>
+      </c>
+      <c r="B19" s="101" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="102">
+        <v>2000.0</v>
+      </c>
+      <c r="D19" s="101" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="109">
+        <v>46177.0</v>
+      </c>
+      <c r="B20" s="101" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="102">
+        <v>240.0</v>
+      </c>
+      <c r="D20" s="101" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="109">
+        <v>46178.0</v>
+      </c>
+      <c r="B21" s="101" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="102">
+        <v>512.0</v>
+      </c>
+      <c r="D21" s="101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="109">
+        <v>46179.0</v>
+      </c>
+      <c r="B22" s="101" t="s">
+        <v>159</v>
+      </c>
+      <c r="C22" s="102">
+        <v>3000.0</v>
+      </c>
+      <c r="D22" s="101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="109">
+        <v>46180.0</v>
+      </c>
+      <c r="B23" s="101" t="s">
+        <v>160</v>
+      </c>
+      <c r="C23" s="102">
+        <v>15230.0</v>
+      </c>
+      <c r="D23" s="101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="109">
+        <v>46181.0</v>
+      </c>
+      <c r="B24" s="101" t="s">
+        <v>161</v>
+      </c>
+      <c r="C24" s="102">
+        <v>1950.0</v>
+      </c>
+      <c r="D24" s="101" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="109">
+        <v>46182.0</v>
+      </c>
+      <c r="B25" s="101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C25" s="102">
+        <v>500.0</v>
+      </c>
+      <c r="D25" s="101" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="109">
         <v>46183.0</v>
       </c>
-      <c r="B13" s="101" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13" s="102">
-        <v>2000.0</v>
-      </c>
-      <c r="D13" s="101" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="100">
+      <c r="B26" s="101" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="102">
+        <v>850.0</v>
+      </c>
+      <c r="D26" s="101" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="109">
         <v>46184.0</v>
       </c>
-      <c r="B14" s="101" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" s="102">
-        <v>600.0</v>
-      </c>
-      <c r="D14" s="101" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="108"/>
-      <c r="B15" s="108"/>
-      <c r="C15" s="109"/>
-      <c r="D15" s="108"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="108"/>
-      <c r="B16" s="108"/>
-      <c r="C16" s="109"/>
-      <c r="D16" s="108"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="108"/>
-      <c r="B17" s="108"/>
-      <c r="C17" s="109"/>
-      <c r="D17" s="108"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="108"/>
-      <c r="B18" s="108"/>
-      <c r="C18" s="109"/>
-      <c r="D18" s="108"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="108"/>
-      <c r="B19" s="108"/>
-      <c r="C19" s="109"/>
-      <c r="D19" s="108"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="108"/>
-      <c r="B20" s="108"/>
-      <c r="C20" s="109"/>
-      <c r="D20" s="108"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="108"/>
-      <c r="B21" s="108"/>
-      <c r="C21" s="109"/>
-      <c r="D21" s="108"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="108"/>
-      <c r="B22" s="108"/>
-      <c r="C22" s="109"/>
-      <c r="D22" s="108"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="108"/>
-      <c r="B23" s="108"/>
-      <c r="C23" s="109"/>
-      <c r="D23" s="108"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="108"/>
-      <c r="B24" s="108"/>
-      <c r="C24" s="109"/>
-      <c r="D24" s="108"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="108"/>
-      <c r="B25" s="108"/>
-      <c r="C25" s="109"/>
-      <c r="D25" s="108"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="108"/>
-      <c r="B26" s="108"/>
-      <c r="C26" s="109"/>
-      <c r="D26" s="108"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="108"/>
       <c r="B27" s="108"/>
-      <c r="C27" s="109"/>
+      <c r="C27" s="110"/>
       <c r="D27" s="108"/>
     </row>
     <row r="28">
-      <c r="A28" s="108"/>
+      <c r="A28" s="109">
+        <v>46185.0</v>
+      </c>
       <c r="B28" s="108"/>
-      <c r="C28" s="109"/>
+      <c r="C28" s="110"/>
       <c r="D28" s="108"/>
     </row>
     <row r="29">
-      <c r="A29" s="108"/>
+      <c r="A29" s="109">
+        <v>46186.0</v>
+      </c>
       <c r="B29" s="108"/>
-      <c r="C29" s="109"/>
+      <c r="C29" s="110"/>
       <c r="D29" s="108"/>
     </row>
     <row r="30">
       <c r="A30" s="108"/>
       <c r="B30" s="108"/>
-      <c r="C30" s="109"/>
+      <c r="C30" s="110"/>
       <c r="D30" s="108"/>
     </row>
     <row r="31">
       <c r="A31" s="108"/>
       <c r="B31" s="108"/>
-      <c r="C31" s="109"/>
+      <c r="C31" s="110"/>
       <c r="D31" s="108"/>
     </row>
     <row r="32">
       <c r="A32" s="108"/>
       <c r="B32" s="108"/>
-      <c r="C32" s="109"/>
+      <c r="C32" s="110"/>
       <c r="D32" s="108"/>
     </row>
     <row r="33">
       <c r="A33" s="108"/>
       <c r="B33" s="108"/>
-      <c r="C33" s="109"/>
+      <c r="C33" s="110"/>
       <c r="D33" s="108"/>
     </row>
     <row r="34">
       <c r="A34" s="108"/>
       <c r="B34" s="108"/>
-      <c r="C34" s="109"/>
+      <c r="C34" s="110"/>
       <c r="D34" s="108"/>
     </row>
     <row r="35">
       <c r="A35" s="108"/>
       <c r="B35" s="108"/>
-      <c r="C35" s="109"/>
+      <c r="C35" s="110"/>
       <c r="D35" s="108"/>
     </row>
     <row r="36">
       <c r="A36" s="108"/>
       <c r="B36" s="108"/>
-      <c r="C36" s="109"/>
+      <c r="C36" s="110"/>
       <c r="D36" s="108"/>
     </row>
     <row r="37">
       <c r="A37" s="108"/>
       <c r="B37" s="108"/>
-      <c r="C37" s="109"/>
+      <c r="C37" s="110"/>
       <c r="D37" s="108"/>
     </row>
     <row r="38">
       <c r="A38" s="108"/>
       <c r="B38" s="108"/>
-      <c r="C38" s="109"/>
+      <c r="C38" s="110"/>
       <c r="D38" s="108"/>
     </row>
     <row r="39">
       <c r="A39" s="108"/>
       <c r="B39" s="108"/>
-      <c r="C39" s="109"/>
+      <c r="C39" s="110"/>
       <c r="D39" s="108"/>
     </row>
     <row r="40">
       <c r="A40" s="108"/>
       <c r="B40" s="108"/>
-      <c r="C40" s="109"/>
+      <c r="C40" s="110"/>
       <c r="D40" s="108"/>
     </row>
     <row r="41">
       <c r="A41" s="108"/>
       <c r="B41" s="108"/>
-      <c r="C41" s="109"/>
+      <c r="C41" s="110"/>
       <c r="D41" s="108"/>
     </row>
     <row r="42">
       <c r="A42" s="108"/>
       <c r="B42" s="108"/>
-      <c r="C42" s="109"/>
+      <c r="C42" s="110"/>
       <c r="D42" s="108"/>
     </row>
     <row r="43">
       <c r="A43" s="108"/>
       <c r="B43" s="108"/>
-      <c r="C43" s="109"/>
+      <c r="C43" s="110"/>
       <c r="D43" s="108"/>
     </row>
     <row r="44">
       <c r="A44" s="108"/>
       <c r="B44" s="108"/>
-      <c r="C44" s="109"/>
+      <c r="C44" s="110"/>
       <c r="D44" s="108"/>
     </row>
     <row r="45">
       <c r="A45" s="108"/>
       <c r="B45" s="108"/>
-      <c r="C45" s="109"/>
+      <c r="C45" s="110"/>
       <c r="D45" s="108"/>
     </row>
     <row r="46">
       <c r="A46" s="108"/>
       <c r="B46" s="108"/>
-      <c r="C46" s="109"/>
+      <c r="C46" s="110"/>
       <c r="D46" s="108"/>
     </row>
     <row r="47">
       <c r="A47" s="108"/>
       <c r="B47" s="108"/>
-      <c r="C47" s="109"/>
+      <c r="C47" s="110"/>
       <c r="D47" s="108"/>
     </row>
     <row r="48">
       <c r="A48" s="108"/>
       <c r="B48" s="108"/>
-      <c r="C48" s="109"/>
+      <c r="C48" s="110"/>
       <c r="D48" s="108"/>
     </row>
     <row r="49">
       <c r="A49" s="108"/>
       <c r="B49" s="108"/>
-      <c r="C49" s="109"/>
+      <c r="C49" s="110"/>
       <c r="D49" s="108"/>
     </row>
     <row r="50">
       <c r="A50" s="108"/>
       <c r="B50" s="108"/>
-      <c r="C50" s="109"/>
+      <c r="C50" s="110"/>
       <c r="D50" s="108"/>
     </row>
     <row r="51">
       <c r="A51" s="108"/>
       <c r="B51" s="108"/>
-      <c r="C51" s="109"/>
+      <c r="C51" s="110"/>
       <c r="D51" s="108"/>
     </row>
     <row r="52">
       <c r="A52" s="108"/>
       <c r="B52" s="108"/>
-      <c r="C52" s="109"/>
+      <c r="C52" s="110"/>
       <c r="D52" s="108"/>
     </row>
     <row r="53">
       <c r="A53" s="108"/>
       <c r="B53" s="108"/>
-      <c r="C53" s="109"/>
+      <c r="C53" s="110"/>
       <c r="D53" s="108"/>
     </row>
     <row r="54">
       <c r="A54" s="108"/>
       <c r="B54" s="108"/>
-      <c r="C54" s="109"/>
+      <c r="C54" s="110"/>
       <c r="D54" s="108"/>
     </row>
     <row r="55">
       <c r="A55" s="108"/>
       <c r="B55" s="108"/>
-      <c r="C55" s="109"/>
+      <c r="C55" s="110"/>
       <c r="D55" s="108"/>
     </row>
     <row r="56">
       <c r="A56" s="108"/>
       <c r="B56" s="108"/>
-      <c r="C56" s="109"/>
+      <c r="C56" s="110"/>
       <c r="D56" s="108"/>
     </row>
     <row r="57">
       <c r="A57" s="108"/>
       <c r="B57" s="108"/>
-      <c r="C57" s="109"/>
+      <c r="C57" s="110"/>
       <c r="D57" s="108"/>
     </row>
     <row r="58">
       <c r="A58" s="108"/>
       <c r="B58" s="108"/>
-      <c r="C58" s="109"/>
+      <c r="C58" s="110"/>
       <c r="D58" s="108"/>
     </row>
     <row r="59">
       <c r="A59" s="108"/>
       <c r="B59" s="108"/>
-      <c r="C59" s="109"/>
+      <c r="C59" s="110"/>
       <c r="D59" s="108"/>
     </row>
     <row r="60">
       <c r="A60" s="108"/>
       <c r="B60" s="108"/>
-      <c r="C60" s="109"/>
+      <c r="C60" s="110"/>
       <c r="D60" s="108"/>
     </row>
     <row r="61">
       <c r="A61" s="108"/>
       <c r="B61" s="108"/>
-      <c r="C61" s="109"/>
+      <c r="C61" s="110"/>
       <c r="D61" s="108"/>
     </row>
     <row r="62">
       <c r="A62" s="108"/>
       <c r="B62" s="108"/>
-      <c r="C62" s="109"/>
+      <c r="C62" s="110"/>
       <c r="D62" s="108"/>
     </row>
     <row r="63">
       <c r="A63" s="108"/>
       <c r="B63" s="108"/>
-      <c r="C63" s="109"/>
+      <c r="C63" s="110"/>
       <c r="D63" s="108"/>
     </row>
     <row r="64">
       <c r="A64" s="108"/>
       <c r="B64" s="108"/>
-      <c r="C64" s="109"/>
+      <c r="C64" s="110"/>
       <c r="D64" s="108"/>
     </row>
     <row r="65">
       <c r="A65" s="108"/>
       <c r="B65" s="108"/>
-      <c r="C65" s="109"/>
+      <c r="C65" s="110"/>
       <c r="D65" s="108"/>
     </row>
     <row r="66">
       <c r="A66" s="108"/>
       <c r="B66" s="108"/>
-      <c r="C66" s="109"/>
+      <c r="C66" s="110"/>
       <c r="D66" s="108"/>
     </row>
     <row r="67">
       <c r="A67" s="108"/>
       <c r="B67" s="108"/>
-      <c r="C67" s="109"/>
+      <c r="C67" s="110"/>
       <c r="D67" s="108"/>
     </row>
     <row r="68">
       <c r="A68" s="108"/>
       <c r="B68" s="108"/>
-      <c r="C68" s="109"/>
+      <c r="C68" s="110"/>
       <c r="D68" s="108"/>
     </row>
     <row r="69">
       <c r="A69" s="108"/>
       <c r="B69" s="108"/>
-      <c r="C69" s="109"/>
+      <c r="C69" s="110"/>
       <c r="D69" s="108"/>
     </row>
     <row r="70">
       <c r="A70" s="108"/>
       <c r="B70" s="108"/>
-      <c r="C70" s="109"/>
+      <c r="C70" s="110"/>
       <c r="D70" s="108"/>
     </row>
     <row r="71">
       <c r="A71" s="108"/>
       <c r="B71" s="108"/>
-      <c r="C71" s="109"/>
+      <c r="C71" s="110"/>
       <c r="D71" s="108"/>
     </row>
     <row r="72">
       <c r="A72" s="108"/>
       <c r="B72" s="108"/>
-      <c r="C72" s="109"/>
+      <c r="C72" s="110"/>
       <c r="D72" s="108"/>
     </row>
     <row r="73">
       <c r="A73" s="108"/>
       <c r="B73" s="108"/>
-      <c r="C73" s="109"/>
+      <c r="C73" s="110"/>
       <c r="D73" s="108"/>
     </row>
     <row r="74">
       <c r="A74" s="108"/>
       <c r="B74" s="108"/>
-      <c r="C74" s="109"/>
+      <c r="C74" s="110"/>
       <c r="D74" s="108"/>
     </row>
     <row r="75">
       <c r="A75" s="108"/>
       <c r="B75" s="108"/>
-      <c r="C75" s="109"/>
+      <c r="C75" s="110"/>
       <c r="D75" s="108"/>
     </row>
     <row r="76">
       <c r="A76" s="108"/>
       <c r="B76" s="108"/>
-      <c r="C76" s="109"/>
+      <c r="C76" s="110"/>
       <c r="D76" s="108"/>
     </row>
     <row r="77">
       <c r="A77" s="108"/>
       <c r="B77" s="108"/>
-      <c r="C77" s="109"/>
+      <c r="C77" s="110"/>
       <c r="D77" s="108"/>
     </row>
     <row r="78">
       <c r="A78" s="108"/>
       <c r="B78" s="108"/>
-      <c r="C78" s="109"/>
+      <c r="C78" s="110"/>
       <c r="D78" s="108"/>
     </row>
     <row r="79">
       <c r="A79" s="108"/>
       <c r="B79" s="108"/>
-      <c r="C79" s="109"/>
+      <c r="C79" s="110"/>
       <c r="D79" s="108"/>
     </row>
     <row r="80">
       <c r="A80" s="108"/>
       <c r="B80" s="108"/>
-      <c r="C80" s="109"/>
+      <c r="C80" s="110"/>
       <c r="D80" s="108"/>
     </row>
     <row r="81">
       <c r="A81" s="108"/>
       <c r="B81" s="108"/>
-      <c r="C81" s="109"/>
+      <c r="C81" s="110"/>
       <c r="D81" s="108"/>
     </row>
     <row r="82">
       <c r="A82" s="108"/>
       <c r="B82" s="108"/>
-      <c r="C82" s="109"/>
+      <c r="C82" s="110"/>
       <c r="D82" s="108"/>
     </row>
     <row r="83">
       <c r="A83" s="108"/>
       <c r="B83" s="108"/>
-      <c r="C83" s="109"/>
+      <c r="C83" s="110"/>
       <c r="D83" s="108"/>
     </row>
     <row r="84">
       <c r="A84" s="108"/>
       <c r="B84" s="108"/>
-      <c r="C84" s="109"/>
+      <c r="C84" s="110"/>
       <c r="D84" s="108"/>
     </row>
     <row r="85">
       <c r="A85" s="108"/>
       <c r="B85" s="108"/>
-      <c r="C85" s="109"/>
+      <c r="C85" s="110"/>
       <c r="D85" s="108"/>
     </row>
     <row r="86">
       <c r="A86" s="108"/>
       <c r="B86" s="108"/>
-      <c r="C86" s="109"/>
+      <c r="C86" s="110"/>
       <c r="D86" s="108"/>
     </row>
     <row r="87">
       <c r="A87" s="108"/>
       <c r="B87" s="108"/>
-      <c r="C87" s="109"/>
+      <c r="C87" s="110"/>
       <c r="D87" s="108"/>
     </row>
     <row r="88">
       <c r="A88" s="108"/>
       <c r="B88" s="108"/>
-      <c r="C88" s="109"/>
+      <c r="C88" s="110"/>
       <c r="D88" s="108"/>
     </row>
     <row r="89">
       <c r="A89" s="108"/>
       <c r="B89" s="108"/>
-      <c r="C89" s="109"/>
+      <c r="C89" s="110"/>
       <c r="D89" s="108"/>
     </row>
     <row r="90">
       <c r="A90" s="108"/>
       <c r="B90" s="108"/>
-      <c r="C90" s="109"/>
+      <c r="C90" s="110"/>
       <c r="D90" s="108"/>
     </row>
     <row r="91">
       <c r="A91" s="108"/>
       <c r="B91" s="108"/>
-      <c r="C91" s="109"/>
+      <c r="C91" s="110"/>
       <c r="D91" s="108"/>
     </row>
     <row r="92">
       <c r="A92" s="108"/>
       <c r="B92" s="108"/>
-      <c r="C92" s="109"/>
+      <c r="C92" s="110"/>
       <c r="D92" s="108"/>
     </row>
     <row r="93">
       <c r="A93" s="108"/>
       <c r="B93" s="108"/>
-      <c r="C93" s="109"/>
+      <c r="C93" s="110"/>
       <c r="D93" s="108"/>
     </row>
     <row r="94">
       <c r="A94" s="108"/>
       <c r="B94" s="108"/>
-      <c r="C94" s="109"/>
+      <c r="C94" s="110"/>
       <c r="D94" s="108"/>
     </row>
     <row r="95">
       <c r="A95" s="108"/>
       <c r="B95" s="108"/>
-      <c r="C95" s="109"/>
+      <c r="C95" s="110"/>
       <c r="D95" s="108"/>
     </row>
     <row r="96">
       <c r="A96" s="108"/>
       <c r="B96" s="108"/>
-      <c r="C96" s="109"/>
+      <c r="C96" s="110"/>
       <c r="D96" s="108"/>
     </row>
     <row r="97">
       <c r="A97" s="108"/>
       <c r="B97" s="108"/>
-      <c r="C97" s="109"/>
+      <c r="C97" s="110"/>
       <c r="D97" s="108"/>
     </row>
     <row r="98">
       <c r="A98" s="108"/>
       <c r="B98" s="108"/>
-      <c r="C98" s="109"/>
+      <c r="C98" s="110"/>
       <c r="D98" s="108"/>
     </row>
     <row r="99">
       <c r="A99" s="108"/>
       <c r="B99" s="108"/>
-      <c r="C99" s="109"/>
+      <c r="C99" s="110"/>
       <c r="D99" s="108"/>
     </row>
     <row r="100">
       <c r="A100" s="108"/>
       <c r="B100" s="108"/>
-      <c r="C100" s="109"/>
+      <c r="C100" s="110"/>
       <c r="D100" s="108"/>
     </row>
   </sheetData>
@@ -8580,120 +8734,120 @@
   <sheetData>
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
-      <c r="B2" s="110" t="s">
-        <v>149</v>
+      <c r="B2" s="111" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="111" t="s">
-        <v>150</v>
-      </c>
-      <c r="C4" s="111" t="s">
-        <v>151</v>
-      </c>
-      <c r="D4" s="111" t="s">
-        <v>152</v>
-      </c>
-      <c r="E4" s="111" t="s">
-        <v>153</v>
-      </c>
-      <c r="F4" s="111" t="s">
-        <v>154</v>
-      </c>
-      <c r="G4" s="111" t="s">
-        <v>155</v>
-      </c>
-      <c r="H4" s="112" t="s">
-        <v>156</v>
+      <c r="B4" s="112" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="112" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" s="112" t="s">
+        <v>168</v>
+      </c>
+      <c r="E4" s="112" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="112" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="112" t="s">
+        <v>171</v>
+      </c>
+      <c r="H4" s="113" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="113">
+      <c r="B5" s="114">
         <v>55.8</v>
       </c>
-      <c r="C5" s="114">
+      <c r="C5" s="115">
         <v>0.11</v>
       </c>
-      <c r="D5" s="113" t="s">
-        <v>157</v>
-      </c>
-      <c r="E5" s="113" t="s">
-        <v>158</v>
-      </c>
-      <c r="F5" s="115">
+      <c r="D5" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" s="114" t="s">
+        <v>174</v>
+      </c>
+      <c r="F5" s="116">
         <v>391560.0</v>
       </c>
-      <c r="G5" s="116">
+      <c r="G5" s="117">
         <v>46010.0</v>
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20296.75397</v>
+        <v>20414.75836</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="113">
+      <c r="B6" s="114">
         <v>30.0</v>
       </c>
-      <c r="C6" s="114">
+      <c r="C6" s="115">
         <v>0.1</v>
       </c>
-      <c r="D6" s="113" t="s">
-        <v>157</v>
-      </c>
-      <c r="E6" s="113" t="s">
-        <v>159</v>
-      </c>
-      <c r="F6" s="115">
+      <c r="D6" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E6" s="114" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6" s="116">
         <v>229500.0</v>
       </c>
-      <c r="G6" s="116">
+      <c r="G6" s="117">
         <v>45966.0</v>
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13581.36986</v>
+        <v>13644.24658</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="113">
+      <c r="B7" s="114">
         <v>36.9</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="115">
         <v>0.105</v>
       </c>
-      <c r="D7" s="113" t="s">
-        <v>157</v>
-      </c>
-      <c r="E7" s="113" t="s">
-        <v>160</v>
-      </c>
-      <c r="F7" s="115">
+      <c r="D7" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="114" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" s="116">
         <v>300000.0</v>
       </c>
-      <c r="G7" s="116">
+      <c r="G7" s="117">
         <v>46169.0</v>
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1121.917808</v>
+        <v>1208.219178</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="113">
+      <c r="B8" s="114">
         <v>15.0</v>
       </c>
-      <c r="C8" s="117"/>
-      <c r="D8" s="113" t="s">
-        <v>157</v>
-      </c>
-      <c r="E8" s="113" t="s">
-        <v>160</v>
-      </c>
-      <c r="F8" s="115">
+      <c r="C8" s="118"/>
+      <c r="D8" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E8" s="114" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="116">
         <v>135000.0</v>
       </c>
-      <c r="G8" s="116">
+      <c r="G8" s="117">
         <v>46178.0</v>
       </c>
       <c r="H8" s="10">
@@ -8702,18 +8856,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="118"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="113" t="s">
-        <v>157</v>
-      </c>
-      <c r="E9" s="113" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="115">
+      <c r="B9" s="119"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="114" t="s">
+        <v>173</v>
+      </c>
+      <c r="E9" s="114" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="116">
         <v>297698.0</v>
       </c>
-      <c r="G9" s="116">
+      <c r="G9" s="117">
         <v>46035.0</v>
       </c>
       <c r="H9" s="10">
@@ -8722,1044 +8876,1044 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="118"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="118"/>
-      <c r="E10" s="118"/>
-      <c r="F10" s="119"/>
-      <c r="G10" s="120"/>
+      <c r="B10" s="119"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="119"/>
+      <c r="E10" s="119"/>
+      <c r="F10" s="120"/>
+      <c r="G10" s="121"/>
       <c r="H10" s="10" t="str">
         <f t="shared" ref="H10:H96" si="2">IF(OR(ISBLANK(F10), ISBLANK(G10)), "", F10 * (C10/100) * (TODAY() - G10) / 365)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="118"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="118"/>
-      <c r="F11" s="119"/>
-      <c r="G11" s="120"/>
+      <c r="B11" s="119"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="119"/>
+      <c r="E11" s="119"/>
+      <c r="F11" s="120"/>
+      <c r="G11" s="121"/>
       <c r="H11" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="118"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="119"/>
-      <c r="G12" s="120"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="120"/>
+      <c r="G12" s="121"/>
       <c r="H12" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="118"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="118"/>
-      <c r="E13" s="118"/>
-      <c r="F13" s="119"/>
-      <c r="G13" s="120"/>
+      <c r="B13" s="119"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="120"/>
+      <c r="G13" s="121"/>
       <c r="H13" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="118"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="118"/>
-      <c r="F14" s="119"/>
-      <c r="G14" s="120"/>
+      <c r="B14" s="119"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="120"/>
+      <c r="G14" s="121"/>
       <c r="H14" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="118"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="118"/>
-      <c r="E15" s="118"/>
-      <c r="F15" s="119"/>
-      <c r="G15" s="120"/>
+      <c r="B15" s="119"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="121"/>
       <c r="H15" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="118"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="118"/>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="120"/>
+      <c r="B16" s="119"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="120"/>
+      <c r="G16" s="121"/>
       <c r="H16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="118"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="118"/>
-      <c r="F17" s="119"/>
-      <c r="G17" s="120"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="120"/>
+      <c r="G17" s="121"/>
       <c r="H17" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="118"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="118"/>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="120"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="120"/>
+      <c r="G18" s="121"/>
       <c r="H18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="118"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="118"/>
-      <c r="E19" s="118"/>
-      <c r="F19" s="119"/>
-      <c r="G19" s="120"/>
+      <c r="B19" s="119"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="120"/>
+      <c r="G19" s="121"/>
       <c r="H19" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="118"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="118"/>
-      <c r="F20" s="119"/>
-      <c r="G20" s="120"/>
+      <c r="B20" s="119"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="120"/>
+      <c r="G20" s="121"/>
       <c r="H20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="118"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="118"/>
-      <c r="E21" s="118"/>
-      <c r="F21" s="119"/>
-      <c r="G21" s="120"/>
+      <c r="B21" s="119"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="120"/>
+      <c r="G21" s="121"/>
       <c r="H21" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="118"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="118"/>
-      <c r="E22" s="118"/>
-      <c r="F22" s="119"/>
-      <c r="G22" s="120"/>
+      <c r="B22" s="119"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="120"/>
+      <c r="G22" s="121"/>
       <c r="H22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="118"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="118"/>
-      <c r="E23" s="118"/>
-      <c r="F23" s="119"/>
-      <c r="G23" s="120"/>
+      <c r="B23" s="119"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="120"/>
+      <c r="G23" s="121"/>
       <c r="H23" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="118"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="118"/>
-      <c r="E24" s="118"/>
-      <c r="F24" s="119"/>
-      <c r="G24" s="120"/>
+      <c r="B24" s="119"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="120"/>
+      <c r="G24" s="121"/>
       <c r="H24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="118"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="118"/>
-      <c r="E25" s="118"/>
-      <c r="F25" s="119"/>
-      <c r="G25" s="120"/>
+      <c r="B25" s="119"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="119"/>
+      <c r="F25" s="120"/>
+      <c r="G25" s="121"/>
       <c r="H25" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="118"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="118"/>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="120"/>
+      <c r="B26" s="119"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="119"/>
+      <c r="E26" s="119"/>
+      <c r="F26" s="120"/>
+      <c r="G26" s="121"/>
       <c r="H26" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="118"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="118"/>
-      <c r="E27" s="118"/>
-      <c r="F27" s="119"/>
-      <c r="G27" s="120"/>
+      <c r="B27" s="119"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="119"/>
+      <c r="E27" s="119"/>
+      <c r="F27" s="120"/>
+      <c r="G27" s="121"/>
       <c r="H27" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="118"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="118"/>
-      <c r="E28" s="118"/>
-      <c r="F28" s="119"/>
-      <c r="G28" s="120"/>
+      <c r="B28" s="119"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="119"/>
+      <c r="E28" s="119"/>
+      <c r="F28" s="120"/>
+      <c r="G28" s="121"/>
       <c r="H28" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="118"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="118"/>
-      <c r="E29" s="118"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="120"/>
+      <c r="B29" s="119"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="120"/>
+      <c r="G29" s="121"/>
       <c r="H29" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="118"/>
-      <c r="C30" s="117"/>
-      <c r="D30" s="118"/>
-      <c r="E30" s="118"/>
-      <c r="F30" s="119"/>
-      <c r="G30" s="120"/>
+      <c r="B30" s="119"/>
+      <c r="C30" s="118"/>
+      <c r="D30" s="119"/>
+      <c r="E30" s="119"/>
+      <c r="F30" s="120"/>
+      <c r="G30" s="121"/>
       <c r="H30" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="118"/>
-      <c r="C31" s="117"/>
-      <c r="D31" s="118"/>
-      <c r="E31" s="118"/>
-      <c r="F31" s="119"/>
-      <c r="G31" s="120"/>
+      <c r="B31" s="119"/>
+      <c r="C31" s="118"/>
+      <c r="D31" s="119"/>
+      <c r="E31" s="119"/>
+      <c r="F31" s="120"/>
+      <c r="G31" s="121"/>
       <c r="H31" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="118"/>
-      <c r="C32" s="117"/>
-      <c r="D32" s="118"/>
-      <c r="E32" s="118"/>
-      <c r="F32" s="119"/>
-      <c r="G32" s="120"/>
+      <c r="B32" s="119"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="119"/>
+      <c r="E32" s="119"/>
+      <c r="F32" s="120"/>
+      <c r="G32" s="121"/>
       <c r="H32" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="118"/>
-      <c r="C33" s="117"/>
-      <c r="D33" s="118"/>
-      <c r="E33" s="118"/>
-      <c r="F33" s="119"/>
-      <c r="G33" s="120"/>
+      <c r="B33" s="119"/>
+      <c r="C33" s="118"/>
+      <c r="D33" s="119"/>
+      <c r="E33" s="119"/>
+      <c r="F33" s="120"/>
+      <c r="G33" s="121"/>
       <c r="H33" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="118"/>
-      <c r="C34" s="117"/>
-      <c r="D34" s="118"/>
-      <c r="E34" s="118"/>
-      <c r="F34" s="119"/>
-      <c r="G34" s="120"/>
+      <c r="B34" s="119"/>
+      <c r="C34" s="118"/>
+      <c r="D34" s="119"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="120"/>
+      <c r="G34" s="121"/>
       <c r="H34" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="118"/>
-      <c r="C35" s="117"/>
-      <c r="D35" s="118"/>
-      <c r="E35" s="118"/>
-      <c r="F35" s="119"/>
-      <c r="G35" s="120"/>
+      <c r="B35" s="119"/>
+      <c r="C35" s="118"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="119"/>
+      <c r="F35" s="120"/>
+      <c r="G35" s="121"/>
       <c r="H35" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="118"/>
-      <c r="C36" s="117"/>
-      <c r="D36" s="118"/>
-      <c r="E36" s="118"/>
-      <c r="F36" s="119"/>
-      <c r="G36" s="120"/>
+      <c r="B36" s="119"/>
+      <c r="C36" s="118"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="119"/>
+      <c r="F36" s="120"/>
+      <c r="G36" s="121"/>
       <c r="H36" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="118"/>
-      <c r="C37" s="117"/>
-      <c r="D37" s="118"/>
-      <c r="E37" s="118"/>
-      <c r="F37" s="119"/>
-      <c r="G37" s="120"/>
+      <c r="B37" s="119"/>
+      <c r="C37" s="118"/>
+      <c r="D37" s="119"/>
+      <c r="E37" s="119"/>
+      <c r="F37" s="120"/>
+      <c r="G37" s="121"/>
       <c r="H37" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="118"/>
-      <c r="C38" s="117"/>
-      <c r="D38" s="118"/>
-      <c r="E38" s="118"/>
-      <c r="F38" s="119"/>
-      <c r="G38" s="120"/>
+      <c r="B38" s="119"/>
+      <c r="C38" s="118"/>
+      <c r="D38" s="119"/>
+      <c r="E38" s="119"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="121"/>
       <c r="H38" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="118"/>
-      <c r="C39" s="117"/>
-      <c r="D39" s="118"/>
-      <c r="E39" s="118"/>
-      <c r="F39" s="119"/>
-      <c r="G39" s="120"/>
+      <c r="B39" s="119"/>
+      <c r="C39" s="118"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="121"/>
       <c r="H39" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="118"/>
-      <c r="C40" s="117"/>
-      <c r="D40" s="118"/>
-      <c r="E40" s="118"/>
-      <c r="F40" s="119"/>
-      <c r="G40" s="120"/>
+      <c r="B40" s="119"/>
+      <c r="C40" s="118"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="121"/>
       <c r="H40" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="118"/>
-      <c r="C41" s="117"/>
-      <c r="D41" s="118"/>
-      <c r="E41" s="118"/>
-      <c r="F41" s="119"/>
-      <c r="G41" s="120"/>
+      <c r="B41" s="119"/>
+      <c r="C41" s="118"/>
+      <c r="D41" s="119"/>
+      <c r="E41" s="119"/>
+      <c r="F41" s="120"/>
+      <c r="G41" s="121"/>
       <c r="H41" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="118"/>
-      <c r="C42" s="117"/>
-      <c r="D42" s="118"/>
-      <c r="E42" s="118"/>
-      <c r="F42" s="119"/>
-      <c r="G42" s="120"/>
+      <c r="B42" s="119"/>
+      <c r="C42" s="118"/>
+      <c r="D42" s="119"/>
+      <c r="E42" s="119"/>
+      <c r="F42" s="120"/>
+      <c r="G42" s="121"/>
       <c r="H42" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="118"/>
-      <c r="C43" s="117"/>
-      <c r="D43" s="118"/>
-      <c r="E43" s="118"/>
-      <c r="F43" s="119"/>
-      <c r="G43" s="120"/>
+      <c r="B43" s="119"/>
+      <c r="C43" s="118"/>
+      <c r="D43" s="119"/>
+      <c r="E43" s="119"/>
+      <c r="F43" s="120"/>
+      <c r="G43" s="121"/>
       <c r="H43" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="118"/>
-      <c r="C44" s="117"/>
-      <c r="D44" s="118"/>
-      <c r="E44" s="118"/>
-      <c r="F44" s="119"/>
-      <c r="G44" s="120"/>
+      <c r="B44" s="119"/>
+      <c r="C44" s="118"/>
+      <c r="D44" s="119"/>
+      <c r="E44" s="119"/>
+      <c r="F44" s="120"/>
+      <c r="G44" s="121"/>
       <c r="H44" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="118"/>
-      <c r="C45" s="117"/>
-      <c r="D45" s="118"/>
-      <c r="E45" s="118"/>
-      <c r="F45" s="119"/>
-      <c r="G45" s="120"/>
+      <c r="B45" s="119"/>
+      <c r="C45" s="118"/>
+      <c r="D45" s="119"/>
+      <c r="E45" s="119"/>
+      <c r="F45" s="120"/>
+      <c r="G45" s="121"/>
       <c r="H45" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="118"/>
-      <c r="C46" s="117"/>
-      <c r="D46" s="118"/>
-      <c r="E46" s="118"/>
-      <c r="F46" s="119"/>
-      <c r="G46" s="120"/>
+      <c r="B46" s="119"/>
+      <c r="C46" s="118"/>
+      <c r="D46" s="119"/>
+      <c r="E46" s="119"/>
+      <c r="F46" s="120"/>
+      <c r="G46" s="121"/>
       <c r="H46" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="118"/>
-      <c r="C47" s="117"/>
-      <c r="D47" s="118"/>
-      <c r="E47" s="118"/>
-      <c r="F47" s="119"/>
-      <c r="G47" s="120"/>
+      <c r="B47" s="119"/>
+      <c r="C47" s="118"/>
+      <c r="D47" s="119"/>
+      <c r="E47" s="119"/>
+      <c r="F47" s="120"/>
+      <c r="G47" s="121"/>
       <c r="H47" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="118"/>
-      <c r="C48" s="117"/>
-      <c r="D48" s="118"/>
-      <c r="E48" s="118"/>
-      <c r="F48" s="119"/>
-      <c r="G48" s="120"/>
+      <c r="B48" s="119"/>
+      <c r="C48" s="118"/>
+      <c r="D48" s="119"/>
+      <c r="E48" s="119"/>
+      <c r="F48" s="120"/>
+      <c r="G48" s="121"/>
       <c r="H48" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="118"/>
-      <c r="C49" s="117"/>
-      <c r="D49" s="118"/>
-      <c r="E49" s="118"/>
-      <c r="F49" s="119"/>
-      <c r="G49" s="120"/>
+      <c r="B49" s="119"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="119"/>
+      <c r="E49" s="119"/>
+      <c r="F49" s="120"/>
+      <c r="G49" s="121"/>
       <c r="H49" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="118"/>
-      <c r="C50" s="117"/>
-      <c r="D50" s="118"/>
-      <c r="E50" s="118"/>
-      <c r="F50" s="119"/>
-      <c r="G50" s="120"/>
+      <c r="B50" s="119"/>
+      <c r="C50" s="118"/>
+      <c r="D50" s="119"/>
+      <c r="E50" s="119"/>
+      <c r="F50" s="120"/>
+      <c r="G50" s="121"/>
       <c r="H50" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="118"/>
-      <c r="C51" s="117"/>
-      <c r="D51" s="118"/>
-      <c r="E51" s="118"/>
-      <c r="F51" s="119"/>
-      <c r="G51" s="120"/>
+      <c r="B51" s="119"/>
+      <c r="C51" s="118"/>
+      <c r="D51" s="119"/>
+      <c r="E51" s="119"/>
+      <c r="F51" s="120"/>
+      <c r="G51" s="121"/>
       <c r="H51" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="118"/>
-      <c r="C52" s="117"/>
-      <c r="D52" s="118"/>
-      <c r="E52" s="118"/>
-      <c r="F52" s="119"/>
-      <c r="G52" s="120"/>
+      <c r="B52" s="119"/>
+      <c r="C52" s="118"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="119"/>
+      <c r="F52" s="120"/>
+      <c r="G52" s="121"/>
       <c r="H52" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="118"/>
-      <c r="C53" s="117"/>
-      <c r="D53" s="118"/>
-      <c r="E53" s="118"/>
-      <c r="F53" s="119"/>
-      <c r="G53" s="120"/>
+      <c r="B53" s="119"/>
+      <c r="C53" s="118"/>
+      <c r="D53" s="119"/>
+      <c r="E53" s="119"/>
+      <c r="F53" s="120"/>
+      <c r="G53" s="121"/>
       <c r="H53" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="118"/>
-      <c r="C54" s="117"/>
-      <c r="D54" s="118"/>
-      <c r="E54" s="118"/>
-      <c r="F54" s="119"/>
-      <c r="G54" s="120"/>
+      <c r="B54" s="119"/>
+      <c r="C54" s="118"/>
+      <c r="D54" s="119"/>
+      <c r="E54" s="119"/>
+      <c r="F54" s="120"/>
+      <c r="G54" s="121"/>
       <c r="H54" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="118"/>
-      <c r="C55" s="117"/>
-      <c r="D55" s="118"/>
-      <c r="E55" s="118"/>
-      <c r="F55" s="119"/>
-      <c r="G55" s="120"/>
+      <c r="B55" s="119"/>
+      <c r="C55" s="118"/>
+      <c r="D55" s="119"/>
+      <c r="E55" s="119"/>
+      <c r="F55" s="120"/>
+      <c r="G55" s="121"/>
       <c r="H55" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="118"/>
-      <c r="C56" s="117"/>
-      <c r="D56" s="118"/>
-      <c r="E56" s="118"/>
-      <c r="F56" s="119"/>
-      <c r="G56" s="120"/>
+      <c r="B56" s="119"/>
+      <c r="C56" s="118"/>
+      <c r="D56" s="119"/>
+      <c r="E56" s="119"/>
+      <c r="F56" s="120"/>
+      <c r="G56" s="121"/>
       <c r="H56" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="118"/>
-      <c r="C57" s="117"/>
-      <c r="D57" s="118"/>
-      <c r="E57" s="118"/>
-      <c r="F57" s="119"/>
-      <c r="G57" s="120"/>
+      <c r="B57" s="119"/>
+      <c r="C57" s="118"/>
+      <c r="D57" s="119"/>
+      <c r="E57" s="119"/>
+      <c r="F57" s="120"/>
+      <c r="G57" s="121"/>
       <c r="H57" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="118"/>
-      <c r="C58" s="117"/>
-      <c r="D58" s="118"/>
-      <c r="E58" s="118"/>
-      <c r="F58" s="119"/>
-      <c r="G58" s="120"/>
+      <c r="B58" s="119"/>
+      <c r="C58" s="118"/>
+      <c r="D58" s="119"/>
+      <c r="E58" s="119"/>
+      <c r="F58" s="120"/>
+      <c r="G58" s="121"/>
       <c r="H58" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="118"/>
-      <c r="C59" s="117"/>
-      <c r="D59" s="118"/>
-      <c r="E59" s="118"/>
-      <c r="F59" s="119"/>
-      <c r="G59" s="120"/>
+      <c r="B59" s="119"/>
+      <c r="C59" s="118"/>
+      <c r="D59" s="119"/>
+      <c r="E59" s="119"/>
+      <c r="F59" s="120"/>
+      <c r="G59" s="121"/>
       <c r="H59" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="118"/>
-      <c r="C60" s="117"/>
-      <c r="D60" s="118"/>
-      <c r="E60" s="118"/>
-      <c r="F60" s="119"/>
-      <c r="G60" s="120"/>
+      <c r="B60" s="119"/>
+      <c r="C60" s="118"/>
+      <c r="D60" s="119"/>
+      <c r="E60" s="119"/>
+      <c r="F60" s="120"/>
+      <c r="G60" s="121"/>
       <c r="H60" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="118"/>
-      <c r="C61" s="117"/>
-      <c r="D61" s="118"/>
-      <c r="E61" s="118"/>
-      <c r="F61" s="119"/>
-      <c r="G61" s="120"/>
+      <c r="B61" s="119"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="119"/>
+      <c r="E61" s="119"/>
+      <c r="F61" s="120"/>
+      <c r="G61" s="121"/>
       <c r="H61" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="118"/>
-      <c r="C62" s="117"/>
-      <c r="D62" s="118"/>
-      <c r="E62" s="118"/>
-      <c r="F62" s="119"/>
-      <c r="G62" s="120"/>
+      <c r="B62" s="119"/>
+      <c r="C62" s="118"/>
+      <c r="D62" s="119"/>
+      <c r="E62" s="119"/>
+      <c r="F62" s="120"/>
+      <c r="G62" s="121"/>
       <c r="H62" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="118"/>
-      <c r="C63" s="117"/>
-      <c r="D63" s="118"/>
-      <c r="E63" s="118"/>
-      <c r="F63" s="119"/>
-      <c r="G63" s="120"/>
+      <c r="B63" s="119"/>
+      <c r="C63" s="118"/>
+      <c r="D63" s="119"/>
+      <c r="E63" s="119"/>
+      <c r="F63" s="120"/>
+      <c r="G63" s="121"/>
       <c r="H63" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="118"/>
-      <c r="C64" s="117"/>
-      <c r="D64" s="118"/>
-      <c r="E64" s="118"/>
-      <c r="F64" s="119"/>
-      <c r="G64" s="120"/>
+      <c r="B64" s="119"/>
+      <c r="C64" s="118"/>
+      <c r="D64" s="119"/>
+      <c r="E64" s="119"/>
+      <c r="F64" s="120"/>
+      <c r="G64" s="121"/>
       <c r="H64" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="118"/>
-      <c r="C65" s="117"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="118"/>
-      <c r="F65" s="119"/>
-      <c r="G65" s="120"/>
+      <c r="B65" s="119"/>
+      <c r="C65" s="118"/>
+      <c r="D65" s="119"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="121"/>
       <c r="H65" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="118"/>
-      <c r="C66" s="117"/>
-      <c r="D66" s="118"/>
-      <c r="E66" s="118"/>
-      <c r="F66" s="119"/>
-      <c r="G66" s="120"/>
+      <c r="B66" s="119"/>
+      <c r="C66" s="118"/>
+      <c r="D66" s="119"/>
+      <c r="E66" s="119"/>
+      <c r="F66" s="120"/>
+      <c r="G66" s="121"/>
       <c r="H66" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="118"/>
-      <c r="C67" s="117"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="118"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="120"/>
+      <c r="B67" s="119"/>
+      <c r="C67" s="118"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="119"/>
+      <c r="F67" s="120"/>
+      <c r="G67" s="121"/>
       <c r="H67" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="118"/>
-      <c r="C68" s="117"/>
-      <c r="D68" s="118"/>
-      <c r="E68" s="118"/>
-      <c r="F68" s="119"/>
-      <c r="G68" s="120"/>
+      <c r="B68" s="119"/>
+      <c r="C68" s="118"/>
+      <c r="D68" s="119"/>
+      <c r="E68" s="119"/>
+      <c r="F68" s="120"/>
+      <c r="G68" s="121"/>
       <c r="H68" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="118"/>
-      <c r="C69" s="117"/>
-      <c r="D69" s="118"/>
-      <c r="E69" s="118"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="120"/>
+      <c r="B69" s="119"/>
+      <c r="C69" s="118"/>
+      <c r="D69" s="119"/>
+      <c r="E69" s="119"/>
+      <c r="F69" s="120"/>
+      <c r="G69" s="121"/>
       <c r="H69" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="118"/>
-      <c r="C70" s="117"/>
-      <c r="D70" s="118"/>
-      <c r="E70" s="118"/>
-      <c r="F70" s="119"/>
-      <c r="G70" s="120"/>
+      <c r="B70" s="119"/>
+      <c r="C70" s="118"/>
+      <c r="D70" s="119"/>
+      <c r="E70" s="119"/>
+      <c r="F70" s="120"/>
+      <c r="G70" s="121"/>
       <c r="H70" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="118"/>
-      <c r="C71" s="117"/>
-      <c r="D71" s="118"/>
-      <c r="E71" s="118"/>
-      <c r="F71" s="119"/>
-      <c r="G71" s="120"/>
+      <c r="B71" s="119"/>
+      <c r="C71" s="118"/>
+      <c r="D71" s="119"/>
+      <c r="E71" s="119"/>
+      <c r="F71" s="120"/>
+      <c r="G71" s="121"/>
       <c r="H71" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="118"/>
-      <c r="C72" s="117"/>
-      <c r="D72" s="118"/>
-      <c r="E72" s="118"/>
-      <c r="F72" s="119"/>
-      <c r="G72" s="120"/>
+      <c r="B72" s="119"/>
+      <c r="C72" s="118"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="120"/>
+      <c r="G72" s="121"/>
       <c r="H72" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="118"/>
-      <c r="C73" s="117"/>
-      <c r="D73" s="118"/>
-      <c r="E73" s="118"/>
-      <c r="F73" s="119"/>
-      <c r="G73" s="120"/>
+      <c r="B73" s="119"/>
+      <c r="C73" s="118"/>
+      <c r="D73" s="119"/>
+      <c r="E73" s="119"/>
+      <c r="F73" s="120"/>
+      <c r="G73" s="121"/>
       <c r="H73" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="118"/>
-      <c r="C74" s="117"/>
-      <c r="D74" s="118"/>
-      <c r="E74" s="118"/>
-      <c r="F74" s="119"/>
-      <c r="G74" s="120"/>
+      <c r="B74" s="119"/>
+      <c r="C74" s="118"/>
+      <c r="D74" s="119"/>
+      <c r="E74" s="119"/>
+      <c r="F74" s="120"/>
+      <c r="G74" s="121"/>
       <c r="H74" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="118"/>
-      <c r="C75" s="117"/>
-      <c r="D75" s="118"/>
-      <c r="E75" s="118"/>
-      <c r="F75" s="119"/>
-      <c r="G75" s="120"/>
+      <c r="B75" s="119"/>
+      <c r="C75" s="118"/>
+      <c r="D75" s="119"/>
+      <c r="E75" s="119"/>
+      <c r="F75" s="120"/>
+      <c r="G75" s="121"/>
       <c r="H75" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="118"/>
-      <c r="C76" s="117"/>
-      <c r="D76" s="118"/>
-      <c r="E76" s="118"/>
-      <c r="F76" s="119"/>
-      <c r="G76" s="120"/>
+      <c r="B76" s="119"/>
+      <c r="C76" s="118"/>
+      <c r="D76" s="119"/>
+      <c r="E76" s="119"/>
+      <c r="F76" s="120"/>
+      <c r="G76" s="121"/>
       <c r="H76" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="118"/>
-      <c r="C77" s="117"/>
-      <c r="D77" s="118"/>
-      <c r="E77" s="118"/>
-      <c r="F77" s="119"/>
-      <c r="G77" s="120"/>
+      <c r="B77" s="119"/>
+      <c r="C77" s="118"/>
+      <c r="D77" s="119"/>
+      <c r="E77" s="119"/>
+      <c r="F77" s="120"/>
+      <c r="G77" s="121"/>
       <c r="H77" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="118"/>
-      <c r="C78" s="117"/>
-      <c r="D78" s="118"/>
-      <c r="E78" s="118"/>
-      <c r="F78" s="119"/>
-      <c r="G78" s="120"/>
+      <c r="B78" s="119"/>
+      <c r="C78" s="118"/>
+      <c r="D78" s="119"/>
+      <c r="E78" s="119"/>
+      <c r="F78" s="120"/>
+      <c r="G78" s="121"/>
       <c r="H78" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="118"/>
-      <c r="C79" s="117"/>
-      <c r="D79" s="118"/>
-      <c r="E79" s="118"/>
-      <c r="F79" s="119"/>
-      <c r="G79" s="120"/>
+      <c r="B79" s="119"/>
+      <c r="C79" s="118"/>
+      <c r="D79" s="119"/>
+      <c r="E79" s="119"/>
+      <c r="F79" s="120"/>
+      <c r="G79" s="121"/>
       <c r="H79" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="118"/>
-      <c r="C80" s="117"/>
-      <c r="D80" s="118"/>
-      <c r="E80" s="118"/>
-      <c r="F80" s="119"/>
-      <c r="G80" s="120"/>
+      <c r="B80" s="119"/>
+      <c r="C80" s="118"/>
+      <c r="D80" s="119"/>
+      <c r="E80" s="119"/>
+      <c r="F80" s="120"/>
+      <c r="G80" s="121"/>
       <c r="H80" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="118"/>
-      <c r="C81" s="117"/>
-      <c r="D81" s="118"/>
-      <c r="E81" s="118"/>
-      <c r="F81" s="119"/>
-      <c r="G81" s="120"/>
+      <c r="B81" s="119"/>
+      <c r="C81" s="118"/>
+      <c r="D81" s="119"/>
+      <c r="E81" s="119"/>
+      <c r="F81" s="120"/>
+      <c r="G81" s="121"/>
       <c r="H81" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="118"/>
-      <c r="C82" s="117"/>
-      <c r="D82" s="118"/>
-      <c r="E82" s="118"/>
-      <c r="F82" s="119"/>
-      <c r="G82" s="120"/>
+      <c r="B82" s="119"/>
+      <c r="C82" s="118"/>
+      <c r="D82" s="119"/>
+      <c r="E82" s="119"/>
+      <c r="F82" s="120"/>
+      <c r="G82" s="121"/>
       <c r="H82" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="118"/>
-      <c r="C83" s="117"/>
-      <c r="D83" s="118"/>
-      <c r="E83" s="118"/>
-      <c r="F83" s="119"/>
-      <c r="G83" s="120"/>
+      <c r="B83" s="119"/>
+      <c r="C83" s="118"/>
+      <c r="D83" s="119"/>
+      <c r="E83" s="119"/>
+      <c r="F83" s="120"/>
+      <c r="G83" s="121"/>
       <c r="H83" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="118"/>
-      <c r="C84" s="117"/>
-      <c r="D84" s="118"/>
-      <c r="E84" s="118"/>
-      <c r="F84" s="119"/>
-      <c r="G84" s="120"/>
+      <c r="B84" s="119"/>
+      <c r="C84" s="118"/>
+      <c r="D84" s="119"/>
+      <c r="E84" s="119"/>
+      <c r="F84" s="120"/>
+      <c r="G84" s="121"/>
       <c r="H84" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="118"/>
-      <c r="C85" s="117"/>
-      <c r="D85" s="118"/>
-      <c r="E85" s="118"/>
-      <c r="F85" s="119"/>
-      <c r="G85" s="120"/>
+      <c r="B85" s="119"/>
+      <c r="C85" s="118"/>
+      <c r="D85" s="119"/>
+      <c r="E85" s="119"/>
+      <c r="F85" s="120"/>
+      <c r="G85" s="121"/>
       <c r="H85" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="118"/>
-      <c r="C86" s="117"/>
-      <c r="D86" s="118"/>
-      <c r="E86" s="118"/>
-      <c r="F86" s="119"/>
-      <c r="G86" s="120"/>
+      <c r="B86" s="119"/>
+      <c r="C86" s="118"/>
+      <c r="D86" s="119"/>
+      <c r="E86" s="119"/>
+      <c r="F86" s="120"/>
+      <c r="G86" s="121"/>
       <c r="H86" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="118"/>
-      <c r="C87" s="117"/>
-      <c r="D87" s="118"/>
-      <c r="E87" s="118"/>
-      <c r="F87" s="119"/>
-      <c r="G87" s="120"/>
+      <c r="B87" s="119"/>
+      <c r="C87" s="118"/>
+      <c r="D87" s="119"/>
+      <c r="E87" s="119"/>
+      <c r="F87" s="120"/>
+      <c r="G87" s="121"/>
       <c r="H87" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="118"/>
-      <c r="C88" s="117"/>
-      <c r="D88" s="118"/>
-      <c r="E88" s="118"/>
-      <c r="F88" s="119"/>
-      <c r="G88" s="120"/>
+      <c r="B88" s="119"/>
+      <c r="C88" s="118"/>
+      <c r="D88" s="119"/>
+      <c r="E88" s="119"/>
+      <c r="F88" s="120"/>
+      <c r="G88" s="121"/>
       <c r="H88" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="118"/>
-      <c r="C89" s="117"/>
-      <c r="D89" s="118"/>
-      <c r="E89" s="118"/>
-      <c r="F89" s="119"/>
-      <c r="G89" s="120"/>
+      <c r="B89" s="119"/>
+      <c r="C89" s="118"/>
+      <c r="D89" s="119"/>
+      <c r="E89" s="119"/>
+      <c r="F89" s="120"/>
+      <c r="G89" s="121"/>
       <c r="H89" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="118"/>
-      <c r="C90" s="117"/>
-      <c r="D90" s="118"/>
-      <c r="E90" s="118"/>
-      <c r="F90" s="119"/>
-      <c r="G90" s="120"/>
+      <c r="B90" s="119"/>
+      <c r="C90" s="118"/>
+      <c r="D90" s="119"/>
+      <c r="E90" s="119"/>
+      <c r="F90" s="120"/>
+      <c r="G90" s="121"/>
       <c r="H90" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="118"/>
-      <c r="C91" s="117"/>
-      <c r="D91" s="118"/>
-      <c r="E91" s="118"/>
-      <c r="F91" s="119"/>
-      <c r="G91" s="120"/>
+      <c r="B91" s="119"/>
+      <c r="C91" s="118"/>
+      <c r="D91" s="119"/>
+      <c r="E91" s="119"/>
+      <c r="F91" s="120"/>
+      <c r="G91" s="121"/>
       <c r="H91" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="118"/>
-      <c r="C92" s="117"/>
-      <c r="D92" s="118"/>
-      <c r="E92" s="118"/>
-      <c r="F92" s="119"/>
-      <c r="G92" s="120"/>
+      <c r="B92" s="119"/>
+      <c r="C92" s="118"/>
+      <c r="D92" s="119"/>
+      <c r="E92" s="119"/>
+      <c r="F92" s="120"/>
+      <c r="G92" s="121"/>
       <c r="H92" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="118"/>
-      <c r="C93" s="117"/>
-      <c r="D93" s="118"/>
-      <c r="E93" s="118"/>
-      <c r="F93" s="119"/>
-      <c r="G93" s="120"/>
+      <c r="B93" s="119"/>
+      <c r="C93" s="118"/>
+      <c r="D93" s="119"/>
+      <c r="E93" s="119"/>
+      <c r="F93" s="120"/>
+      <c r="G93" s="121"/>
       <c r="H93" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="118"/>
-      <c r="C94" s="117"/>
-      <c r="D94" s="118"/>
-      <c r="E94" s="118"/>
-      <c r="F94" s="119"/>
-      <c r="G94" s="120"/>
+      <c r="B94" s="119"/>
+      <c r="C94" s="118"/>
+      <c r="D94" s="119"/>
+      <c r="E94" s="119"/>
+      <c r="F94" s="120"/>
+      <c r="G94" s="121"/>
       <c r="H94" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="118"/>
-      <c r="C95" s="117"/>
-      <c r="D95" s="118"/>
-      <c r="E95" s="118"/>
-      <c r="F95" s="119"/>
-      <c r="G95" s="120"/>
+      <c r="B95" s="119"/>
+      <c r="C95" s="118"/>
+      <c r="D95" s="119"/>
+      <c r="E95" s="119"/>
+      <c r="F95" s="120"/>
+      <c r="G95" s="121"/>
       <c r="H95" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="118"/>
-      <c r="C96" s="117"/>
-      <c r="D96" s="118"/>
-      <c r="E96" s="118"/>
-      <c r="F96" s="119"/>
-      <c r="G96" s="120"/>
+      <c r="B96" s="119"/>
+      <c r="C96" s="118"/>
+      <c r="D96" s="119"/>
+      <c r="E96" s="119"/>
+      <c r="F96" s="120"/>
+      <c r="G96" s="121"/>
       <c r="H96" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -9788,333 +9942,333 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="B1" s="121" t="s">
-        <v>162</v>
+      <c r="B1" s="122" t="s">
+        <v>178</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="122" t="s">
-        <v>163</v>
+      <c r="B2" s="123" t="s">
+        <v>179</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
     </row>
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
-      <c r="B4" s="123" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="124" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" s="125" t="s">
-        <v>166</v>
+      <c r="B4" s="124" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="125" t="s">
+        <v>181</v>
+      </c>
+      <c r="D4" s="126" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
-      <c r="B5" s="123" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="124" t="s">
-        <v>168</v>
-      </c>
-      <c r="D5" s="125" t="s">
-        <v>169</v>
+      <c r="B5" s="124" t="s">
+        <v>183</v>
+      </c>
+      <c r="C5" s="125" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="126" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
-      <c r="B6" s="123" t="s">
-        <v>170</v>
-      </c>
-      <c r="C6" s="124" t="s">
-        <v>171</v>
-      </c>
-      <c r="D6" s="125" t="s">
-        <v>172</v>
+      <c r="B6" s="124" t="s">
+        <v>186</v>
+      </c>
+      <c r="C6" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="D6" s="126" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
-      <c r="B7" s="123" t="s">
-        <v>173</v>
-      </c>
-      <c r="C7" s="124" t="s">
-        <v>174</v>
-      </c>
-      <c r="D7" s="125" t="s">
-        <v>175</v>
+      <c r="B7" s="124" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="125" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7" s="126" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
-      <c r="B8" s="126" t="s">
-        <v>176</v>
-      </c>
-      <c r="C8" s="127" t="s">
-        <v>177</v>
-      </c>
-      <c r="D8" s="125" t="s">
-        <v>178</v>
+      <c r="B8" s="127" t="s">
+        <v>192</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>193</v>
+      </c>
+      <c r="D8" s="126" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="B9" s="126" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="125" t="s">
-        <v>181</v>
+      <c r="B9" s="127" t="s">
+        <v>195</v>
+      </c>
+      <c r="C9" s="128" t="s">
+        <v>196</v>
+      </c>
+      <c r="D9" s="126" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
-      <c r="B10" s="128" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="129" t="s">
-        <v>183</v>
-      </c>
-      <c r="D10" s="125" t="s">
-        <v>184</v>
+      <c r="B10" s="129" t="s">
+        <v>198</v>
+      </c>
+      <c r="C10" s="130" t="s">
+        <v>199</v>
+      </c>
+      <c r="D10" s="126" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
-      <c r="B11" s="128" t="s">
-        <v>185</v>
-      </c>
-      <c r="C11" s="129" t="s">
-        <v>186</v>
-      </c>
-      <c r="D11" s="125" t="s">
-        <v>187</v>
+      <c r="B11" s="129" t="s">
+        <v>201</v>
+      </c>
+      <c r="C11" s="130" t="s">
+        <v>202</v>
+      </c>
+      <c r="D11" s="126" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
-      <c r="B12" s="130" t="s">
-        <v>188</v>
-      </c>
-      <c r="C12" s="131" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="125" t="s">
-        <v>190</v>
+      <c r="B12" s="131" t="s">
+        <v>204</v>
+      </c>
+      <c r="C12" s="132" t="s">
+        <v>205</v>
+      </c>
+      <c r="D12" s="126" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
-      <c r="B13" s="130" t="s">
-        <v>191</v>
-      </c>
-      <c r="C13" s="131" t="s">
-        <v>192</v>
-      </c>
-      <c r="D13" s="125" t="s">
-        <v>193</v>
+      <c r="B13" s="131" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="132" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="126" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
-      <c r="B14" s="132" t="s">
-        <v>194</v>
-      </c>
-      <c r="C14" s="133" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="125" t="s">
-        <v>196</v>
+      <c r="B14" s="133" t="s">
+        <v>210</v>
+      </c>
+      <c r="C14" s="134" t="s">
+        <v>211</v>
+      </c>
+      <c r="D14" s="126" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
-      <c r="B15" s="134" t="s">
-        <v>197</v>
-      </c>
-      <c r="C15" s="135" t="s">
-        <v>198</v>
-      </c>
-      <c r="D15" s="125" t="s">
-        <v>199</v>
+      <c r="B15" s="135" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15" s="136" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="126" t="s">
+        <v>215</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
-      <c r="B16" s="128" t="s">
-        <v>200</v>
-      </c>
-      <c r="C16" s="129" t="s">
-        <v>201</v>
-      </c>
-      <c r="D16" s="125" t="s">
-        <v>202</v>
+      <c r="B16" s="129" t="s">
+        <v>216</v>
+      </c>
+      <c r="C16" s="130" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="126" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
-      <c r="B17" s="134" t="s">
-        <v>203</v>
-      </c>
-      <c r="C17" s="135" t="s">
-        <v>204</v>
-      </c>
-      <c r="D17" s="125" t="s">
-        <v>205</v>
+      <c r="B17" s="135" t="s">
+        <v>219</v>
+      </c>
+      <c r="C17" s="136" t="s">
+        <v>220</v>
+      </c>
+      <c r="D17" s="126" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
-      <c r="B18" s="130" t="s">
-        <v>206</v>
-      </c>
-      <c r="C18" s="131" t="s">
-        <v>207</v>
-      </c>
-      <c r="D18" s="125" t="s">
-        <v>208</v>
+      <c r="B18" s="131" t="s">
+        <v>222</v>
+      </c>
+      <c r="C18" s="132" t="s">
+        <v>223</v>
+      </c>
+      <c r="D18" s="126" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="B20" s="136" t="s">
-        <v>209</v>
+      <c r="B20" s="137" t="s">
+        <v>225</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="B21" s="137" t="s">
+      <c r="B21" s="138" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="137" t="s">
-        <v>210</v>
-      </c>
-      <c r="D21" s="137" t="s">
-        <v>211</v>
+      <c r="C21" s="138" t="s">
+        <v>226</v>
+      </c>
+      <c r="D21" s="138" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="139" t="s">
-        <v>212</v>
-      </c>
-      <c r="D22" s="140" t="s">
-        <v>213</v>
+      <c r="C22" s="140" t="s">
+        <v>228</v>
+      </c>
+      <c r="D22" s="141" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="139" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="139" t="s">
-        <v>214</v>
-      </c>
-      <c r="D23" s="140" t="s">
-        <v>215</v>
+      <c r="C23" s="140" t="s">
+        <v>230</v>
+      </c>
+      <c r="D23" s="141" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
-      <c r="B24" s="141" t="s">
+      <c r="B24" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="142" t="s">
-        <v>216</v>
-      </c>
-      <c r="D24" s="140" t="s">
-        <v>217</v>
+      <c r="C24" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D24" s="141" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
-      <c r="B25" s="138" t="s">
+      <c r="B25" s="139" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="139" t="s">
-        <v>218</v>
-      </c>
-      <c r="D25" s="140" t="s">
-        <v>219</v>
+      <c r="C25" s="140" t="s">
+        <v>234</v>
+      </c>
+      <c r="D25" s="141" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="B26" s="143" t="s">
+      <c r="B26" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="144" t="s">
-        <v>220</v>
-      </c>
-      <c r="D26" s="140" t="s">
-        <v>221</v>
+      <c r="C26" s="145" t="s">
+        <v>236</v>
+      </c>
+      <c r="D26" s="141" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
-      <c r="B27" s="145" t="s">
+      <c r="B27" s="146" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="146" t="s">
-        <v>222</v>
-      </c>
-      <c r="D27" s="140" t="s">
-        <v>223</v>
+      <c r="C27" s="147" t="s">
+        <v>238</v>
+      </c>
+      <c r="D27" s="141" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
-      <c r="B28" s="138" t="s">
+      <c r="B28" s="139" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="139" t="s">
-        <v>224</v>
-      </c>
-      <c r="D28" s="140" t="s">
-        <v>225</v>
+      <c r="C28" s="140" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="141" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
-      <c r="B29" s="138" t="s">
+      <c r="B29" s="139" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="139" t="s">
-        <v>226</v>
-      </c>
-      <c r="D29" s="140" t="s">
-        <v>227</v>
+      <c r="C29" s="140" t="s">
+        <v>242</v>
+      </c>
+      <c r="D29" s="141" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
-      <c r="B30" s="143" t="s">
+      <c r="B30" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="144" t="s">
-        <v>228</v>
-      </c>
-      <c r="D30" s="140" t="s">
-        <v>229</v>
+      <c r="C30" s="145" t="s">
+        <v>244</v>
+      </c>
+      <c r="D30" s="141" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="B31" s="143" t="s">
+      <c r="B31" s="144" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="144" t="s">
-        <v>230</v>
-      </c>
-      <c r="D31" s="140" t="s">
-        <v>231</v>
+      <c r="C31" s="145" t="s">
+        <v>246</v>
+      </c>
+      <c r="D31" s="141" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
-      <c r="B32" s="147" t="s">
+      <c r="B32" s="148" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="148" t="s">
-        <v>232</v>
-      </c>
-      <c r="D32" s="140" t="s">
-        <v>233</v>
+      <c r="C32" s="149" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="141" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="B33" s="138" t="s">
+      <c r="B33" s="139" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="139" t="s">
-        <v>234</v>
-      </c>
-      <c r="D33" s="140" t="s">
-        <v>235</v>
+      <c r="C33" s="140" t="s">
+        <v>250</v>
+      </c>
+      <c r="D33" s="141" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11105,967 +11259,967 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="149" t="s">
-        <v>236</v>
-      </c>
-      <c r="B1" s="149" t="s">
-        <v>237</v>
-      </c>
-      <c r="C1" s="149" t="s">
+      <c r="A1" s="150" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="150" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" s="150" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="149"/>
-      <c r="E1" s="149"/>
+      <c r="D1" s="150"/>
+      <c r="E1" s="150"/>
     </row>
     <row r="2">
-      <c r="A2" s="150">
+      <c r="A2" s="151">
         <v>46165.0</v>
       </c>
-      <c r="B2" s="149" t="s">
-        <v>238</v>
-      </c>
-      <c r="C2" s="151">
+      <c r="B2" s="150" t="s">
+        <v>254</v>
+      </c>
+      <c r="C2" s="152">
         <v>10000.0</v>
       </c>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
     </row>
     <row r="3">
-      <c r="A3" s="150">
+      <c r="A3" s="151">
         <v>46166.0</v>
       </c>
-      <c r="B3" s="149" t="s">
-        <v>239</v>
-      </c>
-      <c r="C3" s="151">
+      <c r="B3" s="150" t="s">
+        <v>255</v>
+      </c>
+      <c r="C3" s="152">
         <v>19000.0</v>
       </c>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
+      <c r="D3" s="150"/>
+      <c r="E3" s="150"/>
     </row>
     <row r="4">
-      <c r="A4" s="150">
+      <c r="A4" s="151">
         <v>46168.0</v>
       </c>
-      <c r="B4" s="149" t="s">
-        <v>240</v>
-      </c>
-      <c r="C4" s="152">
+      <c r="B4" s="150" t="s">
+        <v>256</v>
+      </c>
+      <c r="C4" s="153">
         <v>2500.0</v>
       </c>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
+      <c r="D4" s="150"/>
+      <c r="E4" s="150"/>
     </row>
     <row r="5">
-      <c r="A5" s="150">
+      <c r="A5" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B5" s="149" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="151">
+      <c r="B5" s="150" t="s">
+        <v>257</v>
+      </c>
+      <c r="C5" s="152">
         <v>29050.0</v>
       </c>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
+      <c r="D5" s="150"/>
+      <c r="E5" s="150"/>
     </row>
     <row r="6">
-      <c r="A6" s="150">
+      <c r="A6" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B6" s="149" t="s">
-        <v>242</v>
-      </c>
-      <c r="C6" s="152">
+      <c r="B6" s="150" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="153">
         <v>100.0</v>
       </c>
-      <c r="D6" s="149"/>
-      <c r="E6" s="149"/>
+      <c r="D6" s="150"/>
+      <c r="E6" s="150"/>
     </row>
     <row r="7">
-      <c r="A7" s="150">
+      <c r="A7" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B7" s="149" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="152">
+      <c r="B7" s="150" t="s">
+        <v>259</v>
+      </c>
+      <c r="C7" s="153">
         <v>300.0</v>
       </c>
-      <c r="D7" s="149"/>
-      <c r="E7" s="149"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
     </row>
     <row r="8">
-      <c r="A8" s="150">
+      <c r="A8" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B8" s="149" t="s">
-        <v>244</v>
-      </c>
-      <c r="C8" s="152">
+      <c r="B8" s="150" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="153">
         <v>370.0</v>
       </c>
-      <c r="D8" s="149"/>
-      <c r="E8" s="149"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="150"/>
     </row>
     <row r="9">
-      <c r="A9" s="150">
+      <c r="A9" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B9" s="149" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" s="152">
+      <c r="B9" s="150" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="153">
         <v>2494.0</v>
       </c>
-      <c r="D9" s="149"/>
-      <c r="E9" s="149"/>
+      <c r="D9" s="150"/>
+      <c r="E9" s="150"/>
     </row>
     <row r="10">
-      <c r="A10" s="150">
+      <c r="A10" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B10" s="149" t="s">
-        <v>246</v>
-      </c>
-      <c r="C10" s="152">
+      <c r="B10" s="150" t="s">
+        <v>262</v>
+      </c>
+      <c r="C10" s="153">
         <v>5000.0</v>
       </c>
-      <c r="D10" s="149"/>
-      <c r="E10" s="149"/>
+      <c r="D10" s="150"/>
+      <c r="E10" s="150"/>
     </row>
     <row r="11">
-      <c r="A11" s="150">
+      <c r="A11" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B11" s="149" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="151">
+      <c r="B11" s="150" t="s">
+        <v>263</v>
+      </c>
+      <c r="C11" s="152">
         <v>29000.0</v>
       </c>
-      <c r="D11" s="149" t="s">
-        <v>248</v>
-      </c>
-      <c r="E11" s="152">
+      <c r="D11" s="150" t="s">
+        <v>264</v>
+      </c>
+      <c r="E11" s="153">
         <v>24000.0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="150">
+      <c r="A12" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B12" s="149" t="s">
-        <v>249</v>
-      </c>
-      <c r="C12" s="152">
+      <c r="B12" s="150" t="s">
+        <v>265</v>
+      </c>
+      <c r="C12" s="153">
         <v>400.0</v>
       </c>
-      <c r="D12" s="149" t="s">
-        <v>250</v>
-      </c>
-      <c r="E12" s="151">
+      <c r="D12" s="150" t="s">
+        <v>266</v>
+      </c>
+      <c r="E12" s="152">
         <v>53000.0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="150">
+      <c r="A13" s="151">
         <v>46169.0</v>
       </c>
-      <c r="B13" s="149" t="s">
-        <v>251</v>
-      </c>
-      <c r="C13" s="152">
+      <c r="B13" s="150" t="s">
+        <v>267</v>
+      </c>
+      <c r="C13" s="153">
         <v>600.0</v>
       </c>
-      <c r="D13" s="149"/>
-      <c r="E13" s="149"/>
+      <c r="D13" s="150"/>
+      <c r="E13" s="150"/>
     </row>
     <row r="14">
-      <c r="A14" s="150">
+      <c r="A14" s="151">
         <v>46170.0</v>
       </c>
-      <c r="B14" s="149"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="149"/>
-      <c r="E14" s="149"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="150"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="150"/>
     </row>
     <row r="22">
-      <c r="A22" s="149" t="s">
+      <c r="A22" s="150" t="s">
+        <v>268</v>
+      </c>
+      <c r="B22" s="150" t="s">
         <v>252</v>
       </c>
-      <c r="B22" s="149" t="s">
-        <v>236</v>
-      </c>
-      <c r="C22" s="149" t="s">
-        <v>253</v>
-      </c>
-      <c r="D22" s="149" t="s">
+      <c r="C22" s="150" t="s">
+        <v>269</v>
+      </c>
+      <c r="D22" s="150" t="s">
         <v>136</v>
       </c>
-      <c r="E22" s="149" t="s">
-        <v>254</v>
+      <c r="E22" s="150" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="149" t="s">
-        <v>255</v>
-      </c>
-      <c r="B23" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="C23" s="149" t="s">
-        <v>257</v>
-      </c>
-      <c r="D23" s="152">
+      <c r="A23" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="B23" s="150" t="s">
+        <v>272</v>
+      </c>
+      <c r="C23" s="150" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" s="153">
         <v>3150.0</v>
       </c>
-      <c r="E23" s="153">
+      <c r="E23" s="154">
         <v>46464.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="149" t="s">
-        <v>255</v>
-      </c>
-      <c r="B24" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="C24" s="149" t="s">
-        <v>258</v>
-      </c>
-      <c r="D24" s="152">
+      <c r="A24" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="B24" s="150" t="s">
+        <v>272</v>
+      </c>
+      <c r="C24" s="150" t="s">
+        <v>274</v>
+      </c>
+      <c r="D24" s="153">
         <v>2650.0</v>
       </c>
-      <c r="E24" s="153">
+      <c r="E24" s="154">
         <v>46219.0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="149" t="s">
-        <v>255</v>
-      </c>
-      <c r="B25" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="C25" s="149" t="s">
-        <v>259</v>
-      </c>
-      <c r="D25" s="152">
+      <c r="A25" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" s="150" t="s">
+        <v>272</v>
+      </c>
+      <c r="C25" s="150" t="s">
+        <v>275</v>
+      </c>
+      <c r="D25" s="153">
         <v>2600.0</v>
       </c>
-      <c r="E25" s="153">
+      <c r="E25" s="154">
         <v>46828.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="149" t="s">
-        <v>255</v>
-      </c>
-      <c r="B26" s="149" t="s">
-        <v>256</v>
-      </c>
-      <c r="C26" s="149" t="s">
-        <v>260</v>
-      </c>
-      <c r="D26" s="152">
+      <c r="A26" s="150" t="s">
+        <v>271</v>
+      </c>
+      <c r="B26" s="150" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="150" t="s">
+        <v>276</v>
+      </c>
+      <c r="D26" s="153">
         <v>2680.0</v>
       </c>
-      <c r="E26" s="154">
+      <c r="E26" s="155">
         <v>46863.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="149" t="s">
-        <v>261</v>
-      </c>
-      <c r="B27" s="149" t="s">
-        <v>262</v>
-      </c>
-      <c r="C27" s="149" t="s">
-        <v>263</v>
-      </c>
-      <c r="D27" s="152">
+      <c r="A27" s="150" t="s">
+        <v>277</v>
+      </c>
+      <c r="B27" s="150" t="s">
+        <v>278</v>
+      </c>
+      <c r="C27" s="150" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="153">
         <v>5390.0</v>
       </c>
-      <c r="E27" s="153">
+      <c r="E27" s="154">
         <v>46764.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="149" t="s">
-        <v>261</v>
-      </c>
-      <c r="B28" s="149" t="s">
-        <v>262</v>
-      </c>
-      <c r="C28" s="149" t="s">
-        <v>264</v>
-      </c>
-      <c r="D28" s="152">
+      <c r="A28" s="150" t="s">
+        <v>277</v>
+      </c>
+      <c r="B28" s="150" t="s">
+        <v>278</v>
+      </c>
+      <c r="C28" s="150" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="153">
         <v>3235.0</v>
       </c>
-      <c r="E28" s="153">
+      <c r="E28" s="154">
         <v>46673.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="149" t="s">
-        <v>261</v>
-      </c>
-      <c r="B29" s="149" t="s">
-        <v>262</v>
-      </c>
-      <c r="C29" s="149" t="s">
-        <v>265</v>
-      </c>
-      <c r="D29" s="152">
+      <c r="A29" s="150" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" s="150" t="s">
+        <v>278</v>
+      </c>
+      <c r="C29" s="150" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="153">
         <v>1230.0</v>
       </c>
-      <c r="E29" s="149" t="s">
-        <v>266</v>
+      <c r="E29" s="150" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="149" t="s">
-        <v>267</v>
-      </c>
-      <c r="B30" s="149"/>
-      <c r="C30" s="149" t="s">
-        <v>257</v>
-      </c>
-      <c r="D30" s="152">
+      <c r="A30" s="150" t="s">
+        <v>283</v>
+      </c>
+      <c r="B30" s="150"/>
+      <c r="C30" s="150" t="s">
+        <v>273</v>
+      </c>
+      <c r="D30" s="153">
         <v>2960.0</v>
       </c>
-      <c r="E30" s="149"/>
+      <c r="E30" s="150"/>
     </row>
     <row r="31">
-      <c r="A31" s="149" t="s">
-        <v>267</v>
-      </c>
-      <c r="B31" s="149"/>
-      <c r="C31" s="149" t="s">
-        <v>263</v>
-      </c>
-      <c r="D31" s="152">
+      <c r="A31" s="150" t="s">
+        <v>283</v>
+      </c>
+      <c r="B31" s="150"/>
+      <c r="C31" s="150" t="s">
+        <v>279</v>
+      </c>
+      <c r="D31" s="153">
         <v>2960.0</v>
       </c>
-      <c r="E31" s="149"/>
+      <c r="E31" s="150"/>
     </row>
     <row r="32">
-      <c r="A32" s="149" t="s">
-        <v>268</v>
-      </c>
-      <c r="B32" s="149" t="s">
-        <v>269</v>
-      </c>
-      <c r="C32" s="149"/>
-      <c r="D32" s="152">
+      <c r="A32" s="150" t="s">
+        <v>284</v>
+      </c>
+      <c r="B32" s="150" t="s">
+        <v>285</v>
+      </c>
+      <c r="C32" s="150"/>
+      <c r="D32" s="153">
         <v>5000.0</v>
       </c>
-      <c r="E32" s="149" t="s">
-        <v>270</v>
+      <c r="E32" s="150" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="155" t="s">
-        <v>271</v>
-      </c>
-      <c r="B42" s="149"/>
-      <c r="C42" s="149"/>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
-      <c r="J42" s="149"/>
+      <c r="A42" s="156" t="s">
+        <v>287</v>
+      </c>
+      <c r="B42" s="150"/>
+      <c r="C42" s="150"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="150"/>
+      <c r="I42" s="150"/>
+      <c r="J42" s="150"/>
     </row>
     <row r="43">
-      <c r="A43" s="149"/>
-      <c r="B43" s="149"/>
-      <c r="C43" s="149"/>
-      <c r="D43" s="149"/>
-      <c r="E43" s="149"/>
-      <c r="F43" s="149"/>
-      <c r="G43" s="149"/>
-      <c r="H43" s="149"/>
-      <c r="I43" s="149"/>
-      <c r="J43" s="149"/>
+      <c r="A43" s="150"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="150"/>
+      <c r="D43" s="150"/>
+      <c r="E43" s="150"/>
+      <c r="F43" s="150"/>
+      <c r="G43" s="150"/>
+      <c r="H43" s="150"/>
+      <c r="I43" s="150"/>
+      <c r="J43" s="150"/>
     </row>
     <row r="44">
-      <c r="A44" s="149"/>
-      <c r="B44" s="149"/>
-      <c r="C44" s="149"/>
-      <c r="D44" s="149"/>
-      <c r="E44" s="149"/>
-      <c r="F44" s="149"/>
-      <c r="G44" s="149"/>
-      <c r="H44" s="149"/>
-      <c r="I44" s="149"/>
-      <c r="J44" s="149"/>
+      <c r="A44" s="150"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="150"/>
+      <c r="D44" s="150"/>
+      <c r="E44" s="150"/>
+      <c r="F44" s="150"/>
+      <c r="G44" s="150"/>
+      <c r="H44" s="150"/>
+      <c r="I44" s="150"/>
+      <c r="J44" s="150"/>
     </row>
     <row r="45">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="156" t="s">
-        <v>272</v>
-      </c>
-      <c r="C45" s="156" t="s">
-        <v>273</v>
-      </c>
-      <c r="D45" s="156" t="s">
+      <c r="B45" s="157" t="s">
+        <v>288</v>
+      </c>
+      <c r="C45" s="157" t="s">
+        <v>289</v>
+      </c>
+      <c r="D45" s="157" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="156" t="s">
-        <v>274</v>
-      </c>
-      <c r="F45" s="156" t="s">
-        <v>275</v>
-      </c>
-      <c r="G45" s="156" t="s">
-        <v>276</v>
-      </c>
-      <c r="H45" s="156" t="s">
-        <v>277</v>
-      </c>
-      <c r="I45" s="156" t="s">
-        <v>278</v>
-      </c>
-      <c r="J45" s="156" t="s">
-        <v>279</v>
+      <c r="E45" s="157" t="s">
+        <v>290</v>
+      </c>
+      <c r="F45" s="157" t="s">
+        <v>291</v>
+      </c>
+      <c r="G45" s="157" t="s">
+        <v>292</v>
+      </c>
+      <c r="H45" s="157" t="s">
+        <v>293</v>
+      </c>
+      <c r="I45" s="157" t="s">
+        <v>294</v>
+      </c>
+      <c r="J45" s="157" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="157" t="s">
-        <v>280</v>
-      </c>
-      <c r="B46" s="158">
+      <c r="A46" s="158" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" s="159">
         <v>1000000.0</v>
       </c>
-      <c r="C46" s="159">
+      <c r="C46" s="160">
         <v>0.2</v>
       </c>
-      <c r="D46" s="158">
+      <c r="D46" s="159">
         <f>IF(AND(B46&lt;&gt;"", C46&lt;&gt;"", E46&lt;&gt;""), PMT(C46/12, E46, -B46), "")</f>
         <v>26493.88371</v>
       </c>
-      <c r="E46" s="160">
+      <c r="E46" s="161">
         <v>60.0</v>
       </c>
-      <c r="F46" s="160">
+      <c r="F46" s="161">
         <v>0.0</v>
       </c>
-      <c r="G46" s="160">
+      <c r="G46" s="161">
         <f t="shared" ref="G46:G52" si="1">IF(E46="", "", E46 - F46)</f>
         <v>60</v>
       </c>
-      <c r="H46" s="158">
+      <c r="H46" s="159">
         <f t="shared" ref="H46:H52" si="2">IF(D46="", "", D46 * F46)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="158">
+      <c r="I46" s="159">
         <f t="shared" ref="I46:I52" si="3">IF(G46="", "", IFERROR(PV(C46/12, G46, -D46), ""))</f>
         <v>1000000</v>
       </c>
-      <c r="J46" s="161">
+      <c r="J46" s="162">
         <f t="shared" ref="J46:J52" si="4">IF(AND(D46&lt;&gt;"", E46&lt;&gt;""), (D46 * E46) - B46, "")</f>
         <v>589633.0229</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="162" t="s">
-        <v>281</v>
-      </c>
-      <c r="B47" s="163">
+      <c r="A47" s="163" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" s="164">
         <v>596000.0</v>
       </c>
-      <c r="C47" s="164">
+      <c r="C47" s="165">
         <v>0.126</v>
       </c>
-      <c r="D47" s="163">
+      <c r="D47" s="164">
         <f>IF(AND(B47&lt;&gt;"", C47&lt;&gt;"", E47&lt;&gt;""), PMT(C47/12, E47, -B47), 11839)</f>
         <v>11838.71102</v>
       </c>
-      <c r="E47" s="165">
+      <c r="E47" s="166">
         <v>72.0</v>
       </c>
-      <c r="F47" s="165">
+      <c r="F47" s="166">
         <v>52.0</v>
       </c>
-      <c r="G47" s="165">
+      <c r="G47" s="166">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="H47" s="163">
+      <c r="H47" s="164">
         <f t="shared" si="2"/>
         <v>615612.9729</v>
       </c>
-      <c r="I47" s="163">
+      <c r="I47" s="164">
         <f t="shared" si="3"/>
         <v>212564.401</v>
       </c>
-      <c r="J47" s="166">
+      <c r="J47" s="167">
         <f t="shared" si="4"/>
         <v>256387.1932</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="157" t="s">
-        <v>282</v>
-      </c>
-      <c r="B48" s="167"/>
-      <c r="C48" s="168"/>
-      <c r="D48" s="158">
+      <c r="A48" s="158" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" s="168"/>
+      <c r="C48" s="169"/>
+      <c r="D48" s="159">
         <f>IF(AND(B48&lt;&gt;"", C48&lt;&gt;"", E48&lt;&gt;""), PMT(C48/12, E48, -B48), 15250)</f>
         <v>15250</v>
       </c>
-      <c r="E48" s="169"/>
-      <c r="F48" s="160">
+      <c r="E48" s="170"/>
+      <c r="F48" s="161">
         <v>0.0</v>
       </c>
-      <c r="G48" s="169" t="str">
+      <c r="G48" s="170" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="158">
+      <c r="H48" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="167" t="str">
+      <c r="I48" s="168" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J48" s="170" t="str">
+      <c r="J48" s="171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="162" t="s">
+      <c r="A49" s="163" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="163">
+      <c r="B49" s="164">
         <v>97110.0</v>
       </c>
-      <c r="C49" s="171"/>
-      <c r="D49" s="163">
+      <c r="C49" s="172"/>
+      <c r="D49" s="164">
         <f>IF(AND(B49&lt;&gt;"", C49&lt;&gt;"", E49&lt;&gt;""), PMT(C49/12, E49, -B49), 18972)</f>
         <v>18972</v>
       </c>
-      <c r="E49" s="172"/>
-      <c r="F49" s="165">
+      <c r="E49" s="173"/>
+      <c r="F49" s="166">
         <v>0.0</v>
       </c>
-      <c r="G49" s="172" t="str">
+      <c r="G49" s="173" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="163">
+      <c r="H49" s="164">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="173" t="str">
+      <c r="I49" s="174" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J49" s="174" t="str">
+      <c r="J49" s="175" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="157" t="s">
-        <v>283</v>
-      </c>
-      <c r="B50" s="158">
+      <c r="A50" s="158" t="s">
+        <v>299</v>
+      </c>
+      <c r="B50" s="159">
         <v>83419.0</v>
       </c>
-      <c r="C50" s="159">
+      <c r="C50" s="160">
         <v>0.12</v>
       </c>
-      <c r="D50" s="158">
+      <c r="D50" s="159">
         <f t="shared" ref="D50:D51" si="5">IF(AND(B50&lt;&gt;"", C50&lt;&gt;"", E50&lt;&gt;""), PMT(C50/12, E50, -B50), 4627)</f>
         <v>5087.061453</v>
       </c>
-      <c r="E50" s="160">
+      <c r="E50" s="161">
         <v>18.0</v>
       </c>
-      <c r="F50" s="160">
+      <c r="F50" s="161">
         <v>3.0</v>
       </c>
-      <c r="G50" s="160">
+      <c r="G50" s="161">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H50" s="158">
+      <c r="H50" s="159">
         <f t="shared" si="2"/>
         <v>15261.18436</v>
       </c>
-      <c r="I50" s="158">
+      <c r="I50" s="159">
         <f t="shared" si="3"/>
         <v>70532.37421</v>
       </c>
-      <c r="J50" s="161">
+      <c r="J50" s="162">
         <f t="shared" si="4"/>
         <v>8148.106161</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="175" t="s">
-        <v>284</v>
-      </c>
-      <c r="B51" s="176">
+      <c r="A51" s="176" t="s">
+        <v>300</v>
+      </c>
+      <c r="B51" s="177">
         <v>149100.0</v>
       </c>
-      <c r="C51" s="177">
+      <c r="C51" s="178">
         <v>0.1</v>
       </c>
-      <c r="D51" s="176">
+      <c r="D51" s="177">
         <f t="shared" si="5"/>
         <v>5637.681256</v>
       </c>
-      <c r="E51" s="178">
+      <c r="E51" s="179">
         <v>30.0</v>
       </c>
-      <c r="F51" s="178">
+      <c r="F51" s="179">
         <v>15.0</v>
       </c>
-      <c r="G51" s="178">
+      <c r="G51" s="179">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H51" s="176">
+      <c r="H51" s="177">
         <f t="shared" si="2"/>
         <v>84565.21884</v>
       </c>
-      <c r="I51" s="176">
+      <c r="I51" s="177">
         <f t="shared" si="3"/>
         <v>79184.0856</v>
       </c>
-      <c r="J51" s="179">
+      <c r="J51" s="180">
         <f t="shared" si="4"/>
         <v>20030.43769</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="157" t="s">
-        <v>285</v>
-      </c>
-      <c r="B52" s="167"/>
-      <c r="C52" s="168"/>
-      <c r="D52" s="158">
+      <c r="A52" s="158" t="s">
+        <v>301</v>
+      </c>
+      <c r="B52" s="168"/>
+      <c r="C52" s="169"/>
+      <c r="D52" s="159">
         <f>IF(AND(B52&lt;&gt;"", C52&lt;&gt;"", E52&lt;&gt;""), PMT(C52/12, E52, -B52), 3850)</f>
         <v>3850</v>
       </c>
-      <c r="E52" s="169"/>
-      <c r="F52" s="160">
+      <c r="E52" s="170"/>
+      <c r="F52" s="161">
         <v>0.0</v>
       </c>
-      <c r="G52" s="169" t="str">
+      <c r="G52" s="170" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H52" s="158">
+      <c r="H52" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="167" t="str">
+      <c r="I52" s="168" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J52" s="170" t="str">
+      <c r="J52" s="171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="180" t="s">
-        <v>236</v>
-      </c>
-      <c r="B61" s="180" t="s">
-        <v>286</v>
-      </c>
-      <c r="C61" s="180" t="s">
+      <c r="A61" s="181" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" s="181" t="s">
+        <v>302</v>
+      </c>
+      <c r="C61" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="D61" s="180" t="s">
-        <v>287</v>
-      </c>
-      <c r="E61" s="180" t="s">
-        <v>288</v>
-      </c>
-      <c r="F61" s="180" t="s">
-        <v>289</v>
-      </c>
-      <c r="G61" s="180" t="s">
+      <c r="D61" s="181" t="s">
+        <v>303</v>
+      </c>
+      <c r="E61" s="181" t="s">
+        <v>304</v>
+      </c>
+      <c r="F61" s="181" t="s">
+        <v>305</v>
+      </c>
+      <c r="G61" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="H61" s="149"/>
-      <c r="I61" s="180" t="s">
-        <v>290</v>
-      </c>
-      <c r="J61" s="149" t="s">
-        <v>291</v>
+      <c r="H61" s="150"/>
+      <c r="I61" s="181" t="s">
+        <v>306</v>
+      </c>
+      <c r="J61" s="150" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="150">
+      <c r="A62" s="151">
         <v>46143.0</v>
       </c>
-      <c r="B62" s="149" t="s">
-        <v>292</v>
-      </c>
-      <c r="C62" s="181">
+      <c r="B62" s="150" t="s">
+        <v>308</v>
+      </c>
+      <c r="C62" s="182">
         <v>11839.0</v>
       </c>
-      <c r="D62" s="182" t="b">
+      <c r="D62" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="149" t="s">
-        <v>293</v>
-      </c>
-      <c r="F62" s="149" t="s">
-        <v>294</v>
-      </c>
-      <c r="G62" s="181">
+      <c r="E62" s="150" t="s">
+        <v>309</v>
+      </c>
+      <c r="F62" s="150" t="s">
+        <v>310</v>
+      </c>
+      <c r="G62" s="182">
         <v>71000.0</v>
       </c>
-      <c r="H62" s="149"/>
-      <c r="I62" s="180" t="s">
-        <v>295</v>
-      </c>
-      <c r="J62" s="181">
+      <c r="H62" s="150"/>
+      <c r="I62" s="181" t="s">
+        <v>311</v>
+      </c>
+      <c r="J62" s="182">
         <f>SUM(C62:C1000)</f>
         <v>84657</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="150">
+      <c r="A63" s="151">
         <v>46144.0</v>
       </c>
-      <c r="B63" s="149" t="s">
-        <v>296</v>
-      </c>
-      <c r="C63" s="181">
+      <c r="B63" s="150" t="s">
+        <v>312</v>
+      </c>
+      <c r="C63" s="182">
         <v>3850.0</v>
       </c>
-      <c r="D63" s="182" t="b">
+      <c r="D63" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="149" t="s">
-        <v>297</v>
-      </c>
-      <c r="F63" s="149"/>
-      <c r="G63" s="183"/>
-      <c r="H63" s="149"/>
-      <c r="I63" s="180" t="s">
-        <v>277</v>
-      </c>
-      <c r="J63" s="181">
+      <c r="E63" s="150" t="s">
+        <v>313</v>
+      </c>
+      <c r="F63" s="150"/>
+      <c r="G63" s="184"/>
+      <c r="H63" s="150"/>
+      <c r="I63" s="181" t="s">
+        <v>293</v>
+      </c>
+      <c r="J63" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
         <v>50435</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="150">
+      <c r="A64" s="151">
         <v>46145.0</v>
       </c>
-      <c r="B64" s="149" t="s">
-        <v>298</v>
-      </c>
-      <c r="C64" s="181">
+      <c r="B64" s="150" t="s">
+        <v>314</v>
+      </c>
+      <c r="C64" s="182">
         <v>4627.0</v>
       </c>
-      <c r="D64" s="182" t="b">
+      <c r="D64" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="149"/>
-      <c r="F64" s="149"/>
-      <c r="G64" s="183"/>
-      <c r="H64" s="149"/>
-      <c r="I64" s="180" t="s">
-        <v>299</v>
-      </c>
-      <c r="J64" s="181">
+      <c r="E64" s="150"/>
+      <c r="F64" s="150"/>
+      <c r="G64" s="184"/>
+      <c r="H64" s="150"/>
+      <c r="I64" s="181" t="s">
+        <v>315</v>
+      </c>
+      <c r="J64" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
         <v>34222</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="150">
+      <c r="A65" s="151">
         <v>46147.0</v>
       </c>
-      <c r="B65" s="149" t="s">
-        <v>300</v>
-      </c>
-      <c r="C65" s="181">
+      <c r="B65" s="150" t="s">
+        <v>316</v>
+      </c>
+      <c r="C65" s="182">
         <v>5000.0</v>
       </c>
-      <c r="D65" s="182" t="b">
+      <c r="D65" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="149"/>
-      <c r="F65" s="149"/>
-      <c r="G65" s="183"/>
-      <c r="H65" s="149"/>
-      <c r="I65" s="180" t="s">
-        <v>301</v>
-      </c>
-      <c r="J65" s="181">
+      <c r="E65" s="150"/>
+      <c r="F65" s="150"/>
+      <c r="G65" s="184"/>
+      <c r="H65" s="150"/>
+      <c r="I65" s="181" t="s">
+        <v>317</v>
+      </c>
+      <c r="J65" s="182">
         <f>SUM(G62:G1000)</f>
         <v>71000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="150">
+      <c r="A66" s="151">
         <v>46167.0</v>
       </c>
-      <c r="B66" s="149" t="s">
-        <v>302</v>
-      </c>
-      <c r="C66" s="181">
+      <c r="B66" s="150" t="s">
+        <v>318</v>
+      </c>
+      <c r="C66" s="182">
         <v>18972.0</v>
       </c>
-      <c r="D66" s="182" t="b">
+      <c r="D66" s="183" t="b">
         <v>0</v>
       </c>
-      <c r="E66" s="184">
+      <c r="E66" s="185">
         <v>97110.0</v>
       </c>
-      <c r="F66" s="149"/>
-      <c r="G66" s="183"/>
-      <c r="H66" s="149"/>
-      <c r="I66" s="180" t="s">
-        <v>303</v>
-      </c>
-      <c r="J66" s="181">
+      <c r="F66" s="150"/>
+      <c r="G66" s="184"/>
+      <c r="H66" s="150"/>
+      <c r="I66" s="181" t="s">
+        <v>319</v>
+      </c>
+      <c r="J66" s="182">
         <f>J65-J62</f>
         <v>-13657</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="150">
+      <c r="A67" s="151">
         <v>46146.0</v>
       </c>
-      <c r="B67" s="149" t="s">
-        <v>304</v>
-      </c>
-      <c r="C67" s="181">
+      <c r="B67" s="150" t="s">
+        <v>320</v>
+      </c>
+      <c r="C67" s="182">
         <v>13625.0</v>
       </c>
-      <c r="D67" s="182" t="b">
+      <c r="D67" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="149" t="s">
-        <v>305</v>
-      </c>
-      <c r="F67" s="149"/>
-      <c r="G67" s="183"/>
-      <c r="H67" s="149"/>
-      <c r="I67" s="149"/>
-      <c r="J67" s="149"/>
+      <c r="E67" s="150" t="s">
+        <v>321</v>
+      </c>
+      <c r="F67" s="150"/>
+      <c r="G67" s="184"/>
+      <c r="H67" s="150"/>
+      <c r="I67" s="150"/>
+      <c r="J67" s="150"/>
     </row>
     <row r="68">
-      <c r="A68" s="150">
+      <c r="A68" s="151">
         <v>46145.0</v>
       </c>
-      <c r="B68" s="149" t="s">
-        <v>306</v>
-      </c>
-      <c r="C68" s="181">
+      <c r="B68" s="150" t="s">
+        <v>322</v>
+      </c>
+      <c r="C68" s="182">
         <v>2494.0</v>
       </c>
-      <c r="D68" s="182" t="b">
+      <c r="D68" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="149"/>
-      <c r="F68" s="149"/>
-      <c r="G68" s="183"/>
-      <c r="H68" s="149"/>
-      <c r="I68" s="149"/>
-      <c r="J68" s="149"/>
+      <c r="E68" s="150"/>
+      <c r="F68" s="150"/>
+      <c r="G68" s="184"/>
+      <c r="H68" s="150"/>
+      <c r="I68" s="150"/>
+      <c r="J68" s="150"/>
     </row>
     <row r="69">
-      <c r="A69" s="150">
+      <c r="A69" s="151">
         <v>46144.0</v>
       </c>
-      <c r="B69" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C69" s="181">
+      <c r="B69" s="150" t="s">
+        <v>323</v>
+      </c>
+      <c r="C69" s="182">
         <v>4500.0</v>
       </c>
-      <c r="D69" s="182" t="b">
+      <c r="D69" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E69" s="149"/>
-      <c r="F69" s="149"/>
-      <c r="G69" s="183"/>
-      <c r="H69" s="149"/>
-      <c r="I69" s="149"/>
-      <c r="J69" s="149"/>
+      <c r="E69" s="150"/>
+      <c r="F69" s="150"/>
+      <c r="G69" s="184"/>
+      <c r="H69" s="150"/>
+      <c r="I69" s="150"/>
+      <c r="J69" s="150"/>
     </row>
     <row r="70">
-      <c r="A70" s="150">
+      <c r="A70" s="151">
         <v>46152.0</v>
       </c>
-      <c r="B70" s="149" t="s">
-        <v>308</v>
-      </c>
-      <c r="C70" s="181">
+      <c r="B70" s="150" t="s">
+        <v>324</v>
+      </c>
+      <c r="C70" s="182">
         <v>1500.0</v>
       </c>
-      <c r="D70" s="182" t="b">
+      <c r="D70" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="149"/>
-      <c r="F70" s="149"/>
-      <c r="G70" s="183"/>
-      <c r="H70" s="149"/>
-      <c r="I70" s="149"/>
-      <c r="J70" s="149"/>
+      <c r="E70" s="150"/>
+      <c r="F70" s="150"/>
+      <c r="G70" s="184"/>
+      <c r="H70" s="150"/>
+      <c r="I70" s="150"/>
+      <c r="J70" s="150"/>
     </row>
     <row r="71">
-      <c r="A71" s="150">
+      <c r="A71" s="151">
         <v>46152.0</v>
       </c>
-      <c r="B71" s="149" t="s">
-        <v>309</v>
-      </c>
-      <c r="C71" s="181">
+      <c r="B71" s="150" t="s">
+        <v>325</v>
+      </c>
+      <c r="C71" s="182">
         <v>3000.0</v>
       </c>
-      <c r="D71" s="182" t="b">
+      <c r="D71" s="183" t="b">
         <v>1</v>
       </c>
-      <c r="E71" s="149"/>
-      <c r="F71" s="149"/>
-      <c r="G71" s="183"/>
-      <c r="H71" s="149"/>
-      <c r="I71" s="149"/>
-      <c r="J71" s="149"/>
+      <c r="E71" s="150"/>
+      <c r="F71" s="150"/>
+      <c r="G71" s="184"/>
+      <c r="H71" s="150"/>
+      <c r="I71" s="150"/>
+      <c r="J71" s="150"/>
     </row>
     <row r="72">
-      <c r="A72" s="150">
+      <c r="A72" s="151">
         <v>46157.0</v>
       </c>
-      <c r="B72" s="149" t="s">
-        <v>310</v>
-      </c>
-      <c r="C72" s="181">
+      <c r="B72" s="150" t="s">
+        <v>326</v>
+      </c>
+      <c r="C72" s="182">
         <v>15250.0</v>
       </c>
-      <c r="D72" s="182" t="b">
+      <c r="D72" s="183" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="149"/>
-      <c r="F72" s="149"/>
-      <c r="G72" s="183"/>
-      <c r="H72" s="149"/>
-      <c r="I72" s="149"/>
-      <c r="J72" s="149"/>
+      <c r="E72" s="150"/>
+      <c r="F72" s="150"/>
+      <c r="G72" s="184"/>
+      <c r="H72" s="150"/>
+      <c r="I72" s="150"/>
+      <c r="J72" s="150"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20414.75836</v>
+        <v>20532.76274</v>
       </c>
     </row>
     <row r="6">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13644.24658</v>
+        <v>13707.12329</v>
       </c>
     </row>
     <row r="7">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1208.219178</v>
+        <v>1294.520548</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8782,7 +8782,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20532.76274</v>
+        <v>20650.76712</v>
       </c>
     </row>
     <row r="6">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13707.12329</v>
+        <v>13770</v>
       </c>
     </row>
     <row r="7">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1294.520548</v>
+        <v>1380.821918</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="332">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -517,6 +517,21 @@
   </si>
   <si>
     <t>Muthu Chithapa</t>
+  </si>
+  <si>
+    <t>Car loan Rent</t>
+  </si>
+  <si>
+    <t>Dinner on June 10 at chennai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMMA </t>
+  </si>
+  <si>
+    <t>Net Recharge</t>
+  </si>
+  <si>
+    <t>Appa</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -4058,11 +4073,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>74178</v>
+        <v>93898</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-57514</v>
+        <v>-77234</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -7894,7 +7909,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="17.29"/>
-    <col customWidth="1" min="2" max="2" width="21.57"/>
+    <col customWidth="1" min="2" max="2" width="31.86"/>
     <col customWidth="1" min="3" max="3" width="17.29"/>
     <col customWidth="1" min="4" max="4" width="35.86"/>
   </cols>
@@ -8264,37 +8279,71 @@
       <c r="A27" s="109">
         <v>46184.0</v>
       </c>
-      <c r="B27" s="108"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="108"/>
+      <c r="B27" s="101" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="102">
+        <v>6600.0</v>
+      </c>
+      <c r="D27" s="103">
+        <v>46183.0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="109">
         <v>46185.0</v>
       </c>
-      <c r="B28" s="108"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="108"/>
+      <c r="B28" s="101" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="102">
+        <v>530.0</v>
+      </c>
+      <c r="D28" s="103">
+        <v>46183.0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="109">
         <v>46186.0</v>
       </c>
-      <c r="B29" s="108"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="108"/>
+      <c r="B29" s="101" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="102">
+        <v>10000.0</v>
+      </c>
+      <c r="D29" s="103">
+        <v>46183.0</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="108"/>
-      <c r="B30" s="108"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="108"/>
+      <c r="A30" s="109">
+        <v>46187.0</v>
+      </c>
+      <c r="B30" s="101" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="102">
+        <v>590.0</v>
+      </c>
+      <c r="D30" s="103">
+        <v>46181.0</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="108"/>
-      <c r="B31" s="108"/>
-      <c r="C31" s="110"/>
-      <c r="D31" s="108"/>
+      <c r="A31" s="109">
+        <v>46188.0</v>
+      </c>
+      <c r="B31" s="101" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="102">
+        <v>2000.0</v>
+      </c>
+      <c r="D31" s="103">
+        <v>46184.0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="108"/>
@@ -8735,30 +8784,30 @@
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
       <c r="B2" s="111" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="112" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="C4" s="112" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D4" s="112" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E4" s="112" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F4" s="112" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G4" s="112" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="H4" s="113" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5">
@@ -8769,10 +8818,10 @@
         <v>0.11</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E5" s="114" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F5" s="116">
         <v>391560.0</v>
@@ -8793,10 +8842,10 @@
         <v>0.1</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E6" s="114" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="F6" s="116">
         <v>229500.0</v>
@@ -8817,10 +8866,10 @@
         <v>0.105</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F7" s="116">
         <v>300000.0</v>
@@ -8839,10 +8888,10 @@
       </c>
       <c r="C8" s="118"/>
       <c r="D8" s="114" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E8" s="114" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F8" s="116">
         <v>135000.0</v>
@@ -8859,10 +8908,10 @@
       <c r="B9" s="119"/>
       <c r="C9" s="118"/>
       <c r="D9" s="114" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E9" s="114" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F9" s="116">
         <v>297698.0</v>
@@ -9943,14 +9992,14 @@
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
       <c r="B1" s="122" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="123" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
@@ -9958,172 +10007,172 @@
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
       <c r="B4" s="124" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
       <c r="B5" s="124" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D5" s="126" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
       <c r="B6" s="124" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C6" s="125" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D6" s="126" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="B7" s="124" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C7" s="125" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="D7" s="126" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
       <c r="B8" s="127" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D8" s="126" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="B9" s="127" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="D9" s="126" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
       <c r="B10" s="129" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="C10" s="130" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D10" s="126" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
       <c r="B11" s="129" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C11" s="130" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="D11" s="126" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
       <c r="B12" s="131" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="C12" s="132" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="D12" s="126" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
       <c r="B13" s="131" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="C13" s="132" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
       <c r="B14" s="133" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
       <c r="B15" s="135" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D15" s="126" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
       <c r="B16" s="129" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C16" s="130" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
       <c r="B17" s="135" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C17" s="136" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D17" s="126" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
       <c r="B18" s="131" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C18" s="132" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="137" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
@@ -10133,10 +10182,10 @@
         <v>70</v>
       </c>
       <c r="C21" s="138" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="D21" s="138" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -10144,10 +10193,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="140" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
@@ -10155,10 +10204,10 @@
         <v>26</v>
       </c>
       <c r="C23" s="140" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
@@ -10166,10 +10215,10 @@
         <v>83</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D24" s="141" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
@@ -10177,10 +10226,10 @@
         <v>85</v>
       </c>
       <c r="C25" s="140" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="D25" s="141" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
@@ -10188,10 +10237,10 @@
         <v>35</v>
       </c>
       <c r="C26" s="145" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
@@ -10199,10 +10248,10 @@
         <v>90</v>
       </c>
       <c r="C27" s="147" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
@@ -10210,10 +10259,10 @@
         <v>49</v>
       </c>
       <c r="C28" s="140" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
@@ -10221,10 +10270,10 @@
         <v>47</v>
       </c>
       <c r="C29" s="140" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
@@ -10232,10 +10281,10 @@
         <v>19</v>
       </c>
       <c r="C30" s="145" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
@@ -10243,10 +10292,10 @@
         <v>43</v>
       </c>
       <c r="C31" s="145" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D31" s="141" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -10254,10 +10303,10 @@
         <v>115</v>
       </c>
       <c r="C32" s="149" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D32" s="141" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
@@ -10265,10 +10314,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="140" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11260,10 +11309,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="150" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B1" s="150" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C1" s="150" t="s">
         <v>136</v>
@@ -11276,7 +11325,7 @@
         <v>46165.0</v>
       </c>
       <c r="B2" s="150" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="C2" s="152">
         <v>10000.0</v>
@@ -11289,7 +11338,7 @@
         <v>46166.0</v>
       </c>
       <c r="B3" s="150" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C3" s="152">
         <v>19000.0</v>
@@ -11302,7 +11351,7 @@
         <v>46168.0</v>
       </c>
       <c r="B4" s="150" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C4" s="153">
         <v>2500.0</v>
@@ -11315,7 +11364,7 @@
         <v>46169.0</v>
       </c>
       <c r="B5" s="150" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="C5" s="152">
         <v>29050.0</v>
@@ -11328,7 +11377,7 @@
         <v>46169.0</v>
       </c>
       <c r="B6" s="150" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C6" s="153">
         <v>100.0</v>
@@ -11341,7 +11390,7 @@
         <v>46169.0</v>
       </c>
       <c r="B7" s="150" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C7" s="153">
         <v>300.0</v>
@@ -11354,7 +11403,7 @@
         <v>46169.0</v>
       </c>
       <c r="B8" s="150" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C8" s="153">
         <v>370.0</v>
@@ -11367,7 +11416,7 @@
         <v>46169.0</v>
       </c>
       <c r="B9" s="150" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C9" s="153">
         <v>2494.0</v>
@@ -11380,7 +11429,7 @@
         <v>46169.0</v>
       </c>
       <c r="B10" s="150" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C10" s="153">
         <v>5000.0</v>
@@ -11393,13 +11442,13 @@
         <v>46169.0</v>
       </c>
       <c r="B11" s="150" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C11" s="152">
         <v>29000.0</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="E11" s="153">
         <v>24000.0</v>
@@ -11410,13 +11459,13 @@
         <v>46169.0</v>
       </c>
       <c r="B12" s="150" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C12" s="153">
         <v>400.0</v>
       </c>
       <c r="D12" s="150" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E12" s="152">
         <v>53000.0</v>
@@ -11427,7 +11476,7 @@
         <v>46169.0</v>
       </c>
       <c r="B13" s="150" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C13" s="153">
         <v>600.0</v>
@@ -11446,30 +11495,30 @@
     </row>
     <row r="22">
       <c r="A22" s="150" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B22" s="150" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C22" s="150" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D22" s="150" t="s">
         <v>136</v>
       </c>
       <c r="E22" s="150" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="150" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B23" s="150" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C23" s="150" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D23" s="153">
         <v>3150.0</v>
@@ -11480,13 +11529,13 @@
     </row>
     <row r="24">
       <c r="A24" s="150" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B24" s="150" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C24" s="150" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D24" s="153">
         <v>2650.0</v>
@@ -11497,13 +11546,13 @@
     </row>
     <row r="25">
       <c r="A25" s="150" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B25" s="150" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C25" s="150" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D25" s="153">
         <v>2600.0</v>
@@ -11514,13 +11563,13 @@
     </row>
     <row r="26">
       <c r="A26" s="150" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B26" s="150" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C26" s="150" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="D26" s="153">
         <v>2680.0</v>
@@ -11531,13 +11580,13 @@
     </row>
     <row r="27">
       <c r="A27" s="150" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B27" s="150" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C27" s="150" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D27" s="153">
         <v>5390.0</v>
@@ -11548,13 +11597,13 @@
     </row>
     <row r="28">
       <c r="A28" s="150" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B28" s="150" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C28" s="150" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D28" s="153">
         <v>3235.0</v>
@@ -11565,28 +11614,28 @@
     </row>
     <row r="29">
       <c r="A29" s="150" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B29" s="150" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C29" s="150" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D29" s="153">
         <v>1230.0</v>
       </c>
       <c r="E29" s="150" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="150" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B30" s="150"/>
       <c r="C30" s="150" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="D30" s="153">
         <v>2960.0</v>
@@ -11595,11 +11644,11 @@
     </row>
     <row r="31">
       <c r="A31" s="150" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B31" s="150"/>
       <c r="C31" s="150" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D31" s="153">
         <v>2960.0</v>
@@ -11608,22 +11657,22 @@
     </row>
     <row r="32">
       <c r="A32" s="150" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B32" s="150" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C32" s="150"/>
       <c r="D32" s="153">
         <v>5000.0</v>
       </c>
       <c r="E32" s="150" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="156" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B42" s="150"/>
       <c r="C42" s="150"/>
@@ -11664,36 +11713,36 @@
         <v>6</v>
       </c>
       <c r="B45" s="157" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C45" s="157" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D45" s="157" t="s">
         <v>77</v>
       </c>
       <c r="E45" s="157" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F45" s="157" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="G45" s="157" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="H45" s="157" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="I45" s="157" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J45" s="157" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="158" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B46" s="159">
         <v>1000000.0</v>
@@ -11730,7 +11779,7 @@
     </row>
     <row r="47">
       <c r="A47" s="163" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="B47" s="164">
         <v>596000.0</v>
@@ -11767,7 +11816,7 @@
     </row>
     <row r="48">
       <c r="A48" s="158" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="B48" s="168"/>
       <c r="C48" s="169"/>
@@ -11831,7 +11880,7 @@
     </row>
     <row r="50">
       <c r="A50" s="158" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="B50" s="159">
         <v>83419.0</v>
@@ -11868,7 +11917,7 @@
     </row>
     <row r="51">
       <c r="A51" s="176" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B51" s="177">
         <v>149100.0</v>
@@ -11905,7 +11954,7 @@
     </row>
     <row r="52">
       <c r="A52" s="158" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B52" s="168"/>
       <c r="C52" s="169"/>
@@ -11936,32 +11985,32 @@
     </row>
     <row r="61">
       <c r="A61" s="181" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B61" s="181" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="D61" s="181" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="E61" s="181" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F61" s="181" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="G61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="H61" s="150"/>
       <c r="I61" s="181" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J61" s="150" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
     </row>
     <row r="62">
@@ -11969,7 +12018,7 @@
         <v>46143.0</v>
       </c>
       <c r="B62" s="150" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="C62" s="182">
         <v>11839.0</v>
@@ -11978,17 +12027,17 @@
         <v>1</v>
       </c>
       <c r="E62" s="150" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F62" s="150" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="G62" s="182">
         <v>71000.0</v>
       </c>
       <c r="H62" s="150"/>
       <c r="I62" s="181" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J62" s="182">
         <f>SUM(C62:C1000)</f>
@@ -12000,7 +12049,7 @@
         <v>46144.0</v>
       </c>
       <c r="B63" s="150" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="C63" s="182">
         <v>3850.0</v>
@@ -12009,13 +12058,13 @@
         <v>1</v>
       </c>
       <c r="E63" s="150" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F63" s="150"/>
       <c r="G63" s="184"/>
       <c r="H63" s="150"/>
       <c r="I63" s="181" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J63" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
@@ -12027,7 +12076,7 @@
         <v>46145.0</v>
       </c>
       <c r="B64" s="150" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C64" s="182">
         <v>4627.0</v>
@@ -12040,7 +12089,7 @@
       <c r="G64" s="184"/>
       <c r="H64" s="150"/>
       <c r="I64" s="181" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J64" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
@@ -12052,7 +12101,7 @@
         <v>46147.0</v>
       </c>
       <c r="B65" s="150" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="C65" s="182">
         <v>5000.0</v>
@@ -12065,7 +12114,7 @@
       <c r="G65" s="184"/>
       <c r="H65" s="150"/>
       <c r="I65" s="181" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J65" s="182">
         <f>SUM(G62:G1000)</f>
@@ -12077,7 +12126,7 @@
         <v>46167.0</v>
       </c>
       <c r="B66" s="150" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="C66" s="182">
         <v>18972.0</v>
@@ -12092,7 +12141,7 @@
       <c r="G66" s="184"/>
       <c r="H66" s="150"/>
       <c r="I66" s="181" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J66" s="182">
         <f>J65-J62</f>
@@ -12104,7 +12153,7 @@
         <v>46146.0</v>
       </c>
       <c r="B67" s="150" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C67" s="182">
         <v>13625.0</v>
@@ -12113,7 +12162,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="150" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F67" s="150"/>
       <c r="G67" s="184"/>
@@ -12126,7 +12175,7 @@
         <v>46145.0</v>
       </c>
       <c r="B68" s="150" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="C68" s="182">
         <v>2494.0</v>
@@ -12146,7 +12195,7 @@
         <v>46144.0</v>
       </c>
       <c r="B69" s="150" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="C69" s="182">
         <v>4500.0</v>
@@ -12166,7 +12215,7 @@
         <v>46152.0</v>
       </c>
       <c r="B70" s="150" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="C70" s="182">
         <v>1500.0</v>
@@ -12186,7 +12235,7 @@
         <v>46152.0</v>
       </c>
       <c r="B71" s="150" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C71" s="182">
         <v>3000.0</v>
@@ -12206,7 +12255,7 @@
         <v>46157.0</v>
       </c>
       <c r="B72" s="150" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C72" s="182">
         <v>15250.0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8831,7 +8831,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20650.76712</v>
+        <v>20768.77151</v>
       </c>
     </row>
     <row r="6">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13770</v>
+        <v>13832.87671</v>
       </c>
     </row>
     <row r="7">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1380.821918</v>
+        <v>1467.123288</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8831,7 +8831,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20768.77151</v>
+        <v>20886.77589</v>
       </c>
     </row>
     <row r="6">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13832.87671</v>
+        <v>13895.75342</v>
       </c>
     </row>
     <row r="7">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1467.123288</v>
+        <v>1553.424658</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8831,7 +8831,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>20886.77589</v>
+        <v>21004.78027</v>
       </c>
     </row>
     <row r="6">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13895.75342</v>
+        <v>13958.63014</v>
       </c>
     </row>
     <row r="7">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1553.424658</v>
+        <v>1639.726027</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8831,7 +8831,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21004.78027</v>
+        <v>21122.78466</v>
       </c>
     </row>
     <row r="6">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>13958.63014</v>
+        <v>14021.50685</v>
       </c>
     </row>
     <row r="7">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1639.726027</v>
+        <v>1726.027397</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8831,7 +8831,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21122.78466</v>
+        <v>21240.78904</v>
       </c>
     </row>
     <row r="6">
@@ -8855,7 +8855,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14021.50685</v>
+        <v>14084.38356</v>
       </c>
     </row>
     <row r="7">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1726.027397</v>
+        <v>1812.328767</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="332">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -519,13 +519,19 @@
     <t>Muthu Chithapa</t>
   </si>
   <si>
-    <t>Car loan Rent</t>
-  </si>
-  <si>
-    <t>Dinner on June 10 at chennai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AMMA </t>
+    <t xml:space="preserve">Scooty service </t>
+  </si>
+  <si>
+    <t xml:space="preserve">From Gold Loan.                                 8 June </t>
+  </si>
+  <si>
+    <t>Veera Dress</t>
+  </si>
+  <si>
+    <t>ESAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,000 from Naresh </t>
   </si>
   <si>
     <t>Net Recharge</t>
@@ -822,9 +828,6 @@
     <t>Snacks</t>
   </si>
   <si>
-    <t>Veera Dress</t>
-  </si>
-  <si>
     <t>Thiliban</t>
   </si>
   <si>
@@ -868,9 +871,6 @@
   </si>
   <si>
     <t>Thavamani</t>
-  </si>
-  <si>
-    <t>ESAF</t>
   </si>
   <si>
     <t xml:space="preserve">2nd Wednesday </t>
@@ -4073,11 +4073,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>93898</v>
+        <v>93623</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-77234</v>
+        <v>-76959</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -8283,10 +8283,10 @@
         <v>165</v>
       </c>
       <c r="C27" s="102">
-        <v>6600.0</v>
-      </c>
-      <c r="D27" s="103">
-        <v>46183.0</v>
+        <v>3000.0</v>
+      </c>
+      <c r="D27" s="101" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="28">
@@ -8294,13 +8294,13 @@
         <v>46185.0</v>
       </c>
       <c r="B28" s="101" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="102">
+        <v>4000.0</v>
+      </c>
+      <c r="D28" s="101" t="s">
         <v>166</v>
-      </c>
-      <c r="C28" s="102">
-        <v>530.0</v>
-      </c>
-      <c r="D28" s="103">
-        <v>46183.0</v>
       </c>
     </row>
     <row r="29">
@@ -8308,13 +8308,13 @@
         <v>46186.0</v>
       </c>
       <c r="B29" s="101" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C29" s="102">
-        <v>10000.0</v>
-      </c>
-      <c r="D29" s="103">
-        <v>46183.0</v>
+        <v>9855.0</v>
+      </c>
+      <c r="D29" s="101" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="30">
@@ -8322,7 +8322,7 @@
         <v>46187.0</v>
       </c>
       <c r="B30" s="101" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C30" s="102">
         <v>590.0</v>
@@ -8336,7 +8336,7 @@
         <v>46188.0</v>
       </c>
       <c r="B31" s="101" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C31" s="102">
         <v>2000.0</v>
@@ -8784,30 +8784,30 @@
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
       <c r="B2" s="111" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="112" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C4" s="112" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D4" s="112" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E4" s="112" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F4" s="112" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G4" s="112" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H4" s="113" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5">
@@ -8818,10 +8818,10 @@
         <v>0.11</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E5" s="114" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F5" s="116">
         <v>391560.0</v>
@@ -8842,10 +8842,10 @@
         <v>0.1</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E6" s="114" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F6" s="116">
         <v>229500.0</v>
@@ -8866,10 +8866,10 @@
         <v>0.105</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F7" s="116">
         <v>300000.0</v>
@@ -8888,10 +8888,10 @@
       </c>
       <c r="C8" s="118"/>
       <c r="D8" s="114" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E8" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F8" s="116">
         <v>135000.0</v>
@@ -8908,10 +8908,10 @@
       <c r="B9" s="119"/>
       <c r="C9" s="118"/>
       <c r="D9" s="114" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E9" s="114" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F9" s="116">
         <v>297698.0</v>
@@ -9992,14 +9992,14 @@
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
       <c r="B1" s="122" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="123" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
@@ -10007,172 +10007,172 @@
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
       <c r="B4" s="124" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
       <c r="B5" s="124" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D5" s="126" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
       <c r="B6" s="124" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C6" s="125" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D6" s="126" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="B7" s="124" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C7" s="125" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D7" s="126" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
       <c r="B8" s="127" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D8" s="126" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="B9" s="127" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D9" s="126" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
       <c r="B10" s="129" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C10" s="130" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D10" s="126" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
       <c r="B11" s="129" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C11" s="130" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D11" s="126" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
       <c r="B12" s="131" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C12" s="132" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D12" s="126" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
       <c r="B13" s="131" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C13" s="132" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
       <c r="B14" s="133" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
       <c r="B15" s="135" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D15" s="126" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
       <c r="B16" s="129" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C16" s="130" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
       <c r="B17" s="135" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C17" s="136" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D17" s="126" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
       <c r="B18" s="131" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C18" s="132" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="137" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
@@ -10182,10 +10182,10 @@
         <v>70</v>
       </c>
       <c r="C21" s="138" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D21" s="138" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -10193,10 +10193,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="140" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
@@ -10204,10 +10204,10 @@
         <v>26</v>
       </c>
       <c r="C23" s="140" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
@@ -10215,10 +10215,10 @@
         <v>83</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D24" s="141" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
@@ -10226,10 +10226,10 @@
         <v>85</v>
       </c>
       <c r="C25" s="140" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D25" s="141" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
@@ -10237,10 +10237,10 @@
         <v>35</v>
       </c>
       <c r="C26" s="145" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
@@ -10248,10 +10248,10 @@
         <v>90</v>
       </c>
       <c r="C27" s="147" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
@@ -10259,10 +10259,10 @@
         <v>49</v>
       </c>
       <c r="C28" s="140" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
@@ -10270,10 +10270,10 @@
         <v>47</v>
       </c>
       <c r="C29" s="140" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
@@ -10281,10 +10281,10 @@
         <v>19</v>
       </c>
       <c r="C30" s="145" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
@@ -10292,10 +10292,10 @@
         <v>43</v>
       </c>
       <c r="C31" s="145" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D31" s="141" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -10303,10 +10303,10 @@
         <v>115</v>
       </c>
       <c r="C32" s="149" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D32" s="141" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
@@ -10314,10 +10314,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="140" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11309,10 +11309,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="150" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B1" s="150" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C1" s="150" t="s">
         <v>136</v>
@@ -11325,7 +11325,7 @@
         <v>46165.0</v>
       </c>
       <c r="B2" s="150" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C2" s="152">
         <v>10000.0</v>
@@ -11338,7 +11338,7 @@
         <v>46166.0</v>
       </c>
       <c r="B3" s="150" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C3" s="152">
         <v>19000.0</v>
@@ -11351,7 +11351,7 @@
         <v>46168.0</v>
       </c>
       <c r="B4" s="150" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C4" s="153">
         <v>2500.0</v>
@@ -11364,7 +11364,7 @@
         <v>46169.0</v>
       </c>
       <c r="B5" s="150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C5" s="152">
         <v>29050.0</v>
@@ -11377,7 +11377,7 @@
         <v>46169.0</v>
       </c>
       <c r="B6" s="150" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C6" s="153">
         <v>100.0</v>
@@ -11390,7 +11390,7 @@
         <v>46169.0</v>
       </c>
       <c r="B7" s="150" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C7" s="153">
         <v>300.0</v>
@@ -11403,7 +11403,7 @@
         <v>46169.0</v>
       </c>
       <c r="B8" s="150" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C8" s="153">
         <v>370.0</v>
@@ -11416,7 +11416,7 @@
         <v>46169.0</v>
       </c>
       <c r="B9" s="150" t="s">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="C9" s="153">
         <v>2494.0</v>
@@ -11429,7 +11429,7 @@
         <v>46169.0</v>
       </c>
       <c r="B10" s="150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C10" s="153">
         <v>5000.0</v>
@@ -11442,13 +11442,13 @@
         <v>46169.0</v>
       </c>
       <c r="B11" s="150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C11" s="152">
         <v>29000.0</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E11" s="153">
         <v>24000.0</v>
@@ -11459,13 +11459,13 @@
         <v>46169.0</v>
       </c>
       <c r="B12" s="150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C12" s="153">
         <v>400.0</v>
       </c>
       <c r="D12" s="150" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E12" s="152">
         <v>53000.0</v>
@@ -11476,7 +11476,7 @@
         <v>46169.0</v>
       </c>
       <c r="B13" s="150" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C13" s="153">
         <v>600.0</v>
@@ -11495,30 +11495,30 @@
     </row>
     <row r="22">
       <c r="A22" s="150" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B22" s="150" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C22" s="150" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D22" s="150" t="s">
         <v>136</v>
       </c>
       <c r="E22" s="150" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B23" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C23" s="150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D23" s="153">
         <v>3150.0</v>
@@ -11529,13 +11529,13 @@
     </row>
     <row r="24">
       <c r="A24" s="150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B24" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C24" s="150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D24" s="153">
         <v>2650.0</v>
@@ -11546,13 +11546,13 @@
     </row>
     <row r="25">
       <c r="A25" s="150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B25" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C25" s="150" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D25" s="153">
         <v>2600.0</v>
@@ -11563,13 +11563,13 @@
     </row>
     <row r="26">
       <c r="A26" s="150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B26" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C26" s="150" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D26" s="153">
         <v>2680.0</v>
@@ -11580,7 +11580,7 @@
     </row>
     <row r="27">
       <c r="A27" s="150" t="s">
-        <v>282</v>
+        <v>168</v>
       </c>
       <c r="B27" s="150" t="s">
         <v>283</v>
@@ -11597,7 +11597,7 @@
     </row>
     <row r="28">
       <c r="A28" s="150" t="s">
-        <v>282</v>
+        <v>168</v>
       </c>
       <c r="B28" s="150" t="s">
         <v>283</v>
@@ -11614,7 +11614,7 @@
     </row>
     <row r="29">
       <c r="A29" s="150" t="s">
-        <v>282</v>
+        <v>168</v>
       </c>
       <c r="B29" s="150" t="s">
         <v>283</v>
@@ -11635,7 +11635,7 @@
       </c>
       <c r="B30" s="150"/>
       <c r="C30" s="150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D30" s="153">
         <v>2960.0</v>
@@ -11985,7 +11985,7 @@
     </row>
     <row r="61">
       <c r="A61" s="181" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B61" s="181" t="s">
         <v>307</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="333">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -538,6 +538,9 @@
   </si>
   <si>
     <t>Appa</t>
+  </si>
+  <si>
+    <t>AMMA - Microloan</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -4073,11 +4076,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>93623</v>
+        <v>99623</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-76959</v>
+        <v>-82959</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -8346,10 +8349,18 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="108"/>
-      <c r="B32" s="108"/>
-      <c r="C32" s="110"/>
-      <c r="D32" s="108"/>
+      <c r="A32" s="109">
+        <v>46189.0</v>
+      </c>
+      <c r="B32" s="101" t="s">
+        <v>172</v>
+      </c>
+      <c r="C32" s="102">
+        <v>6000.0</v>
+      </c>
+      <c r="D32" s="103">
+        <v>46191.0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="108"/>
@@ -8784,30 +8795,30 @@
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
       <c r="B2" s="111" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="112" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C4" s="112" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D4" s="112" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E4" s="112" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F4" s="112" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G4" s="112" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H4" s="113" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
@@ -8818,10 +8829,10 @@
         <v>0.11</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E5" s="114" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F5" s="116">
         <v>391560.0</v>
@@ -8831,7 +8842,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21240.78904</v>
+        <v>21358.79342</v>
       </c>
     </row>
     <row r="6">
@@ -8842,10 +8853,10 @@
         <v>0.1</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E6" s="114" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F6" s="116">
         <v>229500.0</v>
@@ -8855,7 +8866,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14084.38356</v>
+        <v>14147.26027</v>
       </c>
     </row>
     <row r="7">
@@ -8866,10 +8877,10 @@
         <v>0.105</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F7" s="116">
         <v>300000.0</v>
@@ -8879,7 +8890,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1812.328767</v>
+        <v>1898.630137</v>
       </c>
     </row>
     <row r="8">
@@ -8888,10 +8899,10 @@
       </c>
       <c r="C8" s="118"/>
       <c r="D8" s="114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E8" s="114" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F8" s="116">
         <v>135000.0</v>
@@ -8908,10 +8919,10 @@
       <c r="B9" s="119"/>
       <c r="C9" s="118"/>
       <c r="D9" s="114" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="E9" s="114" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F9" s="116">
         <v>297698.0</v>
@@ -9992,14 +10003,14 @@
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
       <c r="B1" s="122" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="123" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
@@ -10007,172 +10018,172 @@
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
       <c r="B4" s="124" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
       <c r="B5" s="124" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D5" s="126" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
       <c r="B6" s="124" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C6" s="125" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D6" s="126" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="B7" s="124" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C7" s="125" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D7" s="126" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
       <c r="B8" s="127" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D8" s="126" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="B9" s="127" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D9" s="126" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
       <c r="B10" s="129" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C10" s="130" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D10" s="126" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
       <c r="B11" s="129" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C11" s="130" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D11" s="126" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
       <c r="B12" s="131" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12" s="132" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D12" s="126" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
       <c r="B13" s="131" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C13" s="132" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
       <c r="B14" s="133" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
       <c r="B15" s="135" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D15" s="126" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
       <c r="B16" s="129" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C16" s="130" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
       <c r="B17" s="135" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C17" s="136" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D17" s="126" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
       <c r="B18" s="131" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C18" s="132" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="137" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
@@ -10182,10 +10193,10 @@
         <v>70</v>
       </c>
       <c r="C21" s="138" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D21" s="138" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -10193,10 +10204,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="140" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
@@ -10204,10 +10215,10 @@
         <v>26</v>
       </c>
       <c r="C23" s="140" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
@@ -10215,10 +10226,10 @@
         <v>83</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D24" s="141" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
@@ -10226,10 +10237,10 @@
         <v>85</v>
       </c>
       <c r="C25" s="140" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D25" s="141" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
@@ -10237,10 +10248,10 @@
         <v>35</v>
       </c>
       <c r="C26" s="145" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
@@ -10248,10 +10259,10 @@
         <v>90</v>
       </c>
       <c r="C27" s="147" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
@@ -10259,10 +10270,10 @@
         <v>49</v>
       </c>
       <c r="C28" s="140" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
@@ -10270,10 +10281,10 @@
         <v>47</v>
       </c>
       <c r="C29" s="140" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
@@ -10281,10 +10292,10 @@
         <v>19</v>
       </c>
       <c r="C30" s="145" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
@@ -10292,10 +10303,10 @@
         <v>43</v>
       </c>
       <c r="C31" s="145" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D31" s="141" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -10303,10 +10314,10 @@
         <v>115</v>
       </c>
       <c r="C32" s="149" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D32" s="141" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
@@ -10314,10 +10325,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="140" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11309,10 +11320,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="150" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B1" s="150" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C1" s="150" t="s">
         <v>136</v>
@@ -11325,7 +11336,7 @@
         <v>46165.0</v>
       </c>
       <c r="B2" s="150" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C2" s="152">
         <v>10000.0</v>
@@ -11338,7 +11349,7 @@
         <v>46166.0</v>
       </c>
       <c r="B3" s="150" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C3" s="152">
         <v>19000.0</v>
@@ -11351,7 +11362,7 @@
         <v>46168.0</v>
       </c>
       <c r="B4" s="150" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C4" s="153">
         <v>2500.0</v>
@@ -11364,7 +11375,7 @@
         <v>46169.0</v>
       </c>
       <c r="B5" s="150" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C5" s="152">
         <v>29050.0</v>
@@ -11377,7 +11388,7 @@
         <v>46169.0</v>
       </c>
       <c r="B6" s="150" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C6" s="153">
         <v>100.0</v>
@@ -11390,7 +11401,7 @@
         <v>46169.0</v>
       </c>
       <c r="B7" s="150" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C7" s="153">
         <v>300.0</v>
@@ -11403,7 +11414,7 @@
         <v>46169.0</v>
       </c>
       <c r="B8" s="150" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C8" s="153">
         <v>370.0</v>
@@ -11429,7 +11440,7 @@
         <v>46169.0</v>
       </c>
       <c r="B10" s="150" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C10" s="153">
         <v>5000.0</v>
@@ -11442,13 +11453,13 @@
         <v>46169.0</v>
       </c>
       <c r="B11" s="150" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C11" s="152">
         <v>29000.0</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E11" s="153">
         <v>24000.0</v>
@@ -11459,13 +11470,13 @@
         <v>46169.0</v>
       </c>
       <c r="B12" s="150" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C12" s="153">
         <v>400.0</v>
       </c>
       <c r="D12" s="150" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E12" s="152">
         <v>53000.0</v>
@@ -11476,7 +11487,7 @@
         <v>46169.0</v>
       </c>
       <c r="B13" s="150" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C13" s="153">
         <v>600.0</v>
@@ -11495,30 +11506,30 @@
     </row>
     <row r="22">
       <c r="A22" s="150" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B22" s="150" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C22" s="150" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D22" s="150" t="s">
         <v>136</v>
       </c>
       <c r="E22" s="150" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B23" s="150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C23" s="150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D23" s="153">
         <v>3150.0</v>
@@ -11529,13 +11540,13 @@
     </row>
     <row r="24">
       <c r="A24" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B24" s="150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C24" s="150" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D24" s="153">
         <v>2650.0</v>
@@ -11546,13 +11557,13 @@
     </row>
     <row r="25">
       <c r="A25" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B25" s="150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C25" s="150" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D25" s="153">
         <v>2600.0</v>
@@ -11563,13 +11574,13 @@
     </row>
     <row r="26">
       <c r="A26" s="150" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B26" s="150" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C26" s="150" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D26" s="153">
         <v>2680.0</v>
@@ -11583,10 +11594,10 @@
         <v>168</v>
       </c>
       <c r="B27" s="150" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C27" s="150" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D27" s="153">
         <v>5390.0</v>
@@ -11600,10 +11611,10 @@
         <v>168</v>
       </c>
       <c r="B28" s="150" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C28" s="150" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D28" s="153">
         <v>3235.0</v>
@@ -11617,25 +11628,25 @@
         <v>168</v>
       </c>
       <c r="B29" s="150" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C29" s="150" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D29" s="153">
         <v>1230.0</v>
       </c>
       <c r="E29" s="150" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="150" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B30" s="150"/>
       <c r="C30" s="150" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D30" s="153">
         <v>2960.0</v>
@@ -11644,11 +11655,11 @@
     </row>
     <row r="31">
       <c r="A31" s="150" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B31" s="150"/>
       <c r="C31" s="150" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D31" s="153">
         <v>2960.0</v>
@@ -11657,22 +11668,22 @@
     </row>
     <row r="32">
       <c r="A32" s="150" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B32" s="150" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C32" s="150"/>
       <c r="D32" s="153">
         <v>5000.0</v>
       </c>
       <c r="E32" s="150" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="156" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B42" s="150"/>
       <c r="C42" s="150"/>
@@ -11713,36 +11724,36 @@
         <v>6</v>
       </c>
       <c r="B45" s="157" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C45" s="157" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D45" s="157" t="s">
         <v>77</v>
       </c>
       <c r="E45" s="157" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F45" s="157" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G45" s="157" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H45" s="157" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I45" s="157" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="J45" s="157" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="158" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B46" s="159">
         <v>1000000.0</v>
@@ -11779,7 +11790,7 @@
     </row>
     <row r="47">
       <c r="A47" s="163" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B47" s="164">
         <v>596000.0</v>
@@ -11816,7 +11827,7 @@
     </row>
     <row r="48">
       <c r="A48" s="158" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B48" s="168"/>
       <c r="C48" s="169"/>
@@ -11880,7 +11891,7 @@
     </row>
     <row r="50">
       <c r="A50" s="158" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B50" s="159">
         <v>83419.0</v>
@@ -11917,7 +11928,7 @@
     </row>
     <row r="51">
       <c r="A51" s="176" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B51" s="177">
         <v>149100.0</v>
@@ -11954,7 +11965,7 @@
     </row>
     <row r="52">
       <c r="A52" s="158" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B52" s="168"/>
       <c r="C52" s="169"/>
@@ -11985,32 +11996,32 @@
     </row>
     <row r="61">
       <c r="A61" s="181" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B61" s="181" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="D61" s="181" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E61" s="181" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F61" s="181" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="H61" s="150"/>
       <c r="I61" s="181" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="J61" s="150" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="62">
@@ -12018,7 +12029,7 @@
         <v>46143.0</v>
       </c>
       <c r="B62" s="150" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C62" s="182">
         <v>11839.0</v>
@@ -12027,17 +12038,17 @@
         <v>1</v>
       </c>
       <c r="E62" s="150" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F62" s="150" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="G62" s="182">
         <v>71000.0</v>
       </c>
       <c r="H62" s="150"/>
       <c r="I62" s="181" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="J62" s="182">
         <f>SUM(C62:C1000)</f>
@@ -12049,7 +12060,7 @@
         <v>46144.0</v>
       </c>
       <c r="B63" s="150" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C63" s="182">
         <v>3850.0</v>
@@ -12058,13 +12069,13 @@
         <v>1</v>
       </c>
       <c r="E63" s="150" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F63" s="150"/>
       <c r="G63" s="184"/>
       <c r="H63" s="150"/>
       <c r="I63" s="181" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J63" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
@@ -12076,7 +12087,7 @@
         <v>46145.0</v>
       </c>
       <c r="B64" s="150" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C64" s="182">
         <v>4627.0</v>
@@ -12089,7 +12100,7 @@
       <c r="G64" s="184"/>
       <c r="H64" s="150"/>
       <c r="I64" s="181" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="J64" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
@@ -12101,7 +12112,7 @@
         <v>46147.0</v>
       </c>
       <c r="B65" s="150" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C65" s="182">
         <v>5000.0</v>
@@ -12114,7 +12125,7 @@
       <c r="G65" s="184"/>
       <c r="H65" s="150"/>
       <c r="I65" s="181" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J65" s="182">
         <f>SUM(G62:G1000)</f>
@@ -12126,7 +12137,7 @@
         <v>46167.0</v>
       </c>
       <c r="B66" s="150" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C66" s="182">
         <v>18972.0</v>
@@ -12141,7 +12152,7 @@
       <c r="G66" s="184"/>
       <c r="H66" s="150"/>
       <c r="I66" s="181" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J66" s="182">
         <f>J65-J62</f>
@@ -12153,7 +12164,7 @@
         <v>46146.0</v>
       </c>
       <c r="B67" s="150" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C67" s="182">
         <v>13625.0</v>
@@ -12162,7 +12173,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="150" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F67" s="150"/>
       <c r="G67" s="184"/>
@@ -12175,7 +12186,7 @@
         <v>46145.0</v>
       </c>
       <c r="B68" s="150" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C68" s="182">
         <v>2494.0</v>
@@ -12195,7 +12206,7 @@
         <v>46144.0</v>
       </c>
       <c r="B69" s="150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C69" s="182">
         <v>4500.0</v>
@@ -12215,7 +12226,7 @@
         <v>46152.0</v>
       </c>
       <c r="B70" s="150" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C70" s="182">
         <v>1500.0</v>
@@ -12235,7 +12246,7 @@
         <v>46152.0</v>
       </c>
       <c r="B71" s="150" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C71" s="182">
         <v>3000.0</v>
@@ -12255,7 +12266,7 @@
         <v>46157.0</v>
       </c>
       <c r="B72" s="150" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C72" s="182">
         <v>15250.0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8842,7 +8842,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21358.79342</v>
+        <v>21476.79781</v>
       </c>
     </row>
     <row r="6">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14147.26027</v>
+        <v>14210.13699</v>
       </c>
     </row>
     <row r="7">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1898.630137</v>
+        <v>1984.931507</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="335">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -541,6 +541,12 @@
   </si>
   <si>
     <t>AMMA - Microloan</t>
+  </si>
+  <si>
+    <t>Cylinder</t>
+  </si>
+  <si>
+    <t>Other loan</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -4076,11 +4082,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>99623</v>
+        <v>105693</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-82959</v>
+        <v>-89029</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -8363,16 +8369,32 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="108"/>
-      <c r="B33" s="108"/>
-      <c r="C33" s="110"/>
-      <c r="D33" s="108"/>
+      <c r="A33" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B33" s="101" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33" s="102">
+        <v>1070.0</v>
+      </c>
+      <c r="D33" s="103">
+        <v>46193.0</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="108"/>
-      <c r="B34" s="108"/>
-      <c r="C34" s="110"/>
-      <c r="D34" s="108"/>
+      <c r="A34" s="109">
+        <v>46174.0</v>
+      </c>
+      <c r="B34" s="101" t="s">
+        <v>174</v>
+      </c>
+      <c r="C34" s="102">
+        <v>5000.0</v>
+      </c>
+      <c r="D34" s="103">
+        <v>46193.0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="108"/>
@@ -8795,30 +8817,30 @@
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
       <c r="B2" s="111" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="112" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C4" s="112" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D4" s="112" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E4" s="112" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F4" s="112" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G4" s="112" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H4" s="113" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5">
@@ -8829,10 +8851,10 @@
         <v>0.11</v>
       </c>
       <c r="D5" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E5" s="114" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F5" s="116">
         <v>391560.0</v>
@@ -8842,7 +8864,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21476.79781</v>
+        <v>21594.80219</v>
       </c>
     </row>
     <row r="6">
@@ -8853,10 +8875,10 @@
         <v>0.1</v>
       </c>
       <c r="D6" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E6" s="114" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F6" s="116">
         <v>229500.0</v>
@@ -8866,7 +8888,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14210.13699</v>
+        <v>14273.0137</v>
       </c>
     </row>
     <row r="7">
@@ -8877,10 +8899,10 @@
         <v>0.105</v>
       </c>
       <c r="D7" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E7" s="114" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F7" s="116">
         <v>300000.0</v>
@@ -8890,7 +8912,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>1984.931507</v>
+        <v>2071.232877</v>
       </c>
     </row>
     <row r="8">
@@ -8899,10 +8921,10 @@
       </c>
       <c r="C8" s="118"/>
       <c r="D8" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E8" s="114" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F8" s="116">
         <v>135000.0</v>
@@ -8919,10 +8941,10 @@
       <c r="B9" s="119"/>
       <c r="C9" s="118"/>
       <c r="D9" s="114" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E9" s="114" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F9" s="116">
         <v>297698.0</v>
@@ -10003,14 +10025,14 @@
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
       <c r="B1" s="122" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="123" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
@@ -10018,172 +10040,172 @@
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
       <c r="B4" s="124" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C4" s="125" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D4" s="126" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
       <c r="B5" s="124" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" s="125" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D5" s="126" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
       <c r="B6" s="124" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C6" s="125" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D6" s="126" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="B7" s="124" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C7" s="125" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D7" s="126" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
       <c r="B8" s="127" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D8" s="126" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="B9" s="127" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D9" s="126" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
       <c r="B10" s="129" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C10" s="130" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D10" s="126" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
       <c r="B11" s="129" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C11" s="130" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D11" s="126" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
       <c r="B12" s="131" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C12" s="132" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D12" s="126" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
       <c r="B13" s="131" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C13" s="132" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D13" s="126" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
       <c r="B14" s="133" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C14" s="134" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D14" s="126" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
       <c r="B15" s="135" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C15" s="136" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D15" s="126" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
       <c r="B16" s="129" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C16" s="130" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D16" s="126" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
       <c r="B17" s="135" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C17" s="136" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D17" s="126" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
       <c r="B18" s="131" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C18" s="132" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D18" s="126" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="137" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
@@ -10193,10 +10215,10 @@
         <v>70</v>
       </c>
       <c r="C21" s="138" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D21" s="138" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -10204,10 +10226,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="140" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D22" s="141" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
@@ -10215,10 +10237,10 @@
         <v>26</v>
       </c>
       <c r="C23" s="140" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D23" s="141" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
@@ -10226,10 +10248,10 @@
         <v>83</v>
       </c>
       <c r="C24" s="143" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D24" s="141" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
@@ -10237,10 +10259,10 @@
         <v>85</v>
       </c>
       <c r="C25" s="140" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D25" s="141" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
@@ -10248,10 +10270,10 @@
         <v>35</v>
       </c>
       <c r="C26" s="145" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D26" s="141" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
@@ -10259,10 +10281,10 @@
         <v>90</v>
       </c>
       <c r="C27" s="147" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D27" s="141" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
@@ -10270,10 +10292,10 @@
         <v>49</v>
       </c>
       <c r="C28" s="140" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D28" s="141" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
@@ -10281,10 +10303,10 @@
         <v>47</v>
       </c>
       <c r="C29" s="140" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D29" s="141" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
@@ -10292,10 +10314,10 @@
         <v>19</v>
       </c>
       <c r="C30" s="145" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D30" s="141" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
@@ -10303,10 +10325,10 @@
         <v>43</v>
       </c>
       <c r="C31" s="145" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D31" s="141" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -10314,10 +10336,10 @@
         <v>115</v>
       </c>
       <c r="C32" s="149" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D32" s="141" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
@@ -10325,10 +10347,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="140" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D33" s="141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11320,10 +11342,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="150" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B1" s="150" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="C1" s="150" t="s">
         <v>136</v>
@@ -11336,7 +11358,7 @@
         <v>46165.0</v>
       </c>
       <c r="B2" s="150" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C2" s="152">
         <v>10000.0</v>
@@ -11349,7 +11371,7 @@
         <v>46166.0</v>
       </c>
       <c r="B3" s="150" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C3" s="152">
         <v>19000.0</v>
@@ -11362,7 +11384,7 @@
         <v>46168.0</v>
       </c>
       <c r="B4" s="150" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C4" s="153">
         <v>2500.0</v>
@@ -11375,7 +11397,7 @@
         <v>46169.0</v>
       </c>
       <c r="B5" s="150" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C5" s="152">
         <v>29050.0</v>
@@ -11388,7 +11410,7 @@
         <v>46169.0</v>
       </c>
       <c r="B6" s="150" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C6" s="153">
         <v>100.0</v>
@@ -11401,7 +11423,7 @@
         <v>46169.0</v>
       </c>
       <c r="B7" s="150" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C7" s="153">
         <v>300.0</v>
@@ -11414,7 +11436,7 @@
         <v>46169.0</v>
       </c>
       <c r="B8" s="150" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C8" s="153">
         <v>370.0</v>
@@ -11440,7 +11462,7 @@
         <v>46169.0</v>
       </c>
       <c r="B10" s="150" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C10" s="153">
         <v>5000.0</v>
@@ -11453,13 +11475,13 @@
         <v>46169.0</v>
       </c>
       <c r="B11" s="150" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C11" s="152">
         <v>29000.0</v>
       </c>
       <c r="D11" s="150" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E11" s="153">
         <v>24000.0</v>
@@ -11470,13 +11492,13 @@
         <v>46169.0</v>
       </c>
       <c r="B12" s="150" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C12" s="153">
         <v>400.0</v>
       </c>
       <c r="D12" s="150" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E12" s="152">
         <v>53000.0</v>
@@ -11487,7 +11509,7 @@
         <v>46169.0</v>
       </c>
       <c r="B13" s="150" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C13" s="153">
         <v>600.0</v>
@@ -11506,30 +11528,30 @@
     </row>
     <row r="22">
       <c r="A22" s="150" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B22" s="150" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C22" s="150" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D22" s="150" t="s">
         <v>136</v>
       </c>
       <c r="E22" s="150" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B23" s="150" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C23" s="150" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D23" s="153">
         <v>3150.0</v>
@@ -11540,13 +11562,13 @@
     </row>
     <row r="24">
       <c r="A24" s="150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B24" s="150" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C24" s="150" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="D24" s="153">
         <v>2650.0</v>
@@ -11557,13 +11579,13 @@
     </row>
     <row r="25">
       <c r="A25" s="150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B25" s="150" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" s="150" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D25" s="153">
         <v>2600.0</v>
@@ -11574,13 +11596,13 @@
     </row>
     <row r="26">
       <c r="A26" s="150" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B26" s="150" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C26" s="150" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D26" s="153">
         <v>2680.0</v>
@@ -11594,10 +11616,10 @@
         <v>168</v>
       </c>
       <c r="B27" s="150" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C27" s="150" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D27" s="153">
         <v>5390.0</v>
@@ -11611,10 +11633,10 @@
         <v>168</v>
       </c>
       <c r="B28" s="150" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C28" s="150" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D28" s="153">
         <v>3235.0</v>
@@ -11628,25 +11650,25 @@
         <v>168</v>
       </c>
       <c r="B29" s="150" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C29" s="150" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D29" s="153">
         <v>1230.0</v>
       </c>
       <c r="E29" s="150" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="150" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B30" s="150"/>
       <c r="C30" s="150" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D30" s="153">
         <v>2960.0</v>
@@ -11655,11 +11677,11 @@
     </row>
     <row r="31">
       <c r="A31" s="150" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B31" s="150"/>
       <c r="C31" s="150" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D31" s="153">
         <v>2960.0</v>
@@ -11668,22 +11690,22 @@
     </row>
     <row r="32">
       <c r="A32" s="150" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B32" s="150" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C32" s="150"/>
       <c r="D32" s="153">
         <v>5000.0</v>
       </c>
       <c r="E32" s="150" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="156" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B42" s="150"/>
       <c r="C42" s="150"/>
@@ -11724,36 +11746,36 @@
         <v>6</v>
       </c>
       <c r="B45" s="157" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C45" s="157" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D45" s="157" t="s">
         <v>77</v>
       </c>
       <c r="E45" s="157" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F45" s="157" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G45" s="157" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H45" s="157" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="I45" s="157" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J45" s="157" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="158" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B46" s="159">
         <v>1000000.0</v>
@@ -11790,7 +11812,7 @@
     </row>
     <row r="47">
       <c r="A47" s="163" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B47" s="164">
         <v>596000.0</v>
@@ -11827,7 +11849,7 @@
     </row>
     <row r="48">
       <c r="A48" s="158" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B48" s="168"/>
       <c r="C48" s="169"/>
@@ -11891,7 +11913,7 @@
     </row>
     <row r="50">
       <c r="A50" s="158" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B50" s="159">
         <v>83419.0</v>
@@ -11928,7 +11950,7 @@
     </row>
     <row r="51">
       <c r="A51" s="176" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B51" s="177">
         <v>149100.0</v>
@@ -11965,7 +11987,7 @@
     </row>
     <row r="52">
       <c r="A52" s="158" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B52" s="168"/>
       <c r="C52" s="169"/>
@@ -11996,32 +12018,32 @@
     </row>
     <row r="61">
       <c r="A61" s="181" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B61" s="181" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="D61" s="181" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E61" s="181" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F61" s="181" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="H61" s="150"/>
       <c r="I61" s="181" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J61" s="150" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="62">
@@ -12029,7 +12051,7 @@
         <v>46143.0</v>
       </c>
       <c r="B62" s="150" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C62" s="182">
         <v>11839.0</v>
@@ -12038,17 +12060,17 @@
         <v>1</v>
       </c>
       <c r="E62" s="150" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F62" s="150" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G62" s="182">
         <v>71000.0</v>
       </c>
       <c r="H62" s="150"/>
       <c r="I62" s="181" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="J62" s="182">
         <f>SUM(C62:C1000)</f>
@@ -12060,7 +12082,7 @@
         <v>46144.0</v>
       </c>
       <c r="B63" s="150" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C63" s="182">
         <v>3850.0</v>
@@ -12069,13 +12091,13 @@
         <v>1</v>
       </c>
       <c r="E63" s="150" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F63" s="150"/>
       <c r="G63" s="184"/>
       <c r="H63" s="150"/>
       <c r="I63" s="181" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="J63" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
@@ -12087,7 +12109,7 @@
         <v>46145.0</v>
       </c>
       <c r="B64" s="150" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C64" s="182">
         <v>4627.0</v>
@@ -12100,7 +12122,7 @@
       <c r="G64" s="184"/>
       <c r="H64" s="150"/>
       <c r="I64" s="181" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J64" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
@@ -12112,7 +12134,7 @@
         <v>46147.0</v>
       </c>
       <c r="B65" s="150" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C65" s="182">
         <v>5000.0</v>
@@ -12125,7 +12147,7 @@
       <c r="G65" s="184"/>
       <c r="H65" s="150"/>
       <c r="I65" s="181" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="J65" s="182">
         <f>SUM(G62:G1000)</f>
@@ -12137,7 +12159,7 @@
         <v>46167.0</v>
       </c>
       <c r="B66" s="150" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C66" s="182">
         <v>18972.0</v>
@@ -12152,7 +12174,7 @@
       <c r="G66" s="184"/>
       <c r="H66" s="150"/>
       <c r="I66" s="181" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="J66" s="182">
         <f>J65-J62</f>
@@ -12164,7 +12186,7 @@
         <v>46146.0</v>
       </c>
       <c r="B67" s="150" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C67" s="182">
         <v>13625.0</v>
@@ -12173,7 +12195,7 @@
         <v>1</v>
       </c>
       <c r="E67" s="150" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F67" s="150"/>
       <c r="G67" s="184"/>
@@ -12186,7 +12208,7 @@
         <v>46145.0</v>
       </c>
       <c r="B68" s="150" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C68" s="182">
         <v>2494.0</v>
@@ -12206,7 +12228,7 @@
         <v>46144.0</v>
       </c>
       <c r="B69" s="150" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C69" s="182">
         <v>4500.0</v>
@@ -12226,7 +12248,7 @@
         <v>46152.0</v>
       </c>
       <c r="B70" s="150" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C70" s="182">
         <v>1500.0</v>
@@ -12246,7 +12268,7 @@
         <v>46152.0</v>
       </c>
       <c r="B71" s="150" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C71" s="182">
         <v>3000.0</v>
@@ -12266,7 +12288,7 @@
         <v>46157.0</v>
       </c>
       <c r="B72" s="150" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C72" s="182">
         <v>15250.0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8864,7 +8864,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21594.80219</v>
+        <v>21712.80658</v>
       </c>
     </row>
     <row r="6">
@@ -8888,7 +8888,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14273.0137</v>
+        <v>14335.89041</v>
       </c>
     </row>
     <row r="7">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2071.232877</v>
+        <v>2157.534247</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="337">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -547,6 +547,12 @@
   </si>
   <si>
     <t>Other loan</t>
+  </si>
+  <si>
+    <t>Movie</t>
+  </si>
+  <si>
+    <t>Mat</t>
   </si>
   <si>
     <t>Gold Loan Tracker</t>
@@ -1033,18 +1039,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0;\(&quot;₹&quot;#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="₹#,##0"/>
-    <numFmt numFmtId="167" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="167" formatCode="mmmm yyyy"/>
     <numFmt numFmtId="168" formatCode="₹#,##0.00"/>
     <numFmt numFmtId="169" formatCode="d mmmm"/>
-    <numFmt numFmtId="170" formatCode="mmmm yyyy"/>
-    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="173" formatCode="d mmm yyyy"/>
-    <numFmt numFmtId="174" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="172" formatCode="d mmm yyyy"/>
+    <numFmt numFmtId="173" formatCode="d mmmm yyyy"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1419,7 +1424,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="185">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1727,9 +1732,6 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="168" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1747,13 +1749,13 @@
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="10" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="22" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="22" numFmtId="171" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="170" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="6" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1841,19 +1843,19 @@
     <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="171" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="172" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="174" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -4082,11 +4084,11 @@
       </c>
       <c r="E5" s="56">
         <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>105693</v>
+        <v>106763</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-89029</v>
+        <v>-90099</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -8089,7 +8091,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="109">
+      <c r="A13" s="100">
         <v>46174.0</v>
       </c>
       <c r="B13" s="101" t="s">
@@ -8103,7 +8105,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="109">
+      <c r="A14" s="100">
         <v>46174.0</v>
       </c>
       <c r="B14" s="101" t="s">
@@ -8117,7 +8119,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="109">
+      <c r="A15" s="100">
         <v>46174.0</v>
       </c>
       <c r="B15" s="101" t="s">
@@ -8131,7 +8133,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="109">
+      <c r="A16" s="100">
         <v>46174.0</v>
       </c>
       <c r="B16" s="101" t="s">
@@ -8145,7 +8147,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="109">
+      <c r="A17" s="100">
         <v>46174.0</v>
       </c>
       <c r="B17" s="101" t="s">
@@ -8159,7 +8161,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="109">
+      <c r="A18" s="100">
         <v>46175.0</v>
       </c>
       <c r="B18" s="101" t="s">
@@ -8173,7 +8175,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="109">
+      <c r="A19" s="100">
         <v>46176.0</v>
       </c>
       <c r="B19" s="101" t="s">
@@ -8187,7 +8189,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="109">
+      <c r="A20" s="100">
         <v>46177.0</v>
       </c>
       <c r="B20" s="101" t="s">
@@ -8201,7 +8203,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="109">
+      <c r="A21" s="100">
         <v>46178.0</v>
       </c>
       <c r="B21" s="101" t="s">
@@ -8215,7 +8217,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="109">
+      <c r="A22" s="100">
         <v>46179.0</v>
       </c>
       <c r="B22" s="101" t="s">
@@ -8229,7 +8231,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="109">
+      <c r="A23" s="100">
         <v>46180.0</v>
       </c>
       <c r="B23" s="101" t="s">
@@ -8243,7 +8245,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="109">
+      <c r="A24" s="100">
         <v>46181.0</v>
       </c>
       <c r="B24" s="101" t="s">
@@ -8257,7 +8259,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="109">
+      <c r="A25" s="100">
         <v>46182.0</v>
       </c>
       <c r="B25" s="101" t="s">
@@ -8271,7 +8273,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="109">
+      <c r="A26" s="100">
         <v>46183.0</v>
       </c>
       <c r="B26" s="101" t="s">
@@ -8285,7 +8287,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="109">
+      <c r="A27" s="100">
         <v>46184.0</v>
       </c>
       <c r="B27" s="101" t="s">
@@ -8299,7 +8301,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="109">
+      <c r="A28" s="100">
         <v>46185.0</v>
       </c>
       <c r="B28" s="101" t="s">
@@ -8313,7 +8315,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="109">
+      <c r="A29" s="100">
         <v>46186.0</v>
       </c>
       <c r="B29" s="101" t="s">
@@ -8327,7 +8329,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="109">
+      <c r="A30" s="100">
         <v>46187.0</v>
       </c>
       <c r="B30" s="101" t="s">
@@ -8341,7 +8343,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="109">
+      <c r="A31" s="100">
         <v>46188.0</v>
       </c>
       <c r="B31" s="101" t="s">
@@ -8355,7 +8357,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="109">
+      <c r="A32" s="100">
         <v>46189.0</v>
       </c>
       <c r="B32" s="101" t="s">
@@ -8369,7 +8371,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="109">
+      <c r="A33" s="100">
         <v>46174.0</v>
       </c>
       <c r="B33" s="101" t="s">
@@ -8383,7 +8385,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="109">
+      <c r="A34" s="100">
         <v>46174.0</v>
       </c>
       <c r="B34" s="101" t="s">
@@ -8397,399 +8399,415 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="108"/>
-      <c r="B35" s="108"/>
-      <c r="C35" s="110"/>
-      <c r="D35" s="108"/>
+      <c r="A35" s="100">
+        <v>46174.0</v>
+      </c>
+      <c r="B35" s="101" t="s">
+        <v>175</v>
+      </c>
+      <c r="C35" s="102">
+        <v>850.0</v>
+      </c>
+      <c r="D35" s="103">
+        <v>46194.0</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="108"/>
-      <c r="B36" s="108"/>
-      <c r="C36" s="110"/>
-      <c r="D36" s="108"/>
+      <c r="A36" s="100">
+        <v>46174.0</v>
+      </c>
+      <c r="B36" s="101" t="s">
+        <v>176</v>
+      </c>
+      <c r="C36" s="102">
+        <v>220.0</v>
+      </c>
+      <c r="D36" s="103">
+        <v>46194.0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="108"/>
       <c r="B37" s="108"/>
-      <c r="C37" s="110"/>
+      <c r="C37" s="109"/>
       <c r="D37" s="108"/>
     </row>
     <row r="38">
       <c r="A38" s="108"/>
       <c r="B38" s="108"/>
-      <c r="C38" s="110"/>
+      <c r="C38" s="109"/>
       <c r="D38" s="108"/>
     </row>
     <row r="39">
       <c r="A39" s="108"/>
       <c r="B39" s="108"/>
-      <c r="C39" s="110"/>
+      <c r="C39" s="109"/>
       <c r="D39" s="108"/>
     </row>
     <row r="40">
       <c r="A40" s="108"/>
       <c r="B40" s="108"/>
-      <c r="C40" s="110"/>
+      <c r="C40" s="109"/>
       <c r="D40" s="108"/>
     </row>
     <row r="41">
       <c r="A41" s="108"/>
       <c r="B41" s="108"/>
-      <c r="C41" s="110"/>
+      <c r="C41" s="109"/>
       <c r="D41" s="108"/>
     </row>
     <row r="42">
       <c r="A42" s="108"/>
       <c r="B42" s="108"/>
-      <c r="C42" s="110"/>
+      <c r="C42" s="109"/>
       <c r="D42" s="108"/>
     </row>
     <row r="43">
       <c r="A43" s="108"/>
       <c r="B43" s="108"/>
-      <c r="C43" s="110"/>
+      <c r="C43" s="109"/>
       <c r="D43" s="108"/>
     </row>
     <row r="44">
       <c r="A44" s="108"/>
       <c r="B44" s="108"/>
-      <c r="C44" s="110"/>
+      <c r="C44" s="109"/>
       <c r="D44" s="108"/>
     </row>
     <row r="45">
       <c r="A45" s="108"/>
       <c r="B45" s="108"/>
-      <c r="C45" s="110"/>
+      <c r="C45" s="109"/>
       <c r="D45" s="108"/>
     </row>
     <row r="46">
       <c r="A46" s="108"/>
       <c r="B46" s="108"/>
-      <c r="C46" s="110"/>
+      <c r="C46" s="109"/>
       <c r="D46" s="108"/>
     </row>
     <row r="47">
       <c r="A47" s="108"/>
       <c r="B47" s="108"/>
-      <c r="C47" s="110"/>
+      <c r="C47" s="109"/>
       <c r="D47" s="108"/>
     </row>
     <row r="48">
       <c r="A48" s="108"/>
       <c r="B48" s="108"/>
-      <c r="C48" s="110"/>
+      <c r="C48" s="109"/>
       <c r="D48" s="108"/>
     </row>
     <row r="49">
       <c r="A49" s="108"/>
       <c r="B49" s="108"/>
-      <c r="C49" s="110"/>
+      <c r="C49" s="109"/>
       <c r="D49" s="108"/>
     </row>
     <row r="50">
       <c r="A50" s="108"/>
       <c r="B50" s="108"/>
-      <c r="C50" s="110"/>
+      <c r="C50" s="109"/>
       <c r="D50" s="108"/>
     </row>
     <row r="51">
       <c r="A51" s="108"/>
       <c r="B51" s="108"/>
-      <c r="C51" s="110"/>
+      <c r="C51" s="109"/>
       <c r="D51" s="108"/>
     </row>
     <row r="52">
       <c r="A52" s="108"/>
       <c r="B52" s="108"/>
-      <c r="C52" s="110"/>
+      <c r="C52" s="109"/>
       <c r="D52" s="108"/>
     </row>
     <row r="53">
       <c r="A53" s="108"/>
       <c r="B53" s="108"/>
-      <c r="C53" s="110"/>
+      <c r="C53" s="109"/>
       <c r="D53" s="108"/>
     </row>
     <row r="54">
       <c r="A54" s="108"/>
       <c r="B54" s="108"/>
-      <c r="C54" s="110"/>
+      <c r="C54" s="109"/>
       <c r="D54" s="108"/>
     </row>
     <row r="55">
       <c r="A55" s="108"/>
       <c r="B55" s="108"/>
-      <c r="C55" s="110"/>
+      <c r="C55" s="109"/>
       <c r="D55" s="108"/>
     </row>
     <row r="56">
       <c r="A56" s="108"/>
       <c r="B56" s="108"/>
-      <c r="C56" s="110"/>
+      <c r="C56" s="109"/>
       <c r="D56" s="108"/>
     </row>
     <row r="57">
       <c r="A57" s="108"/>
       <c r="B57" s="108"/>
-      <c r="C57" s="110"/>
+      <c r="C57" s="109"/>
       <c r="D57" s="108"/>
     </row>
     <row r="58">
       <c r="A58" s="108"/>
       <c r="B58" s="108"/>
-      <c r="C58" s="110"/>
+      <c r="C58" s="109"/>
       <c r="D58" s="108"/>
     </row>
     <row r="59">
       <c r="A59" s="108"/>
       <c r="B59" s="108"/>
-      <c r="C59" s="110"/>
+      <c r="C59" s="109"/>
       <c r="D59" s="108"/>
     </row>
     <row r="60">
       <c r="A60" s="108"/>
       <c r="B60" s="108"/>
-      <c r="C60" s="110"/>
+      <c r="C60" s="109"/>
       <c r="D60" s="108"/>
     </row>
     <row r="61">
       <c r="A61" s="108"/>
       <c r="B61" s="108"/>
-      <c r="C61" s="110"/>
+      <c r="C61" s="109"/>
       <c r="D61" s="108"/>
     </row>
     <row r="62">
       <c r="A62" s="108"/>
       <c r="B62" s="108"/>
-      <c r="C62" s="110"/>
+      <c r="C62" s="109"/>
       <c r="D62" s="108"/>
     </row>
     <row r="63">
       <c r="A63" s="108"/>
       <c r="B63" s="108"/>
-      <c r="C63" s="110"/>
+      <c r="C63" s="109"/>
       <c r="D63" s="108"/>
     </row>
     <row r="64">
       <c r="A64" s="108"/>
       <c r="B64" s="108"/>
-      <c r="C64" s="110"/>
+      <c r="C64" s="109"/>
       <c r="D64" s="108"/>
     </row>
     <row r="65">
       <c r="A65" s="108"/>
       <c r="B65" s="108"/>
-      <c r="C65" s="110"/>
+      <c r="C65" s="109"/>
       <c r="D65" s="108"/>
     </row>
     <row r="66">
       <c r="A66" s="108"/>
       <c r="B66" s="108"/>
-      <c r="C66" s="110"/>
+      <c r="C66" s="109"/>
       <c r="D66" s="108"/>
     </row>
     <row r="67">
       <c r="A67" s="108"/>
       <c r="B67" s="108"/>
-      <c r="C67" s="110"/>
+      <c r="C67" s="109"/>
       <c r="D67" s="108"/>
     </row>
     <row r="68">
       <c r="A68" s="108"/>
       <c r="B68" s="108"/>
-      <c r="C68" s="110"/>
+      <c r="C68" s="109"/>
       <c r="D68" s="108"/>
     </row>
     <row r="69">
       <c r="A69" s="108"/>
       <c r="B69" s="108"/>
-      <c r="C69" s="110"/>
+      <c r="C69" s="109"/>
       <c r="D69" s="108"/>
     </row>
     <row r="70">
       <c r="A70" s="108"/>
       <c r="B70" s="108"/>
-      <c r="C70" s="110"/>
+      <c r="C70" s="109"/>
       <c r="D70" s="108"/>
     </row>
     <row r="71">
       <c r="A71" s="108"/>
       <c r="B71" s="108"/>
-      <c r="C71" s="110"/>
+      <c r="C71" s="109"/>
       <c r="D71" s="108"/>
     </row>
     <row r="72">
       <c r="A72" s="108"/>
       <c r="B72" s="108"/>
-      <c r="C72" s="110"/>
+      <c r="C72" s="109"/>
       <c r="D72" s="108"/>
     </row>
     <row r="73">
       <c r="A73" s="108"/>
       <c r="B73" s="108"/>
-      <c r="C73" s="110"/>
+      <c r="C73" s="109"/>
       <c r="D73" s="108"/>
     </row>
     <row r="74">
       <c r="A74" s="108"/>
       <c r="B74" s="108"/>
-      <c r="C74" s="110"/>
+      <c r="C74" s="109"/>
       <c r="D74" s="108"/>
     </row>
     <row r="75">
       <c r="A75" s="108"/>
       <c r="B75" s="108"/>
-      <c r="C75" s="110"/>
+      <c r="C75" s="109"/>
       <c r="D75" s="108"/>
     </row>
     <row r="76">
       <c r="A76" s="108"/>
       <c r="B76" s="108"/>
-      <c r="C76" s="110"/>
+      <c r="C76" s="109"/>
       <c r="D76" s="108"/>
     </row>
     <row r="77">
       <c r="A77" s="108"/>
       <c r="B77" s="108"/>
-      <c r="C77" s="110"/>
+      <c r="C77" s="109"/>
       <c r="D77" s="108"/>
     </row>
     <row r="78">
       <c r="A78" s="108"/>
       <c r="B78" s="108"/>
-      <c r="C78" s="110"/>
+      <c r="C78" s="109"/>
       <c r="D78" s="108"/>
     </row>
     <row r="79">
       <c r="A79" s="108"/>
       <c r="B79" s="108"/>
-      <c r="C79" s="110"/>
+      <c r="C79" s="109"/>
       <c r="D79" s="108"/>
     </row>
     <row r="80">
       <c r="A80" s="108"/>
       <c r="B80" s="108"/>
-      <c r="C80" s="110"/>
+      <c r="C80" s="109"/>
       <c r="D80" s="108"/>
     </row>
     <row r="81">
       <c r="A81" s="108"/>
       <c r="B81" s="108"/>
-      <c r="C81" s="110"/>
+      <c r="C81" s="109"/>
       <c r="D81" s="108"/>
     </row>
     <row r="82">
       <c r="A82" s="108"/>
       <c r="B82" s="108"/>
-      <c r="C82" s="110"/>
+      <c r="C82" s="109"/>
       <c r="D82" s="108"/>
     </row>
     <row r="83">
       <c r="A83" s="108"/>
       <c r="B83" s="108"/>
-      <c r="C83" s="110"/>
+      <c r="C83" s="109"/>
       <c r="D83" s="108"/>
     </row>
     <row r="84">
       <c r="A84" s="108"/>
       <c r="B84" s="108"/>
-      <c r="C84" s="110"/>
+      <c r="C84" s="109"/>
       <c r="D84" s="108"/>
     </row>
     <row r="85">
       <c r="A85" s="108"/>
       <c r="B85" s="108"/>
-      <c r="C85" s="110"/>
+      <c r="C85" s="109"/>
       <c r="D85" s="108"/>
     </row>
     <row r="86">
       <c r="A86" s="108"/>
       <c r="B86" s="108"/>
-      <c r="C86" s="110"/>
+      <c r="C86" s="109"/>
       <c r="D86" s="108"/>
     </row>
     <row r="87">
       <c r="A87" s="108"/>
       <c r="B87" s="108"/>
-      <c r="C87" s="110"/>
+      <c r="C87" s="109"/>
       <c r="D87" s="108"/>
     </row>
     <row r="88">
       <c r="A88" s="108"/>
       <c r="B88" s="108"/>
-      <c r="C88" s="110"/>
+      <c r="C88" s="109"/>
       <c r="D88" s="108"/>
     </row>
     <row r="89">
       <c r="A89" s="108"/>
       <c r="B89" s="108"/>
-      <c r="C89" s="110"/>
+      <c r="C89" s="109"/>
       <c r="D89" s="108"/>
     </row>
     <row r="90">
       <c r="A90" s="108"/>
       <c r="B90" s="108"/>
-      <c r="C90" s="110"/>
+      <c r="C90" s="109"/>
       <c r="D90" s="108"/>
     </row>
     <row r="91">
       <c r="A91" s="108"/>
       <c r="B91" s="108"/>
-      <c r="C91" s="110"/>
+      <c r="C91" s="109"/>
       <c r="D91" s="108"/>
     </row>
     <row r="92">
       <c r="A92" s="108"/>
       <c r="B92" s="108"/>
-      <c r="C92" s="110"/>
+      <c r="C92" s="109"/>
       <c r="D92" s="108"/>
     </row>
     <row r="93">
       <c r="A93" s="108"/>
       <c r="B93" s="108"/>
-      <c r="C93" s="110"/>
+      <c r="C93" s="109"/>
       <c r="D93" s="108"/>
     </row>
     <row r="94">
       <c r="A94" s="108"/>
       <c r="B94" s="108"/>
-      <c r="C94" s="110"/>
+      <c r="C94" s="109"/>
       <c r="D94" s="108"/>
     </row>
     <row r="95">
       <c r="A95" s="108"/>
       <c r="B95" s="108"/>
-      <c r="C95" s="110"/>
+      <c r="C95" s="109"/>
       <c r="D95" s="108"/>
     </row>
     <row r="96">
       <c r="A96" s="108"/>
       <c r="B96" s="108"/>
-      <c r="C96" s="110"/>
+      <c r="C96" s="109"/>
       <c r="D96" s="108"/>
     </row>
     <row r="97">
       <c r="A97" s="108"/>
       <c r="B97" s="108"/>
-      <c r="C97" s="110"/>
+      <c r="C97" s="109"/>
       <c r="D97" s="108"/>
     </row>
     <row r="98">
       <c r="A98" s="108"/>
       <c r="B98" s="108"/>
-      <c r="C98" s="110"/>
+      <c r="C98" s="109"/>
       <c r="D98" s="108"/>
     </row>
     <row r="99">
       <c r="A99" s="108"/>
       <c r="B99" s="108"/>
-      <c r="C99" s="110"/>
+      <c r="C99" s="109"/>
       <c r="D99" s="108"/>
     </row>
     <row r="100">
       <c r="A100" s="108"/>
       <c r="B100" s="108"/>
-      <c r="C100" s="110"/>
+      <c r="C100" s="109"/>
       <c r="D100" s="108"/>
     </row>
   </sheetData>
@@ -8816,50 +8834,50 @@
   <sheetData>
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
-      <c r="B2" s="111" t="s">
-        <v>175</v>
+      <c r="B2" s="110" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="112" t="s">
-        <v>176</v>
-      </c>
-      <c r="C4" s="112" t="s">
-        <v>177</v>
-      </c>
-      <c r="D4" s="112" t="s">
+      <c r="B4" s="111" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="112" t="s">
+      <c r="C4" s="111" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="112" t="s">
+      <c r="D4" s="111" t="s">
         <v>180</v>
       </c>
-      <c r="G4" s="112" t="s">
+      <c r="E4" s="111" t="s">
         <v>181</v>
       </c>
-      <c r="H4" s="113" t="s">
+      <c r="F4" s="111" t="s">
         <v>182</v>
       </c>
+      <c r="G4" s="111" t="s">
+        <v>183</v>
+      </c>
+      <c r="H4" s="112" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" s="114">
+      <c r="B5" s="113">
         <v>55.8</v>
       </c>
-      <c r="C5" s="115">
+      <c r="C5" s="114">
         <v>0.11</v>
       </c>
-      <c r="D5" s="114" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="114" t="s">
-        <v>184</v>
-      </c>
-      <c r="F5" s="116">
+      <c r="D5" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="E5" s="113" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5" s="115">
         <v>391560.0</v>
       </c>
-      <c r="G5" s="117">
+      <c r="G5" s="116">
         <v>46010.0</v>
       </c>
       <c r="H5" s="10">
@@ -8868,22 +8886,22 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="114">
+      <c r="B6" s="113">
         <v>30.0</v>
       </c>
-      <c r="C6" s="115">
+      <c r="C6" s="114">
         <v>0.1</v>
       </c>
-      <c r="D6" s="114" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" s="114" t="s">
+      <c r="D6" s="113" t="s">
         <v>185</v>
       </c>
-      <c r="F6" s="116">
+      <c r="E6" s="113" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="115">
         <v>229500.0</v>
       </c>
-      <c r="G6" s="117">
+      <c r="G6" s="116">
         <v>45966.0</v>
       </c>
       <c r="H6" s="10">
@@ -8892,22 +8910,22 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="114">
+      <c r="B7" s="113">
         <v>36.9</v>
       </c>
-      <c r="C7" s="115">
+      <c r="C7" s="114">
         <v>0.105</v>
       </c>
-      <c r="D7" s="114" t="s">
-        <v>183</v>
-      </c>
-      <c r="E7" s="114" t="s">
-        <v>186</v>
-      </c>
-      <c r="F7" s="116">
+      <c r="D7" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="E7" s="113" t="s">
+        <v>188</v>
+      </c>
+      <c r="F7" s="115">
         <v>300000.0</v>
       </c>
-      <c r="G7" s="117">
+      <c r="G7" s="116">
         <v>46169.0</v>
       </c>
       <c r="H7" s="10">
@@ -8916,20 +8934,20 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="114">
+      <c r="B8" s="113">
         <v>15.0</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="114" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" s="114" t="s">
-        <v>186</v>
-      </c>
-      <c r="F8" s="116">
+      <c r="C8" s="117"/>
+      <c r="D8" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="E8" s="113" t="s">
+        <v>188</v>
+      </c>
+      <c r="F8" s="115">
         <v>135000.0</v>
       </c>
-      <c r="G8" s="117">
+      <c r="G8" s="116">
         <v>46178.0</v>
       </c>
       <c r="H8" s="10">
@@ -8938,18 +8956,18 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="119"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="114" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" s="114" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="116">
+      <c r="B9" s="118"/>
+      <c r="C9" s="117"/>
+      <c r="D9" s="113" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="113" t="s">
+        <v>189</v>
+      </c>
+      <c r="F9" s="115">
         <v>297698.0</v>
       </c>
-      <c r="G9" s="117">
+      <c r="G9" s="116">
         <v>46035.0</v>
       </c>
       <c r="H9" s="10">
@@ -8958,1044 +8976,1044 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="119"/>
-      <c r="C10" s="118"/>
-      <c r="D10" s="119"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="121"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="117"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="F10" s="119"/>
+      <c r="G10" s="120"/>
       <c r="H10" s="10" t="str">
         <f t="shared" ref="H10:H96" si="2">IF(OR(ISBLANK(F10), ISBLANK(G10)), "", F10 * (C10/100) * (TODAY() - G10) / 365)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="119"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="119"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="121"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="F11" s="119"/>
+      <c r="G11" s="120"/>
       <c r="H11" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="119"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="119"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="121"/>
+      <c r="B12" s="118"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="120"/>
       <c r="H12" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="119"/>
-      <c r="C13" s="118"/>
-      <c r="D13" s="119"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="121"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="120"/>
       <c r="H13" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="119"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="119"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="121"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="120"/>
       <c r="H14" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="119"/>
-      <c r="C15" s="118"/>
-      <c r="D15" s="119"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="121"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="120"/>
       <c r="H15" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="119"/>
-      <c r="C16" s="118"/>
-      <c r="D16" s="119"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="120"/>
-      <c r="G16" s="121"/>
+      <c r="B16" s="118"/>
+      <c r="C16" s="117"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="120"/>
       <c r="H16" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="119"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="119"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="120"/>
-      <c r="G17" s="121"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="117"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="120"/>
       <c r="H17" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="119"/>
-      <c r="C18" s="118"/>
-      <c r="D18" s="119"/>
-      <c r="E18" s="119"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="117"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="120"/>
       <c r="H18" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="119"/>
-      <c r="C19" s="118"/>
-      <c r="D19" s="119"/>
-      <c r="E19" s="119"/>
-      <c r="F19" s="120"/>
-      <c r="G19" s="121"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="120"/>
       <c r="H19" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="119"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="119"/>
-      <c r="E20" s="119"/>
-      <c r="F20" s="120"/>
-      <c r="G20" s="121"/>
+      <c r="B20" s="118"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="120"/>
       <c r="H20" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="119"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="119"/>
-      <c r="E21" s="119"/>
-      <c r="F21" s="120"/>
-      <c r="G21" s="121"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="117"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="120"/>
       <c r="H21" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="119"/>
-      <c r="C22" s="118"/>
-      <c r="D22" s="119"/>
-      <c r="E22" s="119"/>
-      <c r="F22" s="120"/>
-      <c r="G22" s="121"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="117"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="120"/>
       <c r="H22" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="119"/>
-      <c r="C23" s="118"/>
-      <c r="D23" s="119"/>
-      <c r="E23" s="119"/>
-      <c r="F23" s="120"/>
-      <c r="G23" s="121"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="117"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="120"/>
       <c r="H23" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="119"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="119"/>
-      <c r="F24" s="120"/>
-      <c r="G24" s="121"/>
+      <c r="B24" s="118"/>
+      <c r="C24" s="117"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="120"/>
       <c r="H24" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="119"/>
-      <c r="C25" s="118"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="119"/>
-      <c r="F25" s="120"/>
-      <c r="G25" s="121"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
+      <c r="F25" s="119"/>
+      <c r="G25" s="120"/>
       <c r="H25" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="119"/>
-      <c r="C26" s="118"/>
-      <c r="D26" s="119"/>
-      <c r="E26" s="119"/>
-      <c r="F26" s="120"/>
-      <c r="G26" s="121"/>
+      <c r="B26" s="118"/>
+      <c r="C26" s="117"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="F26" s="119"/>
+      <c r="G26" s="120"/>
       <c r="H26" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="119"/>
-      <c r="C27" s="118"/>
-      <c r="D27" s="119"/>
-      <c r="E27" s="119"/>
-      <c r="F27" s="120"/>
-      <c r="G27" s="121"/>
+      <c r="B27" s="118"/>
+      <c r="C27" s="117"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="F27" s="119"/>
+      <c r="G27" s="120"/>
       <c r="H27" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="119"/>
-      <c r="C28" s="118"/>
-      <c r="D28" s="119"/>
-      <c r="E28" s="119"/>
-      <c r="F28" s="120"/>
-      <c r="G28" s="121"/>
+      <c r="B28" s="118"/>
+      <c r="C28" s="117"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
+      <c r="F28" s="119"/>
+      <c r="G28" s="120"/>
       <c r="H28" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="119"/>
-      <c r="C29" s="118"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="120"/>
-      <c r="G29" s="121"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="117"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="120"/>
       <c r="H29" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="119"/>
-      <c r="C30" s="118"/>
-      <c r="D30" s="119"/>
-      <c r="E30" s="119"/>
-      <c r="F30" s="120"/>
-      <c r="G30" s="121"/>
+      <c r="B30" s="118"/>
+      <c r="C30" s="117"/>
+      <c r="D30" s="118"/>
+      <c r="E30" s="118"/>
+      <c r="F30" s="119"/>
+      <c r="G30" s="120"/>
       <c r="H30" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="119"/>
-      <c r="C31" s="118"/>
-      <c r="D31" s="119"/>
-      <c r="E31" s="119"/>
-      <c r="F31" s="120"/>
-      <c r="G31" s="121"/>
+      <c r="B31" s="118"/>
+      <c r="C31" s="117"/>
+      <c r="D31" s="118"/>
+      <c r="E31" s="118"/>
+      <c r="F31" s="119"/>
+      <c r="G31" s="120"/>
       <c r="H31" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="119"/>
-      <c r="C32" s="118"/>
-      <c r="D32" s="119"/>
-      <c r="E32" s="119"/>
-      <c r="F32" s="120"/>
-      <c r="G32" s="121"/>
+      <c r="B32" s="118"/>
+      <c r="C32" s="117"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="118"/>
+      <c r="F32" s="119"/>
+      <c r="G32" s="120"/>
       <c r="H32" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="119"/>
-      <c r="C33" s="118"/>
-      <c r="D33" s="119"/>
-      <c r="E33" s="119"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="121"/>
+      <c r="B33" s="118"/>
+      <c r="C33" s="117"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="118"/>
+      <c r="F33" s="119"/>
+      <c r="G33" s="120"/>
       <c r="H33" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="119"/>
-      <c r="C34" s="118"/>
-      <c r="D34" s="119"/>
-      <c r="E34" s="119"/>
-      <c r="F34" s="120"/>
-      <c r="G34" s="121"/>
+      <c r="B34" s="118"/>
+      <c r="C34" s="117"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="118"/>
+      <c r="F34" s="119"/>
+      <c r="G34" s="120"/>
       <c r="H34" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="119"/>
-      <c r="C35" s="118"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="119"/>
-      <c r="F35" s="120"/>
-      <c r="G35" s="121"/>
+      <c r="B35" s="118"/>
+      <c r="C35" s="117"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="118"/>
+      <c r="F35" s="119"/>
+      <c r="G35" s="120"/>
       <c r="H35" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="119"/>
-      <c r="C36" s="118"/>
-      <c r="D36" s="119"/>
-      <c r="E36" s="119"/>
-      <c r="F36" s="120"/>
-      <c r="G36" s="121"/>
+      <c r="B36" s="118"/>
+      <c r="C36" s="117"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="118"/>
+      <c r="F36" s="119"/>
+      <c r="G36" s="120"/>
       <c r="H36" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="119"/>
-      <c r="C37" s="118"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="119"/>
-      <c r="F37" s="120"/>
-      <c r="G37" s="121"/>
+      <c r="B37" s="118"/>
+      <c r="C37" s="117"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="118"/>
+      <c r="F37" s="119"/>
+      <c r="G37" s="120"/>
       <c r="H37" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="119"/>
-      <c r="C38" s="118"/>
-      <c r="D38" s="119"/>
-      <c r="E38" s="119"/>
-      <c r="F38" s="120"/>
-      <c r="G38" s="121"/>
+      <c r="B38" s="118"/>
+      <c r="C38" s="117"/>
+      <c r="D38" s="118"/>
+      <c r="E38" s="118"/>
+      <c r="F38" s="119"/>
+      <c r="G38" s="120"/>
       <c r="H38" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="119"/>
-      <c r="C39" s="118"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="121"/>
+      <c r="B39" s="118"/>
+      <c r="C39" s="117"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="118"/>
+      <c r="F39" s="119"/>
+      <c r="G39" s="120"/>
       <c r="H39" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="119"/>
-      <c r="C40" s="118"/>
-      <c r="D40" s="119"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="121"/>
+      <c r="B40" s="118"/>
+      <c r="C40" s="117"/>
+      <c r="D40" s="118"/>
+      <c r="E40" s="118"/>
+      <c r="F40" s="119"/>
+      <c r="G40" s="120"/>
       <c r="H40" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="119"/>
-      <c r="C41" s="118"/>
-      <c r="D41" s="119"/>
-      <c r="E41" s="119"/>
-      <c r="F41" s="120"/>
-      <c r="G41" s="121"/>
+      <c r="B41" s="118"/>
+      <c r="C41" s="117"/>
+      <c r="D41" s="118"/>
+      <c r="E41" s="118"/>
+      <c r="F41" s="119"/>
+      <c r="G41" s="120"/>
       <c r="H41" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="119"/>
-      <c r="C42" s="118"/>
-      <c r="D42" s="119"/>
-      <c r="E42" s="119"/>
-      <c r="F42" s="120"/>
-      <c r="G42" s="121"/>
+      <c r="B42" s="118"/>
+      <c r="C42" s="117"/>
+      <c r="D42" s="118"/>
+      <c r="E42" s="118"/>
+      <c r="F42" s="119"/>
+      <c r="G42" s="120"/>
       <c r="H42" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="119"/>
-      <c r="C43" s="118"/>
-      <c r="D43" s="119"/>
-      <c r="E43" s="119"/>
-      <c r="F43" s="120"/>
-      <c r="G43" s="121"/>
+      <c r="B43" s="118"/>
+      <c r="C43" s="117"/>
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+      <c r="F43" s="119"/>
+      <c r="G43" s="120"/>
       <c r="H43" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="119"/>
-      <c r="C44" s="118"/>
-      <c r="D44" s="119"/>
-      <c r="E44" s="119"/>
-      <c r="F44" s="120"/>
-      <c r="G44" s="121"/>
+      <c r="B44" s="118"/>
+      <c r="C44" s="117"/>
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+      <c r="F44" s="119"/>
+      <c r="G44" s="120"/>
       <c r="H44" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="119"/>
-      <c r="C45" s="118"/>
-      <c r="D45" s="119"/>
-      <c r="E45" s="119"/>
-      <c r="F45" s="120"/>
-      <c r="G45" s="121"/>
+      <c r="B45" s="118"/>
+      <c r="C45" s="117"/>
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+      <c r="F45" s="119"/>
+      <c r="G45" s="120"/>
       <c r="H45" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="119"/>
-      <c r="C46" s="118"/>
-      <c r="D46" s="119"/>
-      <c r="E46" s="119"/>
-      <c r="F46" s="120"/>
-      <c r="G46" s="121"/>
+      <c r="B46" s="118"/>
+      <c r="C46" s="117"/>
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+      <c r="F46" s="119"/>
+      <c r="G46" s="120"/>
       <c r="H46" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="119"/>
-      <c r="C47" s="118"/>
-      <c r="D47" s="119"/>
-      <c r="E47" s="119"/>
-      <c r="F47" s="120"/>
-      <c r="G47" s="121"/>
+      <c r="B47" s="118"/>
+      <c r="C47" s="117"/>
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+      <c r="F47" s="119"/>
+      <c r="G47" s="120"/>
       <c r="H47" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="119"/>
-      <c r="C48" s="118"/>
-      <c r="D48" s="119"/>
-      <c r="E48" s="119"/>
-      <c r="F48" s="120"/>
-      <c r="G48" s="121"/>
+      <c r="B48" s="118"/>
+      <c r="C48" s="117"/>
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+      <c r="F48" s="119"/>
+      <c r="G48" s="120"/>
       <c r="H48" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="119"/>
-      <c r="C49" s="118"/>
-      <c r="D49" s="119"/>
-      <c r="E49" s="119"/>
-      <c r="F49" s="120"/>
-      <c r="G49" s="121"/>
+      <c r="B49" s="118"/>
+      <c r="C49" s="117"/>
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="119"/>
+      <c r="G49" s="120"/>
       <c r="H49" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="119"/>
-      <c r="C50" s="118"/>
-      <c r="D50" s="119"/>
-      <c r="E50" s="119"/>
-      <c r="F50" s="120"/>
-      <c r="G50" s="121"/>
+      <c r="B50" s="118"/>
+      <c r="C50" s="117"/>
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+      <c r="F50" s="119"/>
+      <c r="G50" s="120"/>
       <c r="H50" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="119"/>
-      <c r="C51" s="118"/>
-      <c r="D51" s="119"/>
-      <c r="E51" s="119"/>
-      <c r="F51" s="120"/>
-      <c r="G51" s="121"/>
+      <c r="B51" s="118"/>
+      <c r="C51" s="117"/>
+      <c r="D51" s="118"/>
+      <c r="E51" s="118"/>
+      <c r="F51" s="119"/>
+      <c r="G51" s="120"/>
       <c r="H51" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="119"/>
-      <c r="C52" s="118"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="119"/>
-      <c r="F52" s="120"/>
-      <c r="G52" s="121"/>
+      <c r="B52" s="118"/>
+      <c r="C52" s="117"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+      <c r="F52" s="119"/>
+      <c r="G52" s="120"/>
       <c r="H52" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="119"/>
-      <c r="C53" s="118"/>
-      <c r="D53" s="119"/>
-      <c r="E53" s="119"/>
-      <c r="F53" s="120"/>
-      <c r="G53" s="121"/>
+      <c r="B53" s="118"/>
+      <c r="C53" s="117"/>
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+      <c r="F53" s="119"/>
+      <c r="G53" s="120"/>
       <c r="H53" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="119"/>
-      <c r="C54" s="118"/>
-      <c r="D54" s="119"/>
-      <c r="E54" s="119"/>
-      <c r="F54" s="120"/>
-      <c r="G54" s="121"/>
+      <c r="B54" s="118"/>
+      <c r="C54" s="117"/>
+      <c r="D54" s="118"/>
+      <c r="E54" s="118"/>
+      <c r="F54" s="119"/>
+      <c r="G54" s="120"/>
       <c r="H54" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="119"/>
-      <c r="C55" s="118"/>
-      <c r="D55" s="119"/>
-      <c r="E55" s="119"/>
-      <c r="F55" s="120"/>
-      <c r="G55" s="121"/>
+      <c r="B55" s="118"/>
+      <c r="C55" s="117"/>
+      <c r="D55" s="118"/>
+      <c r="E55" s="118"/>
+      <c r="F55" s="119"/>
+      <c r="G55" s="120"/>
       <c r="H55" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="119"/>
-      <c r="C56" s="118"/>
-      <c r="D56" s="119"/>
-      <c r="E56" s="119"/>
-      <c r="F56" s="120"/>
-      <c r="G56" s="121"/>
+      <c r="B56" s="118"/>
+      <c r="C56" s="117"/>
+      <c r="D56" s="118"/>
+      <c r="E56" s="118"/>
+      <c r="F56" s="119"/>
+      <c r="G56" s="120"/>
       <c r="H56" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="119"/>
-      <c r="C57" s="118"/>
-      <c r="D57" s="119"/>
-      <c r="E57" s="119"/>
-      <c r="F57" s="120"/>
-      <c r="G57" s="121"/>
+      <c r="B57" s="118"/>
+      <c r="C57" s="117"/>
+      <c r="D57" s="118"/>
+      <c r="E57" s="118"/>
+      <c r="F57" s="119"/>
+      <c r="G57" s="120"/>
       <c r="H57" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="119"/>
-      <c r="C58" s="118"/>
-      <c r="D58" s="119"/>
-      <c r="E58" s="119"/>
-      <c r="F58" s="120"/>
-      <c r="G58" s="121"/>
+      <c r="B58" s="118"/>
+      <c r="C58" s="117"/>
+      <c r="D58" s="118"/>
+      <c r="E58" s="118"/>
+      <c r="F58" s="119"/>
+      <c r="G58" s="120"/>
       <c r="H58" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="119"/>
-      <c r="C59" s="118"/>
-      <c r="D59" s="119"/>
-      <c r="E59" s="119"/>
-      <c r="F59" s="120"/>
-      <c r="G59" s="121"/>
+      <c r="B59" s="118"/>
+      <c r="C59" s="117"/>
+      <c r="D59" s="118"/>
+      <c r="E59" s="118"/>
+      <c r="F59" s="119"/>
+      <c r="G59" s="120"/>
       <c r="H59" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="119"/>
-      <c r="C60" s="118"/>
-      <c r="D60" s="119"/>
-      <c r="E60" s="119"/>
-      <c r="F60" s="120"/>
-      <c r="G60" s="121"/>
+      <c r="B60" s="118"/>
+      <c r="C60" s="117"/>
+      <c r="D60" s="118"/>
+      <c r="E60" s="118"/>
+      <c r="F60" s="119"/>
+      <c r="G60" s="120"/>
       <c r="H60" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="119"/>
-      <c r="C61" s="118"/>
-      <c r="D61" s="119"/>
-      <c r="E61" s="119"/>
-      <c r="F61" s="120"/>
-      <c r="G61" s="121"/>
+      <c r="B61" s="118"/>
+      <c r="C61" s="117"/>
+      <c r="D61" s="118"/>
+      <c r="E61" s="118"/>
+      <c r="F61" s="119"/>
+      <c r="G61" s="120"/>
       <c r="H61" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="119"/>
-      <c r="C62" s="118"/>
-      <c r="D62" s="119"/>
-      <c r="E62" s="119"/>
-      <c r="F62" s="120"/>
-      <c r="G62" s="121"/>
+      <c r="B62" s="118"/>
+      <c r="C62" s="117"/>
+      <c r="D62" s="118"/>
+      <c r="E62" s="118"/>
+      <c r="F62" s="119"/>
+      <c r="G62" s="120"/>
       <c r="H62" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="119"/>
-      <c r="C63" s="118"/>
-      <c r="D63" s="119"/>
-      <c r="E63" s="119"/>
-      <c r="F63" s="120"/>
-      <c r="G63" s="121"/>
+      <c r="B63" s="118"/>
+      <c r="C63" s="117"/>
+      <c r="D63" s="118"/>
+      <c r="E63" s="118"/>
+      <c r="F63" s="119"/>
+      <c r="G63" s="120"/>
       <c r="H63" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="119"/>
-      <c r="C64" s="118"/>
-      <c r="D64" s="119"/>
-      <c r="E64" s="119"/>
-      <c r="F64" s="120"/>
-      <c r="G64" s="121"/>
+      <c r="B64" s="118"/>
+      <c r="C64" s="117"/>
+      <c r="D64" s="118"/>
+      <c r="E64" s="118"/>
+      <c r="F64" s="119"/>
+      <c r="G64" s="120"/>
       <c r="H64" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="119"/>
-      <c r="C65" s="118"/>
-      <c r="D65" s="119"/>
-      <c r="E65" s="119"/>
-      <c r="F65" s="120"/>
-      <c r="G65" s="121"/>
+      <c r="B65" s="118"/>
+      <c r="C65" s="117"/>
+      <c r="D65" s="118"/>
+      <c r="E65" s="118"/>
+      <c r="F65" s="119"/>
+      <c r="G65" s="120"/>
       <c r="H65" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="119"/>
-      <c r="C66" s="118"/>
-      <c r="D66" s="119"/>
-      <c r="E66" s="119"/>
-      <c r="F66" s="120"/>
-      <c r="G66" s="121"/>
+      <c r="B66" s="118"/>
+      <c r="C66" s="117"/>
+      <c r="D66" s="118"/>
+      <c r="E66" s="118"/>
+      <c r="F66" s="119"/>
+      <c r="G66" s="120"/>
       <c r="H66" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="119"/>
-      <c r="C67" s="118"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="119"/>
-      <c r="F67" s="120"/>
-      <c r="G67" s="121"/>
+      <c r="B67" s="118"/>
+      <c r="C67" s="117"/>
+      <c r="D67" s="118"/>
+      <c r="E67" s="118"/>
+      <c r="F67" s="119"/>
+      <c r="G67" s="120"/>
       <c r="H67" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="119"/>
-      <c r="C68" s="118"/>
-      <c r="D68" s="119"/>
-      <c r="E68" s="119"/>
-      <c r="F68" s="120"/>
-      <c r="G68" s="121"/>
+      <c r="B68" s="118"/>
+      <c r="C68" s="117"/>
+      <c r="D68" s="118"/>
+      <c r="E68" s="118"/>
+      <c r="F68" s="119"/>
+      <c r="G68" s="120"/>
       <c r="H68" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="119"/>
-      <c r="C69" s="118"/>
-      <c r="D69" s="119"/>
-      <c r="E69" s="119"/>
-      <c r="F69" s="120"/>
-      <c r="G69" s="121"/>
+      <c r="B69" s="118"/>
+      <c r="C69" s="117"/>
+      <c r="D69" s="118"/>
+      <c r="E69" s="118"/>
+      <c r="F69" s="119"/>
+      <c r="G69" s="120"/>
       <c r="H69" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="119"/>
-      <c r="C70" s="118"/>
-      <c r="D70" s="119"/>
-      <c r="E70" s="119"/>
-      <c r="F70" s="120"/>
-      <c r="G70" s="121"/>
+      <c r="B70" s="118"/>
+      <c r="C70" s="117"/>
+      <c r="D70" s="118"/>
+      <c r="E70" s="118"/>
+      <c r="F70" s="119"/>
+      <c r="G70" s="120"/>
       <c r="H70" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="119"/>
-      <c r="C71" s="118"/>
-      <c r="D71" s="119"/>
-      <c r="E71" s="119"/>
-      <c r="F71" s="120"/>
-      <c r="G71" s="121"/>
+      <c r="B71" s="118"/>
+      <c r="C71" s="117"/>
+      <c r="D71" s="118"/>
+      <c r="E71" s="118"/>
+      <c r="F71" s="119"/>
+      <c r="G71" s="120"/>
       <c r="H71" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="119"/>
-      <c r="C72" s="118"/>
-      <c r="D72" s="119"/>
-      <c r="E72" s="119"/>
-      <c r="F72" s="120"/>
-      <c r="G72" s="121"/>
+      <c r="B72" s="118"/>
+      <c r="C72" s="117"/>
+      <c r="D72" s="118"/>
+      <c r="E72" s="118"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="120"/>
       <c r="H72" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="119"/>
-      <c r="C73" s="118"/>
-      <c r="D73" s="119"/>
-      <c r="E73" s="119"/>
-      <c r="F73" s="120"/>
-      <c r="G73" s="121"/>
+      <c r="B73" s="118"/>
+      <c r="C73" s="117"/>
+      <c r="D73" s="118"/>
+      <c r="E73" s="118"/>
+      <c r="F73" s="119"/>
+      <c r="G73" s="120"/>
       <c r="H73" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="119"/>
-      <c r="C74" s="118"/>
-      <c r="D74" s="119"/>
-      <c r="E74" s="119"/>
-      <c r="F74" s="120"/>
-      <c r="G74" s="121"/>
+      <c r="B74" s="118"/>
+      <c r="C74" s="117"/>
+      <c r="D74" s="118"/>
+      <c r="E74" s="118"/>
+      <c r="F74" s="119"/>
+      <c r="G74" s="120"/>
       <c r="H74" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="119"/>
-      <c r="C75" s="118"/>
-      <c r="D75" s="119"/>
-      <c r="E75" s="119"/>
-      <c r="F75" s="120"/>
-      <c r="G75" s="121"/>
+      <c r="B75" s="118"/>
+      <c r="C75" s="117"/>
+      <c r="D75" s="118"/>
+      <c r="E75" s="118"/>
+      <c r="F75" s="119"/>
+      <c r="G75" s="120"/>
       <c r="H75" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="119"/>
-      <c r="C76" s="118"/>
-      <c r="D76" s="119"/>
-      <c r="E76" s="119"/>
-      <c r="F76" s="120"/>
-      <c r="G76" s="121"/>
+      <c r="B76" s="118"/>
+      <c r="C76" s="117"/>
+      <c r="D76" s="118"/>
+      <c r="E76" s="118"/>
+      <c r="F76" s="119"/>
+      <c r="G76" s="120"/>
       <c r="H76" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="119"/>
-      <c r="C77" s="118"/>
-      <c r="D77" s="119"/>
-      <c r="E77" s="119"/>
-      <c r="F77" s="120"/>
-      <c r="G77" s="121"/>
+      <c r="B77" s="118"/>
+      <c r="C77" s="117"/>
+      <c r="D77" s="118"/>
+      <c r="E77" s="118"/>
+      <c r="F77" s="119"/>
+      <c r="G77" s="120"/>
       <c r="H77" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="119"/>
-      <c r="C78" s="118"/>
-      <c r="D78" s="119"/>
-      <c r="E78" s="119"/>
-      <c r="F78" s="120"/>
-      <c r="G78" s="121"/>
+      <c r="B78" s="118"/>
+      <c r="C78" s="117"/>
+      <c r="D78" s="118"/>
+      <c r="E78" s="118"/>
+      <c r="F78" s="119"/>
+      <c r="G78" s="120"/>
       <c r="H78" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="119"/>
-      <c r="C79" s="118"/>
-      <c r="D79" s="119"/>
-      <c r="E79" s="119"/>
-      <c r="F79" s="120"/>
-      <c r="G79" s="121"/>
+      <c r="B79" s="118"/>
+      <c r="C79" s="117"/>
+      <c r="D79" s="118"/>
+      <c r="E79" s="118"/>
+      <c r="F79" s="119"/>
+      <c r="G79" s="120"/>
       <c r="H79" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="119"/>
-      <c r="C80" s="118"/>
-      <c r="D80" s="119"/>
-      <c r="E80" s="119"/>
-      <c r="F80" s="120"/>
-      <c r="G80" s="121"/>
+      <c r="B80" s="118"/>
+      <c r="C80" s="117"/>
+      <c r="D80" s="118"/>
+      <c r="E80" s="118"/>
+      <c r="F80" s="119"/>
+      <c r="G80" s="120"/>
       <c r="H80" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="119"/>
-      <c r="C81" s="118"/>
-      <c r="D81" s="119"/>
-      <c r="E81" s="119"/>
-      <c r="F81" s="120"/>
-      <c r="G81" s="121"/>
+      <c r="B81" s="118"/>
+      <c r="C81" s="117"/>
+      <c r="D81" s="118"/>
+      <c r="E81" s="118"/>
+      <c r="F81" s="119"/>
+      <c r="G81" s="120"/>
       <c r="H81" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="119"/>
-      <c r="C82" s="118"/>
-      <c r="D82" s="119"/>
-      <c r="E82" s="119"/>
-      <c r="F82" s="120"/>
-      <c r="G82" s="121"/>
+      <c r="B82" s="118"/>
+      <c r="C82" s="117"/>
+      <c r="D82" s="118"/>
+      <c r="E82" s="118"/>
+      <c r="F82" s="119"/>
+      <c r="G82" s="120"/>
       <c r="H82" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="119"/>
-      <c r="C83" s="118"/>
-      <c r="D83" s="119"/>
-      <c r="E83" s="119"/>
-      <c r="F83" s="120"/>
-      <c r="G83" s="121"/>
+      <c r="B83" s="118"/>
+      <c r="C83" s="117"/>
+      <c r="D83" s="118"/>
+      <c r="E83" s="118"/>
+      <c r="F83" s="119"/>
+      <c r="G83" s="120"/>
       <c r="H83" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="119"/>
-      <c r="C84" s="118"/>
-      <c r="D84" s="119"/>
-      <c r="E84" s="119"/>
-      <c r="F84" s="120"/>
-      <c r="G84" s="121"/>
+      <c r="B84" s="118"/>
+      <c r="C84" s="117"/>
+      <c r="D84" s="118"/>
+      <c r="E84" s="118"/>
+      <c r="F84" s="119"/>
+      <c r="G84" s="120"/>
       <c r="H84" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="119"/>
-      <c r="C85" s="118"/>
-      <c r="D85" s="119"/>
-      <c r="E85" s="119"/>
-      <c r="F85" s="120"/>
-      <c r="G85" s="121"/>
+      <c r="B85" s="118"/>
+      <c r="C85" s="117"/>
+      <c r="D85" s="118"/>
+      <c r="E85" s="118"/>
+      <c r="F85" s="119"/>
+      <c r="G85" s="120"/>
       <c r="H85" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="119"/>
-      <c r="C86" s="118"/>
-      <c r="D86" s="119"/>
-      <c r="E86" s="119"/>
-      <c r="F86" s="120"/>
-      <c r="G86" s="121"/>
+      <c r="B86" s="118"/>
+      <c r="C86" s="117"/>
+      <c r="D86" s="118"/>
+      <c r="E86" s="118"/>
+      <c r="F86" s="119"/>
+      <c r="G86" s="120"/>
       <c r="H86" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="119"/>
-      <c r="C87" s="118"/>
-      <c r="D87" s="119"/>
-      <c r="E87" s="119"/>
-      <c r="F87" s="120"/>
-      <c r="G87" s="121"/>
+      <c r="B87" s="118"/>
+      <c r="C87" s="117"/>
+      <c r="D87" s="118"/>
+      <c r="E87" s="118"/>
+      <c r="F87" s="119"/>
+      <c r="G87" s="120"/>
       <c r="H87" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="119"/>
-      <c r="C88" s="118"/>
-      <c r="D88" s="119"/>
-      <c r="E88" s="119"/>
-      <c r="F88" s="120"/>
-      <c r="G88" s="121"/>
+      <c r="B88" s="118"/>
+      <c r="C88" s="117"/>
+      <c r="D88" s="118"/>
+      <c r="E88" s="118"/>
+      <c r="F88" s="119"/>
+      <c r="G88" s="120"/>
       <c r="H88" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="119"/>
-      <c r="C89" s="118"/>
-      <c r="D89" s="119"/>
-      <c r="E89" s="119"/>
-      <c r="F89" s="120"/>
-      <c r="G89" s="121"/>
+      <c r="B89" s="118"/>
+      <c r="C89" s="117"/>
+      <c r="D89" s="118"/>
+      <c r="E89" s="118"/>
+      <c r="F89" s="119"/>
+      <c r="G89" s="120"/>
       <c r="H89" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="119"/>
-      <c r="C90" s="118"/>
-      <c r="D90" s="119"/>
-      <c r="E90" s="119"/>
-      <c r="F90" s="120"/>
-      <c r="G90" s="121"/>
+      <c r="B90" s="118"/>
+      <c r="C90" s="117"/>
+      <c r="D90" s="118"/>
+      <c r="E90" s="118"/>
+      <c r="F90" s="119"/>
+      <c r="G90" s="120"/>
       <c r="H90" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="119"/>
-      <c r="C91" s="118"/>
-      <c r="D91" s="119"/>
-      <c r="E91" s="119"/>
-      <c r="F91" s="120"/>
-      <c r="G91" s="121"/>
+      <c r="B91" s="118"/>
+      <c r="C91" s="117"/>
+      <c r="D91" s="118"/>
+      <c r="E91" s="118"/>
+      <c r="F91" s="119"/>
+      <c r="G91" s="120"/>
       <c r="H91" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="119"/>
-      <c r="C92" s="118"/>
-      <c r="D92" s="119"/>
-      <c r="E92" s="119"/>
-      <c r="F92" s="120"/>
-      <c r="G92" s="121"/>
+      <c r="B92" s="118"/>
+      <c r="C92" s="117"/>
+      <c r="D92" s="118"/>
+      <c r="E92" s="118"/>
+      <c r="F92" s="119"/>
+      <c r="G92" s="120"/>
       <c r="H92" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="119"/>
-      <c r="C93" s="118"/>
-      <c r="D93" s="119"/>
-      <c r="E93" s="119"/>
-      <c r="F93" s="120"/>
-      <c r="G93" s="121"/>
+      <c r="B93" s="118"/>
+      <c r="C93" s="117"/>
+      <c r="D93" s="118"/>
+      <c r="E93" s="118"/>
+      <c r="F93" s="119"/>
+      <c r="G93" s="120"/>
       <c r="H93" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="119"/>
-      <c r="C94" s="118"/>
-      <c r="D94" s="119"/>
-      <c r="E94" s="119"/>
-      <c r="F94" s="120"/>
-      <c r="G94" s="121"/>
+      <c r="B94" s="118"/>
+      <c r="C94" s="117"/>
+      <c r="D94" s="118"/>
+      <c r="E94" s="118"/>
+      <c r="F94" s="119"/>
+      <c r="G94" s="120"/>
       <c r="H94" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="119"/>
-      <c r="C95" s="118"/>
-      <c r="D95" s="119"/>
-      <c r="E95" s="119"/>
-      <c r="F95" s="120"/>
-      <c r="G95" s="121"/>
+      <c r="B95" s="118"/>
+      <c r="C95" s="117"/>
+      <c r="D95" s="118"/>
+      <c r="E95" s="118"/>
+      <c r="F95" s="119"/>
+      <c r="G95" s="120"/>
       <c r="H95" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="119"/>
-      <c r="C96" s="118"/>
-      <c r="D96" s="119"/>
-      <c r="E96" s="119"/>
-      <c r="F96" s="120"/>
-      <c r="G96" s="121"/>
+      <c r="B96" s="118"/>
+      <c r="C96" s="117"/>
+      <c r="D96" s="118"/>
+      <c r="E96" s="118"/>
+      <c r="F96" s="119"/>
+      <c r="G96" s="120"/>
       <c r="H96" s="10" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -10024,333 +10042,333 @@
   </cols>
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
-      <c r="B1" s="122" t="s">
-        <v>188</v>
+      <c r="B1" s="121" t="s">
+        <v>190</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="B2" s="123" t="s">
-        <v>189</v>
+      <c r="B2" s="122" t="s">
+        <v>191</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
     </row>
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
-      <c r="B4" s="124" t="s">
-        <v>190</v>
-      </c>
-      <c r="C4" s="125" t="s">
-        <v>191</v>
-      </c>
-      <c r="D4" s="126" t="s">
+      <c r="B4" s="123" t="s">
         <v>192</v>
       </c>
+      <c r="C4" s="124" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="125" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
-      <c r="B5" s="124" t="s">
-        <v>193</v>
-      </c>
-      <c r="C5" s="125" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="126" t="s">
+      <c r="B5" s="123" t="s">
         <v>195</v>
       </c>
+      <c r="C5" s="124" t="s">
+        <v>196</v>
+      </c>
+      <c r="D5" s="125" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
-      <c r="B6" s="124" t="s">
-        <v>196</v>
-      </c>
-      <c r="C6" s="125" t="s">
-        <v>197</v>
-      </c>
-      <c r="D6" s="126" t="s">
+      <c r="B6" s="123" t="s">
         <v>198</v>
       </c>
+      <c r="C6" s="124" t="s">
+        <v>199</v>
+      </c>
+      <c r="D6" s="125" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
-      <c r="B7" s="124" t="s">
-        <v>199</v>
-      </c>
-      <c r="C7" s="125" t="s">
-        <v>200</v>
-      </c>
-      <c r="D7" s="126" t="s">
+      <c r="B7" s="123" t="s">
         <v>201</v>
       </c>
+      <c r="C7" s="124" t="s">
+        <v>202</v>
+      </c>
+      <c r="D7" s="125" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
-      <c r="B8" s="127" t="s">
-        <v>202</v>
-      </c>
-      <c r="C8" s="128" t="s">
-        <v>203</v>
-      </c>
-      <c r="D8" s="126" t="s">
+      <c r="B8" s="126" t="s">
         <v>204</v>
       </c>
+      <c r="C8" s="127" t="s">
+        <v>205</v>
+      </c>
+      <c r="D8" s="125" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="B9" s="127" t="s">
-        <v>205</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>206</v>
-      </c>
-      <c r="D9" s="126" t="s">
+      <c r="B9" s="126" t="s">
         <v>207</v>
       </c>
+      <c r="C9" s="127" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" s="125" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
-      <c r="B10" s="129" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="130" t="s">
-        <v>209</v>
-      </c>
-      <c r="D10" s="126" t="s">
+      <c r="B10" s="128" t="s">
         <v>210</v>
       </c>
+      <c r="C10" s="129" t="s">
+        <v>211</v>
+      </c>
+      <c r="D10" s="125" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
-      <c r="B11" s="129" t="s">
-        <v>211</v>
-      </c>
-      <c r="C11" s="130" t="s">
-        <v>212</v>
-      </c>
-      <c r="D11" s="126" t="s">
+      <c r="B11" s="128" t="s">
         <v>213</v>
       </c>
+      <c r="C11" s="129" t="s">
+        <v>214</v>
+      </c>
+      <c r="D11" s="125" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
-      <c r="B12" s="131" t="s">
-        <v>214</v>
-      </c>
-      <c r="C12" s="132" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="126" t="s">
+      <c r="B12" s="130" t="s">
         <v>216</v>
       </c>
+      <c r="C12" s="131" t="s">
+        <v>217</v>
+      </c>
+      <c r="D12" s="125" t="s">
+        <v>218</v>
+      </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
-      <c r="B13" s="131" t="s">
-        <v>217</v>
-      </c>
-      <c r="C13" s="132" t="s">
-        <v>218</v>
-      </c>
-      <c r="D13" s="126" t="s">
+      <c r="B13" s="130" t="s">
         <v>219</v>
       </c>
+      <c r="C13" s="131" t="s">
+        <v>220</v>
+      </c>
+      <c r="D13" s="125" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
-      <c r="B14" s="133" t="s">
-        <v>220</v>
-      </c>
-      <c r="C14" s="134" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="126" t="s">
+      <c r="B14" s="132" t="s">
         <v>222</v>
       </c>
+      <c r="C14" s="133" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="125" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
-      <c r="B15" s="135" t="s">
-        <v>223</v>
-      </c>
-      <c r="C15" s="136" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="126" t="s">
+      <c r="B15" s="134" t="s">
         <v>225</v>
       </c>
+      <c r="C15" s="135" t="s">
+        <v>226</v>
+      </c>
+      <c r="D15" s="125" t="s">
+        <v>227</v>
+      </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
-      <c r="B16" s="129" t="s">
-        <v>226</v>
-      </c>
-      <c r="C16" s="130" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" s="126" t="s">
+      <c r="B16" s="128" t="s">
         <v>228</v>
       </c>
+      <c r="C16" s="129" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="125" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
-      <c r="B17" s="135" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="136" t="s">
-        <v>230</v>
-      </c>
-      <c r="D17" s="126" t="s">
+      <c r="B17" s="134" t="s">
         <v>231</v>
       </c>
+      <c r="C17" s="135" t="s">
+        <v>232</v>
+      </c>
+      <c r="D17" s="125" t="s">
+        <v>233</v>
+      </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
-      <c r="B18" s="131" t="s">
-        <v>232</v>
-      </c>
-      <c r="C18" s="132" t="s">
-        <v>233</v>
-      </c>
-      <c r="D18" s="126" t="s">
+      <c r="B18" s="130" t="s">
         <v>234</v>
       </c>
+      <c r="C18" s="131" t="s">
+        <v>235</v>
+      </c>
+      <c r="D18" s="125" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="B20" s="137" t="s">
-        <v>235</v>
+      <c r="B20" s="136" t="s">
+        <v>237</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
     </row>
     <row r="21" ht="18.0" customHeight="1">
-      <c r="B21" s="138" t="s">
+      <c r="B21" s="137" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="138" t="s">
-        <v>236</v>
-      </c>
-      <c r="D21" s="138" t="s">
-        <v>237</v>
+      <c r="C21" s="137" t="s">
+        <v>238</v>
+      </c>
+      <c r="D21" s="137" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
-      <c r="B22" s="139" t="s">
+      <c r="B22" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="140" t="s">
-        <v>238</v>
-      </c>
-      <c r="D22" s="141" t="s">
-        <v>239</v>
+      <c r="C22" s="139" t="s">
+        <v>240</v>
+      </c>
+      <c r="D22" s="140" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
-      <c r="B23" s="139" t="s">
+      <c r="B23" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="140" t="s">
-        <v>240</v>
-      </c>
-      <c r="D23" s="141" t="s">
-        <v>241</v>
+      <c r="C23" s="139" t="s">
+        <v>242</v>
+      </c>
+      <c r="D23" s="140" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
-      <c r="B24" s="142" t="s">
+      <c r="B24" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="143" t="s">
-        <v>242</v>
-      </c>
-      <c r="D24" s="141" t="s">
-        <v>243</v>
+      <c r="C24" s="142" t="s">
+        <v>244</v>
+      </c>
+      <c r="D24" s="140" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="138" t="s">
         <v>85</v>
       </c>
-      <c r="C25" s="140" t="s">
-        <v>244</v>
-      </c>
-      <c r="D25" s="141" t="s">
-        <v>245</v>
+      <c r="C25" s="139" t="s">
+        <v>246</v>
+      </c>
+      <c r="D25" s="140" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="B26" s="144" t="s">
+      <c r="B26" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="145" t="s">
-        <v>246</v>
-      </c>
-      <c r="D26" s="141" t="s">
-        <v>247</v>
+      <c r="C26" s="144" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26" s="140" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
-      <c r="B27" s="146" t="s">
+      <c r="B27" s="145" t="s">
         <v>90</v>
       </c>
-      <c r="C27" s="147" t="s">
-        <v>248</v>
-      </c>
-      <c r="D27" s="141" t="s">
-        <v>249</v>
+      <c r="C27" s="146" t="s">
+        <v>250</v>
+      </c>
+      <c r="D27" s="140" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
-      <c r="B28" s="139" t="s">
+      <c r="B28" s="138" t="s">
         <v>49</v>
       </c>
-      <c r="C28" s="140" t="s">
-        <v>250</v>
-      </c>
-      <c r="D28" s="141" t="s">
-        <v>251</v>
+      <c r="C28" s="139" t="s">
+        <v>252</v>
+      </c>
+      <c r="D28" s="140" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
-      <c r="B29" s="139" t="s">
+      <c r="B29" s="138" t="s">
         <v>47</v>
       </c>
-      <c r="C29" s="140" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" s="141" t="s">
-        <v>253</v>
+      <c r="C29" s="139" t="s">
+        <v>254</v>
+      </c>
+      <c r="D29" s="140" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
-      <c r="B30" s="144" t="s">
+      <c r="B30" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="C30" s="145" t="s">
-        <v>254</v>
-      </c>
-      <c r="D30" s="141" t="s">
-        <v>255</v>
+      <c r="C30" s="144" t="s">
+        <v>256</v>
+      </c>
+      <c r="D30" s="140" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="B31" s="144" t="s">
+      <c r="B31" s="143" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="145" t="s">
-        <v>256</v>
-      </c>
-      <c r="D31" s="141" t="s">
-        <v>257</v>
+      <c r="C31" s="144" t="s">
+        <v>258</v>
+      </c>
+      <c r="D31" s="140" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
-      <c r="B32" s="148" t="s">
+      <c r="B32" s="147" t="s">
         <v>115</v>
       </c>
-      <c r="C32" s="149" t="s">
-        <v>258</v>
-      </c>
-      <c r="D32" s="141" t="s">
-        <v>259</v>
+      <c r="C32" s="148" t="s">
+        <v>260</v>
+      </c>
+      <c r="D32" s="140" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
-      <c r="B33" s="139" t="s">
+      <c r="B33" s="138" t="s">
         <v>23</v>
       </c>
-      <c r="C33" s="140" t="s">
-        <v>260</v>
-      </c>
-      <c r="D33" s="141" t="s">
-        <v>261</v>
+      <c r="C33" s="139" t="s">
+        <v>262</v>
+      </c>
+      <c r="D33" s="140" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11341,967 +11359,967 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="150" t="s">
-        <v>262</v>
-      </c>
-      <c r="B1" s="150" t="s">
-        <v>263</v>
-      </c>
-      <c r="C1" s="150" t="s">
+      <c r="A1" s="149" t="s">
+        <v>264</v>
+      </c>
+      <c r="B1" s="149" t="s">
+        <v>265</v>
+      </c>
+      <c r="C1" s="149" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="150"/>
-      <c r="E1" s="150"/>
+      <c r="D1" s="149"/>
+      <c r="E1" s="149"/>
     </row>
     <row r="2">
-      <c r="A2" s="151">
+      <c r="A2" s="150">
         <v>46165.0</v>
       </c>
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="149" t="s">
+        <v>266</v>
+      </c>
+      <c r="C2" s="151">
+        <v>10000.0</v>
+      </c>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="150">
+        <v>46166.0</v>
+      </c>
+      <c r="B3" s="149" t="s">
+        <v>267</v>
+      </c>
+      <c r="C3" s="151">
+        <v>19000.0</v>
+      </c>
+      <c r="D3" s="149"/>
+      <c r="E3" s="149"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="150">
+        <v>46168.0</v>
+      </c>
+      <c r="B4" s="149" t="s">
+        <v>268</v>
+      </c>
+      <c r="C4" s="152">
+        <v>2500.0</v>
+      </c>
+      <c r="D4" s="149"/>
+      <c r="E4" s="149"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B5" s="149" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="151">
+        <v>29050.0</v>
+      </c>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B6" s="149" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="152">
+        <v>100.0</v>
+      </c>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B7" s="149" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="152">
+        <v>300.0</v>
+      </c>
+      <c r="D7" s="149"/>
+      <c r="E7" s="149"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B8" s="149" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="152">
+        <v>370.0</v>
+      </c>
+      <c r="D8" s="149"/>
+      <c r="E8" s="149"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B9" s="149" t="s">
+        <v>167</v>
+      </c>
+      <c r="C9" s="152">
+        <v>2494.0</v>
+      </c>
+      <c r="D9" s="149"/>
+      <c r="E9" s="149"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B10" s="149" t="s">
+        <v>273</v>
+      </c>
+      <c r="C10" s="152">
+        <v>5000.0</v>
+      </c>
+      <c r="D10" s="149"/>
+      <c r="E10" s="149"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B11" s="149" t="s">
+        <v>274</v>
+      </c>
+      <c r="C11" s="151">
+        <v>29000.0</v>
+      </c>
+      <c r="D11" s="149" t="s">
+        <v>275</v>
+      </c>
+      <c r="E11" s="152">
+        <v>24000.0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B12" s="149" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="152">
+        <v>400.0</v>
+      </c>
+      <c r="D12" s="149" t="s">
+        <v>277</v>
+      </c>
+      <c r="E12" s="151">
+        <v>53000.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="150">
+        <v>46169.0</v>
+      </c>
+      <c r="B13" s="149" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="152">
+        <v>600.0</v>
+      </c>
+      <c r="D13" s="149"/>
+      <c r="E13" s="149"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="150">
+        <v>46170.0</v>
+      </c>
+      <c r="B14" s="149"/>
+      <c r="C14" s="149"/>
+      <c r="D14" s="149"/>
+      <c r="E14" s="149"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="149" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" s="149" t="s">
         <v>264</v>
       </c>
-      <c r="C2" s="152">
-        <v>10000.0</v>
-      </c>
-      <c r="D2" s="150"/>
-      <c r="E2" s="150"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="151">
-        <v>46166.0</v>
-      </c>
-      <c r="B3" s="150" t="s">
-        <v>265</v>
-      </c>
-      <c r="C3" s="152">
-        <v>19000.0</v>
-      </c>
-      <c r="D3" s="150"/>
-      <c r="E3" s="150"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="151">
-        <v>46168.0</v>
-      </c>
-      <c r="B4" s="150" t="s">
-        <v>266</v>
-      </c>
-      <c r="C4" s="153">
-        <v>2500.0</v>
-      </c>
-      <c r="D4" s="150"/>
-      <c r="E4" s="150"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B5" s="150" t="s">
-        <v>267</v>
-      </c>
-      <c r="C5" s="152">
-        <v>29050.0</v>
-      </c>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B6" s="150" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="153">
-        <v>100.0</v>
-      </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="150"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B7" s="150" t="s">
-        <v>269</v>
-      </c>
-      <c r="C7" s="153">
-        <v>300.0</v>
-      </c>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B8" s="150" t="s">
-        <v>270</v>
-      </c>
-      <c r="C8" s="153">
-        <v>370.0</v>
-      </c>
-      <c r="D8" s="150"/>
-      <c r="E8" s="150"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B9" s="150" t="s">
-        <v>167</v>
-      </c>
-      <c r="C9" s="153">
-        <v>2494.0</v>
-      </c>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B10" s="150" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="153">
+      <c r="C22" s="149" t="s">
+        <v>280</v>
+      </c>
+      <c r="D22" s="149" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" s="149" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="149" t="s">
+        <v>282</v>
+      </c>
+      <c r="B23" s="149" t="s">
+        <v>283</v>
+      </c>
+      <c r="C23" s="149" t="s">
+        <v>284</v>
+      </c>
+      <c r="D23" s="152">
+        <v>3150.0</v>
+      </c>
+      <c r="E23" s="153">
+        <v>46464.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="149" t="s">
+        <v>282</v>
+      </c>
+      <c r="B24" s="149" t="s">
+        <v>283</v>
+      </c>
+      <c r="C24" s="149" t="s">
+        <v>285</v>
+      </c>
+      <c r="D24" s="152">
+        <v>2650.0</v>
+      </c>
+      <c r="E24" s="153">
+        <v>46219.0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="149" t="s">
+        <v>282</v>
+      </c>
+      <c r="B25" s="149" t="s">
+        <v>283</v>
+      </c>
+      <c r="C25" s="149" t="s">
+        <v>286</v>
+      </c>
+      <c r="D25" s="152">
+        <v>2600.0</v>
+      </c>
+      <c r="E25" s="153">
+        <v>46828.0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="149" t="s">
+        <v>282</v>
+      </c>
+      <c r="B26" s="149" t="s">
+        <v>283</v>
+      </c>
+      <c r="C26" s="149" t="s">
+        <v>287</v>
+      </c>
+      <c r="D26" s="152">
+        <v>2680.0</v>
+      </c>
+      <c r="E26" s="154">
+        <v>46863.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="B27" s="149" t="s">
+        <v>288</v>
+      </c>
+      <c r="C27" s="149" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="152">
+        <v>5390.0</v>
+      </c>
+      <c r="E27" s="153">
+        <v>46764.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="B28" s="149" t="s">
+        <v>288</v>
+      </c>
+      <c r="C28" s="149" t="s">
+        <v>290</v>
+      </c>
+      <c r="D28" s="152">
+        <v>3235.0</v>
+      </c>
+      <c r="E28" s="153">
+        <v>46673.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="149" t="s">
+        <v>168</v>
+      </c>
+      <c r="B29" s="149" t="s">
+        <v>288</v>
+      </c>
+      <c r="C29" s="149" t="s">
+        <v>291</v>
+      </c>
+      <c r="D29" s="152">
+        <v>1230.0</v>
+      </c>
+      <c r="E29" s="149" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="149" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" s="149"/>
+      <c r="C30" s="149" t="s">
+        <v>284</v>
+      </c>
+      <c r="D30" s="152">
+        <v>2960.0</v>
+      </c>
+      <c r="E30" s="149"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="149" t="s">
+        <v>293</v>
+      </c>
+      <c r="B31" s="149"/>
+      <c r="C31" s="149" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="152">
+        <v>2960.0</v>
+      </c>
+      <c r="E31" s="149"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="149" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" s="149" t="s">
+        <v>295</v>
+      </c>
+      <c r="C32" s="149"/>
+      <c r="D32" s="152">
         <v>5000.0</v>
       </c>
-      <c r="D10" s="150"/>
-      <c r="E10" s="150"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B11" s="150" t="s">
-        <v>272</v>
-      </c>
-      <c r="C11" s="152">
-        <v>29000.0</v>
-      </c>
-      <c r="D11" s="150" t="s">
-        <v>273</v>
-      </c>
-      <c r="E11" s="153">
-        <v>24000.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B12" s="150" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="153">
-        <v>400.0</v>
-      </c>
-      <c r="D12" s="150" t="s">
-        <v>275</v>
-      </c>
-      <c r="E12" s="152">
-        <v>53000.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="151">
-        <v>46169.0</v>
-      </c>
-      <c r="B13" s="150" t="s">
-        <v>276</v>
-      </c>
-      <c r="C13" s="153">
-        <v>600.0</v>
-      </c>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="151">
-        <v>46170.0</v>
-      </c>
-      <c r="B14" s="150"/>
-      <c r="C14" s="150"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="150" t="s">
-        <v>277</v>
-      </c>
-      <c r="B22" s="150" t="s">
-        <v>262</v>
-      </c>
-      <c r="C22" s="150" t="s">
-        <v>278</v>
-      </c>
-      <c r="D22" s="150" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="150" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="150" t="s">
-        <v>280</v>
-      </c>
-      <c r="B23" s="150" t="s">
-        <v>281</v>
-      </c>
-      <c r="C23" s="150" t="s">
-        <v>282</v>
-      </c>
-      <c r="D23" s="153">
-        <v>3150.0</v>
-      </c>
-      <c r="E23" s="154">
-        <v>46464.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="150" t="s">
-        <v>280</v>
-      </c>
-      <c r="B24" s="150" t="s">
-        <v>281</v>
-      </c>
-      <c r="C24" s="150" t="s">
-        <v>283</v>
-      </c>
-      <c r="D24" s="153">
-        <v>2650.0</v>
-      </c>
-      <c r="E24" s="154">
-        <v>46219.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="150" t="s">
-        <v>280</v>
-      </c>
-      <c r="B25" s="150" t="s">
-        <v>281</v>
-      </c>
-      <c r="C25" s="150" t="s">
-        <v>284</v>
-      </c>
-      <c r="D25" s="153">
-        <v>2600.0</v>
-      </c>
-      <c r="E25" s="154">
-        <v>46828.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="150" t="s">
-        <v>280</v>
-      </c>
-      <c r="B26" s="150" t="s">
-        <v>281</v>
-      </c>
-      <c r="C26" s="150" t="s">
-        <v>285</v>
-      </c>
-      <c r="D26" s="153">
-        <v>2680.0</v>
-      </c>
-      <c r="E26" s="155">
-        <v>46863.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="150" t="s">
-        <v>168</v>
-      </c>
-      <c r="B27" s="150" t="s">
-        <v>286</v>
-      </c>
-      <c r="C27" s="150" t="s">
-        <v>287</v>
-      </c>
-      <c r="D27" s="153">
-        <v>5390.0</v>
-      </c>
-      <c r="E27" s="154">
-        <v>46764.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="150" t="s">
-        <v>168</v>
-      </c>
-      <c r="B28" s="150" t="s">
-        <v>286</v>
-      </c>
-      <c r="C28" s="150" t="s">
-        <v>288</v>
-      </c>
-      <c r="D28" s="153">
-        <v>3235.0</v>
-      </c>
-      <c r="E28" s="154">
-        <v>46673.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="150" t="s">
-        <v>168</v>
-      </c>
-      <c r="B29" s="150" t="s">
-        <v>286</v>
-      </c>
-      <c r="C29" s="150" t="s">
-        <v>289</v>
-      </c>
-      <c r="D29" s="153">
-        <v>1230.0</v>
-      </c>
-      <c r="E29" s="150" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="150" t="s">
-        <v>291</v>
-      </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="150" t="s">
-        <v>282</v>
-      </c>
-      <c r="D30" s="153">
-        <v>2960.0</v>
-      </c>
-      <c r="E30" s="150"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="150" t="s">
-        <v>291</v>
-      </c>
-      <c r="B31" s="150"/>
-      <c r="C31" s="150" t="s">
-        <v>287</v>
-      </c>
-      <c r="D31" s="153">
-        <v>2960.0</v>
-      </c>
-      <c r="E31" s="150"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="150" t="s">
-        <v>292</v>
-      </c>
-      <c r="B32" s="150" t="s">
-        <v>293</v>
-      </c>
-      <c r="C32" s="150"/>
-      <c r="D32" s="153">
-        <v>5000.0</v>
-      </c>
-      <c r="E32" s="150" t="s">
-        <v>294</v>
+      <c r="E32" s="149" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="156" t="s">
-        <v>295</v>
-      </c>
-      <c r="B42" s="150"/>
-      <c r="C42" s="150"/>
-      <c r="D42" s="150"/>
-      <c r="E42" s="150"/>
-      <c r="F42" s="150"/>
-      <c r="G42" s="150"/>
-      <c r="H42" s="150"/>
-      <c r="I42" s="150"/>
-      <c r="J42" s="150"/>
+      <c r="A42" s="155" t="s">
+        <v>297</v>
+      </c>
+      <c r="B42" s="149"/>
+      <c r="C42" s="149"/>
+      <c r="D42" s="149"/>
+      <c r="E42" s="149"/>
+      <c r="F42" s="149"/>
+      <c r="G42" s="149"/>
+      <c r="H42" s="149"/>
+      <c r="I42" s="149"/>
+      <c r="J42" s="149"/>
     </row>
     <row r="43">
-      <c r="A43" s="150"/>
-      <c r="B43" s="150"/>
-      <c r="C43" s="150"/>
-      <c r="D43" s="150"/>
-      <c r="E43" s="150"/>
-      <c r="F43" s="150"/>
-      <c r="G43" s="150"/>
-      <c r="H43" s="150"/>
-      <c r="I43" s="150"/>
-      <c r="J43" s="150"/>
+      <c r="A43" s="149"/>
+      <c r="B43" s="149"/>
+      <c r="C43" s="149"/>
+      <c r="D43" s="149"/>
+      <c r="E43" s="149"/>
+      <c r="F43" s="149"/>
+      <c r="G43" s="149"/>
+      <c r="H43" s="149"/>
+      <c r="I43" s="149"/>
+      <c r="J43" s="149"/>
     </row>
     <row r="44">
-      <c r="A44" s="150"/>
-      <c r="B44" s="150"/>
-      <c r="C44" s="150"/>
-      <c r="D44" s="150"/>
-      <c r="E44" s="150"/>
-      <c r="F44" s="150"/>
-      <c r="G44" s="150"/>
-      <c r="H44" s="150"/>
-      <c r="I44" s="150"/>
-      <c r="J44" s="150"/>
+      <c r="A44" s="149"/>
+      <c r="B44" s="149"/>
+      <c r="C44" s="149"/>
+      <c r="D44" s="149"/>
+      <c r="E44" s="149"/>
+      <c r="F44" s="149"/>
+      <c r="G44" s="149"/>
+      <c r="H44" s="149"/>
+      <c r="I44" s="149"/>
+      <c r="J44" s="149"/>
     </row>
     <row r="45">
-      <c r="A45" s="157" t="s">
+      <c r="A45" s="156" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="157" t="s">
-        <v>296</v>
-      </c>
-      <c r="C45" s="157" t="s">
-        <v>297</v>
-      </c>
-      <c r="D45" s="157" t="s">
+      <c r="B45" s="156" t="s">
+        <v>298</v>
+      </c>
+      <c r="C45" s="156" t="s">
+        <v>299</v>
+      </c>
+      <c r="D45" s="156" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="157" t="s">
-        <v>298</v>
-      </c>
-      <c r="F45" s="157" t="s">
-        <v>299</v>
-      </c>
-      <c r="G45" s="157" t="s">
+      <c r="E45" s="156" t="s">
         <v>300</v>
       </c>
-      <c r="H45" s="157" t="s">
+      <c r="F45" s="156" t="s">
         <v>301</v>
       </c>
-      <c r="I45" s="157" t="s">
+      <c r="G45" s="156" t="s">
         <v>302</v>
       </c>
-      <c r="J45" s="157" t="s">
+      <c r="H45" s="156" t="s">
         <v>303</v>
       </c>
+      <c r="I45" s="156" t="s">
+        <v>304</v>
+      </c>
+      <c r="J45" s="156" t="s">
+        <v>305</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="158" t="s">
-        <v>304</v>
-      </c>
-      <c r="B46" s="159">
+      <c r="A46" s="157" t="s">
+        <v>306</v>
+      </c>
+      <c r="B46" s="158">
         <v>1000000.0</v>
       </c>
-      <c r="C46" s="160">
+      <c r="C46" s="159">
         <v>0.2</v>
       </c>
-      <c r="D46" s="159">
+      <c r="D46" s="158">
         <f>IF(AND(B46&lt;&gt;"", C46&lt;&gt;"", E46&lt;&gt;""), PMT(C46/12, E46, -B46), "")</f>
         <v>26493.88371</v>
       </c>
-      <c r="E46" s="161">
+      <c r="E46" s="160">
         <v>60.0</v>
       </c>
-      <c r="F46" s="161">
+      <c r="F46" s="160">
         <v>0.0</v>
       </c>
-      <c r="G46" s="161">
+      <c r="G46" s="160">
         <f t="shared" ref="G46:G52" si="1">IF(E46="", "", E46 - F46)</f>
         <v>60</v>
       </c>
-      <c r="H46" s="159">
+      <c r="H46" s="158">
         <f t="shared" ref="H46:H52" si="2">IF(D46="", "", D46 * F46)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="159">
+      <c r="I46" s="158">
         <f t="shared" ref="I46:I52" si="3">IF(G46="", "", IFERROR(PV(C46/12, G46, -D46), ""))</f>
         <v>1000000</v>
       </c>
-      <c r="J46" s="162">
+      <c r="J46" s="161">
         <f t="shared" ref="J46:J52" si="4">IF(AND(D46&lt;&gt;"", E46&lt;&gt;""), (D46 * E46) - B46, "")</f>
         <v>589633.0229</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="163" t="s">
-        <v>305</v>
-      </c>
-      <c r="B47" s="164">
+      <c r="A47" s="162" t="s">
+        <v>307</v>
+      </c>
+      <c r="B47" s="163">
         <v>596000.0</v>
       </c>
-      <c r="C47" s="165">
+      <c r="C47" s="164">
         <v>0.126</v>
       </c>
-      <c r="D47" s="164">
+      <c r="D47" s="163">
         <f>IF(AND(B47&lt;&gt;"", C47&lt;&gt;"", E47&lt;&gt;""), PMT(C47/12, E47, -B47), 11839)</f>
         <v>11838.71102</v>
       </c>
-      <c r="E47" s="166">
+      <c r="E47" s="165">
         <v>72.0</v>
       </c>
-      <c r="F47" s="166">
+      <c r="F47" s="165">
         <v>52.0</v>
       </c>
-      <c r="G47" s="166">
+      <c r="G47" s="165">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="H47" s="164">
+      <c r="H47" s="163">
         <f t="shared" si="2"/>
         <v>615612.9729</v>
       </c>
-      <c r="I47" s="164">
+      <c r="I47" s="163">
         <f t="shared" si="3"/>
         <v>212564.401</v>
       </c>
-      <c r="J47" s="167">
+      <c r="J47" s="166">
         <f t="shared" si="4"/>
         <v>256387.1932</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="158" t="s">
-        <v>306</v>
-      </c>
-      <c r="B48" s="168"/>
-      <c r="C48" s="169"/>
-      <c r="D48" s="159">
+      <c r="A48" s="157" t="s">
+        <v>308</v>
+      </c>
+      <c r="B48" s="167"/>
+      <c r="C48" s="168"/>
+      <c r="D48" s="158">
         <f>IF(AND(B48&lt;&gt;"", C48&lt;&gt;"", E48&lt;&gt;""), PMT(C48/12, E48, -B48), 15250)</f>
         <v>15250</v>
       </c>
-      <c r="E48" s="170"/>
-      <c r="F48" s="161">
+      <c r="E48" s="169"/>
+      <c r="F48" s="160">
         <v>0.0</v>
       </c>
-      <c r="G48" s="170" t="str">
+      <c r="G48" s="169" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="159">
+      <c r="H48" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="168" t="str">
+      <c r="I48" s="167" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J48" s="171" t="str">
+      <c r="J48" s="170" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="163" t="s">
+      <c r="A49" s="162" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="164">
+      <c r="B49" s="163">
         <v>97110.0</v>
       </c>
-      <c r="C49" s="172"/>
-      <c r="D49" s="164">
+      <c r="C49" s="171"/>
+      <c r="D49" s="163">
         <f>IF(AND(B49&lt;&gt;"", C49&lt;&gt;"", E49&lt;&gt;""), PMT(C49/12, E49, -B49), 18972)</f>
         <v>18972</v>
       </c>
-      <c r="E49" s="173"/>
-      <c r="F49" s="166">
+      <c r="E49" s="172"/>
+      <c r="F49" s="165">
         <v>0.0</v>
       </c>
-      <c r="G49" s="173" t="str">
+      <c r="G49" s="172" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="164">
+      <c r="H49" s="163">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="174" t="str">
+      <c r="I49" s="173" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J49" s="175" t="str">
+      <c r="J49" s="174" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="158" t="s">
-        <v>307</v>
-      </c>
-      <c r="B50" s="159">
+      <c r="A50" s="157" t="s">
+        <v>309</v>
+      </c>
+      <c r="B50" s="158">
         <v>83419.0</v>
       </c>
-      <c r="C50" s="160">
+      <c r="C50" s="159">
         <v>0.12</v>
       </c>
-      <c r="D50" s="159">
+      <c r="D50" s="158">
         <f t="shared" ref="D50:D51" si="5">IF(AND(B50&lt;&gt;"", C50&lt;&gt;"", E50&lt;&gt;""), PMT(C50/12, E50, -B50), 4627)</f>
         <v>5087.061453</v>
       </c>
-      <c r="E50" s="161">
+      <c r="E50" s="160">
         <v>18.0</v>
       </c>
-      <c r="F50" s="161">
+      <c r="F50" s="160">
         <v>3.0</v>
       </c>
-      <c r="G50" s="161">
+      <c r="G50" s="160">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H50" s="159">
+      <c r="H50" s="158">
         <f t="shared" si="2"/>
         <v>15261.18436</v>
       </c>
-      <c r="I50" s="159">
+      <c r="I50" s="158">
         <f t="shared" si="3"/>
         <v>70532.37421</v>
       </c>
-      <c r="J50" s="162">
+      <c r="J50" s="161">
         <f t="shared" si="4"/>
         <v>8148.106161</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="176" t="s">
-        <v>308</v>
-      </c>
-      <c r="B51" s="177">
+      <c r="A51" s="175" t="s">
+        <v>310</v>
+      </c>
+      <c r="B51" s="176">
         <v>149100.0</v>
       </c>
-      <c r="C51" s="178">
+      <c r="C51" s="177">
         <v>0.1</v>
       </c>
-      <c r="D51" s="177">
+      <c r="D51" s="176">
         <f t="shared" si="5"/>
         <v>5637.681256</v>
       </c>
-      <c r="E51" s="179">
+      <c r="E51" s="178">
         <v>30.0</v>
       </c>
-      <c r="F51" s="179">
+      <c r="F51" s="178">
         <v>15.0</v>
       </c>
-      <c r="G51" s="179">
+      <c r="G51" s="178">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H51" s="177">
+      <c r="H51" s="176">
         <f t="shared" si="2"/>
         <v>84565.21884</v>
       </c>
-      <c r="I51" s="177">
+      <c r="I51" s="176">
         <f t="shared" si="3"/>
         <v>79184.0856</v>
       </c>
-      <c r="J51" s="180">
+      <c r="J51" s="179">
         <f t="shared" si="4"/>
         <v>20030.43769</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="158" t="s">
-        <v>309</v>
-      </c>
-      <c r="B52" s="168"/>
-      <c r="C52" s="169"/>
-      <c r="D52" s="159">
+      <c r="A52" s="157" t="s">
+        <v>311</v>
+      </c>
+      <c r="B52" s="167"/>
+      <c r="C52" s="168"/>
+      <c r="D52" s="158">
         <f>IF(AND(B52&lt;&gt;"", C52&lt;&gt;"", E52&lt;&gt;""), PMT(C52/12, E52, -B52), 3850)</f>
         <v>3850</v>
       </c>
-      <c r="E52" s="170"/>
-      <c r="F52" s="161">
+      <c r="E52" s="169"/>
+      <c r="F52" s="160">
         <v>0.0</v>
       </c>
-      <c r="G52" s="170" t="str">
+      <c r="G52" s="169" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H52" s="159">
+      <c r="H52" s="158">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="168" t="str">
+      <c r="I52" s="167" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J52" s="171" t="str">
+      <c r="J52" s="170" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="181" t="s">
-        <v>262</v>
-      </c>
-      <c r="B61" s="181" t="s">
-        <v>310</v>
-      </c>
-      <c r="C61" s="181" t="s">
+      <c r="A61" s="180" t="s">
+        <v>264</v>
+      </c>
+      <c r="B61" s="180" t="s">
+        <v>312</v>
+      </c>
+      <c r="C61" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="D61" s="181" t="s">
-        <v>311</v>
-      </c>
-      <c r="E61" s="181" t="s">
-        <v>312</v>
-      </c>
-      <c r="F61" s="181" t="s">
+      <c r="D61" s="180" t="s">
         <v>313</v>
       </c>
-      <c r="G61" s="181" t="s">
+      <c r="E61" s="180" t="s">
+        <v>314</v>
+      </c>
+      <c r="F61" s="180" t="s">
+        <v>315</v>
+      </c>
+      <c r="G61" s="180" t="s">
         <v>136</v>
       </c>
-      <c r="H61" s="150"/>
-      <c r="I61" s="181" t="s">
-        <v>314</v>
-      </c>
-      <c r="J61" s="150" t="s">
-        <v>315</v>
+      <c r="H61" s="149"/>
+      <c r="I61" s="180" t="s">
+        <v>316</v>
+      </c>
+      <c r="J61" s="149" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="151">
+      <c r="A62" s="150">
         <v>46143.0</v>
       </c>
-      <c r="B62" s="150" t="s">
-        <v>316</v>
-      </c>
-      <c r="C62" s="182">
+      <c r="B62" s="149" t="s">
+        <v>318</v>
+      </c>
+      <c r="C62" s="181">
         <v>11839.0</v>
       </c>
-      <c r="D62" s="183" t="b">
+      <c r="D62" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E62" s="150" t="s">
-        <v>317</v>
-      </c>
-      <c r="F62" s="150" t="s">
-        <v>318</v>
-      </c>
-      <c r="G62" s="182">
+      <c r="E62" s="149" t="s">
+        <v>319</v>
+      </c>
+      <c r="F62" s="149" t="s">
+        <v>320</v>
+      </c>
+      <c r="G62" s="181">
         <v>71000.0</v>
       </c>
-      <c r="H62" s="150"/>
-      <c r="I62" s="181" t="s">
-        <v>319</v>
-      </c>
-      <c r="J62" s="182">
+      <c r="H62" s="149"/>
+      <c r="I62" s="180" t="s">
+        <v>321</v>
+      </c>
+      <c r="J62" s="181">
         <f>SUM(C62:C1000)</f>
         <v>84657</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="151">
+      <c r="A63" s="150">
         <v>46144.0</v>
       </c>
-      <c r="B63" s="150" t="s">
-        <v>320</v>
-      </c>
-      <c r="C63" s="182">
+      <c r="B63" s="149" t="s">
+        <v>322</v>
+      </c>
+      <c r="C63" s="181">
         <v>3850.0</v>
       </c>
-      <c r="D63" s="183" t="b">
+      <c r="D63" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="150" t="s">
-        <v>321</v>
-      </c>
-      <c r="F63" s="150"/>
-      <c r="G63" s="184"/>
-      <c r="H63" s="150"/>
-      <c r="I63" s="181" t="s">
-        <v>301</v>
-      </c>
-      <c r="J63" s="182">
+      <c r="E63" s="149" t="s">
+        <v>323</v>
+      </c>
+      <c r="F63" s="149"/>
+      <c r="G63" s="183"/>
+      <c r="H63" s="149"/>
+      <c r="I63" s="180" t="s">
+        <v>303</v>
+      </c>
+      <c r="J63" s="181">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
         <v>50435</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="151">
+      <c r="A64" s="150">
         <v>46145.0</v>
       </c>
-      <c r="B64" s="150" t="s">
-        <v>322</v>
-      </c>
-      <c r="C64" s="182">
+      <c r="B64" s="149" t="s">
+        <v>324</v>
+      </c>
+      <c r="C64" s="181">
         <v>4627.0</v>
       </c>
-      <c r="D64" s="183" t="b">
+      <c r="D64" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E64" s="150"/>
-      <c r="F64" s="150"/>
-      <c r="G64" s="184"/>
-      <c r="H64" s="150"/>
-      <c r="I64" s="181" t="s">
-        <v>323</v>
-      </c>
-      <c r="J64" s="182">
+      <c r="E64" s="149"/>
+      <c r="F64" s="149"/>
+      <c r="G64" s="183"/>
+      <c r="H64" s="149"/>
+      <c r="I64" s="180" t="s">
+        <v>325</v>
+      </c>
+      <c r="J64" s="181">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
         <v>34222</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="151">
+      <c r="A65" s="150">
         <v>46147.0</v>
       </c>
-      <c r="B65" s="150" t="s">
-        <v>324</v>
-      </c>
-      <c r="C65" s="182">
+      <c r="B65" s="149" t="s">
+        <v>326</v>
+      </c>
+      <c r="C65" s="181">
         <v>5000.0</v>
       </c>
-      <c r="D65" s="183" t="b">
+      <c r="D65" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E65" s="150"/>
-      <c r="F65" s="150"/>
-      <c r="G65" s="184"/>
-      <c r="H65" s="150"/>
-      <c r="I65" s="181" t="s">
-        <v>325</v>
-      </c>
-      <c r="J65" s="182">
+      <c r="E65" s="149"/>
+      <c r="F65" s="149"/>
+      <c r="G65" s="183"/>
+      <c r="H65" s="149"/>
+      <c r="I65" s="180" t="s">
+        <v>327</v>
+      </c>
+      <c r="J65" s="181">
         <f>SUM(G62:G1000)</f>
         <v>71000</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="151">
+      <c r="A66" s="150">
         <v>46167.0</v>
       </c>
-      <c r="B66" s="150" t="s">
-        <v>326</v>
-      </c>
-      <c r="C66" s="182">
+      <c r="B66" s="149" t="s">
+        <v>328</v>
+      </c>
+      <c r="C66" s="181">
         <v>18972.0</v>
       </c>
-      <c r="D66" s="183" t="b">
+      <c r="D66" s="182" t="b">
         <v>0</v>
       </c>
-      <c r="E66" s="185">
+      <c r="E66" s="184">
         <v>97110.0</v>
       </c>
-      <c r="F66" s="150"/>
-      <c r="G66" s="184"/>
-      <c r="H66" s="150"/>
-      <c r="I66" s="181" t="s">
-        <v>327</v>
-      </c>
-      <c r="J66" s="182">
+      <c r="F66" s="149"/>
+      <c r="G66" s="183"/>
+      <c r="H66" s="149"/>
+      <c r="I66" s="180" t="s">
+        <v>329</v>
+      </c>
+      <c r="J66" s="181">
         <f>J65-J62</f>
         <v>-13657</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="151">
+      <c r="A67" s="150">
         <v>46146.0</v>
       </c>
-      <c r="B67" s="150" t="s">
-        <v>328</v>
-      </c>
-      <c r="C67" s="182">
+      <c r="B67" s="149" t="s">
+        <v>330</v>
+      </c>
+      <c r="C67" s="181">
         <v>13625.0</v>
       </c>
-      <c r="D67" s="183" t="b">
+      <c r="D67" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E67" s="150" t="s">
-        <v>329</v>
-      </c>
-      <c r="F67" s="150"/>
-      <c r="G67" s="184"/>
-      <c r="H67" s="150"/>
-      <c r="I67" s="150"/>
-      <c r="J67" s="150"/>
+      <c r="E67" s="149" t="s">
+        <v>331</v>
+      </c>
+      <c r="F67" s="149"/>
+      <c r="G67" s="183"/>
+      <c r="H67" s="149"/>
+      <c r="I67" s="149"/>
+      <c r="J67" s="149"/>
     </row>
     <row r="68">
-      <c r="A68" s="151">
+      <c r="A68" s="150">
         <v>46145.0</v>
       </c>
-      <c r="B68" s="150" t="s">
-        <v>330</v>
-      </c>
-      <c r="C68" s="182">
+      <c r="B68" s="149" t="s">
+        <v>332</v>
+      </c>
+      <c r="C68" s="181">
         <v>2494.0</v>
       </c>
-      <c r="D68" s="183" t="b">
+      <c r="D68" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E68" s="150"/>
-      <c r="F68" s="150"/>
-      <c r="G68" s="184"/>
-      <c r="H68" s="150"/>
-      <c r="I68" s="150"/>
-      <c r="J68" s="150"/>
+      <c r="E68" s="149"/>
+      <c r="F68" s="149"/>
+      <c r="G68" s="183"/>
+      <c r="H68" s="149"/>
+      <c r="I68" s="149"/>
+      <c r="J68" s="149"/>
     </row>
     <row r="69">
-      <c r="A69" s="151">
+      <c r="A69" s="150">
         <v>46144.0</v>
       </c>
-      <c r="B69" s="150" t="s">
-        <v>331</v>
-      </c>
-      <c r="C69" s="182">
+      <c r="B69" s="149" t="s">
+        <v>333</v>
+      </c>
+      <c r="C69" s="181">
         <v>4500.0</v>
       </c>
-      <c r="D69" s="183" t="b">
+      <c r="D69" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E69" s="150"/>
-      <c r="F69" s="150"/>
-      <c r="G69" s="184"/>
-      <c r="H69" s="150"/>
-      <c r="I69" s="150"/>
-      <c r="J69" s="150"/>
+      <c r="E69" s="149"/>
+      <c r="F69" s="149"/>
+      <c r="G69" s="183"/>
+      <c r="H69" s="149"/>
+      <c r="I69" s="149"/>
+      <c r="J69" s="149"/>
     </row>
     <row r="70">
-      <c r="A70" s="151">
+      <c r="A70" s="150">
         <v>46152.0</v>
       </c>
-      <c r="B70" s="150" t="s">
-        <v>332</v>
-      </c>
-      <c r="C70" s="182">
+      <c r="B70" s="149" t="s">
+        <v>334</v>
+      </c>
+      <c r="C70" s="181">
         <v>1500.0</v>
       </c>
-      <c r="D70" s="183" t="b">
+      <c r="D70" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E70" s="150"/>
-      <c r="F70" s="150"/>
-      <c r="G70" s="184"/>
-      <c r="H70" s="150"/>
-      <c r="I70" s="150"/>
-      <c r="J70" s="150"/>
+      <c r="E70" s="149"/>
+      <c r="F70" s="149"/>
+      <c r="G70" s="183"/>
+      <c r="H70" s="149"/>
+      <c r="I70" s="149"/>
+      <c r="J70" s="149"/>
     </row>
     <row r="71">
-      <c r="A71" s="151">
+      <c r="A71" s="150">
         <v>46152.0</v>
       </c>
-      <c r="B71" s="150" t="s">
-        <v>333</v>
-      </c>
-      <c r="C71" s="182">
+      <c r="B71" s="149" t="s">
+        <v>335</v>
+      </c>
+      <c r="C71" s="181">
         <v>3000.0</v>
       </c>
-      <c r="D71" s="183" t="b">
+      <c r="D71" s="182" t="b">
         <v>1</v>
       </c>
-      <c r="E71" s="150"/>
-      <c r="F71" s="150"/>
-      <c r="G71" s="184"/>
-      <c r="H71" s="150"/>
-      <c r="I71" s="150"/>
-      <c r="J71" s="150"/>
+      <c r="E71" s="149"/>
+      <c r="F71" s="149"/>
+      <c r="G71" s="183"/>
+      <c r="H71" s="149"/>
+      <c r="I71" s="149"/>
+      <c r="J71" s="149"/>
     </row>
     <row r="72">
-      <c r="A72" s="151">
+      <c r="A72" s="150">
         <v>46157.0</v>
       </c>
-      <c r="B72" s="150" t="s">
-        <v>334</v>
-      </c>
-      <c r="C72" s="182">
+      <c r="B72" s="149" t="s">
+        <v>336</v>
+      </c>
+      <c r="C72" s="181">
         <v>15250.0</v>
       </c>
-      <c r="D72" s="183" t="b">
+      <c r="D72" s="182" t="b">
         <v>0</v>
       </c>
-      <c r="E72" s="150"/>
-      <c r="F72" s="150"/>
-      <c r="G72" s="184"/>
-      <c r="H72" s="150"/>
-      <c r="I72" s="150"/>
-      <c r="J72" s="150"/>
+      <c r="E72" s="149"/>
+      <c r="F72" s="149"/>
+      <c r="G72" s="183"/>
+      <c r="H72" s="149"/>
+      <c r="I72" s="149"/>
+      <c r="J72" s="149"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21712.80658</v>
+        <v>21830.81096</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14335.89041</v>
+        <v>14398.76712</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2157.534247</v>
+        <v>2243.835616</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21830.81096</v>
+        <v>21948.81534</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14398.76712</v>
+        <v>14461.64384</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2243.835616</v>
+        <v>2330.136986</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>21948.81534</v>
+        <v>22066.81973</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14461.64384</v>
+        <v>14524.52055</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2330.136986</v>
+        <v>2416.438356</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22066.81973</v>
+        <v>22184.82411</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14524.52055</v>
+        <v>14587.39726</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2416.438356</v>
+        <v>2502.739726</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22184.82411</v>
+        <v>22302.82849</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14587.39726</v>
+        <v>14650.27397</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2502.739726</v>
+        <v>2589.041096</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22302.82849</v>
+        <v>22420.83288</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14650.27397</v>
+        <v>14713.15068</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2589.041096</v>
+        <v>2675.342466</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22420.83288</v>
+        <v>22538.83726</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14713.15068</v>
+        <v>14776.0274</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2675.342466</v>
+        <v>2761.643836</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22538.83726</v>
+        <v>22656.84164</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14776.0274</v>
+        <v>14838.90411</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2761.643836</v>
+        <v>2847.945205</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22656.84164</v>
+        <v>22774.84603</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14838.90411</v>
+        <v>14901.78082</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2847.945205</v>
+        <v>2934.246575</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22774.84603</v>
+        <v>22892.85041</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14901.78082</v>
+        <v>14964.65753</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>2934.246575</v>
+        <v>3020.547945</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>22892.85041</v>
+        <v>23010.85479</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>14964.65753</v>
+        <v>15027.53425</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3020.547945</v>
+        <v>3106.849315</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23010.85479</v>
+        <v>23128.85918</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15027.53425</v>
+        <v>15090.41096</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3106.849315</v>
+        <v>3193.150685</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23128.85918</v>
+        <v>23246.86356</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15090.41096</v>
+        <v>15153.28767</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3193.150685</v>
+        <v>3279.452055</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23246.86356</v>
+        <v>23364.86795</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15153.28767</v>
+        <v>15216.16438</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3279.452055</v>
+        <v>3365.753425</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23364.86795</v>
+        <v>23482.87233</v>
       </c>
     </row>
     <row r="6">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15216.16438</v>
+        <v>15279.0411</v>
       </c>
     </row>
     <row r="7">
@@ -8930,7 +8930,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3365.753425</v>
+        <v>3452.054795</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,11 @@
   <sheets>
     <sheet state="visible" name="Loans" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Monthly View" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Monthly Expenses" sheetId="3" r:id="rId7"/>
+    <sheet state="visible" name="June 2026 Expenses" sheetId="3" r:id="rId7"/>
     <sheet state="visible" name="Gold Loan" sheetId="4" r:id="rId8"/>
     <sheet state="visible" name="Tips to Close Faster" sheetId="5" r:id="rId9"/>
     <sheet state="visible" name="General" sheetId="6" r:id="rId10"/>
+    <sheet state="visible" name="July 2026 Expense " sheetId="7" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="341">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -555,6 +556,12 @@
     <t>Mat</t>
   </si>
   <si>
+    <t>Gold coin -2 grams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">credit card.                                        25 June </t>
+  </si>
+  <si>
     <t>Gold Loan Tracker</t>
   </si>
   <si>
@@ -1033,6 +1040,12 @@
   </si>
   <si>
     <t>Equites Home loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category Expense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amount </t>
   </si>
 </sst>
 </file>
@@ -1214,7 +1227,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="20">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1329,6 +1342,12 @@
         <bgColor rgb="FFF8F8FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border/>
@@ -1424,7 +1443,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="187">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1518,11 +1537,11 @@
     <xf borderId="5" fillId="7" fontId="6" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="7" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="5" fillId="7" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="7" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="5" fillId="7" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
@@ -1857,6 +1876,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="173" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -1927,6 +1949,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="25" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="20" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2044,7 +2069,7 @@
       <tableStyleElement dxfId="3" type="secondRowStripe"/>
       <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
     </tableStyle>
-    <tableStyle count="2" pivot="0" name="Monthly Expenses-style">
+    <tableStyle count="2" pivot="0" name="June 2026 Expenses-style">
       <tableStyleElement dxfId="5" type="firstRowStripe"/>
       <tableStyleElement dxfId="6" type="secondRowStripe"/>
     </tableStyle>
@@ -2083,6 +2108,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -2129,7 +2158,7 @@
     <tableColumn name="Column3" id="3"/>
     <tableColumn name="Column4" id="4"/>
   </tableColumns>
-  <tableStyleInfo name="Monthly Expenses-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="June 2026 Expenses-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -2748,8 +2777,8 @@
       <c r="B21" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="30">
-        <v>5920.0</v>
+      <c r="C21" s="35">
+        <v>2970.0</v>
       </c>
       <c r="D21" s="31" t="s">
         <v>34</v>
@@ -2763,7 +2792,7 @@
       <c r="G21" s="30">
         <v>148000.0</v>
       </c>
-      <c r="H21" s="35" t="s">
+      <c r="H21" s="36" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2771,8 +2800,8 @@
       <c r="B22" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="30">
-        <v>5920.0</v>
+      <c r="C22" s="35">
+        <v>2970.0</v>
       </c>
       <c r="D22" s="31" t="s">
         <v>34</v>
@@ -2786,7 +2815,7 @@
       <c r="G22" s="30">
         <v>148000.0</v>
       </c>
-      <c r="H22" s="35" t="s">
+      <c r="H22" s="36" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2817,7 +2846,7 @@
       <c r="B24" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="35">
         <v>1740.0</v>
       </c>
       <c r="D24" s="37" t="s">
@@ -2829,10 +2858,10 @@
       <c r="F24" s="38">
         <v>6.0</v>
       </c>
-      <c r="G24" s="36">
+      <c r="G24" s="35">
         <v>12590.0</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="36" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2842,7 +2871,7 @@
       </c>
       <c r="C25" s="40">
         <f>SUM(C8:C24)</f>
-        <v>96301</v>
+        <v>90401</v>
       </c>
       <c r="D25" s="41"/>
       <c r="E25" s="41"/>
@@ -2856,7 +2885,7 @@
       </c>
       <c r="C26" s="40">
         <f>C5-C25</f>
-        <v>13699</v>
+        <v>19599</v>
       </c>
       <c r="D26" s="41"/>
       <c r="E26" s="41"/>
@@ -4083,12 +4112,12 @@
         <v>93336</v>
       </c>
       <c r="E5" s="56">
-        <f>IF(B5="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
-        <v>106763</v>
+        <f>IF(B5="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B5), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B5), 0)))</f>
+        <v>134263</v>
       </c>
       <c r="F5" s="57">
         <f t="shared" ref="F5:F59" si="2">C5-D5-E5</f>
-        <v>-90099</v>
+        <v>-117599</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="59">
@@ -4156,7 +4185,7 @@
         <v>121570</v>
       </c>
       <c r="E6" s="64">
-        <f>IF(B6="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B6), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B6), 0)))</f>
+        <f>IF(B6="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B6), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B6), 0)))</f>
         <v>0</v>
       </c>
       <c r="F6" s="57">
@@ -4231,7 +4260,7 @@
         <v>118920</v>
       </c>
       <c r="E7" s="56">
-        <f>IF(B7="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B7), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B7), 0)))</f>
+        <f>IF(B7="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B7), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B7), 0)))</f>
         <v>0</v>
       </c>
       <c r="F7" s="57">
@@ -4302,7 +4331,7 @@
         <v>118920</v>
       </c>
       <c r="E8" s="73">
-        <f>IF(B8="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B8), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B8), 0)))</f>
+        <f>IF(B8="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B8), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B8), 0)))</f>
         <v>0</v>
       </c>
       <c r="F8" s="57">
@@ -4373,7 +4402,7 @@
         <v>118920</v>
       </c>
       <c r="E9" s="64">
-        <f>IF(B9="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B9), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B9), 0)))</f>
+        <f>IF(B9="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B9), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B9), 0)))</f>
         <v>0</v>
       </c>
       <c r="F9" s="57">
@@ -4446,7 +4475,7 @@
         <v>99948</v>
       </c>
       <c r="E10" s="77">
-        <f>IF(B10="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B10), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B10), 0)))</f>
+        <f>IF(B10="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B10), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B10), 0)))</f>
         <v>0</v>
       </c>
       <c r="F10" s="78">
@@ -4515,7 +4544,7 @@
         <v>99948</v>
       </c>
       <c r="E11" s="79">
-        <f>IF(B11="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B11), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B11), 0)))</f>
+        <f>IF(B11="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B11), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B11), 0)))</f>
         <v>0</v>
       </c>
       <c r="F11" s="80">
@@ -4584,7 +4613,7 @@
         <v>98208</v>
       </c>
       <c r="E12" s="77">
-        <f>IF(B12="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B12), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B12), 0)))</f>
+        <f>IF(B12="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B12), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B12), 0)))</f>
         <v>0</v>
       </c>
       <c r="F12" s="78">
@@ -4651,7 +4680,7 @@
         <v>98208</v>
       </c>
       <c r="E13" s="81">
-        <f>IF(B13="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B13), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B13), 0)))</f>
+        <f>IF(B13="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B13), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B13), 0)))</f>
         <v>0</v>
       </c>
       <c r="F13" s="82">
@@ -4720,7 +4749,7 @@
         <v>96978</v>
       </c>
       <c r="E14" s="81">
-        <f>IF(B14="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B14), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B14), 0)))</f>
+        <f>IF(B14="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B14), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B14), 0)))</f>
         <v>0</v>
       </c>
       <c r="F14" s="82">
@@ -4787,7 +4816,7 @@
         <v>93828</v>
       </c>
       <c r="E15" s="79">
-        <f>IF(B15="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B15), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B15), 0)))</f>
+        <f>IF(B15="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B15), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B15), 0)))</f>
         <v>0</v>
       </c>
       <c r="F15" s="80">
@@ -4850,7 +4879,7 @@
         <v>93828</v>
       </c>
       <c r="E16" s="77">
-        <f>IF(B16="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B16), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B16), 0)))</f>
+        <f>IF(B16="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B16), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B16), 0)))</f>
         <v>0</v>
       </c>
       <c r="F16" s="78">
@@ -4913,7 +4942,7 @@
         <v>93828</v>
       </c>
       <c r="E17" s="87">
-        <f>IF(B17="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B17), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B17), 0)))</f>
+        <f>IF(B17="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B17), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B17), 0)))</f>
         <v>0</v>
       </c>
       <c r="F17" s="88">
@@ -4978,7 +5007,7 @@
         <v>93828</v>
       </c>
       <c r="E18" s="93">
-        <f>IF(B18="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B18), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B18), 0)))</f>
+        <f>IF(B18="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B18), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B18), 0)))</f>
         <v>0</v>
       </c>
       <c r="F18" s="94">
@@ -5043,7 +5072,7 @@
         <v>84328</v>
       </c>
       <c r="E19" s="79">
-        <f>IF(B19="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B19), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B19), 0)))</f>
+        <f>IF(B19="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B19), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B19), 0)))</f>
         <v>0</v>
       </c>
       <c r="F19" s="80">
@@ -5102,7 +5131,7 @@
         <v>84328</v>
       </c>
       <c r="E20" s="77">
-        <f>IF(B20="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B20), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B20), 0)))</f>
+        <f>IF(B20="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B20), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B20), 0)))</f>
         <v>0</v>
       </c>
       <c r="F20" s="78">
@@ -5161,7 +5190,7 @@
         <v>84328</v>
       </c>
       <c r="E21" s="81">
-        <f>IF(B21="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B21), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B21), 0)))</f>
+        <f>IF(B21="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B21), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B21), 0)))</f>
         <v>0</v>
       </c>
       <c r="F21" s="82">
@@ -5222,7 +5251,7 @@
         <v>81093</v>
       </c>
       <c r="E22" s="77">
-        <f>IF(B22="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B22), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B22), 0)))</f>
+        <f>IF(B22="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B22), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B22), 0)))</f>
         <v>0</v>
       </c>
       <c r="F22" s="78">
@@ -5279,7 +5308,7 @@
         <v>81093</v>
       </c>
       <c r="E23" s="79">
-        <f>IF(B23="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B23), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B23), 0)))</f>
+        <f>IF(B23="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B23), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B23), 0)))</f>
         <v>0</v>
       </c>
       <c r="F23" s="80">
@@ -5336,7 +5365,7 @@
         <v>81093</v>
       </c>
       <c r="E24" s="93">
-        <f>IF(B24="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B24), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B24), 0)))</f>
+        <f>IF(B24="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B24), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B24), 0)))</f>
         <v>0</v>
       </c>
       <c r="F24" s="94">
@@ -5395,7 +5424,7 @@
         <v>63864</v>
       </c>
       <c r="E25" s="79">
-        <f>IF(B25="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B25), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B25), 0)))</f>
+        <f>IF(B25="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B25), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B25), 0)))</f>
         <v>0</v>
       </c>
       <c r="F25" s="80">
@@ -5448,7 +5477,7 @@
         <v>63864</v>
       </c>
       <c r="E26" s="81">
-        <f>IF(B26="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B26), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B26), 0)))</f>
+        <f>IF(B26="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B26), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B26), 0)))</f>
         <v>0</v>
       </c>
       <c r="F26" s="82">
@@ -5503,7 +5532,7 @@
         <v>61264</v>
       </c>
       <c r="E27" s="81">
-        <f>IF(B27="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B27), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B27), 0)))</f>
+        <f>IF(B27="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B27), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B27), 0)))</f>
         <v>0</v>
       </c>
       <c r="F27" s="82">
@@ -5556,7 +5585,7 @@
         <v>58584</v>
       </c>
       <c r="E28" s="77">
-        <f>IF(B28="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B28), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B28), 0)))</f>
+        <f>IF(B28="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B28), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B28), 0)))</f>
         <v>0</v>
       </c>
       <c r="F28" s="78">
@@ -5605,7 +5634,7 @@
         <v>58584</v>
       </c>
       <c r="E29" s="81">
-        <f>IF(B29="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B29), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B29), 0)))</f>
+        <f>IF(B29="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B29), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B29), 0)))</f>
         <v>0</v>
       </c>
       <c r="F29" s="82">
@@ -5656,7 +5685,7 @@
         <v>46744</v>
       </c>
       <c r="E30" s="77">
-        <f>IF(B30="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B30), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B30), 0)))</f>
+        <f>IF(B30="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B30), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B30), 0)))</f>
         <v>0</v>
       </c>
       <c r="F30" s="78">
@@ -5701,7 +5730,7 @@
         <v>46744</v>
       </c>
       <c r="E31" s="79">
-        <f>IF(B31="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B31), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B31), 0)))</f>
+        <f>IF(B31="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B31), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B31), 0)))</f>
         <v>0</v>
       </c>
       <c r="F31" s="80">
@@ -5746,7 +5775,7 @@
         <v>46744</v>
       </c>
       <c r="E32" s="77">
-        <f>IF(B32="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B32), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B32), 0)))</f>
+        <f>IF(B32="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B32), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B32), 0)))</f>
         <v>0</v>
       </c>
       <c r="F32" s="78">
@@ -5791,7 +5820,7 @@
         <v>46744</v>
       </c>
       <c r="E33" s="79">
-        <f>IF(B33="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B33), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B33), 0)))</f>
+        <f>IF(B33="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B33), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B33), 0)))</f>
         <v>0</v>
       </c>
       <c r="F33" s="80">
@@ -5836,7 +5865,7 @@
         <v>46744</v>
       </c>
       <c r="E34" s="77">
-        <f>IF(B34="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B34), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B34), 0)))</f>
+        <f>IF(B34="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B34), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B34), 0)))</f>
         <v>0</v>
       </c>
       <c r="F34" s="78">
@@ -5881,7 +5910,7 @@
         <v>46744</v>
       </c>
       <c r="E35" s="81">
-        <f>IF(B35="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B35), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B35), 0)))</f>
+        <f>IF(B35="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B35), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B35), 0)))</f>
         <v>0</v>
       </c>
       <c r="F35" s="82">
@@ -5928,7 +5957,7 @@
         <v>41744</v>
       </c>
       <c r="E36" s="77">
-        <f>IF(B36="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B36), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B36), 0)))</f>
+        <f>IF(B36="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B36), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B36), 0)))</f>
         <v>0</v>
       </c>
       <c r="F36" s="78">
@@ -5971,7 +6000,7 @@
         <v>41744</v>
       </c>
       <c r="E37" s="79">
-        <f>IF(B37="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B37), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B37), 0)))</f>
+        <f>IF(B37="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B37), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B37), 0)))</f>
         <v>0</v>
       </c>
       <c r="F37" s="80">
@@ -6014,7 +6043,7 @@
         <v>41744</v>
       </c>
       <c r="E38" s="77">
-        <f>IF(B38="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B38), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B38), 0)))</f>
+        <f>IF(B38="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B38), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B38), 0)))</f>
         <v>0</v>
       </c>
       <c r="F38" s="78">
@@ -6057,7 +6086,7 @@
         <v>41744</v>
       </c>
       <c r="E39" s="79">
-        <f>IF(B39="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B39), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B39), 0)))</f>
+        <f>IF(B39="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B39), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B39), 0)))</f>
         <v>0</v>
       </c>
       <c r="F39" s="80">
@@ -6100,7 +6129,7 @@
         <v>41744</v>
       </c>
       <c r="E40" s="77">
-        <f>IF(B40="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B40), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B40), 0)))</f>
+        <f>IF(B40="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B40), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B40), 0)))</f>
         <v>0</v>
       </c>
       <c r="F40" s="78">
@@ -6143,7 +6172,7 @@
         <v>41744</v>
       </c>
       <c r="E41" s="79">
-        <f>IF(B41="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B41), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B41), 0)))</f>
+        <f>IF(B41="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B41), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B41), 0)))</f>
         <v>0</v>
       </c>
       <c r="F41" s="80">
@@ -6188,7 +6217,7 @@
         <v>41744</v>
       </c>
       <c r="E42" s="77">
-        <f>IF(B42="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B42), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B42), 0)))</f>
+        <f>IF(B42="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B42), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B42), 0)))</f>
         <v>0</v>
       </c>
       <c r="F42" s="78">
@@ -6231,7 +6260,7 @@
         <v>41744</v>
       </c>
       <c r="E43" s="79">
-        <f>IF(B43="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B43), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B43), 0)))</f>
+        <f>IF(B43="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B43), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B43), 0)))</f>
         <v>0</v>
       </c>
       <c r="F43" s="80">
@@ -6274,7 +6303,7 @@
         <v>41744</v>
       </c>
       <c r="E44" s="77">
-        <f>IF(B44="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B44), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B44), 0)))</f>
+        <f>IF(B44="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B44), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B44), 0)))</f>
         <v>0</v>
       </c>
       <c r="F44" s="78">
@@ -6317,7 +6346,7 @@
         <v>41744</v>
       </c>
       <c r="E45" s="79">
-        <f>IF(B45="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B45), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B45), 0)))</f>
+        <f>IF(B45="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B45), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B45), 0)))</f>
         <v>0</v>
       </c>
       <c r="F45" s="80">
@@ -6360,7 +6389,7 @@
         <v>41744</v>
       </c>
       <c r="E46" s="77">
-        <f>IF(B46="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B46), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B46), 0)))</f>
+        <f>IF(B46="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B46), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B46), 0)))</f>
         <v>0</v>
       </c>
       <c r="F46" s="78">
@@ -6403,7 +6432,7 @@
         <v>41744</v>
       </c>
       <c r="E47" s="79">
-        <f>IF(B47="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B47), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B47), 0)))</f>
+        <f>IF(B47="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B47), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B47), 0)))</f>
         <v>0</v>
       </c>
       <c r="F47" s="80">
@@ -6446,7 +6475,7 @@
         <v>41744</v>
       </c>
       <c r="E48" s="77">
-        <f>IF(B48="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B48), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B48), 0)))</f>
+        <f>IF(B48="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B48), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B48), 0)))</f>
         <v>0</v>
       </c>
       <c r="F48" s="78">
@@ -6489,7 +6518,7 @@
         <v>41744</v>
       </c>
       <c r="E49" s="79">
-        <f>IF(B49="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B49), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B49), 0)))</f>
+        <f>IF(B49="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B49), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B49), 0)))</f>
         <v>0</v>
       </c>
       <c r="F49" s="80">
@@ -6532,7 +6561,7 @@
         <v>41744</v>
       </c>
       <c r="E50" s="77">
-        <f>IF(B50="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B50), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B50), 0)))</f>
+        <f>IF(B50="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B50), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B50), 0)))</f>
         <v>0</v>
       </c>
       <c r="F50" s="78">
@@ -6575,7 +6604,7 @@
         <v>41744</v>
       </c>
       <c r="E51" s="79">
-        <f>IF(B51="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B51), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B51), 0)))</f>
+        <f>IF(B51="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B51), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B51), 0)))</f>
         <v>0</v>
       </c>
       <c r="F51" s="80">
@@ -6618,7 +6647,7 @@
         <v>41744</v>
       </c>
       <c r="E52" s="77">
-        <f>IF(B52="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B52), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B52), 0)))</f>
+        <f>IF(B52="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B52), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B52), 0)))</f>
         <v>0</v>
       </c>
       <c r="F52" s="78">
@@ -6661,7 +6690,7 @@
         <v>41744</v>
       </c>
       <c r="E53" s="79">
-        <f>IF(B53="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B53), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B53), 0)))</f>
+        <f>IF(B53="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B53), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B53), 0)))</f>
         <v>0</v>
       </c>
       <c r="F53" s="80">
@@ -6704,7 +6733,7 @@
         <v>41744</v>
       </c>
       <c r="E54" s="77">
-        <f>IF(B54="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B54), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B54), 0)))</f>
+        <f>IF(B54="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B54), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B54), 0)))</f>
         <v>0</v>
       </c>
       <c r="F54" s="78">
@@ -6747,7 +6776,7 @@
         <v>41744</v>
       </c>
       <c r="E55" s="79">
-        <f>IF(B55="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B55), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B55), 0)))</f>
+        <f>IF(B55="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B55), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B55), 0)))</f>
         <v>0</v>
       </c>
       <c r="F55" s="80">
@@ -6790,7 +6819,7 @@
         <v>41744</v>
       </c>
       <c r="E56" s="77">
-        <f>IF(B56="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B56), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B56), 0)))</f>
+        <f>IF(B56="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B56), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B56), 0)))</f>
         <v>0</v>
       </c>
       <c r="F56" s="78">
@@ -6833,7 +6862,7 @@
         <v>41744</v>
       </c>
       <c r="E57" s="79">
-        <f>IF(B57="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B57), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B57), 0)))</f>
+        <f>IF(B57="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B57), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B57), 0)))</f>
         <v>0</v>
       </c>
       <c r="F57" s="80">
@@ -6876,7 +6905,7 @@
         <v>41744</v>
       </c>
       <c r="E58" s="77">
-        <f>IF(B58="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B58), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B58), 0)))</f>
+        <f>IF(B58="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B58), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B58), 0)))</f>
         <v>0</v>
       </c>
       <c r="F58" s="78">
@@ -6919,7 +6948,7 @@
         <v>41744</v>
       </c>
       <c r="E59" s="81">
-        <f>IF(B59="","",SUMIFS('Monthly Expenses'!C:C, 'Monthly Expenses'!A:A, "&gt;="&amp;DATEVALUE(B59), 'Monthly Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B59), 0)))</f>
+        <f>IF(B59="","",SUMIFS('June 2026 Expenses'!C:C, 'June 2026 Expenses'!A:A, "&gt;="&amp;DATEVALUE(B59), 'June 2026 Expenses'!A:A, "&lt;="&amp;EOMONTH(DATEVALUE(B59), 0)))</f>
         <v>0</v>
       </c>
       <c r="F59" s="82">
@@ -8427,10 +8456,18 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="108"/>
-      <c r="B37" s="108"/>
-      <c r="C37" s="109"/>
-      <c r="D37" s="108"/>
+      <c r="A37" s="100">
+        <v>46174.0</v>
+      </c>
+      <c r="B37" s="101" t="s">
+        <v>177</v>
+      </c>
+      <c r="C37" s="102">
+        <v>27500.0</v>
+      </c>
+      <c r="D37" s="101" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="108"/>
@@ -8835,30 +8872,30 @@
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
       <c r="B2" s="110" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="111" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C4" s="111" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D4" s="111" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E4" s="111" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F4" s="111" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G4" s="111" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H4" s="112" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5">
@@ -8869,10 +8906,10 @@
         <v>0.11</v>
       </c>
       <c r="D5" s="113" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E5" s="113" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F5" s="115">
         <v>391560.0</v>
@@ -8893,10 +8930,10 @@
         <v>0.1</v>
       </c>
       <c r="D6" s="113" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E6" s="113" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F6" s="115">
         <v>229500.0</v>
@@ -8917,10 +8954,10 @@
         <v>0.105</v>
       </c>
       <c r="D7" s="113" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E7" s="113" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F7" s="115">
         <v>300000.0</v>
@@ -8939,10 +8976,10 @@
       </c>
       <c r="C8" s="117"/>
       <c r="D8" s="113" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E8" s="113" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F8" s="115">
         <v>135000.0</v>
@@ -8959,10 +8996,10 @@
       <c r="B9" s="118"/>
       <c r="C9" s="117"/>
       <c r="D9" s="113" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E9" s="113" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F9" s="115">
         <v>297698.0</v>
@@ -10043,14 +10080,14 @@
   <sheetData>
     <row r="1" ht="30.0" customHeight="1">
       <c r="B1" s="121" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C1" s="43"/>
       <c r="D1" s="44"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="B2" s="122" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C2" s="43"/>
       <c r="D2" s="44"/>
@@ -10058,172 +10095,172 @@
     <row r="3" ht="7.5" customHeight="1"/>
     <row r="4" ht="66.75" customHeight="1">
       <c r="B4" s="123" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C4" s="124" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D4" s="125" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" ht="48.75" customHeight="1">
       <c r="B5" s="123" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C5" s="124" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D5" s="125" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" ht="54.75" customHeight="1">
       <c r="B6" s="123" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C6" s="124" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D6" s="125" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="7" ht="31.5" customHeight="1">
       <c r="B7" s="123" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C7" s="124" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D7" s="125" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" ht="75.75" customHeight="1">
       <c r="B8" s="126" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C8" s="127" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D8" s="125" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="B9" s="126" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C9" s="127" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D9" s="125" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" ht="64.5" customHeight="1">
       <c r="B10" s="128" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C10" s="129" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D10" s="125" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11" ht="60.0" customHeight="1">
       <c r="B11" s="128" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C11" s="129" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D11" s="125" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" ht="82.5" customHeight="1">
       <c r="B12" s="130" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C12" s="131" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D12" s="125" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" ht="67.5" customHeight="1">
       <c r="B13" s="130" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C13" s="131" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D13" s="125" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" ht="81.75" customHeight="1">
       <c r="B14" s="132" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C14" s="133" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D14" s="125" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" ht="72.0" customHeight="1">
       <c r="B15" s="134" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C15" s="135" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D15" s="125" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" ht="61.5" customHeight="1">
       <c r="B16" s="128" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C16" s="129" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D16" s="125" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" ht="67.5" customHeight="1">
       <c r="B17" s="134" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C17" s="135" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D17" s="125" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" ht="66.75" customHeight="1">
       <c r="B18" s="130" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C18" s="131" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D18" s="125" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" ht="19.5" customHeight="1">
       <c r="B20" s="136" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="44"/>
@@ -10233,10 +10270,10 @@
         <v>70</v>
       </c>
       <c r="C21" s="137" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D21" s="137" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1">
@@ -10244,10 +10281,10 @@
         <v>38</v>
       </c>
       <c r="C22" s="139" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D22" s="140" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1">
@@ -10255,10 +10292,10 @@
         <v>26</v>
       </c>
       <c r="C23" s="139" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D23" s="140" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1">
@@ -10266,10 +10303,10 @@
         <v>83</v>
       </c>
       <c r="C24" s="142" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D24" s="140" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1">
@@ -10277,10 +10314,10 @@
         <v>85</v>
       </c>
       <c r="C25" s="139" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D25" s="140" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1">
@@ -10288,10 +10325,10 @@
         <v>35</v>
       </c>
       <c r="C26" s="144" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D26" s="140" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1">
@@ -10299,10 +10336,10 @@
         <v>90</v>
       </c>
       <c r="C27" s="146" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D27" s="140" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1">
@@ -10310,10 +10347,10 @@
         <v>49</v>
       </c>
       <c r="C28" s="139" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D28" s="140" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1">
@@ -10321,10 +10358,10 @@
         <v>47</v>
       </c>
       <c r="C29" s="139" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D29" s="140" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1">
@@ -10332,10 +10369,10 @@
         <v>19</v>
       </c>
       <c r="C30" s="144" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D30" s="140" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1">
@@ -10343,10 +10380,10 @@
         <v>43</v>
       </c>
       <c r="C31" s="144" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D31" s="140" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" ht="16.5" customHeight="1">
@@ -10354,10 +10391,10 @@
         <v>115</v>
       </c>
       <c r="C32" s="148" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D32" s="140" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1">
@@ -10365,10 +10402,10 @@
         <v>23</v>
       </c>
       <c r="C33" s="139" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D33" s="140" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -11360,10 +11397,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="149" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B1" s="149" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C1" s="149" t="s">
         <v>136</v>
@@ -11376,7 +11413,7 @@
         <v>46165.0</v>
       </c>
       <c r="B2" s="149" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C2" s="151">
         <v>10000.0</v>
@@ -11389,7 +11426,7 @@
         <v>46166.0</v>
       </c>
       <c r="B3" s="149" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C3" s="151">
         <v>19000.0</v>
@@ -11402,7 +11439,7 @@
         <v>46168.0</v>
       </c>
       <c r="B4" s="149" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C4" s="152">
         <v>2500.0</v>
@@ -11415,7 +11452,7 @@
         <v>46169.0</v>
       </c>
       <c r="B5" s="149" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C5" s="151">
         <v>29050.0</v>
@@ -11428,7 +11465,7 @@
         <v>46169.0</v>
       </c>
       <c r="B6" s="149" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C6" s="152">
         <v>100.0</v>
@@ -11441,7 +11478,7 @@
         <v>46169.0</v>
       </c>
       <c r="B7" s="149" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C7" s="152">
         <v>300.0</v>
@@ -11454,7 +11491,7 @@
         <v>46169.0</v>
       </c>
       <c r="B8" s="149" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C8" s="152">
         <v>370.0</v>
@@ -11480,7 +11517,7 @@
         <v>46169.0</v>
       </c>
       <c r="B10" s="149" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C10" s="152">
         <v>5000.0</v>
@@ -11493,13 +11530,13 @@
         <v>46169.0</v>
       </c>
       <c r="B11" s="149" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C11" s="151">
         <v>29000.0</v>
       </c>
       <c r="D11" s="149" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E11" s="152">
         <v>24000.0</v>
@@ -11510,13 +11547,13 @@
         <v>46169.0</v>
       </c>
       <c r="B12" s="149" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C12" s="152">
         <v>400.0</v>
       </c>
       <c r="D12" s="149" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E12" s="151">
         <v>53000.0</v>
@@ -11527,7 +11564,7 @@
         <v>46169.0</v>
       </c>
       <c r="B13" s="149" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C13" s="152">
         <v>600.0</v>
@@ -11546,30 +11583,30 @@
     </row>
     <row r="22">
       <c r="A22" s="149" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B22" s="149" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C22" s="149" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D22" s="149" t="s">
         <v>136</v>
       </c>
       <c r="E22" s="149" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="149" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B23" s="149" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C23" s="149" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D23" s="152">
         <v>3150.0</v>
@@ -11580,13 +11617,13 @@
     </row>
     <row r="24">
       <c r="A24" s="149" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B24" s="149" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C24" s="149" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D24" s="152">
         <v>2650.0</v>
@@ -11597,13 +11634,13 @@
     </row>
     <row r="25">
       <c r="A25" s="149" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B25" s="149" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C25" s="149" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D25" s="152">
         <v>2600.0</v>
@@ -11614,13 +11651,13 @@
     </row>
     <row r="26">
       <c r="A26" s="149" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B26" s="149" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C26" s="149" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="D26" s="152">
         <v>2680.0</v>
@@ -11634,10 +11671,10 @@
         <v>168</v>
       </c>
       <c r="B27" s="149" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C27" s="149" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D27" s="152">
         <v>5390.0</v>
@@ -11651,10 +11688,10 @@
         <v>168</v>
       </c>
       <c r="B28" s="149" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="149" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D28" s="152">
         <v>3235.0</v>
@@ -11668,62 +11705,62 @@
         <v>168</v>
       </c>
       <c r="B29" s="149" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C29" s="149" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D29" s="152">
         <v>1230.0</v>
       </c>
       <c r="E29" s="149" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="149" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B30" s="149"/>
       <c r="C30" s="149" t="s">
-        <v>284</v>
-      </c>
-      <c r="D30" s="152">
-        <v>2960.0</v>
+        <v>286</v>
+      </c>
+      <c r="D30" s="155">
+        <v>2970.0</v>
       </c>
       <c r="E30" s="149"/>
     </row>
     <row r="31">
       <c r="A31" s="149" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B31" s="149"/>
       <c r="C31" s="149" t="s">
-        <v>289</v>
-      </c>
-      <c r="D31" s="152">
-        <v>2960.0</v>
+        <v>291</v>
+      </c>
+      <c r="D31" s="155">
+        <v>2970.0</v>
       </c>
       <c r="E31" s="149"/>
     </row>
     <row r="32">
       <c r="A32" s="149" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B32" s="149" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C32" s="149"/>
       <c r="D32" s="152">
         <v>5000.0</v>
       </c>
       <c r="E32" s="149" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="155" t="s">
-        <v>297</v>
+      <c r="A42" s="156" t="s">
+        <v>299</v>
       </c>
       <c r="B42" s="149"/>
       <c r="C42" s="149"/>
@@ -11760,308 +11797,308 @@
       <c r="J44" s="149"/>
     </row>
     <row r="45">
-      <c r="A45" s="156" t="s">
+      <c r="A45" s="157" t="s">
         <v>6</v>
       </c>
-      <c r="B45" s="156" t="s">
-        <v>298</v>
-      </c>
-      <c r="C45" s="156" t="s">
-        <v>299</v>
-      </c>
-      <c r="D45" s="156" t="s">
+      <c r="B45" s="157" t="s">
+        <v>300</v>
+      </c>
+      <c r="C45" s="157" t="s">
+        <v>301</v>
+      </c>
+      <c r="D45" s="157" t="s">
         <v>77</v>
       </c>
-      <c r="E45" s="156" t="s">
-        <v>300</v>
-      </c>
-      <c r="F45" s="156" t="s">
-        <v>301</v>
-      </c>
-      <c r="G45" s="156" t="s">
+      <c r="E45" s="157" t="s">
         <v>302</v>
       </c>
-      <c r="H45" s="156" t="s">
+      <c r="F45" s="157" t="s">
         <v>303</v>
       </c>
-      <c r="I45" s="156" t="s">
+      <c r="G45" s="157" t="s">
         <v>304</v>
       </c>
-      <c r="J45" s="156" t="s">
+      <c r="H45" s="157" t="s">
         <v>305</v>
       </c>
+      <c r="I45" s="157" t="s">
+        <v>306</v>
+      </c>
+      <c r="J45" s="157" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="157" t="s">
-        <v>306</v>
-      </c>
-      <c r="B46" s="158">
+      <c r="A46" s="158" t="s">
+        <v>308</v>
+      </c>
+      <c r="B46" s="159">
         <v>1000000.0</v>
       </c>
-      <c r="C46" s="159">
+      <c r="C46" s="160">
         <v>0.2</v>
       </c>
-      <c r="D46" s="158">
+      <c r="D46" s="159">
         <f>IF(AND(B46&lt;&gt;"", C46&lt;&gt;"", E46&lt;&gt;""), PMT(C46/12, E46, -B46), "")</f>
         <v>26493.88371</v>
       </c>
-      <c r="E46" s="160">
+      <c r="E46" s="161">
         <v>60.0</v>
       </c>
-      <c r="F46" s="160">
+      <c r="F46" s="161">
         <v>0.0</v>
       </c>
-      <c r="G46" s="160">
+      <c r="G46" s="161">
         <f t="shared" ref="G46:G52" si="1">IF(E46="", "", E46 - F46)</f>
         <v>60</v>
       </c>
-      <c r="H46" s="158">
+      <c r="H46" s="159">
         <f t="shared" ref="H46:H52" si="2">IF(D46="", "", D46 * F46)</f>
         <v>0</v>
       </c>
-      <c r="I46" s="158">
+      <c r="I46" s="159">
         <f t="shared" ref="I46:I52" si="3">IF(G46="", "", IFERROR(PV(C46/12, G46, -D46), ""))</f>
         <v>1000000</v>
       </c>
-      <c r="J46" s="161">
+      <c r="J46" s="162">
         <f t="shared" ref="J46:J52" si="4">IF(AND(D46&lt;&gt;"", E46&lt;&gt;""), (D46 * E46) - B46, "")</f>
         <v>589633.0229</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="162" t="s">
-        <v>307</v>
-      </c>
-      <c r="B47" s="163">
+      <c r="A47" s="163" t="s">
+        <v>309</v>
+      </c>
+      <c r="B47" s="164">
         <v>596000.0</v>
       </c>
-      <c r="C47" s="164">
+      <c r="C47" s="165">
         <v>0.126</v>
       </c>
-      <c r="D47" s="163">
+      <c r="D47" s="164">
         <f>IF(AND(B47&lt;&gt;"", C47&lt;&gt;"", E47&lt;&gt;""), PMT(C47/12, E47, -B47), 11839)</f>
         <v>11838.71102</v>
       </c>
-      <c r="E47" s="165">
+      <c r="E47" s="166">
         <v>72.0</v>
       </c>
-      <c r="F47" s="165">
+      <c r="F47" s="166">
         <v>52.0</v>
       </c>
-      <c r="G47" s="165">
+      <c r="G47" s="166">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="H47" s="163">
+      <c r="H47" s="164">
         <f t="shared" si="2"/>
         <v>615612.9729</v>
       </c>
-      <c r="I47" s="163">
+      <c r="I47" s="164">
         <f t="shared" si="3"/>
         <v>212564.401</v>
       </c>
-      <c r="J47" s="166">
+      <c r="J47" s="167">
         <f t="shared" si="4"/>
         <v>256387.1932</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="157" t="s">
-        <v>308</v>
-      </c>
-      <c r="B48" s="167"/>
-      <c r="C48" s="168"/>
-      <c r="D48" s="158">
+      <c r="A48" s="158" t="s">
+        <v>310</v>
+      </c>
+      <c r="B48" s="168"/>
+      <c r="C48" s="169"/>
+      <c r="D48" s="159">
         <f>IF(AND(B48&lt;&gt;"", C48&lt;&gt;"", E48&lt;&gt;""), PMT(C48/12, E48, -B48), 15250)</f>
         <v>15250</v>
       </c>
-      <c r="E48" s="169"/>
-      <c r="F48" s="160">
+      <c r="E48" s="170"/>
+      <c r="F48" s="161">
         <v>0.0</v>
       </c>
-      <c r="G48" s="169" t="str">
+      <c r="G48" s="170" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H48" s="158">
+      <c r="H48" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I48" s="167" t="str">
+      <c r="I48" s="168" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J48" s="170" t="str">
+      <c r="J48" s="171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="162" t="s">
+      <c r="A49" s="163" t="s">
         <v>25</v>
       </c>
-      <c r="B49" s="163">
+      <c r="B49" s="164">
         <v>97110.0</v>
       </c>
-      <c r="C49" s="171"/>
-      <c r="D49" s="163">
+      <c r="C49" s="172"/>
+      <c r="D49" s="164">
         <f>IF(AND(B49&lt;&gt;"", C49&lt;&gt;"", E49&lt;&gt;""), PMT(C49/12, E49, -B49), 18972)</f>
         <v>18972</v>
       </c>
-      <c r="E49" s="172"/>
-      <c r="F49" s="165">
+      <c r="E49" s="173"/>
+      <c r="F49" s="166">
         <v>0.0</v>
       </c>
-      <c r="G49" s="172" t="str">
+      <c r="G49" s="173" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H49" s="163">
+      <c r="H49" s="164">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I49" s="173" t="str">
+      <c r="I49" s="174" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J49" s="174" t="str">
+      <c r="J49" s="175" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="157" t="s">
-        <v>309</v>
-      </c>
-      <c r="B50" s="158">
+      <c r="A50" s="158" t="s">
+        <v>311</v>
+      </c>
+      <c r="B50" s="159">
         <v>83419.0</v>
       </c>
-      <c r="C50" s="159">
+      <c r="C50" s="160">
         <v>0.12</v>
       </c>
-      <c r="D50" s="158">
+      <c r="D50" s="159">
         <f t="shared" ref="D50:D51" si="5">IF(AND(B50&lt;&gt;"", C50&lt;&gt;"", E50&lt;&gt;""), PMT(C50/12, E50, -B50), 4627)</f>
         <v>5087.061453</v>
       </c>
-      <c r="E50" s="160">
+      <c r="E50" s="161">
         <v>18.0</v>
       </c>
-      <c r="F50" s="160">
+      <c r="F50" s="161">
         <v>3.0</v>
       </c>
-      <c r="G50" s="160">
+      <c r="G50" s="161">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H50" s="158">
+      <c r="H50" s="159">
         <f t="shared" si="2"/>
         <v>15261.18436</v>
       </c>
-      <c r="I50" s="158">
+      <c r="I50" s="159">
         <f t="shared" si="3"/>
         <v>70532.37421</v>
       </c>
-      <c r="J50" s="161">
+      <c r="J50" s="162">
         <f t="shared" si="4"/>
         <v>8148.106161</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="175" t="s">
-        <v>310</v>
-      </c>
-      <c r="B51" s="176">
+      <c r="A51" s="176" t="s">
+        <v>312</v>
+      </c>
+      <c r="B51" s="177">
         <v>149100.0</v>
       </c>
-      <c r="C51" s="177">
+      <c r="C51" s="178">
         <v>0.1</v>
       </c>
-      <c r="D51" s="176">
+      <c r="D51" s="177">
         <f t="shared" si="5"/>
         <v>5637.681256</v>
       </c>
-      <c r="E51" s="178">
+      <c r="E51" s="179">
         <v>30.0</v>
       </c>
-      <c r="F51" s="178">
+      <c r="F51" s="179">
         <v>15.0</v>
       </c>
-      <c r="G51" s="178">
+      <c r="G51" s="179">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="H51" s="176">
+      <c r="H51" s="177">
         <f t="shared" si="2"/>
         <v>84565.21884</v>
       </c>
-      <c r="I51" s="176">
+      <c r="I51" s="177">
         <f t="shared" si="3"/>
         <v>79184.0856</v>
       </c>
-      <c r="J51" s="179">
+      <c r="J51" s="180">
         <f t="shared" si="4"/>
         <v>20030.43769</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="157" t="s">
-        <v>311</v>
-      </c>
-      <c r="B52" s="167"/>
-      <c r="C52" s="168"/>
-      <c r="D52" s="158">
+      <c r="A52" s="158" t="s">
+        <v>313</v>
+      </c>
+      <c r="B52" s="168"/>
+      <c r="C52" s="169"/>
+      <c r="D52" s="159">
         <f>IF(AND(B52&lt;&gt;"", C52&lt;&gt;"", E52&lt;&gt;""), PMT(C52/12, E52, -B52), 3850)</f>
         <v>3850</v>
       </c>
-      <c r="E52" s="169"/>
-      <c r="F52" s="160">
+      <c r="E52" s="170"/>
+      <c r="F52" s="161">
         <v>0.0</v>
       </c>
-      <c r="G52" s="169" t="str">
+      <c r="G52" s="170" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="H52" s="158">
+      <c r="H52" s="159">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I52" s="167" t="str">
+      <c r="I52" s="168" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="J52" s="170" t="str">
+      <c r="J52" s="171" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="180" t="s">
-        <v>264</v>
-      </c>
-      <c r="B61" s="180" t="s">
-        <v>312</v>
-      </c>
-      <c r="C61" s="180" t="s">
+      <c r="A61" s="181" t="s">
+        <v>266</v>
+      </c>
+      <c r="B61" s="181" t="s">
+        <v>314</v>
+      </c>
+      <c r="C61" s="181" t="s">
         <v>136</v>
       </c>
-      <c r="D61" s="180" t="s">
-        <v>313</v>
-      </c>
-      <c r="E61" s="180" t="s">
-        <v>314</v>
-      </c>
-      <c r="F61" s="180" t="s">
+      <c r="D61" s="181" t="s">
         <v>315</v>
       </c>
-      <c r="G61" s="180" t="s">
+      <c r="E61" s="181" t="s">
+        <v>316</v>
+      </c>
+      <c r="F61" s="181" t="s">
+        <v>317</v>
+      </c>
+      <c r="G61" s="181" t="s">
         <v>136</v>
       </c>
       <c r="H61" s="149"/>
-      <c r="I61" s="180" t="s">
-        <v>316</v>
+      <c r="I61" s="181" t="s">
+        <v>318</v>
       </c>
       <c r="J61" s="149" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62">
@@ -12069,28 +12106,28 @@
         <v>46143.0</v>
       </c>
       <c r="B62" s="149" t="s">
-        <v>318</v>
-      </c>
-      <c r="C62" s="181">
+        <v>320</v>
+      </c>
+      <c r="C62" s="182">
         <v>11839.0</v>
       </c>
-      <c r="D62" s="182" t="b">
+      <c r="D62" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E62" s="149" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F62" s="149" t="s">
-        <v>320</v>
-      </c>
-      <c r="G62" s="181">
+        <v>322</v>
+      </c>
+      <c r="G62" s="182">
         <v>71000.0</v>
       </c>
       <c r="H62" s="149"/>
-      <c r="I62" s="180" t="s">
-        <v>321</v>
-      </c>
-      <c r="J62" s="181">
+      <c r="I62" s="181" t="s">
+        <v>323</v>
+      </c>
+      <c r="J62" s="182">
         <f>SUM(C62:C1000)</f>
         <v>84657</v>
       </c>
@@ -12100,24 +12137,24 @@
         <v>46144.0</v>
       </c>
       <c r="B63" s="149" t="s">
-        <v>322</v>
-      </c>
-      <c r="C63" s="181">
+        <v>324</v>
+      </c>
+      <c r="C63" s="182">
         <v>3850.0</v>
       </c>
-      <c r="D63" s="182" t="b">
+      <c r="D63" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E63" s="149" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F63" s="149"/>
-      <c r="G63" s="183"/>
+      <c r="G63" s="184"/>
       <c r="H63" s="149"/>
-      <c r="I63" s="180" t="s">
-        <v>303</v>
-      </c>
-      <c r="J63" s="181">
+      <c r="I63" s="181" t="s">
+        <v>305</v>
+      </c>
+      <c r="J63" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, TRUE)</f>
         <v>50435</v>
       </c>
@@ -12127,22 +12164,22 @@
         <v>46145.0</v>
       </c>
       <c r="B64" s="149" t="s">
-        <v>324</v>
-      </c>
-      <c r="C64" s="181">
+        <v>326</v>
+      </c>
+      <c r="C64" s="182">
         <v>4627.0</v>
       </c>
-      <c r="D64" s="182" t="b">
+      <c r="D64" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E64" s="149"/>
       <c r="F64" s="149"/>
-      <c r="G64" s="183"/>
+      <c r="G64" s="184"/>
       <c r="H64" s="149"/>
-      <c r="I64" s="180" t="s">
-        <v>325</v>
-      </c>
-      <c r="J64" s="181">
+      <c r="I64" s="181" t="s">
+        <v>327</v>
+      </c>
+      <c r="J64" s="182">
         <f>SUMIFS(C62:C1000, D62:D1000, FALSE)</f>
         <v>34222</v>
       </c>
@@ -12152,22 +12189,22 @@
         <v>46147.0</v>
       </c>
       <c r="B65" s="149" t="s">
-        <v>326</v>
-      </c>
-      <c r="C65" s="181">
+        <v>328</v>
+      </c>
+      <c r="C65" s="182">
         <v>5000.0</v>
       </c>
-      <c r="D65" s="182" t="b">
+      <c r="D65" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E65" s="149"/>
       <c r="F65" s="149"/>
-      <c r="G65" s="183"/>
+      <c r="G65" s="184"/>
       <c r="H65" s="149"/>
-      <c r="I65" s="180" t="s">
-        <v>327</v>
-      </c>
-      <c r="J65" s="181">
+      <c r="I65" s="181" t="s">
+        <v>329</v>
+      </c>
+      <c r="J65" s="182">
         <f>SUM(G62:G1000)</f>
         <v>71000</v>
       </c>
@@ -12177,24 +12214,24 @@
         <v>46167.0</v>
       </c>
       <c r="B66" s="149" t="s">
-        <v>328</v>
-      </c>
-      <c r="C66" s="181">
+        <v>330</v>
+      </c>
+      <c r="C66" s="182">
         <v>18972.0</v>
       </c>
-      <c r="D66" s="182" t="b">
+      <c r="D66" s="183" t="b">
         <v>0</v>
       </c>
-      <c r="E66" s="184">
+      <c r="E66" s="185">
         <v>97110.0</v>
       </c>
       <c r="F66" s="149"/>
-      <c r="G66" s="183"/>
+      <c r="G66" s="184"/>
       <c r="H66" s="149"/>
-      <c r="I66" s="180" t="s">
-        <v>329</v>
-      </c>
-      <c r="J66" s="181">
+      <c r="I66" s="181" t="s">
+        <v>331</v>
+      </c>
+      <c r="J66" s="182">
         <f>J65-J62</f>
         <v>-13657</v>
       </c>
@@ -12204,19 +12241,19 @@
         <v>46146.0</v>
       </c>
       <c r="B67" s="149" t="s">
-        <v>330</v>
-      </c>
-      <c r="C67" s="181">
+        <v>332</v>
+      </c>
+      <c r="C67" s="182">
         <v>13625.0</v>
       </c>
-      <c r="D67" s="182" t="b">
+      <c r="D67" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E67" s="149" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F67" s="149"/>
-      <c r="G67" s="183"/>
+      <c r="G67" s="184"/>
       <c r="H67" s="149"/>
       <c r="I67" s="149"/>
       <c r="J67" s="149"/>
@@ -12226,17 +12263,17 @@
         <v>46145.0</v>
       </c>
       <c r="B68" s="149" t="s">
-        <v>332</v>
-      </c>
-      <c r="C68" s="181">
+        <v>334</v>
+      </c>
+      <c r="C68" s="182">
         <v>2494.0</v>
       </c>
-      <c r="D68" s="182" t="b">
+      <c r="D68" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E68" s="149"/>
       <c r="F68" s="149"/>
-      <c r="G68" s="183"/>
+      <c r="G68" s="184"/>
       <c r="H68" s="149"/>
       <c r="I68" s="149"/>
       <c r="J68" s="149"/>
@@ -12246,17 +12283,17 @@
         <v>46144.0</v>
       </c>
       <c r="B69" s="149" t="s">
-        <v>333</v>
-      </c>
-      <c r="C69" s="181">
+        <v>335</v>
+      </c>
+      <c r="C69" s="182">
         <v>4500.0</v>
       </c>
-      <c r="D69" s="182" t="b">
+      <c r="D69" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E69" s="149"/>
       <c r="F69" s="149"/>
-      <c r="G69" s="183"/>
+      <c r="G69" s="184"/>
       <c r="H69" s="149"/>
       <c r="I69" s="149"/>
       <c r="J69" s="149"/>
@@ -12266,17 +12303,17 @@
         <v>46152.0</v>
       </c>
       <c r="B70" s="149" t="s">
-        <v>334</v>
-      </c>
-      <c r="C70" s="181">
+        <v>336</v>
+      </c>
+      <c r="C70" s="182">
         <v>1500.0</v>
       </c>
-      <c r="D70" s="182" t="b">
+      <c r="D70" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E70" s="149"/>
       <c r="F70" s="149"/>
-      <c r="G70" s="183"/>
+      <c r="G70" s="184"/>
       <c r="H70" s="149"/>
       <c r="I70" s="149"/>
       <c r="J70" s="149"/>
@@ -12286,17 +12323,17 @@
         <v>46152.0</v>
       </c>
       <c r="B71" s="149" t="s">
-        <v>335</v>
-      </c>
-      <c r="C71" s="181">
+        <v>337</v>
+      </c>
+      <c r="C71" s="182">
         <v>3000.0</v>
       </c>
-      <c r="D71" s="182" t="b">
+      <c r="D71" s="183" t="b">
         <v>1</v>
       </c>
       <c r="E71" s="149"/>
       <c r="F71" s="149"/>
-      <c r="G71" s="183"/>
+      <c r="G71" s="184"/>
       <c r="H71" s="149"/>
       <c r="I71" s="149"/>
       <c r="J71" s="149"/>
@@ -12306,17 +12343,17 @@
         <v>46157.0</v>
       </c>
       <c r="B72" s="149" t="s">
-        <v>336</v>
-      </c>
-      <c r="C72" s="181">
+        <v>338</v>
+      </c>
+      <c r="C72" s="182">
         <v>15250.0</v>
       </c>
-      <c r="D72" s="182" t="b">
+      <c r="D72" s="183" t="b">
         <v>0</v>
       </c>
       <c r="E72" s="149"/>
       <c r="F72" s="149"/>
-      <c r="G72" s="183"/>
+      <c r="G72" s="184"/>
       <c r="H72" s="149"/>
       <c r="I72" s="149"/>
       <c r="J72" s="149"/>
@@ -12327,4 +12364,36 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="26.71"/>
+    <col customWidth="1" min="2" max="2" width="39.57"/>
+    <col customWidth="1" min="3" max="3" width="19.71"/>
+    <col customWidth="1" min="4" max="4" width="41.57"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="186" t="s">
+        <v>70</v>
+      </c>
+      <c r="B1" s="186" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1" s="186" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1" s="186" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23482.87233</v>
+        <v>23600.87671</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15279.0411</v>
+        <v>15341.91781</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3452.054795</v>
+        <v>3538.356164</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23600.87671</v>
+        <v>23718.8811</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15341.91781</v>
+        <v>15404.79452</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3538.356164</v>
+        <v>3624.657534</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23718.8811</v>
+        <v>23836.88548</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15404.79452</v>
+        <v>15467.67123</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3624.657534</v>
+        <v>3710.958904</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23836.88548</v>
+        <v>23954.88986</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15467.67123</v>
+        <v>15530.54795</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3710.958904</v>
+        <v>3797.260274</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>23954.88986</v>
+        <v>24072.89425</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15530.54795</v>
+        <v>15593.42466</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3797.260274</v>
+        <v>3883.561644</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24072.89425</v>
+        <v>24190.89863</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15593.42466</v>
+        <v>15656.30137</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3883.561644</v>
+        <v>3969.863014</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24190.89863</v>
+        <v>24308.90301</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15656.30137</v>
+        <v>15719.17808</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>3969.863014</v>
+        <v>4056.164384</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24308.90301</v>
+        <v>24426.9074</v>
       </c>
     </row>
     <row r="6">
@@ -8943,7 +8943,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15719.17808</v>
+        <v>15782.05479</v>
       </c>
     </row>
     <row r="7">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4056.164384</v>
+        <v>4142.465753</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="350">
   <si>
     <t>Family Loan Master Sheet</t>
   </si>
@@ -1046,13 +1046,40 @@
   </si>
   <si>
     <t xml:space="preserve">Amount </t>
+  </si>
+  <si>
+    <t>20,000 from Naresh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excel EMI </t>
+  </si>
+  <si>
+    <t>Balance-4k Appa</t>
+  </si>
+  <si>
+    <t>13-07-2026</t>
+  </si>
+  <si>
+    <t>Equitas Home Loan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50,000 from Naresh </t>
+  </si>
+  <si>
+    <t>14-07-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">வார தண்டல் </t>
+  </si>
+  <si>
+    <t>Balance 32,500</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="&quot;₹&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;#,##0;\(&quot;₹&quot;#,##0\);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="₹#,##0"/>
@@ -1063,6 +1090,7 @@
     <numFmt numFmtId="171" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="172" formatCode="d mmm yyyy"/>
     <numFmt numFmtId="173" formatCode="d mmmm yyyy"/>
+    <numFmt numFmtId="174" formatCode="mm-dd-yyyy"/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -1443,7 +1471,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="187">
+  <cellXfs count="192">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1951,7 +1979,22 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="20" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="20" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="174" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -12381,17 +12424,3058 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="186" t="s">
-        <v>70</v>
-      </c>
-      <c r="B1" s="186" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="187" t="s">
         <v>339</v>
       </c>
-      <c r="C1" s="186" t="s">
+      <c r="C1" s="187" t="s">
         <v>340</v>
       </c>
-      <c r="D1" s="186" t="s">
+      <c r="D1" s="187" t="s">
         <v>12</v>
       </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="188">
+        <v>46060.0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="189">
+        <v>12000.0</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="188">
+        <v>46060.0</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="9">
+        <v>4600.0</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="190" t="s">
+        <v>344</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="189">
+        <v>15500.0</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="190" t="s">
+        <v>347</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2000.0</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="191"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="191"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="191"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="191"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="191"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="191"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="191"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="191"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="191"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="191"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="191"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="191"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="191"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="191"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="191"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="191"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="191"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="191"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="191"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="191"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="191"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="191"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="191"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="191"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="191"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="191"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="191"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="191"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="191"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="191"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="191"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="191"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="191"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="191"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="191"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="191"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="191"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="191"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="191"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="191"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="191"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="191"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="191"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="191"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="191"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="191"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="191"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="191"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="191"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="191"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="191"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="191"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="191"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="191"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="191"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="191"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="191"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="191"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="191"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="191"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="191"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="191"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="191"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="191"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="191"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="191"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="191"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="191"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="191"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="191"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="191"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="191"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="191"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="191"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="191"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="191"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="191"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="191"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="191"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="191"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="191"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="191"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="191"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="191"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="191"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="191"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="191"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="191"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="191"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="191"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="191"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="191"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="191"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="191"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="191"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="191"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="191"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="191"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="191"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="191"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="191"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="191"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="191"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="191"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="191"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="191"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="191"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="191"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="191"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="191"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="191"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="191"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="191"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="191"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="191"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="191"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="191"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="191"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="191"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="191"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="191"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="191"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="191"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="191"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="191"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="191"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="191"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="191"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="191"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="191"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="191"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="191"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="191"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="191"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="191"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="191"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="191"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="191"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="191"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="191"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="191"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="191"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="191"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="191"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="191"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="191"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="191"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="191"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="191"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="191"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="191"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="191"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="191"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="191"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="191"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="191"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="191"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="191"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="191"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="191"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="191"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="191"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="191"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="191"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="191"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="191"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="191"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="191"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="191"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="191"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="191"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="191"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="191"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="191"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="191"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="191"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="191"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="191"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="191"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="191"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="191"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="191"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="191"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="191"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="191"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="191"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="191"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="191"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="191"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="191"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="191"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="191"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="191"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="191"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="191"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="191"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="191"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="191"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="191"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="191"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="191"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="191"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="191"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="191"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="191"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="191"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="191"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="191"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="191"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="191"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="191"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="191"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="191"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="191"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="191"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="191"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="191"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="191"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="191"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="191"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="191"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="191"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="191"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="191"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="191"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="191"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="191"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="191"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="191"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="191"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="191"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="191"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="191"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="191"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="191"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="191"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="191"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="191"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="191"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="191"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="191"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="191"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="191"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="191"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="191"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="191"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="191"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="191"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="191"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="191"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="191"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="191"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="191"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="191"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="191"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="191"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="191"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="191"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="191"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="191"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="191"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="191"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="191"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="191"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="191"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="191"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="191"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="191"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="191"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="191"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="191"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="191"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="191"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="191"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="191"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="191"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="191"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="191"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="191"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="191"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="191"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="191"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="191"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="191"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="191"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="191"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="191"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="191"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="191"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="191"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="191"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="191"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="191"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="191"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="191"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="191"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="191"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="191"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="191"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="191"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="191"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="191"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="191"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="191"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="191"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="191"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="191"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="191"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="191"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="191"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="191"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="191"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="191"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="191"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="191"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="191"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="191"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="191"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="191"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="191"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="191"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="191"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="191"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="191"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="191"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="191"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="191"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="191"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="191"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="191"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="191"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="191"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="191"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="191"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="191"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="191"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="191"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="191"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="191"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="191"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="191"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="191"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="191"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="191"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="191"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="191"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="191"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="191"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="191"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="191"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="191"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="191"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="191"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="191"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="191"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="191"/>
+    </row>
+    <row r="362">
+      <c r="A362" s="191"/>
+    </row>
+    <row r="363">
+      <c r="A363" s="191"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="191"/>
+    </row>
+    <row r="365">
+      <c r="A365" s="191"/>
+    </row>
+    <row r="366">
+      <c r="A366" s="191"/>
+    </row>
+    <row r="367">
+      <c r="A367" s="191"/>
+    </row>
+    <row r="368">
+      <c r="A368" s="191"/>
+    </row>
+    <row r="369">
+      <c r="A369" s="191"/>
+    </row>
+    <row r="370">
+      <c r="A370" s="191"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="191"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="191"/>
+    </row>
+    <row r="373">
+      <c r="A373" s="191"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="191"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="191"/>
+    </row>
+    <row r="376">
+      <c r="A376" s="191"/>
+    </row>
+    <row r="377">
+      <c r="A377" s="191"/>
+    </row>
+    <row r="378">
+      <c r="A378" s="191"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="191"/>
+    </row>
+    <row r="380">
+      <c r="A380" s="191"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="191"/>
+    </row>
+    <row r="382">
+      <c r="A382" s="191"/>
+    </row>
+    <row r="383">
+      <c r="A383" s="191"/>
+    </row>
+    <row r="384">
+      <c r="A384" s="191"/>
+    </row>
+    <row r="385">
+      <c r="A385" s="191"/>
+    </row>
+    <row r="386">
+      <c r="A386" s="191"/>
+    </row>
+    <row r="387">
+      <c r="A387" s="191"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="191"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="191"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="191"/>
+    </row>
+    <row r="391">
+      <c r="A391" s="191"/>
+    </row>
+    <row r="392">
+      <c r="A392" s="191"/>
+    </row>
+    <row r="393">
+      <c r="A393" s="191"/>
+    </row>
+    <row r="394">
+      <c r="A394" s="191"/>
+    </row>
+    <row r="395">
+      <c r="A395" s="191"/>
+    </row>
+    <row r="396">
+      <c r="A396" s="191"/>
+    </row>
+    <row r="397">
+      <c r="A397" s="191"/>
+    </row>
+    <row r="398">
+      <c r="A398" s="191"/>
+    </row>
+    <row r="399">
+      <c r="A399" s="191"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="191"/>
+    </row>
+    <row r="401">
+      <c r="A401" s="191"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="191"/>
+    </row>
+    <row r="403">
+      <c r="A403" s="191"/>
+    </row>
+    <row r="404">
+      <c r="A404" s="191"/>
+    </row>
+    <row r="405">
+      <c r="A405" s="191"/>
+    </row>
+    <row r="406">
+      <c r="A406" s="191"/>
+    </row>
+    <row r="407">
+      <c r="A407" s="191"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="191"/>
+    </row>
+    <row r="409">
+      <c r="A409" s="191"/>
+    </row>
+    <row r="410">
+      <c r="A410" s="191"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="191"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="191"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="191"/>
+    </row>
+    <row r="414">
+      <c r="A414" s="191"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="191"/>
+    </row>
+    <row r="416">
+      <c r="A416" s="191"/>
+    </row>
+    <row r="417">
+      <c r="A417" s="191"/>
+    </row>
+    <row r="418">
+      <c r="A418" s="191"/>
+    </row>
+    <row r="419">
+      <c r="A419" s="191"/>
+    </row>
+    <row r="420">
+      <c r="A420" s="191"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="191"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="191"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="191"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="191"/>
+    </row>
+    <row r="425">
+      <c r="A425" s="191"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="191"/>
+    </row>
+    <row r="427">
+      <c r="A427" s="191"/>
+    </row>
+    <row r="428">
+      <c r="A428" s="191"/>
+    </row>
+    <row r="429">
+      <c r="A429" s="191"/>
+    </row>
+    <row r="430">
+      <c r="A430" s="191"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="191"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="191"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="191"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="191"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="191"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="191"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="191"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="191"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="191"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="191"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="191"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="191"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="191"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="191"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="191"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="191"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="191"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="191"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="191"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="191"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="191"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="191"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="191"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="191"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="191"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="191"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="191"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="191"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="191"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="191"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="191"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="191"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="191"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="191"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="191"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="191"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="191"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="191"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="191"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="191"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="191"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="191"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="191"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="191"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="191"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="191"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="191"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="191"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="191"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="191"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="191"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="191"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="191"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="191"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="191"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="191"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="191"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="191"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="191"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="191"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="191"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="191"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="191"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="191"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="191"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="191"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="191"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="191"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="191"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="191"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="191"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="191"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="191"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="191"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="191"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="191"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="191"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="191"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="191"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="191"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="191"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="191"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="191"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="191"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="191"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="191"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="191"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="191"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="191"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="191"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="191"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="191"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="191"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="191"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="191"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="191"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="191"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="191"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="191"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="191"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="191"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="191"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="191"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="191"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="191"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="191"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="191"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="191"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="191"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="191"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="191"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="191"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="191"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="191"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="191"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="191"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="191"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="191"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="191"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="191"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="191"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="191"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="191"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="191"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="191"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="191"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="191"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="191"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="191"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="191"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="191"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="191"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="191"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="191"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="191"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="191"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="191"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="191"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="191"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="191"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="191"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="191"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="191"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="191"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="191"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="191"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="191"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="191"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="191"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="191"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="191"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="191"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="191"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="191"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="191"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="191"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="191"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="191"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="191"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="191"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="191"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="191"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="191"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="191"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="191"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="191"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="191"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="191"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="191"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="191"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="191"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="191"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="191"/>
+    </row>
+    <row r="604">
+      <c r="A604" s="191"/>
+    </row>
+    <row r="605">
+      <c r="A605" s="191"/>
+    </row>
+    <row r="606">
+      <c r="A606" s="191"/>
+    </row>
+    <row r="607">
+      <c r="A607" s="191"/>
+    </row>
+    <row r="608">
+      <c r="A608" s="191"/>
+    </row>
+    <row r="609">
+      <c r="A609" s="191"/>
+    </row>
+    <row r="610">
+      <c r="A610" s="191"/>
+    </row>
+    <row r="611">
+      <c r="A611" s="191"/>
+    </row>
+    <row r="612">
+      <c r="A612" s="191"/>
+    </row>
+    <row r="613">
+      <c r="A613" s="191"/>
+    </row>
+    <row r="614">
+      <c r="A614" s="191"/>
+    </row>
+    <row r="615">
+      <c r="A615" s="191"/>
+    </row>
+    <row r="616">
+      <c r="A616" s="191"/>
+    </row>
+    <row r="617">
+      <c r="A617" s="191"/>
+    </row>
+    <row r="618">
+      <c r="A618" s="191"/>
+    </row>
+    <row r="619">
+      <c r="A619" s="191"/>
+    </row>
+    <row r="620">
+      <c r="A620" s="191"/>
+    </row>
+    <row r="621">
+      <c r="A621" s="191"/>
+    </row>
+    <row r="622">
+      <c r="A622" s="191"/>
+    </row>
+    <row r="623">
+      <c r="A623" s="191"/>
+    </row>
+    <row r="624">
+      <c r="A624" s="191"/>
+    </row>
+    <row r="625">
+      <c r="A625" s="191"/>
+    </row>
+    <row r="626">
+      <c r="A626" s="191"/>
+    </row>
+    <row r="627">
+      <c r="A627" s="191"/>
+    </row>
+    <row r="628">
+      <c r="A628" s="191"/>
+    </row>
+    <row r="629">
+      <c r="A629" s="191"/>
+    </row>
+    <row r="630">
+      <c r="A630" s="191"/>
+    </row>
+    <row r="631">
+      <c r="A631" s="191"/>
+    </row>
+    <row r="632">
+      <c r="A632" s="191"/>
+    </row>
+    <row r="633">
+      <c r="A633" s="191"/>
+    </row>
+    <row r="634">
+      <c r="A634" s="191"/>
+    </row>
+    <row r="635">
+      <c r="A635" s="191"/>
+    </row>
+    <row r="636">
+      <c r="A636" s="191"/>
+    </row>
+    <row r="637">
+      <c r="A637" s="191"/>
+    </row>
+    <row r="638">
+      <c r="A638" s="191"/>
+    </row>
+    <row r="639">
+      <c r="A639" s="191"/>
+    </row>
+    <row r="640">
+      <c r="A640" s="191"/>
+    </row>
+    <row r="641">
+      <c r="A641" s="191"/>
+    </row>
+    <row r="642">
+      <c r="A642" s="191"/>
+    </row>
+    <row r="643">
+      <c r="A643" s="191"/>
+    </row>
+    <row r="644">
+      <c r="A644" s="191"/>
+    </row>
+    <row r="645">
+      <c r="A645" s="191"/>
+    </row>
+    <row r="646">
+      <c r="A646" s="191"/>
+    </row>
+    <row r="647">
+      <c r="A647" s="191"/>
+    </row>
+    <row r="648">
+      <c r="A648" s="191"/>
+    </row>
+    <row r="649">
+      <c r="A649" s="191"/>
+    </row>
+    <row r="650">
+      <c r="A650" s="191"/>
+    </row>
+    <row r="651">
+      <c r="A651" s="191"/>
+    </row>
+    <row r="652">
+      <c r="A652" s="191"/>
+    </row>
+    <row r="653">
+      <c r="A653" s="191"/>
+    </row>
+    <row r="654">
+      <c r="A654" s="191"/>
+    </row>
+    <row r="655">
+      <c r="A655" s="191"/>
+    </row>
+    <row r="656">
+      <c r="A656" s="191"/>
+    </row>
+    <row r="657">
+      <c r="A657" s="191"/>
+    </row>
+    <row r="658">
+      <c r="A658" s="191"/>
+    </row>
+    <row r="659">
+      <c r="A659" s="191"/>
+    </row>
+    <row r="660">
+      <c r="A660" s="191"/>
+    </row>
+    <row r="661">
+      <c r="A661" s="191"/>
+    </row>
+    <row r="662">
+      <c r="A662" s="191"/>
+    </row>
+    <row r="663">
+      <c r="A663" s="191"/>
+    </row>
+    <row r="664">
+      <c r="A664" s="191"/>
+    </row>
+    <row r="665">
+      <c r="A665" s="191"/>
+    </row>
+    <row r="666">
+      <c r="A666" s="191"/>
+    </row>
+    <row r="667">
+      <c r="A667" s="191"/>
+    </row>
+    <row r="668">
+      <c r="A668" s="191"/>
+    </row>
+    <row r="669">
+      <c r="A669" s="191"/>
+    </row>
+    <row r="670">
+      <c r="A670" s="191"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="191"/>
+    </row>
+    <row r="672">
+      <c r="A672" s="191"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="191"/>
+    </row>
+    <row r="674">
+      <c r="A674" s="191"/>
+    </row>
+    <row r="675">
+      <c r="A675" s="191"/>
+    </row>
+    <row r="676">
+      <c r="A676" s="191"/>
+    </row>
+    <row r="677">
+      <c r="A677" s="191"/>
+    </row>
+    <row r="678">
+      <c r="A678" s="191"/>
+    </row>
+    <row r="679">
+      <c r="A679" s="191"/>
+    </row>
+    <row r="680">
+      <c r="A680" s="191"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="191"/>
+    </row>
+    <row r="682">
+      <c r="A682" s="191"/>
+    </row>
+    <row r="683">
+      <c r="A683" s="191"/>
+    </row>
+    <row r="684">
+      <c r="A684" s="191"/>
+    </row>
+    <row r="685">
+      <c r="A685" s="191"/>
+    </row>
+    <row r="686">
+      <c r="A686" s="191"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="191"/>
+    </row>
+    <row r="688">
+      <c r="A688" s="191"/>
+    </row>
+    <row r="689">
+      <c r="A689" s="191"/>
+    </row>
+    <row r="690">
+      <c r="A690" s="191"/>
+    </row>
+    <row r="691">
+      <c r="A691" s="191"/>
+    </row>
+    <row r="692">
+      <c r="A692" s="191"/>
+    </row>
+    <row r="693">
+      <c r="A693" s="191"/>
+    </row>
+    <row r="694">
+      <c r="A694" s="191"/>
+    </row>
+    <row r="695">
+      <c r="A695" s="191"/>
+    </row>
+    <row r="696">
+      <c r="A696" s="191"/>
+    </row>
+    <row r="697">
+      <c r="A697" s="191"/>
+    </row>
+    <row r="698">
+      <c r="A698" s="191"/>
+    </row>
+    <row r="699">
+      <c r="A699" s="191"/>
+    </row>
+    <row r="700">
+      <c r="A700" s="191"/>
+    </row>
+    <row r="701">
+      <c r="A701" s="191"/>
+    </row>
+    <row r="702">
+      <c r="A702" s="191"/>
+    </row>
+    <row r="703">
+      <c r="A703" s="191"/>
+    </row>
+    <row r="704">
+      <c r="A704" s="191"/>
+    </row>
+    <row r="705">
+      <c r="A705" s="191"/>
+    </row>
+    <row r="706">
+      <c r="A706" s="191"/>
+    </row>
+    <row r="707">
+      <c r="A707" s="191"/>
+    </row>
+    <row r="708">
+      <c r="A708" s="191"/>
+    </row>
+    <row r="709">
+      <c r="A709" s="191"/>
+    </row>
+    <row r="710">
+      <c r="A710" s="191"/>
+    </row>
+    <row r="711">
+      <c r="A711" s="191"/>
+    </row>
+    <row r="712">
+      <c r="A712" s="191"/>
+    </row>
+    <row r="713">
+      <c r="A713" s="191"/>
+    </row>
+    <row r="714">
+      <c r="A714" s="191"/>
+    </row>
+    <row r="715">
+      <c r="A715" s="191"/>
+    </row>
+    <row r="716">
+      <c r="A716" s="191"/>
+    </row>
+    <row r="717">
+      <c r="A717" s="191"/>
+    </row>
+    <row r="718">
+      <c r="A718" s="191"/>
+    </row>
+    <row r="719">
+      <c r="A719" s="191"/>
+    </row>
+    <row r="720">
+      <c r="A720" s="191"/>
+    </row>
+    <row r="721">
+      <c r="A721" s="191"/>
+    </row>
+    <row r="722">
+      <c r="A722" s="191"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="191"/>
+    </row>
+    <row r="724">
+      <c r="A724" s="191"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="191"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="191"/>
+    </row>
+    <row r="727">
+      <c r="A727" s="191"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="191"/>
+    </row>
+    <row r="729">
+      <c r="A729" s="191"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="191"/>
+    </row>
+    <row r="731">
+      <c r="A731" s="191"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="191"/>
+    </row>
+    <row r="733">
+      <c r="A733" s="191"/>
+    </row>
+    <row r="734">
+      <c r="A734" s="191"/>
+    </row>
+    <row r="735">
+      <c r="A735" s="191"/>
+    </row>
+    <row r="736">
+      <c r="A736" s="191"/>
+    </row>
+    <row r="737">
+      <c r="A737" s="191"/>
+    </row>
+    <row r="738">
+      <c r="A738" s="191"/>
+    </row>
+    <row r="739">
+      <c r="A739" s="191"/>
+    </row>
+    <row r="740">
+      <c r="A740" s="191"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="191"/>
+    </row>
+    <row r="742">
+      <c r="A742" s="191"/>
+    </row>
+    <row r="743">
+      <c r="A743" s="191"/>
+    </row>
+    <row r="744">
+      <c r="A744" s="191"/>
+    </row>
+    <row r="745">
+      <c r="A745" s="191"/>
+    </row>
+    <row r="746">
+      <c r="A746" s="191"/>
+    </row>
+    <row r="747">
+      <c r="A747" s="191"/>
+    </row>
+    <row r="748">
+      <c r="A748" s="191"/>
+    </row>
+    <row r="749">
+      <c r="A749" s="191"/>
+    </row>
+    <row r="750">
+      <c r="A750" s="191"/>
+    </row>
+    <row r="751">
+      <c r="A751" s="191"/>
+    </row>
+    <row r="752">
+      <c r="A752" s="191"/>
+    </row>
+    <row r="753">
+      <c r="A753" s="191"/>
+    </row>
+    <row r="754">
+      <c r="A754" s="191"/>
+    </row>
+    <row r="755">
+      <c r="A755" s="191"/>
+    </row>
+    <row r="756">
+      <c r="A756" s="191"/>
+    </row>
+    <row r="757">
+      <c r="A757" s="191"/>
+    </row>
+    <row r="758">
+      <c r="A758" s="191"/>
+    </row>
+    <row r="759">
+      <c r="A759" s="191"/>
+    </row>
+    <row r="760">
+      <c r="A760" s="191"/>
+    </row>
+    <row r="761">
+      <c r="A761" s="191"/>
+    </row>
+    <row r="762">
+      <c r="A762" s="191"/>
+    </row>
+    <row r="763">
+      <c r="A763" s="191"/>
+    </row>
+    <row r="764">
+      <c r="A764" s="191"/>
+    </row>
+    <row r="765">
+      <c r="A765" s="191"/>
+    </row>
+    <row r="766">
+      <c r="A766" s="191"/>
+    </row>
+    <row r="767">
+      <c r="A767" s="191"/>
+    </row>
+    <row r="768">
+      <c r="A768" s="191"/>
+    </row>
+    <row r="769">
+      <c r="A769" s="191"/>
+    </row>
+    <row r="770">
+      <c r="A770" s="191"/>
+    </row>
+    <row r="771">
+      <c r="A771" s="191"/>
+    </row>
+    <row r="772">
+      <c r="A772" s="191"/>
+    </row>
+    <row r="773">
+      <c r="A773" s="191"/>
+    </row>
+    <row r="774">
+      <c r="A774" s="191"/>
+    </row>
+    <row r="775">
+      <c r="A775" s="191"/>
+    </row>
+    <row r="776">
+      <c r="A776" s="191"/>
+    </row>
+    <row r="777">
+      <c r="A777" s="191"/>
+    </row>
+    <row r="778">
+      <c r="A778" s="191"/>
+    </row>
+    <row r="779">
+      <c r="A779" s="191"/>
+    </row>
+    <row r="780">
+      <c r="A780" s="191"/>
+    </row>
+    <row r="781">
+      <c r="A781" s="191"/>
+    </row>
+    <row r="782">
+      <c r="A782" s="191"/>
+    </row>
+    <row r="783">
+      <c r="A783" s="191"/>
+    </row>
+    <row r="784">
+      <c r="A784" s="191"/>
+    </row>
+    <row r="785">
+      <c r="A785" s="191"/>
+    </row>
+    <row r="786">
+      <c r="A786" s="191"/>
+    </row>
+    <row r="787">
+      <c r="A787" s="191"/>
+    </row>
+    <row r="788">
+      <c r="A788" s="191"/>
+    </row>
+    <row r="789">
+      <c r="A789" s="191"/>
+    </row>
+    <row r="790">
+      <c r="A790" s="191"/>
+    </row>
+    <row r="791">
+      <c r="A791" s="191"/>
+    </row>
+    <row r="792">
+      <c r="A792" s="191"/>
+    </row>
+    <row r="793">
+      <c r="A793" s="191"/>
+    </row>
+    <row r="794">
+      <c r="A794" s="191"/>
+    </row>
+    <row r="795">
+      <c r="A795" s="191"/>
+    </row>
+    <row r="796">
+      <c r="A796" s="191"/>
+    </row>
+    <row r="797">
+      <c r="A797" s="191"/>
+    </row>
+    <row r="798">
+      <c r="A798" s="191"/>
+    </row>
+    <row r="799">
+      <c r="A799" s="191"/>
+    </row>
+    <row r="800">
+      <c r="A800" s="191"/>
+    </row>
+    <row r="801">
+      <c r="A801" s="191"/>
+    </row>
+    <row r="802">
+      <c r="A802" s="191"/>
+    </row>
+    <row r="803">
+      <c r="A803" s="191"/>
+    </row>
+    <row r="804">
+      <c r="A804" s="191"/>
+    </row>
+    <row r="805">
+      <c r="A805" s="191"/>
+    </row>
+    <row r="806">
+      <c r="A806" s="191"/>
+    </row>
+    <row r="807">
+      <c r="A807" s="191"/>
+    </row>
+    <row r="808">
+      <c r="A808" s="191"/>
+    </row>
+    <row r="809">
+      <c r="A809" s="191"/>
+    </row>
+    <row r="810">
+      <c r="A810" s="191"/>
+    </row>
+    <row r="811">
+      <c r="A811" s="191"/>
+    </row>
+    <row r="812">
+      <c r="A812" s="191"/>
+    </row>
+    <row r="813">
+      <c r="A813" s="191"/>
+    </row>
+    <row r="814">
+      <c r="A814" s="191"/>
+    </row>
+    <row r="815">
+      <c r="A815" s="191"/>
+    </row>
+    <row r="816">
+      <c r="A816" s="191"/>
+    </row>
+    <row r="817">
+      <c r="A817" s="191"/>
+    </row>
+    <row r="818">
+      <c r="A818" s="191"/>
+    </row>
+    <row r="819">
+      <c r="A819" s="191"/>
+    </row>
+    <row r="820">
+      <c r="A820" s="191"/>
+    </row>
+    <row r="821">
+      <c r="A821" s="191"/>
+    </row>
+    <row r="822">
+      <c r="A822" s="191"/>
+    </row>
+    <row r="823">
+      <c r="A823" s="191"/>
+    </row>
+    <row r="824">
+      <c r="A824" s="191"/>
+    </row>
+    <row r="825">
+      <c r="A825" s="191"/>
+    </row>
+    <row r="826">
+      <c r="A826" s="191"/>
+    </row>
+    <row r="827">
+      <c r="A827" s="191"/>
+    </row>
+    <row r="828">
+      <c r="A828" s="191"/>
+    </row>
+    <row r="829">
+      <c r="A829" s="191"/>
+    </row>
+    <row r="830">
+      <c r="A830" s="191"/>
+    </row>
+    <row r="831">
+      <c r="A831" s="191"/>
+    </row>
+    <row r="832">
+      <c r="A832" s="191"/>
+    </row>
+    <row r="833">
+      <c r="A833" s="191"/>
+    </row>
+    <row r="834">
+      <c r="A834" s="191"/>
+    </row>
+    <row r="835">
+      <c r="A835" s="191"/>
+    </row>
+    <row r="836">
+      <c r="A836" s="191"/>
+    </row>
+    <row r="837">
+      <c r="A837" s="191"/>
+    </row>
+    <row r="838">
+      <c r="A838" s="191"/>
+    </row>
+    <row r="839">
+      <c r="A839" s="191"/>
+    </row>
+    <row r="840">
+      <c r="A840" s="191"/>
+    </row>
+    <row r="841">
+      <c r="A841" s="191"/>
+    </row>
+    <row r="842">
+      <c r="A842" s="191"/>
+    </row>
+    <row r="843">
+      <c r="A843" s="191"/>
+    </row>
+    <row r="844">
+      <c r="A844" s="191"/>
+    </row>
+    <row r="845">
+      <c r="A845" s="191"/>
+    </row>
+    <row r="846">
+      <c r="A846" s="191"/>
+    </row>
+    <row r="847">
+      <c r="A847" s="191"/>
+    </row>
+    <row r="848">
+      <c r="A848" s="191"/>
+    </row>
+    <row r="849">
+      <c r="A849" s="191"/>
+    </row>
+    <row r="850">
+      <c r="A850" s="191"/>
+    </row>
+    <row r="851">
+      <c r="A851" s="191"/>
+    </row>
+    <row r="852">
+      <c r="A852" s="191"/>
+    </row>
+    <row r="853">
+      <c r="A853" s="191"/>
+    </row>
+    <row r="854">
+      <c r="A854" s="191"/>
+    </row>
+    <row r="855">
+      <c r="A855" s="191"/>
+    </row>
+    <row r="856">
+      <c r="A856" s="191"/>
+    </row>
+    <row r="857">
+      <c r="A857" s="191"/>
+    </row>
+    <row r="858">
+      <c r="A858" s="191"/>
+    </row>
+    <row r="859">
+      <c r="A859" s="191"/>
+    </row>
+    <row r="860">
+      <c r="A860" s="191"/>
+    </row>
+    <row r="861">
+      <c r="A861" s="191"/>
+    </row>
+    <row r="862">
+      <c r="A862" s="191"/>
+    </row>
+    <row r="863">
+      <c r="A863" s="191"/>
+    </row>
+    <row r="864">
+      <c r="A864" s="191"/>
+    </row>
+    <row r="865">
+      <c r="A865" s="191"/>
+    </row>
+    <row r="866">
+      <c r="A866" s="191"/>
+    </row>
+    <row r="867">
+      <c r="A867" s="191"/>
+    </row>
+    <row r="868">
+      <c r="A868" s="191"/>
+    </row>
+    <row r="869">
+      <c r="A869" s="191"/>
+    </row>
+    <row r="870">
+      <c r="A870" s="191"/>
+    </row>
+    <row r="871">
+      <c r="A871" s="191"/>
+    </row>
+    <row r="872">
+      <c r="A872" s="191"/>
+    </row>
+    <row r="873">
+      <c r="A873" s="191"/>
+    </row>
+    <row r="874">
+      <c r="A874" s="191"/>
+    </row>
+    <row r="875">
+      <c r="A875" s="191"/>
+    </row>
+    <row r="876">
+      <c r="A876" s="191"/>
+    </row>
+    <row r="877">
+      <c r="A877" s="191"/>
+    </row>
+    <row r="878">
+      <c r="A878" s="191"/>
+    </row>
+    <row r="879">
+      <c r="A879" s="191"/>
+    </row>
+    <row r="880">
+      <c r="A880" s="191"/>
+    </row>
+    <row r="881">
+      <c r="A881" s="191"/>
+    </row>
+    <row r="882">
+      <c r="A882" s="191"/>
+    </row>
+    <row r="883">
+      <c r="A883" s="191"/>
+    </row>
+    <row r="884">
+      <c r="A884" s="191"/>
+    </row>
+    <row r="885">
+      <c r="A885" s="191"/>
+    </row>
+    <row r="886">
+      <c r="A886" s="191"/>
+    </row>
+    <row r="887">
+      <c r="A887" s="191"/>
+    </row>
+    <row r="888">
+      <c r="A888" s="191"/>
+    </row>
+    <row r="889">
+      <c r="A889" s="191"/>
+    </row>
+    <row r="890">
+      <c r="A890" s="191"/>
+    </row>
+    <row r="891">
+      <c r="A891" s="191"/>
+    </row>
+    <row r="892">
+      <c r="A892" s="191"/>
+    </row>
+    <row r="893">
+      <c r="A893" s="191"/>
+    </row>
+    <row r="894">
+      <c r="A894" s="191"/>
+    </row>
+    <row r="895">
+      <c r="A895" s="191"/>
+    </row>
+    <row r="896">
+      <c r="A896" s="191"/>
+    </row>
+    <row r="897">
+      <c r="A897" s="191"/>
+    </row>
+    <row r="898">
+      <c r="A898" s="191"/>
+    </row>
+    <row r="899">
+      <c r="A899" s="191"/>
+    </row>
+    <row r="900">
+      <c r="A900" s="191"/>
+    </row>
+    <row r="901">
+      <c r="A901" s="191"/>
+    </row>
+    <row r="902">
+      <c r="A902" s="191"/>
+    </row>
+    <row r="903">
+      <c r="A903" s="191"/>
+    </row>
+    <row r="904">
+      <c r="A904" s="191"/>
+    </row>
+    <row r="905">
+      <c r="A905" s="191"/>
+    </row>
+    <row r="906">
+      <c r="A906" s="191"/>
+    </row>
+    <row r="907">
+      <c r="A907" s="191"/>
+    </row>
+    <row r="908">
+      <c r="A908" s="191"/>
+    </row>
+    <row r="909">
+      <c r="A909" s="191"/>
+    </row>
+    <row r="910">
+      <c r="A910" s="191"/>
+    </row>
+    <row r="911">
+      <c r="A911" s="191"/>
+    </row>
+    <row r="912">
+      <c r="A912" s="191"/>
+    </row>
+    <row r="913">
+      <c r="A913" s="191"/>
+    </row>
+    <row r="914">
+      <c r="A914" s="191"/>
+    </row>
+    <row r="915">
+      <c r="A915" s="191"/>
+    </row>
+    <row r="916">
+      <c r="A916" s="191"/>
+    </row>
+    <row r="917">
+      <c r="A917" s="191"/>
+    </row>
+    <row r="918">
+      <c r="A918" s="191"/>
+    </row>
+    <row r="919">
+      <c r="A919" s="191"/>
+    </row>
+    <row r="920">
+      <c r="A920" s="191"/>
+    </row>
+    <row r="921">
+      <c r="A921" s="191"/>
+    </row>
+    <row r="922">
+      <c r="A922" s="191"/>
+    </row>
+    <row r="923">
+      <c r="A923" s="191"/>
+    </row>
+    <row r="924">
+      <c r="A924" s="191"/>
+    </row>
+    <row r="925">
+      <c r="A925" s="191"/>
+    </row>
+    <row r="926">
+      <c r="A926" s="191"/>
+    </row>
+    <row r="927">
+      <c r="A927" s="191"/>
+    </row>
+    <row r="928">
+      <c r="A928" s="191"/>
+    </row>
+    <row r="929">
+      <c r="A929" s="191"/>
+    </row>
+    <row r="930">
+      <c r="A930" s="191"/>
+    </row>
+    <row r="931">
+      <c r="A931" s="191"/>
+    </row>
+    <row r="932">
+      <c r="A932" s="191"/>
+    </row>
+    <row r="933">
+      <c r="A933" s="191"/>
+    </row>
+    <row r="934">
+      <c r="A934" s="191"/>
+    </row>
+    <row r="935">
+      <c r="A935" s="191"/>
+    </row>
+    <row r="936">
+      <c r="A936" s="191"/>
+    </row>
+    <row r="937">
+      <c r="A937" s="191"/>
+    </row>
+    <row r="938">
+      <c r="A938" s="191"/>
+    </row>
+    <row r="939">
+      <c r="A939" s="191"/>
+    </row>
+    <row r="940">
+      <c r="A940" s="191"/>
+    </row>
+    <row r="941">
+      <c r="A941" s="191"/>
+    </row>
+    <row r="942">
+      <c r="A942" s="191"/>
+    </row>
+    <row r="943">
+      <c r="A943" s="191"/>
+    </row>
+    <row r="944">
+      <c r="A944" s="191"/>
+    </row>
+    <row r="945">
+      <c r="A945" s="191"/>
+    </row>
+    <row r="946">
+      <c r="A946" s="191"/>
+    </row>
+    <row r="947">
+      <c r="A947" s="191"/>
+    </row>
+    <row r="948">
+      <c r="A948" s="191"/>
+    </row>
+    <row r="949">
+      <c r="A949" s="191"/>
+    </row>
+    <row r="950">
+      <c r="A950" s="191"/>
+    </row>
+    <row r="951">
+      <c r="A951" s="191"/>
+    </row>
+    <row r="952">
+      <c r="A952" s="191"/>
+    </row>
+    <row r="953">
+      <c r="A953" s="191"/>
+    </row>
+    <row r="954">
+      <c r="A954" s="191"/>
+    </row>
+    <row r="955">
+      <c r="A955" s="191"/>
+    </row>
+    <row r="956">
+      <c r="A956" s="191"/>
+    </row>
+    <row r="957">
+      <c r="A957" s="191"/>
+    </row>
+    <row r="958">
+      <c r="A958" s="191"/>
+    </row>
+    <row r="959">
+      <c r="A959" s="191"/>
+    </row>
+    <row r="960">
+      <c r="A960" s="191"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="191"/>
+    </row>
+    <row r="962">
+      <c r="A962" s="191"/>
+    </row>
+    <row r="963">
+      <c r="A963" s="191"/>
+    </row>
+    <row r="964">
+      <c r="A964" s="191"/>
+    </row>
+    <row r="965">
+      <c r="A965" s="191"/>
+    </row>
+    <row r="966">
+      <c r="A966" s="191"/>
+    </row>
+    <row r="967">
+      <c r="A967" s="191"/>
+    </row>
+    <row r="968">
+      <c r="A968" s="191"/>
+    </row>
+    <row r="969">
+      <c r="A969" s="191"/>
+    </row>
+    <row r="970">
+      <c r="A970" s="191"/>
+    </row>
+    <row r="971">
+      <c r="A971" s="191"/>
+    </row>
+    <row r="972">
+      <c r="A972" s="191"/>
+    </row>
+    <row r="973">
+      <c r="A973" s="191"/>
+    </row>
+    <row r="974">
+      <c r="A974" s="191"/>
+    </row>
+    <row r="975">
+      <c r="A975" s="191"/>
+    </row>
+    <row r="976">
+      <c r="A976" s="191"/>
+    </row>
+    <row r="977">
+      <c r="A977" s="191"/>
+    </row>
+    <row r="978">
+      <c r="A978" s="191"/>
+    </row>
+    <row r="979">
+      <c r="A979" s="191"/>
+    </row>
+    <row r="980">
+      <c r="A980" s="191"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="191"/>
+    </row>
+    <row r="982">
+      <c r="A982" s="191"/>
+    </row>
+    <row r="983">
+      <c r="A983" s="191"/>
+    </row>
+    <row r="984">
+      <c r="A984" s="191"/>
+    </row>
+    <row r="985">
+      <c r="A985" s="191"/>
+    </row>
+    <row r="986">
+      <c r="A986" s="191"/>
+    </row>
+    <row r="987">
+      <c r="A987" s="191"/>
+    </row>
+    <row r="988">
+      <c r="A988" s="191"/>
+    </row>
+    <row r="989">
+      <c r="A989" s="191"/>
+    </row>
+    <row r="990">
+      <c r="A990" s="191"/>
+    </row>
+    <row r="991">
+      <c r="A991" s="191"/>
+    </row>
+    <row r="992">
+      <c r="A992" s="191"/>
+    </row>
+    <row r="993">
+      <c r="A993" s="191"/>
+    </row>
+    <row r="994">
+      <c r="A994" s="191"/>
+    </row>
+    <row r="995">
+      <c r="A995" s="191"/>
+    </row>
+    <row r="996">
+      <c r="A996" s="191"/>
+    </row>
+    <row r="997">
+      <c r="A997" s="191"/>
+    </row>
+    <row r="998">
+      <c r="A998" s="191"/>
+    </row>
+    <row r="999">
+      <c r="A999" s="191"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="191"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24426.9074</v>
+        <v>24544.91178</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15782.05479</v>
+        <v>15844.93151</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4142.465753</v>
+        <v>4228.767123</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24544.91178</v>
+        <v>24662.91616</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15844.93151</v>
+        <v>15907.80822</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4228.767123</v>
+        <v>4315.068493</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24662.91616</v>
+        <v>24780.92055</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15907.80822</v>
+        <v>15970.68493</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4315.068493</v>
+        <v>4401.369863</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24780.92055</v>
+        <v>24898.92493</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>15970.68493</v>
+        <v>16033.56164</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4401.369863</v>
+        <v>4487.671233</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>24898.92493</v>
+        <v>25016.92932</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>16033.56164</v>
+        <v>16096.43836</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4487.671233</v>
+        <v>4573.972603</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>25016.92932</v>
+        <v>25134.9337</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>16096.43836</v>
+        <v>16159.31507</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4573.972603</v>
+        <v>4660.273973</v>
       </c>
     </row>
     <row r="8">

--- a/data.xlsx
+++ b/data.xlsx
@@ -8962,7 +8962,7 @@
       </c>
       <c r="H5" s="10">
         <f t="shared" ref="H5:H9" si="1">IF(OR(ISBLANK(F5), ISBLANK(G5), ISBLANK(C5)), 0, F5 * C5 * (TODAY() - G5) / 365)</f>
-        <v>25134.9337</v>
+        <v>25252.93808</v>
       </c>
     </row>
     <row r="6">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>16159.31507</v>
+        <v>16222.19178</v>
       </c>
     </row>
     <row r="7">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4660.273973</v>
+        <v>4746.575342</v>
       </c>
     </row>
     <row r="8">
